--- a/output/data-ai-jobs.xlsx
+++ b/output/data-ai-jobs.xlsx
@@ -517,17 +517,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Computer Operations Analyst</t>
+          <t>Business Analyst-Level 3 - Senior (11 - 15 Years)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Colorado Springs, Colorado, 80901, USA</t>
+          <t>Houston, TX, 77002, US</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006211688/Computer-Operations-Analyst</t>
+          <t>https://www.apexsystems.com/job/3046327_usa/business-analyst-level-3---senior-11---15-years</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -565,54 +565,54 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>301e1f88c5c589466119</t>
+          <t>2a2d0f46a61decfeb10b</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Job Title: Operations Analyst - COSA Job Description This full-time Operations Analyst role focuses on the daily monitoring, operation, and maintenance of large-scale computer and communications systems in a 24x7 environment . The position provides first-level technical support, performs initial troubleshooting across hardware, software, and networks, and supports both operational and test activities. The role requires experience in system and network administration, an active DoD Secret clearance, and current DoD 8570 IAT Level II certification. Responsibilities Perform daily system monitoring, operations, and maintenance of large-scale computer and communications systems in a 24x7 operational and test environment. Provide first-level technical support to users, including warfighters, and serve as the initial point of contact for technical issues. Perform initial troubleshooting of local hardware, software, and network issues to restore services and minimize downtime. Document and report all events, incidents, and issues to the appropriate watch officer and follow established reporting procedures. Receive tasking and direction from the command and control center for all operations, testing, and real-world events, and execute assigned tasks accurately and on time. Assist with hardware and software installations as directed by local subject matter experts, ensuring proper configuration and functionality. Create and maintain user accounts as directed by the local information system security officer, following established security policies and procedures. Use trouble ticketing tools to log, track, and update incidents and service requests, ensuring clear communication and proper documentation. Collaborate with system and network administrators to resolve complex issues related to UNIX, Linux, Windows, Cisco, and Juniper environments. Support both operations and training assignments as directed by mission requirements. Perform other duties and assignments as required to support mission objectives. Essential Skills Bachelor’s degree from an accredited college in a related discipline, or equivalent combination of education and experience, with 6 years of professional experience .Minimum of 6 years of experience in operations and maintenance of large-scale computer and communications systems or similar environments. Current DoD 8570 IAT Level II certification (such as Security+ CE, CySA+, GSEC, SSCP, CCNA Security or equivalent) and ability to maintain this certification for the full contract period. Active DoD Secret clearance at the time of hire . Strong and experience in system and/or network administration, including UNIX, Linux, and Windows operating systems. Demonstrated ability to troubleshoot hardware components, including servers, workstations, and network devices. Demonstrated ability to troubleshoot software components, including operating systems, applications, and network services. Proficiency with Microsoft Word, Excel, and PowerPoint. Exp</t>
+          <t>This position serves as a business analyst and project lead for customer experience,process, and technology improvements. The individual will partner with businessstakeholders to identify needs, document and evaluate current processes, recommendimprovements, define requirements, and manage initiatives through implementation.A significant portion of the role will involve Salesforce enhancements. The successfulcandidate should be familiar with Salesforce and comfortable coordinating closely withadministrators, developers, and business partners. The role will also support othertechnology platforms, requiring strong technical aptitude and the ability to quickly learnnew systems.Key responsibilities include:• Leads discovery sessions to identify business needs, process gaps, andimprovement opportunities.• Documents current-state and future-state processes, workflows, requirements,user stories, acceptance criteria, and test scenarios.• Evaluates and improves business processes to increase efficiency, consistency,and customer or employee satisfaction.• Manages initiatives from discovery through development, testing, implementation,and adoption.• Coordinates closely with Salesforce and other technology teams to deliver systemenhancements.• Facilitates stakeholder meetings and manages timelines, risks, dependencies,decisions, and project communications.• Supports user acceptance testing, issue resolution, training, and changemanagement activities.• Identifies opportunities to use automation, artificial intelligence, and emergingtechnologies to improve operations and customer experiences.• Independently manages multiple priorities and drives work forward with limitedoversight.• Travels during the initial onboarding and training period, as needed.The ideal candidate will have experience in business analysis, project management,process improvement, and technology implementation. Salesforce experience is stronglypreferred. Familiarity with artificial intelligence is beneficial, but a willingness to learn andexplore practical AI use cases is equally important.EEO Employer Apex Systems is an equal opportunity employer. We do not discriminate or allow discrimination on the basis of race, color, religion, creed, sex (including pregnancy, childbirth, breastfeeding, or related medical conditions), age, sexual orientation, gender identity, national origin, ancestry, citizenship, genetic information, registered domestic partner status, marital status, disability, status as a crime victim, protected veteran status, political affiliation, union membership, or any other characteristic protected by law. Apex will consider qualified applicants with criminal histories in a manner consistent with the requirements of applicable law. If you have visited our website in search of information on employment opportunities or to apply for a position, and you require an accommodation in using our website for a search or application, please contact our Employee Services Department at</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Computer Operations Analyst</t>
+          <t>Supply Chain Analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colorado Springs, Colorado, 80901, USA</t>
+          <t>Juno Beach, FL, 33408, US</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006198519/Computer-Operations-Analyst</t>
+          <t>https://www.apexsystems.com/job/3046086_usa/supply-chain-analyst</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -635,54 +635,49 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>082b81d0b745bbf821be</t>
+          <t>23308ce5133f39944990</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Job Title: Operations Analyst Job Description This full-time Operations Analyst role focuses on the daily monitoring, operation, and maintenance of large-scale computer and communications systems in a 24x7 environment . The position provides first-level technical support, performs initial troubleshooting across hardware, software, and networks, and supports both operational and test activities. The role requires experience in system and network administration, an active DoD Secret clearance, and current DoD 8570 IAT Level II certification. Responsibilities Perform daily system monitoring, operations, and maintenance of large-scale computer and communications systems in a 24x7 operational and test environment. Provide first-level technical support to users, including warfighters, and serve as the initial point of contact for technical issues. Perform initial troubleshooting of local hardware, software, and network issues to restore services and minimize downtime. Document and report all events, incidents, and issues to the appropriate watch officer and follow established reporting procedures. Receive tasking and direction from the command and control center for all operations, testing, and real-world events, and execute assigned tasks accurately and on time. Assist with hardware and software installations as directed by local subject matter experts, ensuring proper configuration and functionality. Create and maintain user accounts as directed by the local information system security officer, following established security policies and procedures. Use trouble ticketing tools to log, track, and update incidents and service requests, ensuring clear communication and proper documentation. Collaborate with system and network administrators to resolve complex issues related to UNIX, Linux, Windows, Cisco, and Juniper environments. Support both operations and training assignments as directed by mission requirements. Perform other duties and assignments as required to support mission objectives. Essential Skills Bachelor’s degree from an accredited college in a related discipline, or equivalent combination of education and experience, with 6 years of professional experience. Minimum of 6 years of background experience in operations and maintenance of large-scale computer and communications systems or similar environments. Current DoD 8570 IAT Level II certification (such as Security+ CE, CySA+, GSEC, SSCP, CCNA Security or equivalent) and ability to maintain this certification for the full contract period. Active DoD Secret clearance at the time of hire . Strong background and experience in system and/or network administration, including UNIX, Linux, and Windows operating systems. Hands-on experience with Cisco and Juniper networking equipment and configurations. Demonstrated ability to troubleshoot hardware components, including servers, workstations, and network devices. Demonstrated ability to troubleshoot software components, including operating syste</t>
+          <t>Supply Chain Analyst\nLocation: Juno Beach, Florida (Onsite)\n \nRole Overview\nThe Supply Chain Analyst provides procurement, operational, and administrative support for Nuclear Circuit Card Laboratory (CCL) and Reverse Engineering (RE) programs. This role is responsible for production reporting, cost savings tracking, procurement coordination, work scheduling, vendor engagement, and management of purchasing activities. The position serves as a critical link between engineering, operations, supply chain, and external suppliers to ensure efficient execution of technical services.\n \nKey Responsibilities\nMaintain and distribute production reports for CCL and Reverse Engineering activities.Calculate, track, and report cost savings generated through repair and reverse engineering initiatives.Compile and maintain operational metrics, performance data, and management reports.Create and process Material Requisitions (MRs), Purchase Requisitions (PRs), Shopping Carts, and Purchase Orders (POs).Utilize SAP, NAMS, GEP SMART, and other business systems to support purchasing activities.Coordinate procurement of materials, equipment, and services required to support repair and reverse engineering projects.Manage and respond to inquiries received through shared departmental mailboxes.Interface with internal customers, engineering personnel, and external vendors to support project execution.Monitor maintenance and procurement activities to identify potential reverse engineering and repair opportunities.\nRequired Qualifications\nEducation: A Bachelor's degree in Business, Economics, Information Systems, or a related field is required.\n \nExperience: 6-10 years of experience in business analysis, market intelligence, or business process improvement is required. Experience in procurement, purchasing, supply chain operations, or technical project support is also necessary.\n \nTechnical Skills: Proficiency with Microsoft Office applications, particularly Excel for reporting and data analysis, is required. Working knowledge of SAP, GEP SMART, NAMS, or similar enterprise resource planning (ERP) systems is also needed. Expertise with Power BI, SQL, and Python is relevant.\n \nCore Competencies\nProcurement &amp; Supply Chain OperationsCost Savings Analysis &amp; ReportingProduction &amp; Performance Metrics ManagementVendor &amp; Supplier CoordinationProject Scheduling &amp; Work CoordinationData Analysis &amp; Process ImprovementCustomer Service &amp; Stakeholder CommunicationAttention to Detail &amp; Organizational EffectivenessEverforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction i</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microbiology Laboratory Analyst II</t>
+          <t>236 results for Data Engineer jobs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hercules, California, 94547, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -692,12 +687,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006193396/Microbiology-Laboratory-Analyst-II</t>
+          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -705,39 +700,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>46f1845291bcf8f05353</t>
+          <t>9685684093f5da63e2bd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Job Title: Microbiology Laboratory Analyst II Job Description The Microbiology Laboratory Analyst II plays a hands-on role in performing microbiology testing, managing samples, and supporting laboratory operations in a GMP/GLP-regulated environment. This client-facing position requires a strong quality mindset, excellent documentation skills, and the ability to perform both routine and advanced microbiological assays while maintaining strict compliance with regulatory and quality standards. Responsibilities Perform microbiological testing in accordance with SOPs, GMP, GLP, USP, EP, and ISO requirements. Conduct bioburden testing following USP / guidelines. Perform endotoxin testing in alignment with USP requirements. Execute sterility testing according to USP standards. Perform antimicrobial effectiveness testing following USP methods. Conduct container closure integrity testing (CCIT). Perform environmental monitoring of cleanrooms and controlled environments. Conduct TOC, conductivity, and pH testing for water and utilities. Support cleaning and disinfection validation activities. Perform environmental monitoring and water/utility sampling as scheduled or requested. Support method development, verification, validation, and method transfers. Investigate out-of-specification (OOS) and non-conforming results and complete associated CAPA activities. Maintain laboratory inventory, reagents, equipment, and associated documentation. Ensure the laboratory remains compliant, clean, organized, and audit-ready at all times. Deliver accurate and reliable test results within required turnaround times. Support custom studies and client-specific projects as needed. Collaborate with internal teams and clients to ensure clear communication of testing requirements and results. Document all activities accurately and contemporaneously in accordance with regulatory and quality expectations. Essential Skills Minimum 2+ years of experience in a GMP/GLP or FDA-regulated laboratory environment. Strong microbiology laboratory techniques and aseptic practices. Hands-on experience with environmental monitoring. Experience performing bioburden testing. Proficiency working within cleanroom and controlled environments. Excellent technical writing and documentation skills. Strong attention to detail and a demonstrated commitment to quality. Ability to thrive in a fast-paced, dynamic laboratory environment. Ability to manage multiple tasks while maintaining accuracy and compliance. Effective communication skills for a client-facing role. Additional Skills &amp; Qualifications BS, MS, or PhD in Microbiology, Biology, Biotechnology, Pharmaceutical Sciences, or a related scientific discipline preferred. Experience supporting method development, verification, validation, and method transfers. Familiarity with USP, EP, ISO, and other relevant regulatory and compendial standards. Experience conducting cleaning and disinfection validations. Background in working within cGMP/GLP testing s</t>
+          <t>236 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Permanent talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2026 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 236 results for Data Engineer jobs Data Engineer Erlanger, KY onsite Temporary / Contract 38 - 44 USD / Hourly We are looking for a detail-focused Engineer/Analyst to join a Long-term Contract assignment supporting technical data quality and material information management in northern Kentucky. In this role, you will help maintain accurate, standardized data for raw materials and packaging components so teams can move product development, supplier onboarding, and manufacturing activities forward efficiently. This position works closely with research, quality, procurement, operations, and master data partners to strengthen consistency across systems and improve the reliability of material records. This role will be onsite 4 days a week and 1 day remote. Must be comfortable working in a lab/plant manufacturing setting. YOU MUST LIVE IN KY or OH to be considered. No option for remote work. Responsibilities: • Manage the collection, review, and entry of technical specifications for raw materials and packaging components within designated data and specification platforms. • Verify that material records are complete, accurate, and aligned with company standards, compliance expectations, and approved documentation. • Apply consistent naming structures, formatting rules, and data standards to improve usability across regional and enterprise systems. • Investigate missing, conflicting, or outdated information in material specifications and resolve issues through coordination with cross-functional stakeholders. • Maintain material master records and ensure proper connections between specification data, system entries, and related documentation. • Build, revise, and validate bills of materials to support production readiness, product updates, supplier changes, and ongoing improvement efforts. • Partner with master data, procurement, operations, and technical teams to enhance data governance practices and streamline data management processes. • Monitor assigned project activities and data deliverables to help keep timelines on track and support broader documentation standardization efforts. 2026-08-10T00:00:00Z Data Engineer Kalamazoo, MI remote Permanent / Full Time 150000 - 225000 USD / Yearly We are looking for a senio</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Project Analyst</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, Texas, 77001, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -747,12 +742,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -767,7 +757,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006196066/Project-Analyst</t>
+          <t>https://www.judge.com/jobs/details/1073820</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -775,39 +765,39 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>64bcb93c6b4e737d64ed</t>
+          <t>c71947cbb7c82f6e5c8f</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Job Title: Project Coordinator Job location: Downtown Houston Job Description This role offers an opportunity for an experienced Project Coordinator to support a busy project team in Houston by providing comprehensive project coordination, cost control, and analytical support for oil and gas and natural gas pipeline projects. The successful candidate will help manage a large portfolio of projects, ensuring accurate cost tracking, forecasting, and reporting while working closely with engineering and project management teams. Responsibilities Provide project coordination and project controls support for oil and gas and natural gas pipeline projects. Support project managers and engineering teams by tracking project costs, schedules, and progress across multiple concurrent projects. Perform cost control activities, including cost analysis, forecasting, and budget monitoring for projects ranging from several million to very large capital investments. Prepare, maintain, and analyze project reports using Excel, including pivot tables and large data sets, to provide clear and accurate information to stakeholders. Assist with project management tasks such as tracking milestones, monitoring performance, and ensuring adherence to project plans and budgets. Coordinate with engineering project managers and engineering teams to collect data, validate information, and resolve discrepancies related to project costs and schedules. Support inventory control and supply chain-related activities as they relate to project materials, costs, and timelines. Contribute to quality assurance efforts by ensuring the accuracy and completeness of project data, documentation, and reports. Utilize ERP systems, such as SAP or similar platforms, to input, track, and reconcile project financials and cost information when applicable. Communicate effectively with team members and stakeholders while managing multiple priorities and projects simultaneously, often supporting 30–40 active projects. Prepare and deliver regular status updates and cost reports to project leadership to support informed decision-making. Essential Skills 5+ years of experience in project controls or project analyst roles, specifically supporting large capital or infrastructure projects. Demonstrated experience providing project coordination, cost controls, and project analyst support in the oil and gas or natural gas sector. Past experience working in the pipeline industry and coordinating with engineering project managers or engineering teams. College degree in business, finance, construction management, accounting, engineering, or a related field. Strong proficiency in Microsoft Excel, including building and using pivot tables and working with large data sets. Proven ability to perform cost analysis, cost control, and forecasting for complex projects. Experience with project management and project control practices, including reporting and performance tracking. Ability to manage and prioritize work across a</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Awards Environmental, Social, and Governance Internal Judge Careers Locations Leadership Job Seekers IT Consulting Cloud Migration Digital, Technology &amp; Data Strategic Roadmaps &amp; Delivery Process &amp; Governance Optimization IT &amp; Business Transformation Infrastructure &amp; Wireless Technology Partners Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Executive Search Engineering Staffing Professional Services Staffing Creative &amp; Marketing Staffing Direct Hire India Solutions Learning Solutions Custom Learning Solutions Learning &amp; Development Staffing Enterprise Learning Solutions Facilitated Learning Events &amp; Bootcamps Organizational Change Management Learning Strategy Consultation Industries We Serve Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media Resources Sitemap Privacy &amp; Cookies Policy Timesheets TIC EEO CCPA Accessibility Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quality Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hayward, California, 94540, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -817,12 +807,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -837,7 +822,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006214748/Quality-Analyst</t>
+          <t>https://careers.wipro.com/job/Analyst/139636-en_US</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -845,39 +830,39 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>cf6368e0ed533a99382e</t>
+          <t>0198f121663e4d27f0da</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Job Title: Quality Analyst Job Description The Quality Analyst plays a key role in ensuring that production-scale materials meet rigorous performance and quality standards. In this role, you operate analytical instruments, generate and analyze test data, maintain quality systems, and contribute directly to the development and optimization of new products. As part of a rapidly growing start-up environment, your work will have a direct and significant impact on the product line and its position as a leader in transparent conductive films. Responsibilities Operate analytical instruments to measure and collect data for production-scale materials. Prepare and produce test samples and accurately measure their performance. Test, compile, and analyze data to assess the quality and consistency of production-scale materials. Maintain quality databases and regularly review quality KPIs to monitor performance and trends. Manage the calibration, maintenance, and general upkeep of quality analytical instruments and equipment. Develop new characterization methodologies as needed and create clear standard operating procedures (SOPs). Assist in defining product specifications for new production materials to align performance with internal and external customer requirements. Participate in product nonconformance investigations and support the development and implementation of corrective actions. Prepare technical reports and summaries for both internal stakeholders and external partners. Collaborate effectively in a multi-disciplinary environment, contributing quality insights to cross-functional teams. Essential Skills 3–5 years of industrial quality control (QC) or quality assurance (QA) experience. Strong background in analytical chemistry and hands-on laboratory experience. Experience operating and maintaining analytical instruments for material characterization. Proficiency in chemical handling and adherence to laboratory safety practices. Familiarity with GMP principles and quality standards. Experience with JMP or similar statistical software for data analysis. Knowledge of design of experiments (DOE) and statistical analysis techniques. Ability to maintain and interpret quality databases and key performance indicators (KPIs). Strong organizational skills and attention to detail. Effective communication skills for preparing technical reports and collaborating with cross-functional teams. Proven ability to work both independently and as part of a team in a multi-disciplinary environment. Additional Skills &amp; Qualifications Degree in Chemical Engineering, Materials Science and Engineering, Chemistry, Physics, or a related discipline. Knowledge of optoelectronic devices and thin film coatings. Hands-on experience with analytical instruments related to thin films and optoelectronic materials. Experience with mixing, blending, and wet coating operations. Experience developing characterization methodologies and authoring SOPs. Comfort working in a dynamic, rapidly</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru, Gurugram State/Province: Haryana, Karnataka Posting Start Date: 6/22/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job De</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sr. Clinical Informatics Analyst</t>
+          <t>DATA ANALYST L4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, California, 92101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -887,12 +872,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -907,7 +887,7 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006204592/Sr-Clinical-Informatics-Analyst</t>
+          <t>https://careers.wipro.com/job/DATA-ANALYST-L4/134575-en_US</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -915,39 +895,39 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>021caefc4f61302fd025</t>
+          <t>ddaa58429851e5c20c52</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Job Title: Senior Clinical Informatics Analyst Job Description The Senior Clinical Informatics Analyst supports clinical research by designing and executing robust data analysis plans, building digital solutions, and transforming complex clinical trial data into actionable insights. This role partners closely with research teams to enhance continuous glucose monitoring trials through advanced analytics, workflow automation, and intuitive data visualizations that inform key decisions and improve trial outcomes. Responsibilities Collaborate with the research team to design and implement data analysis plans for clinical trials. Use statistical methods to analyze clinical trial data and identify trends, patterns, and outliers. Create clear, insightful data visualizations and reports to communicate findings to the research team and other stakeholders. Work with multidisciplinary team members to interpret data and translate results into practical insights that inform decision-making. Develop and implement data governance practices to promote consistency, data quality, and shared understanding across the organization. Stay current with research and industry developments related to continuous glucose monitoring devices and related technologies. Partner with the research team to identify opportunities for digital transformation within clinical trials. Develop and implement digital solutions that streamline data collection, data analysis, and data visualization processes. Design and implement strategies that leverage digital technologies to enhance patient recruitment, engagement, and retention in clinical trials. Analyze and interpret data generated from digital solutions to guide decision-making and improve trial outcomes. Automate analytics workflows using Python and workflow orchestration tools to improve efficiency and reliability. Build, maintain, and optimize dashboards and reports that support ongoing monitoring of trial performance and outcomes. Design, schedule, and monitor data pipelines to ensure timely and accurate data delivery for analysis. Query and manage relational databases to support data extraction, transformation, and modeling for clinical research. Develop or integrate application programming interfaces (APIs) to enable data exchange between digital tools and research systems. Essential Skills Experience working in clinical research with a solid understanding of clinical trial design. Strong analytical and problem-solving skills, with the ability to work with complex datasets and identify meaningful patterns and trends. Excellent communication and presentation skills, with the ability to explain results and insights clearly to non-technical stakeholders. Ability to work both independently and collaboratively within a team environment. Intermediate to advanced Python programming skills, including the ability to develop, test, and maintain analytics automation. Proficiency in Power BI for dashboard and report development and data visua</t>
+          <t>DATA ANALYST L4 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST L4 City: Bengaluru State/Province: Karnataka Posting Start Date: 6/15/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descr</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>**Quality Control Analyst** 24/HR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>Saint Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -957,12 +937,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -972,52 +952,52 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131997/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006209634/-Quality-Control-Analyst-24-HR</t>
         </is>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T07:09:25+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>50fd2fdb0dc885a55d37</t>
+          <t>36015f5985591e74c23c</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>Quality Control Analyst Job Description The Quality Control Analyst performs physical property testing and wet chemistry testing on raw materials, in-process samples, and finished products, and progressively assumes responsibility for a full range of analytical testing, including chromatographic methods. This role prioritizes daily sample testing in a high-throughput environment, ensures the accuracy and completeness of laboratory and compounding records, and supports investigations into out-of-specification and out-of-trend results as well as customer complaints. The analyst works closely with production, engineering, and quality teams to maintain compliance with Good Manufacturing Practices (GMP) and Good Documentation Practices (GDP) while contributing to continuous improvement of laboratory methods, systems, and processes. Responsibilities Perform laboratory analysis on incoming raw materials, in-process samples, and finished products according to established procedures, including physical property testing and wet chemistry methods such as viscosity, pH, and total organic carbon (TOC) for water testing. Conduct analytical testing using chromatographic techniques, including GC and HPLC, and become proficient in routine operation, integration, and result calculations for these instruments. Prioritize and execute daily sample testing to support bulk formula batches and line samples, ensuring timely turnaround in a high-throughput laboratory environment. Prepare samples for chromatographic analysis, including preparation of standard and reagent solutions in accordance with laboratory protocols. Access, input, and retrieve data from the Laboratory Information Management System (LIMS) to manage sample information, test results, and product disposition. Review compounding and laboratory records for accuracy and completeness, ensuring compliance with Good Documentation Practices (GDP) and Good Manufacturing Practices (GMP). Disposition raw materials, in-process samples, and finished products for use or sale based on test results and established specifications. Document deviations in performance or results that are not anticipated or indicated in test procedures, and communicate findings to appropriate quality personnel. Assist with investigations of out-of-specification (OOS) and out-of-trend (OOT) results, as well as customer complaints, by performing additional testing, data review, and documentation as required. Support method development protocols by conducting requisite testing, documenting results, and providing feedback on method performance. Assist with instrument qualification and validation activities, including IQ (Installation Qualification), OQ (Operational Qualification), and PQ (Performance Qualification), as well as calibration tasks. Participate in method transfer protocols by performing comparative testing and ensuring methods are implemented consistently across laboratories or sites. Assist with annual and new supplier validation p</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>**Quality Control Analyst** 24/HR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>Saint Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1027,12 +1007,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1042,52 +1022,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131996/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006215646/-Quality-Control-Analyst-24-HR</t>
         </is>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T07:09:25+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1739427c8572b9e16c54</t>
+          <t>270195dbfa3bd649268f</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>Computer Operations Analyst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>Colorado Springs, Colorado, 80901, USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1097,12 +1077,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1112,16 +1092,16 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131995/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006211688/Computer-Operations-Analyst</t>
         </is>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1130,34 +1110,34 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>d61a9673a94652c8948d</t>
+          <t>301e1f88c5c589466119</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>Job Title: Operations Analyst - COSA Job Description This full-time Operations Analyst role focuses on the daily monitoring, operation, and maintenance of large-scale computer and communications systems in a 24x7 environment . The position provides first-level technical support, performs initial troubleshooting across hardware, software, and networks, and supports both operational and test activities. The role requires experience in system and network administration, an active DoD Secret clearance, and current DoD 8570 IAT Level II certification. Responsibilities Perform daily system monitoring, operations, and maintenance of large-scale computer and communications systems in a 24x7 operational and test environment. Provide first-level technical support to users, including warfighters, and serve as the initial point of contact for technical issues. Perform initial troubleshooting of local hardware, software, and network issues to restore services and minimize downtime. Document and report all events, incidents, and issues to the appropriate watch officer and follow established reporting procedures. Receive tasking and direction from the command and control center for all operations, testing, and real-world events, and execute assigned tasks accurately and on time. Assist with hardware and software installations as directed by local subject matter experts, ensuring proper configuration and functionality. Create and maintain user accounts as directed by the local information system security officer, following established security policies and procedures. Use trouble ticketing tools to log, track, and update incidents and service requests, ensuring clear communication and proper documentation. Collaborate with system and network administrators to resolve complex issues related to UNIX, Linux, Windows, Cisco, and Juniper environments. Support both operations and training assignments as directed by mission requirements. Perform other duties and assignments as required to support mission objectives. Essential Skills Bachelor’s degree from an accredited college in a related discipline, or equivalent combination of education and experience, with 6 years of professional experience .Minimum of 6 years of experience in operations and maintenance of large-scale computer and communications systems or similar environments. Current DoD 8570 IAT Level II certification (such as Security+ CE, CySA+, GSEC, SSCP, CCNA Security or equivalent) and ability to maintain this certification for the full contract period. Active DoD Secret clearance at the time of hire . Strong and experience in system and/or network administration, including UNIX, Linux, and Windows operating systems. Demonstrated ability to troubleshoot hardware components, including servers, workstations, and network devices. Demonstrated ability to troubleshoot software components, including operating systems, applications, and network services. Proficiency with Microsoft Word, Excel, and PowerPoint. Exp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>Computer Operations Analyst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>Colorado Springs, Colorado, 80901, USA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1167,12 +1147,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1182,16 +1162,16 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131994/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006198519/Computer-Operations-Analyst</t>
         </is>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1200,34 +1180,34 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5e2f686de97e73e9af36</t>
+          <t>082b81d0b745bbf821be</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>Job Title: Operations Analyst Job Description This full-time Operations Analyst role focuses on the daily monitoring, operation, and maintenance of large-scale computer and communications systems in a 24x7 environment . The position provides first-level technical support, performs initial troubleshooting across hardware, software, and networks, and supports both operational and test activities. The role requires experience in system and network administration, an active DoD Secret clearance, and current DoD 8570 IAT Level II certification. Responsibilities Perform daily system monitoring, operations, and maintenance of large-scale computer and communications systems in a 24x7 operational and test environment. Provide first-level technical support to users, including warfighters, and serve as the initial point of contact for technical issues. Perform initial troubleshooting of local hardware, software, and network issues to restore services and minimize downtime. Document and report all events, incidents, and issues to the appropriate watch officer and follow established reporting procedures. Receive tasking and direction from the command and control center for all operations, testing, and real-world events, and execute assigned tasks accurately and on time. Assist with hardware and software installations as directed by local subject matter experts, ensuring proper configuration and functionality. Create and maintain user accounts as directed by the local information system security officer, following established security policies and procedures. Use trouble ticketing tools to log, track, and update incidents and service requests, ensuring clear communication and proper documentation. Collaborate with system and network administrators to resolve complex issues related to UNIX, Linux, Windows, Cisco, and Juniper environments. Support both operations and training assignments as directed by mission requirements. Perform other duties and assignments as required to support mission objectives. Essential Skills Bachelor’s degree from an accredited college in a related discipline, or equivalent combination of education and experience, with 6 years of professional experience. Minimum of 6 years of background experience in operations and maintenance of large-scale computer and communications systems or similar environments. Current DoD 8570 IAT Level II certification (such as Security+ CE, CySA+, GSEC, SSCP, CCNA Security or equivalent) and ability to maintain this certification for the full contract period. Active DoD Secret clearance at the time of hire . Strong background and experience in system and/or network administration, including UNIX, Linux, and Windows operating systems. Hands-on experience with Cisco and Juniper networking equipment and configurations. Demonstrated ability to troubleshoot hardware components, including servers, workstations, and network devices. Demonstrated ability to troubleshoot software components, including operating syste</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>Environmental Lab Analyst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>Iowa City, Iowa, 52240, USA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1237,12 +1217,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1252,52 +1232,52 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131993/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006199506/Environmental-Lab-Analyst</t>
         </is>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-13T21:32:27+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>da60c6db3c8bf52b3c59</t>
+          <t>4d36e60c52d5d0be30f9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>Environmental Lab Analyst Job Description The Environmental Lab Analyst evaluates and processes environmental samples to ensure compliance with regulatory and quality standards. This role performs routine and specialized bacteriological and analytical testing, supports infectious disease surveillance through wastewater analysis, and contributes to method development and continuous improvement within a fast-paced, collaborative laboratory environment. Responsibilities Accession and evaluate environmental samples to confirm compliance with holding times and established acceptance criteria. Conduct routine bacteriological testing using standardized procedures and documented quality control protocols. Perform analytical testing across various sample types and matrices, serving as a lead analyst when assigned. Recommend adjustments or enhancements to established analytical methods to address complex or challenging samples. Participate in Food Emergency Response Network activities, including testing for organisms such as E. coli, Listeria, and other bacteria. Perform wastewater testing to support infectious disease surveillance initiatives. Apply aseptic technique and proper plating methods to ensure accurate microbiological results. Document all testing activities accurately and maintain organized records in accordance with laboratory standards. Follow quality assurance and quality control procedures to ensure reliability and reproducibility of data. Collaborate closely with laboratory colleagues to coordinate sample processing and meet turnaround times. Communicate effectively with team members regarding sample status, testing issues, and method improvements. Adhere to all laboratory safety protocols and maintain a clean, orderly work area. Support weekend and overtime testing needs as scheduled to ensure continuity of laboratory operations. Essential Skills Minimum of 6 months of hands-on laboratory experience in chemistry, biology, or microbiology. Strong foundation in chemistry, biology, or microbiology with practical lab skills. Proficiency in routine bacteriological testing using standardized procedures. Ability to apply aseptic technique consistently to prevent contamination. Experience with analytical chemistry methods and quality control practices. Skill in microbiological plating and handling various sample types and matrices. Attention to detail in sample accessioning, evaluation, and documentation. Ability to follow established protocols while recognizing when method adjustments may be needed. Strong organizational skills to manage multiple samples and tasks in a fast-paced environment. Effective communication skills for collaborating within a laboratory team. Commitment to laboratory safety and quality assurance standards. Additional Skills &amp; Qualifications Four-year degree in life sciences required; majors such as biology, chemistry, microbiology, or biochemistry are preferred. Experience working in a quality assurance or quality control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst</t>
+          <t>GIS Analyst</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Englewood, Colorado, United States</t>
+          <t>St. Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1307,12 +1287,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FULL_TIME</t>
+          <t>["OTHER"]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1322,57 +1302,57 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/us-en/jobs/00070131992/entry-level-healthcare-analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
         </is>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-13T21:32:27+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>d00b31e4784f93e29d99</t>
+          <t>2bb0d66e462a56093e20</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
+          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indirect Auto Credit Analyst</t>
+          <t>Geospatial Intelligence Analyst</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>Saint Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1382,7 +1362,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1397,62 +1377,62 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006165749/Indirect-Auto-Credit-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006203486/Geospatial-Intelligence-Analyst</t>
         </is>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T07:09:25+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>65129f2115e0b79bbb2e</t>
+          <t>21af9ec8aa44e879fd75</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Indirect Auto Underwriter | Credit Analyst 🕒 Schedule: 12:00 PM – 9:00 PM MT (weekends required) 📍 Location: Remote - MUST BE LOCATED IN: Colorado, Wyoming, Illinois, Texas, Arizona, Florida, Washington, Georgia, Virginia, OR Hawaii About the Role We’re seeking an experienced Indirect Auto Underwriter to independently review, analyze, and decision auto loan applications sourced through dealerships and credit unions. In this role, you’ll own credit decisions from start to finish while partnering closely with dealers and credit union representatives to maximize funding and approval rates. This position is ideal for underwriters who are confident decision‑makers and thrive in a fast‑paced, high‑volume environment. Key Responsibilities Review and underwrite indirect auto loan applications from dealer and credit union channels Analyze credit bureaus, income calculations, debt‑to‑income (DTI), and loan‑to‑value (LTV) ratios Make final credit decisions: approve, deny, or condition files for additional information Communicate directly with dealers and credit union partners to resolve stipulations and negotiate loan terms Document underwriting decisions clearly across multiple loan origination systems Monitor dealer productivity and support improved look‑to‑book and funding ratios Send completed loan packages to credit unions for final funding Support operational goals related to turnaround time, volume, and quality Mentor junior Credit Analysts as needed Required Qualifications Minimum 2 years of true indirect auto underwriting experience with decision‑making authority Strong experience breaking down credit bureaus, income calculations, LTV, and DTI Hands‑on experience with L360, CUDL, Ideal, Keystone Correlation, Loans PQ, and/or Meridian Link Comfortable working weekends and late shifts (12 PM – 9 PM MT) Strong documentation, communication, and relationship‑building skills Education High school diploma or equivalent required Associate’s or Bachelor’s degree preferred Why This Role Full underwriting autonomy and decision authority High visibility with credit unions and dealers Opportunity to directly influence funding and capture rates Fast‑paced, results‑driven environment with growth potential Pay and Benefits The pay range for this position is $27.00 - $32.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Ty</t>
+          <t>Job Title: Geospatial Intelligence Analyst Job Description The Geospatial Intelligence Analyst analyzes and transforms aeronautical and geospatial data into accurate, high-quality digital aviation navigation products. This role focuses on creating and maintaining enroute charts and terminal procedures while ensuring strict adherence to government specifications and technical standards. The analyst works closely with a distributed team, operates with a high degree of independence, and supports safe and efficient flight operations through precise data analysis and cartographic production. Responsibilities Analyze source material, including host nation aeronautical data, government-provided updates, and current digital maps, to determine the impact of changes on aviation navigation products. Create, maintain, and update digital high- and low-altitude enroute charts and terminal procedure products, including Standard Instrument Departures (SIDs), Standard Terminal Arrival Routes (STARs), and Instrument Approach Procedures (IAPs). Convert worldwide aeronautical data into digital and graphic formats suitable for flight operations and aviation navigation products. Ensure the accuracy, quality, and conformance of all products to government product specifications and technical specifications. Identify and resolve data conflicts, inconsistencies, and anomalies in aeronautical and geospatial datasets. Request clarification of source data issues or specification questions when needed to maintain product integrity. Apply changes in product specifications and implement updates consistently across all assigned products. Collaborate and communicate effectively with team members using email, instant messaging, and voice communication tools. Work remotely with minimal day-to-day oversight while maintaining productivity and meeting deadlines. Prioritize tasks, self-motivate, and operate independently while working weekdays during established team core hours. Leverage GIS, CAD, and digital cartography tools to support the production and maintenance of aviation charts and related products. Utilize aviation knowledge, including aeronautical principles, instrument flight procedures, air traffic control concepts, and chart symbology, in daily analytical and production tasks. Support mission planning and aerial survey-related workflows by integrating geospatial and aeronautical data as needed. Essential Skills Previous experience in the production or use of enroute charts, Instrument Approach Procedures (IAPs), Standard Instrument Departures (SIDs), and/or Standard Terminal Arrival Routes (STARs). Aviation knowledge, including a strong understanding of aeronautical principles, aviation navigation, instrument flight procedures, air traffic control concepts, and chart symbology. Experience with GIS software, CAD software, or similar digital cartography tools, such as Esri ArcGIS Aviation Charting, Bentley OpenCities Map, Esri products, or comparable platforms. Bachelor's d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lead Azure Fabric Data Engineer - Remote Position</t>
+          <t>Microbiology Laboratory Analyst II</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>Hercules, California, 94547, USA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>["FULL_TIME"]</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1467,11 +1447,11 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006210958/Lead-Azure-Fabric-Data-Engineer-Remote-Position</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006193396/Microbiology-Laboratory-Analyst-II</t>
         </is>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1480,34 +1460,34 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>d6b506e44408fdaf87b9</t>
+          <t>46f1845291bcf8f05353</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Think of TEKsystems Global Services (TGS) as the growth solution for enterprises today. We unleash growth through technology, strategy, design, execution and operations with a customer-first mindset for bold business leaders. We deliver cloud, data and customer experience solutions. Our partnerships with leading cloud, design and business intelligence platforms fuel our expertise. We value deep relationships, dedication to serving others and inclusion. We drive positive outcomes for our people and our business, and we stay true to our commitments and act in harmony with our words. We exist to create significant opportunities for people to achieve fulfillment through career success. Ready to join us? Here’s what the opportunity supported through our TGS Talent Acquisition Team requires: Position Overview We are seeking a highly skilled Lead Data Engineer with strong expertise in Microsoft Fabric and Azure analytics ecosystem to design and deliver modern, scalable data platforms. The ideal candidate should be a good team player with 8 or more years of experience in data engineering with Microsoft technologies, deep hands-on expertise in Microsoft Azure Fabric platform (OneLake, Lakehouse, Data Factory pipelines, Synapse Data Engineering, Power BI), and preferably some experience with Azure AI/ML services. This role requires expertise in designing, developing, and deploying secure, scalable, and high-performance cloud-native analytics solutions, mentoring engineering teams, and close collaboration with architects, AI Engineers, Data Scientists, and business stakeholders to deliver impactful, data-driven solutions. This position will require up to 50% travel to customer sites as per project need. Essential Functions • Actively involved in requirement gathering workshops from customers, translating the functional requirements into technical solutions, and translating complex technical concepts into actionable insights for stakeholders • Actively participates in architectural discussions independently or under guidance/supervision from Practice Architect to design and develop effective, efficient, reliable, secure, scalable, and cost-optimized data engineering solutions as per the overall data management strategy • Design and implement modern data platform architectures using Microsoft Fabric, including: o OneLake-based data Lakehouse architectures o Data Factory pipelines within Fabric o Synapse Data Engineering and Data Warehousing experiences • Develop scalable data ingestion, transformation, and orchestration pipelines using Fabric-native tools and Azure services • Design high-performance Lakehouse and Warehouse models following best practices (medallion architecture, dimensional modeling) • Integrate Azure services such as Azure Data Factory, ADLS Gen2, Azure SQL, Databricks (optional) • Build interactive and scalable Power BI semantic models and reports integrated with Fabric • Implement CI/CD pipelines (Azure DevOps/GitHub) for data and analytic</t>
+          <t>Job Title: Microbiology Laboratory Analyst II Job Description The Microbiology Laboratory Analyst II plays a hands-on role in performing microbiology testing, managing samples, and supporting laboratory operations in a GMP/GLP-regulated environment. This client-facing position requires a strong quality mindset, excellent documentation skills, and the ability to perform both routine and advanced microbiological assays while maintaining strict compliance with regulatory and quality standards. Responsibilities Perform microbiological testing in accordance with SOPs, GMP, GLP, USP, EP, and ISO requirements. Conduct bioburden testing following USP / guidelines. Perform endotoxin testing in alignment with USP requirements. Execute sterility testing according to USP standards. Perform antimicrobial effectiveness testing following USP methods. Conduct container closure integrity testing (CCIT). Perform environmental monitoring of cleanrooms and controlled environments. Conduct TOC, conductivity, and pH testing for water and utilities. Support cleaning and disinfection validation activities. Perform environmental monitoring and water/utility sampling as scheduled or requested. Support method development, verification, validation, and method transfers. Investigate out-of-specification (OOS) and non-conforming results and complete associated CAPA activities. Maintain laboratory inventory, reagents, equipment, and associated documentation. Ensure the laboratory remains compliant, clean, organized, and audit-ready at all times. Deliver accurate and reliable test results within required turnaround times. Support custom studies and client-specific projects as needed. Collaborate with internal teams and clients to ensure clear communication of testing requirements and results. Document all activities accurately and contemporaneously in accordance with regulatory and quality expectations. Essential Skills Minimum 2+ years of experience in a GMP/GLP or FDA-regulated laboratory environment. Strong microbiology laboratory techniques and aseptic practices. Hands-on experience with environmental monitoring. Experience performing bioburden testing. Proficiency working within cleanroom and controlled environments. Excellent technical writing and documentation skills. Strong attention to detail and a demonstrated commitment to quality. Ability to thrive in a fast-paced, dynamic laboratory environment. Ability to manage multiple tasks while maintaining accuracy and compliance. Effective communication skills for a client-facing role. Additional Skills &amp; Qualifications BS, MS, or PhD in Microbiology, Biology, Biotechnology, Pharmaceutical Sciences, or a related scientific discipline preferred. Experience supporting method development, verification, validation, and method transfers. Familiarity with USP, EP, ISO, and other relevant regulatory and compendial standards. Experience conducting cleaning and disinfection validations. Background in working within cGMP/GLP testing s</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>Project Analyst</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chandler, Arizona, 85224, USA</t>
+          <t>Houston, Texas, 77001, USA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1522,7 +1502,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1537,11 +1517,11 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006220916/Production-Support-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006196066/Project-Analyst</t>
         </is>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1550,34 +1530,34 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3f0c61efac299216c3d3</t>
+          <t>64bcb93c6b4e737d64ed</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Job Description Strong Attention to Detail: Crucial for tasks like restarting the correct jobs, where a small error can have significant consequences. Independent and Teachable: Must be able to learn quickly, operate with minimal supervision, and adapt to new challenges. Strong Interpersonal Skills: Ability to communicate effectively and assertively with customers and stakeholders to enforce process. Strategic Thinker: Capable of seeing the bigger picture beyond routine tasks and contributing to the long-term improvement of the services. Experience: Experience in a production support or similar operational role is highly preferred. Experience following runbooks and handling operational tasks like monitoring dashboards and escalating issues is expected. Key Responsibilities 24/7 Production Support: Provide on-call support for critical applications, including weekends and holidays, as part of a follow-the-sun model with an existing team in India. Independent Operation: Act as the sole representative of the team during shifts, making decisions and responding to incidents independently. Compliance and Process Adherence: Enforce proper documentation and justification for all requests, pushing back on non-compliant asks that come through informal channels like Teams or email. Incident and Change Management: Handle day-to-day operational tasks, including monitoring queues, managing incidents and change requests, and performing deployments. Process Improvement and Automation: Proactively identify recurring issues, analyze root causes, and drive improvements to streamline processes and reduce manual intervention. The goal is to evolve the role by automating L1-type tasks. Customer Engagement: Meet with application owners to discuss recurring problems and advocate for bug fixes and stability improvements over new feature development. Skills Windows, System administrator, UNIX, linux, autosys, servicenow, splunk, grafana, ticketing, job scheduling, triage, incident Top Skills Details Windows,System administrator,UNIX,linux,autosys,servicenow,splunk,grafana,ticketing,job scheduling,triage,incident Additional Skills &amp; Qualifications NA Experience Level Entry Level Job Type &amp; Location This is a Contract position based out of Chandler, AZ. Pay and Benefits The pay range for this position is $69.25 - $69.25/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO,</t>
+          <t>Job Title: Project Coordinator Job location: Downtown Houston Job Description This role offers an opportunity for an experienced Project Coordinator to support a busy project team in Houston by providing comprehensive project coordination, cost control, and analytical support for oil and gas and natural gas pipeline projects. The successful candidate will help manage a large portfolio of projects, ensuring accurate cost tracking, forecasting, and reporting while working closely with engineering and project management teams. Responsibilities Provide project coordination and project controls support for oil and gas and natural gas pipeline projects. Support project managers and engineering teams by tracking project costs, schedules, and progress across multiple concurrent projects. Perform cost control activities, including cost analysis, forecasting, and budget monitoring for projects ranging from several million to very large capital investments. Prepare, maintain, and analyze project reports using Excel, including pivot tables and large data sets, to provide clear and accurate information to stakeholders. Assist with project management tasks such as tracking milestones, monitoring performance, and ensuring adherence to project plans and budgets. Coordinate with engineering project managers and engineering teams to collect data, validate information, and resolve discrepancies related to project costs and schedules. Support inventory control and supply chain-related activities as they relate to project materials, costs, and timelines. Contribute to quality assurance efforts by ensuring the accuracy and completeness of project data, documentation, and reports. Utilize ERP systems, such as SAP or similar platforms, to input, track, and reconcile project financials and cost information when applicable. Communicate effectively with team members and stakeholders while managing multiple priorities and projects simultaneously, often supporting 30–40 active projects. Prepare and deliver regular status updates and cost reports to project leadership to support informed decision-making. Essential Skills 5+ years of experience in project controls or project analyst roles, specifically supporting large capital or infrastructure projects. Demonstrated experience providing project coordination, cost controls, and project analyst support in the oil and gas or natural gas sector. Past experience working in the pipeline industry and coordinating with engineering project managers or engineering teams. College degree in business, finance, construction management, accounting, engineering, or a related field. Strong proficiency in Microsoft Excel, including building and using pivot tables and working with large data sets. Proven ability to perform cost analysis, cost control, and forecasting for complex projects. Experience with project management and project control practices, including reporting and performance tracking. Ability to manage and prioritize work across a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3</t>
+          <t>QC Analyst</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Saint Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1587,7 +1567,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1602,47 +1587,47 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/DATA-ANALYST-L3/188736-en_US</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006214665/QC-Analyst</t>
         </is>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T07:09:25+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>cdbb628deff24d9065f2</t>
+          <t>482f995d9540ba56230b</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST L3 City: Bengaluru State/Province: Karnataka Posting Start Date: 7/12/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descr</t>
+          <t>QC Analyst Position Summary The QC Analyst supports quality control testing and laboratory operations by evaluating the physical and mechanical properties of materials used in manufacturing and product development. This role performs laboratory testing, sample preparation, data analysis, equipment operation, and documentation activities to ensure product quality and compliance with established standards. The position offers an excellent opportunity for recent graduates and early-career scientists to gain hands-on laboratory experience while developing technical expertise in materials characterization, quality systems, and manufacturing support. Key Responsibilities Perform laboratory testing on raw materials, in-process materials, and finished products according to established procedures and specifications. Conduct physical and mechanical property testing, including tensile strength, elongation, hardness, viscosity, thermal resistance, and related material performance evaluations. Prepare samples and test specimens using cutting, molding, conditioning, and other standardized preparation techniques. Collect, analyze, and record laboratory data accurately while identifying trends, deviations, or unusual results. Operate and maintain laboratory instruments such as universal testing machines, viscometers, ovens, balances, and microscopes. Document testing activities, observations, and results in laboratory records and electronic systems. Support investigations and troubleshooting activities related to product quality, manufacturing processes, or material performance. Collaborate with Quality, Production, R&amp;D, and Engineering teams to support product development and continuous improvement initiatives. Maintain laboratory organization, equipment, and test materials in accordance with quality and safety standards. Follow all laboratory safety procedures, chemical handling requirements, and applicable regulatory or industry standards. Required Qualifications Bachelor's degree in Chemistry, Materials Science, Chemical Engineering, Biology, Physics, Engineering Technology, Environmental Science, or another related scientific discipline. Laboratory experience obtained through academic coursework, undergraduate research, internships, co-ops, or industry experience. Strong attention to detail and ability to accurately document laboratory activities and test results. Basic understanding of scientific testing methods and laboratory best practices. Ability to collect, interpret, and communicate technical data. Strong organizational, analytical, and problem-solving skills. Proficiency with Microsoft Office applications, especially Excel. Ability to work effectively both independently and within a collaborative team environment. Preferred Qualifications Experience performing physical property testing, materials characterization, quality control testing, or manufacturing laboratory work. Experience operating laboratory equipment such as viscometers, testing machine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Senior Analyst</t>
+          <t>Quality Analyst</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hayward, California, 94540, USA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1652,7 +1637,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1667,11 +1657,11 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Senior-Analyst/56838-en_US</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006214748/Quality-Analyst</t>
         </is>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1680,17 +1670,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>cb10e1785491d76e3173</t>
+          <t>cf6368e0ed533a99382e</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 5/22/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descrip</t>
+          <t>Job Title: Quality Analyst Job Description The Quality Analyst plays a key role in ensuring that production-scale materials meet rigorous performance and quality standards. In this role, you operate analytical instruments, generate and analyze test data, maintain quality systems, and contribute directly to the development and optimization of new products. As part of a rapidly growing start-up environment, your work will have a direct and significant impact on the product line and its position as a leader in transparent conductive films. Responsibilities Operate analytical instruments to measure and collect data for production-scale materials. Prepare and produce test samples and accurately measure their performance. Test, compile, and analyze data to assess the quality and consistency of production-scale materials. Maintain quality databases and regularly review quality KPIs to monitor performance and trends. Manage the calibration, maintenance, and general upkeep of quality analytical instruments and equipment. Develop new characterization methodologies as needed and create clear standard operating procedures (SOPs). Assist in defining product specifications for new production materials to align performance with internal and external customer requirements. Participate in product nonconformance investigations and support the development and implementation of corrective actions. Prepare technical reports and summaries for both internal stakeholders and external partners. Collaborate effectively in a multi-disciplinary environment, contributing quality insights to cross-functional teams. Essential Skills 3–5 years of industrial quality control (QC) or quality assurance (QA) experience. Strong background in analytical chemistry and hands-on laboratory experience. Experience operating and maintaining analytical instruments for material characterization. Proficiency in chemical handling and adherence to laboratory safety practices. Familiarity with GMP principles and quality standards. Experience with JMP or similar statistical software for data analysis. Knowledge of design of experiments (DOE) and statistical analysis techniques. Ability to maintain and interpret quality databases and key performance indicators (KPIs). Strong organizational skills and attention to detail. Effective communication skills for preparing technical reports and collaborating with cross-functional teams. Proven ability to work both independently and as part of a team in a multi-disciplinary environment. Additional Skills &amp; Qualifications Degree in Chemical Engineering, Materials Science and Engineering, Chemistry, Physics, or a related discipline. Knowledge of optoelectronic devices and thin film coatings. Hands-on experience with analytical instruments related to thin films and optoelectronic materials. Experience with mixing, blending, and wet coating operations. Experience developing characterization methodologies and authoring SOPs. Comfort working in a dynamic, rapidly</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1692,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Quality Control Analyst** 24/HR</t>
+          <t>Quality Control Analyst</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1722,7 +1712,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1737,7 +1727,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006209634/-Quality-Control-Analyst-24-HR</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006214649/Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1750,17 +1740,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>36015f5985591e74c23c</t>
+          <t>c3c59b3b294b2f2973cd</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Quality Control Analyst Job Description The Quality Control Analyst performs physical property testing and wet chemistry testing on raw materials, in-process samples, and finished products, and progressively assumes responsibility for a full range of analytical testing, including chromatographic methods. This role prioritizes daily sample testing in a high-throughput environment, ensures the accuracy and completeness of laboratory and compounding records, and supports investigations into out-of-specification and out-of-trend results as well as customer complaints. The analyst works closely with production, engineering, and quality teams to maintain compliance with Good Manufacturing Practices (GMP) and Good Documentation Practices (GDP) while contributing to continuous improvement of laboratory methods, systems, and processes. Responsibilities Perform laboratory analysis on incoming raw materials, in-process samples, and finished products according to established procedures, including physical property testing and wet chemistry methods such as viscosity, pH, and total organic carbon (TOC) for water testing. Conduct analytical testing using chromatographic techniques, including GC and HPLC, and become proficient in routine operation, integration, and result calculations for these instruments. Prioritize and execute daily sample testing to support bulk formula batches and line samples, ensuring timely turnaround in a high-throughput laboratory environment. Prepare samples for chromatographic analysis, including preparation of standard and reagent solutions in accordance with laboratory protocols. Access, input, and retrieve data from the Laboratory Information Management System (LIMS) to manage sample information, test results, and product disposition. Review compounding and laboratory records for accuracy and completeness, ensuring compliance with Good Documentation Practices (GDP) and Good Manufacturing Practices (GMP). Disposition raw materials, in-process samples, and finished products for use or sale based on test results and established specifications. Document deviations in performance or results that are not anticipated or indicated in test procedures, and communicate findings to appropriate quality personnel. Assist with investigations of out-of-specification (OOS) and out-of-trend (OOT) results, as well as customer complaints, by performing additional testing, data review, and documentation as required. Support method development protocols by conducting requisite testing, documenting results, and providing feedback on method performance. Assist with instrument qualification and validation activities, including IQ (Installation Qualification), OQ (Operational Qualification), and PQ (Performance Qualification), as well as calibration tasks. Participate in method transfer protocols by performing comparative testing and ensuring methods are implemented consistently across laboratories or sites. Assist with annual and new supplier validation p</t>
+          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1762,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>**Quality Control Analyst** 24/HR</t>
+          <t>Quality Control Analyst - Day Shift (Weekends)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1792,7 +1782,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1807,7 +1797,7 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006215646/-Quality-Control-Analyst-24-HR</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006213012/Quality-Control-Analyst-Day-Shift-Weekends</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -1820,17 +1810,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>270195dbfa3bd649268f</t>
+          <t>e31226ca24349305fae4</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
+          <t>Job Title: Quality Control Analyst - Day Shift (Weekends) Job Description The Quality Control Analyst is responsible for prioritizing and performing daily sampling of incoming raw materials and laboratory testing while ensuring compliance with GMP and FDA requirements. This role supports manufacturing operations through timely testing, disposition decisions, accurate documentation, and communication of quality-related information. Responsibilities Perform sampling of incoming raw materials (liquids and solids) within manufacturing and warehouse areas according to established procedures. Conduct laboratory testing and analysis of raw materials using wet chemistry and chromatographic techniques. Prepare samples for chromatographic analysis. Perform routine GC and HPLC analysis. Review compounding and laboratory records for completeness and accuracy. Investigate customer complaints and document findings. Disposition raw materials for use or sale. Document deviations from established procedures and test methods. Maintain compliance with GMP regulations and laboratory documentation standards. Ensure safe handling, analysis, processing, and storage of hazardous and flammable materials. Coordinate information flow between the laboratory and internal stakeholders. Provide timely and accurate quality information to production personnel. Access, enter, and retrieve data from Quality Control computer systems. Maintain laboratory organization and housekeeping. Participate in required meetings and training programs. Become knowledgeable in manufacturing processes, QC workflows, retain sample programs, and documentation procedures. Work independently while adjusting priorities in response to changing business needs. Perform other duties as assigned. Essential Skills Quality control Chemistry Wet chemistry Strong multi-tasking ability Effective communication with compounding leadership Ability to work independently without constant supervision Problem-solving skills High attention to detail Strong organizational and time-management skills Ability to make sound decisions under pressure Strong compliance mindset regarding GMP and quality standards Additional Skills &amp; Qualifications Bachelor's Degree minimum required, Chemistry preferred but open to Biochemistry, Biology with a Chemistry Minor, or other related science. 1 year of experience in a QC laboratory with exposure to physical testing, volumetric solution sample preparation, GMP/GDP, and exposure to LIMS or other lab sample management systems. Lab Exposure/Experience with: HPLC, GC, FTIR, TOC. General experience working within MS Office including Word, Excel, Teams, Outlook. Strong teamwork and collaboration skills Professional communication with colleagues and internal customers Ability to coordinate effectively across departments Commitment to identifying, documenting, and resolving quality issues Job Type &amp; Location This is a Contract to Hire position based out of Saint Louis, MO. Pay and Benefits The p</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1832,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Environmental Lab Analyst</t>
+          <t>Quality Control Analyst - OVERNIGHTS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iowa City, Iowa, 52240, USA</t>
+          <t>Saint Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1862,7 +1852,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1877,7 +1867,7 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006199506/Environmental-Lab-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006214635/Quality-Control-Analyst-OVERNIGHTS</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -1885,22 +1875,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-13T21:32:27+00:00</t>
+          <t>2026-08-14T07:09:25+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>4d36e60c52d5d0be30f9</t>
+          <t>97c15ff34540d0b546c4</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Environmental Lab Analyst Job Description The Environmental Lab Analyst evaluates and processes environmental samples to ensure compliance with regulatory and quality standards. This role performs routine and specialized bacteriological and analytical testing, supports infectious disease surveillance through wastewater analysis, and contributes to method development and continuous improvement within a fast-paced, collaborative laboratory environment. Responsibilities Accession and evaluate environmental samples to confirm compliance with holding times and established acceptance criteria. Conduct routine bacteriological testing using standardized procedures and documented quality control protocols. Perform analytical testing across various sample types and matrices, serving as a lead analyst when assigned. Recommend adjustments or enhancements to established analytical methods to address complex or challenging samples. Participate in Food Emergency Response Network activities, including testing for organisms such as E. coli, Listeria, and other bacteria. Perform wastewater testing to support infectious disease surveillance initiatives. Apply aseptic technique and proper plating methods to ensure accurate microbiological results. Document all testing activities accurately and maintain organized records in accordance with laboratory standards. Follow quality assurance and quality control procedures to ensure reliability and reproducibility of data. Collaborate closely with laboratory colleagues to coordinate sample processing and meet turnaround times. Communicate effectively with team members regarding sample status, testing issues, and method improvements. Adhere to all laboratory safety protocols and maintain a clean, orderly work area. Support weekend and overtime testing needs as scheduled to ensure continuity of laboratory operations. Essential Skills Minimum of 6 months of hands-on laboratory experience in chemistry, biology, or microbiology. Strong foundation in chemistry, biology, or microbiology with practical lab skills. Proficiency in routine bacteriological testing using standardized procedures. Ability to apply aseptic technique consistently to prevent contamination. Experience with analytical chemistry methods and quality control practices. Skill in microbiological plating and handling various sample types and matrices. Attention to detail in sample accessioning, evaluation, and documentation. Ability to follow established protocols while recognizing when method adjustments may be needed. Strong organizational skills to manage multiple samples and tasks in a fast-paced environment. Effective communication skills for collaborating within a laboratory team. Commitment to laboratory safety and quality assurance standards. Additional Skills &amp; Qualifications Four-year degree in life sciences required; majors such as biology, chemistry, microbiology, or biochemistry are preferred. Experience working in a quality assurance or quality control</t>
+          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1902,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GIS Analyst</t>
+          <t>Sr. Clinical Informatics Analyst</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, 63101, USA</t>
+          <t>San Diego, California, 92101, USA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1927,12 +1917,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>["OTHER"]</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1947,7 +1937,7 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006204592/Sr-Clinical-Informatics-Analyst</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1955,22 +1945,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-13T21:32:27+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2bb0d66e462a56093e20</t>
+          <t>021caefc4f61302fd025</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
+          <t>Job Title: Senior Clinical Informatics Analyst Job Description The Senior Clinical Informatics Analyst supports clinical research by designing and executing robust data analysis plans, building digital solutions, and transforming complex clinical trial data into actionable insights. This role partners closely with research teams to enhance continuous glucose monitoring trials through advanced analytics, workflow automation, and intuitive data visualizations that inform key decisions and improve trial outcomes. Responsibilities Collaborate with the research team to design and implement data analysis plans for clinical trials. Use statistical methods to analyze clinical trial data and identify trends, patterns, and outliers. Create clear, insightful data visualizations and reports to communicate findings to the research team and other stakeholders. Work with multidisciplinary team members to interpret data and translate results into practical insights that inform decision-making. Develop and implement data governance practices to promote consistency, data quality, and shared understanding across the organization. Stay current with research and industry developments related to continuous glucose monitoring devices and related technologies. Partner with the research team to identify opportunities for digital transformation within clinical trials. Develop and implement digital solutions that streamline data collection, data analysis, and data visualization processes. Design and implement strategies that leverage digital technologies to enhance patient recruitment, engagement, and retention in clinical trials. Analyze and interpret data generated from digital solutions to guide decision-making and improve trial outcomes. Automate analytics workflows using Python and workflow orchestration tools to improve efficiency and reliability. Build, maintain, and optimize dashboards and reports that support ongoing monitoring of trial performance and outcomes. Design, schedule, and monitor data pipelines to ensure timely and accurate data delivery for analysis. Query and manage relational databases to support data extraction, transformation, and modeling for clinical research. Develop or integrate application programming interfaces (APIs) to enable data exchange between digital tools and research systems. Essential Skills Experience working in clinical research with a solid understanding of clinical trial design. Strong analytical and problem-solving skills, with the ability to work with complex datasets and identify meaningful patterns and trends. Excellent communication and presentation skills, with the ability to explain results and insights clearly to non-technical stakeholders. Ability to work both independently and collaboratively within a team environment. Intermediate to advanced Python programming skills, including the ability to develop, test, and maintain analytics automation. Proficiency in Power BI for dashboard and report development and data visua</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1972,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Geospatial Intelligence Analyst</t>
+          <t>Supply Chain Analyst</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saint Louis, Missouri, 63101, USA</t>
+          <t>East Peoria, Illinois, 61611, USA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2002,7 +1992,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2017,7 +2007,7 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006203486/Geospatial-Intelligence-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006211353/Supply-Chain-Analyst</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2025,39 +2015,39 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-14T07:09:25+00:00</t>
+          <t>2026-08-14T04:46:20+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>21af9ec8aa44e879fd75</t>
+          <t>048251fc65475b88aad8</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Job Title: Geospatial Intelligence Analyst Job Description The Geospatial Intelligence Analyst analyzes and transforms aeronautical and geospatial data into accurate, high-quality digital aviation navigation products. This role focuses on creating and maintaining enroute charts and terminal procedures while ensuring strict adherence to government specifications and technical standards. The analyst works closely with a distributed team, operates with a high degree of independence, and supports safe and efficient flight operations through precise data analysis and cartographic production. Responsibilities Analyze source material, including host nation aeronautical data, government-provided updates, and current digital maps, to determine the impact of changes on aviation navigation products. Create, maintain, and update digital high- and low-altitude enroute charts and terminal procedure products, including Standard Instrument Departures (SIDs), Standard Terminal Arrival Routes (STARs), and Instrument Approach Procedures (IAPs). Convert worldwide aeronautical data into digital and graphic formats suitable for flight operations and aviation navigation products. Ensure the accuracy, quality, and conformance of all products to government product specifications and technical specifications. Identify and resolve data conflicts, inconsistencies, and anomalies in aeronautical and geospatial datasets. Request clarification of source data issues or specification questions when needed to maintain product integrity. Apply changes in product specifications and implement updates consistently across all assigned products. Collaborate and communicate effectively with team members using email, instant messaging, and voice communication tools. Work remotely with minimal day-to-day oversight while maintaining productivity and meeting deadlines. Prioritize tasks, self-motivate, and operate independently while working weekdays during established team core hours. Leverage GIS, CAD, and digital cartography tools to support the production and maintenance of aviation charts and related products. Utilize aviation knowledge, including aeronautical principles, instrument flight procedures, air traffic control concepts, and chart symbology, in daily analytical and production tasks. Support mission planning and aerial survey-related workflows by integrating geospatial and aeronautical data as needed. Essential Skills Previous experience in the production or use of enroute charts, Instrument Approach Procedures (IAPs), Standard Instrument Departures (SIDs), and/or Standard Terminal Arrival Routes (STARs). Aviation knowledge, including a strong understanding of aeronautical principles, aviation navigation, instrument flight procedures, air traffic control concepts, and chart symbology. Experience with GIS software, CAD software, or similar digital cartography tools, such as Esri ArcGIS Aviation Charting, Bentley OpenCities Map, Esri products, or comparable platforms. Bachelor's d</t>
+          <t>Supply Chain Analyst Job Description This role serves as a line-side planner supporting eight manufacturing value streams, including large wheel loaders, compactors, and motor graders. The supply chain analyst coordinates material flow, manages changes to product configurations, and ensures accurate production data by handling bills of materials, manufacturing execution system updates, kitting activities, and validation tasks. The position requires strong mechanical aptitude, solid computer skills, and the ability to work closely with production teams in a fast-paced manufacturing environment. Responsibilities Act as a line-side planner supporting all eight value streams, including large wheel loaders, compactors, and motor graders. Manage and maintain bills of materials (BOM) to ensure accuracy and reflect current product configurations. Perform updates in the manufacturing execution system (MES) to align with engineering and production changes. Coordinate and oversee kitting activities to ensure correct and timely delivery of parts to the production line. Conduct validation tasks to confirm that BOM changes, MES updates, and kitting processes meet quality and production requirements. Provide technical and process-related support to production teams, extending beyond electronics to broader mechanical and supply chain topics. Collaborate with engineering and operations to implement changes efficiently and minimize disruption to production. Use computer-based tools and systems to track, analyze, and report on material flow, inventory status, and production readiness. Identify and escalate issues related to material availability, configuration changes, or process deviations, and support resolution activities. Contribute to continuous improvement initiatives focused on enhancing supply chain efficiency and line-side planning effectiveness. Essential Skills Demonstrated mechanical aptitude, with the ability to understand mechanical components and assemblies. Supply chain knowledge and experience in planning, material coordination, or related functions. Strong computer skills, including proficiency with production, planning, or data entry systems. Ability to work effectively in a manufacturing environment supporting multiple value streams. Attention to detail when managing BOM changes, MES updates, and kitting activities. Strong communication skills to collaborate with production, engineering, and other stakeholders. Open to candidates with any engineering degree or equivalent technical education. Additional Skills &amp; Qualifications Manufacturing experience is a strong plus, particularly in environments with complex mechanical products. Experience working with bills of materials (BOM) and manufacturing execution systems (MES) is beneficial. Prior exposure to line-side planning, kitting, or material coordination in a production setting is advantageous. Experience in an engineering discipline, such as mechanical or related fields, is preferred. Experienc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QC Analyst</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saint Louis, Missouri, 63101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2067,12 +2057,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2082,12 +2072,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006214665/QC-Analyst</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2095,39 +2085,39 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-14T07:09:25+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>482f995d9540ba56230b</t>
+          <t>9bf4a4e2dae5cc85a155</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>QC Analyst Position Summary The QC Analyst supports quality control testing and laboratory operations by evaluating the physical and mechanical properties of materials used in manufacturing and product development. This role performs laboratory testing, sample preparation, data analysis, equipment operation, and documentation activities to ensure product quality and compliance with established standards. The position offers an excellent opportunity for recent graduates and early-career scientists to gain hands-on laboratory experience while developing technical expertise in materials characterization, quality systems, and manufacturing support. Key Responsibilities Perform laboratory testing on raw materials, in-process materials, and finished products according to established procedures and specifications. Conduct physical and mechanical property testing, including tensile strength, elongation, hardness, viscosity, thermal resistance, and related material performance evaluations. Prepare samples and test specimens using cutting, molding, conditioning, and other standardized preparation techniques. Collect, analyze, and record laboratory data accurately while identifying trends, deviations, or unusual results. Operate and maintain laboratory instruments such as universal testing machines, viscometers, ovens, balances, and microscopes. Document testing activities, observations, and results in laboratory records and electronic systems. Support investigations and troubleshooting activities related to product quality, manufacturing processes, or material performance. Collaborate with Quality, Production, R&amp;D, and Engineering teams to support product development and continuous improvement initiatives. Maintain laboratory organization, equipment, and test materials in accordance with quality and safety standards. Follow all laboratory safety procedures, chemical handling requirements, and applicable regulatory or industry standards. Required Qualifications Bachelor's degree in Chemistry, Materials Science, Chemical Engineering, Biology, Physics, Engineering Technology, Environmental Science, or another related scientific discipline. Laboratory experience obtained through academic coursework, undergraduate research, internships, co-ops, or industry experience. Strong attention to detail and ability to accurately document laboratory activities and test results. Basic understanding of scientific testing methods and laboratory best practices. Ability to collect, interpret, and communicate technical data. Strong organizational, analytical, and problem-solving skills. Proficiency with Microsoft Office applications, especially Excel. Ability to work effectively both independently and within a collaborative team environment. Preferred Qualifications Experience performing physical property testing, materials characterization, quality control testing, or manufacturing laboratory work. Experience operating laboratory equipment such as viscometers, testing machine</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quality Control Analyst</t>
+          <t>Data Analyst R Programming</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saint Louis, Missouri, 63101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2137,12 +2127,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2152,12 +2142,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006214649/Quality-Control-Analyst</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2165,39 +2155,39 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-14T07:09:25+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>c3c59b3b294b2f2973cd</t>
+          <t>21e4d98805199fb268c1</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quality Control Analyst - Day Shift (Weekends)</t>
+          <t>Data Architect ( Hadoop / Spark )</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saint Louis, Missouri, 63101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2207,12 +2197,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2222,12 +2212,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006213012/Quality-Control-Analyst-Day-Shift-Weekends</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -2235,39 +2225,39 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-14T07:09:25+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>e31226ca24349305fae4</t>
+          <t>067704edcb00e117f37a</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Job Title: Quality Control Analyst - Day Shift (Weekends) Job Description The Quality Control Analyst is responsible for prioritizing and performing daily sampling of incoming raw materials and laboratory testing while ensuring compliance with GMP and FDA requirements. This role supports manufacturing operations through timely testing, disposition decisions, accurate documentation, and communication of quality-related information. Responsibilities Perform sampling of incoming raw materials (liquids and solids) within manufacturing and warehouse areas according to established procedures. Conduct laboratory testing and analysis of raw materials using wet chemistry and chromatographic techniques. Prepare samples for chromatographic analysis. Perform routine GC and HPLC analysis. Review compounding and laboratory records for completeness and accuracy. Investigate customer complaints and document findings. Disposition raw materials for use or sale. Document deviations from established procedures and test methods. Maintain compliance with GMP regulations and laboratory documentation standards. Ensure safe handling, analysis, processing, and storage of hazardous and flammable materials. Coordinate information flow between the laboratory and internal stakeholders. Provide timely and accurate quality information to production personnel. Access, enter, and retrieve data from Quality Control computer systems. Maintain laboratory organization and housekeeping. Participate in required meetings and training programs. Become knowledgeable in manufacturing processes, QC workflows, retain sample programs, and documentation procedures. Work independently while adjusting priorities in response to changing business needs. Perform other duties as assigned. Essential Skills Quality control Chemistry Wet chemistry Strong multi-tasking ability Effective communication with compounding leadership Ability to work independently without constant supervision Problem-solving skills High attention to detail Strong organizational and time-management skills Ability to make sound decisions under pressure Strong compliance mindset regarding GMP and quality standards Additional Skills &amp; Qualifications Bachelor's Degree minimum required, Chemistry preferred but open to Biochemistry, Biology with a Chemistry Minor, or other related science. 1 year of experience in a QC laboratory with exposure to physical testing, volumetric solution sample preparation, GMP/GDP, and exposure to LIMS or other lab sample management systems. Lab Exposure/Experience with: HPLC, GC, FTIR, TOC. General experience working within MS Office including Word, Excel, Teams, Outlook. Strong teamwork and collaboration skills Professional communication with colleagues and internal customers Ability to coordinate effectively across departments Commitment to identifying, documenting, and resolving quality issues Job Type &amp; Location This is a Contract to Hire position based out of Saint Louis, MO. Pay and Benefits The p</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quality Control Analyst - OVERNIGHTS</t>
+          <t>Data Architect With Azure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saint Louis, Missouri, 63101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2277,12 +2267,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2292,12 +2282,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006214635/Quality-Control-Analyst-OVERNIGHTS</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2305,39 +2295,39 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-14T07:09:25+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>97c15ff34540d0b546c4</t>
+          <t>5e42a504d189fe30c4fa</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>QC Technician Position Summary The QC Technician supports quality control testing activities for raw materials, in-process samples, and finished products within a fast-paced manufacturing environment. This position performs laboratory testing, sample preparation, data documentation, and quality evaluations to ensure products meet established specifications and quality standards. The role provides excellent opportunities for recent graduates and early-career scientists to develop analytical chemistry, instrumentation, and quality systems expertise through hands-on laboratory experience and structured training. Key Responsibilities Perform quality control testing on incoming raw materials, in-process samples, and finished products according to established procedures. Conduct routine physical property and wet chemistry testing, including pH, viscosity, TOC, and related analytical evaluations. Prepare samples, standards, reagents, and volumetric solutions for laboratory analysis. Collect, analyze, document, and communicate test results accurately and in accordance with laboratory procedures. Review laboratory and production records for completeness, accuracy, and compliance with Good Documentation Practices (GDP) and GMP requirements. Enter, retrieve, and maintain testing data within laboratory information management systems (LIMS). Assist with investigations related to out-of-specification (OOS), out-of-trend (OOT), and customer complaint findings. Support laboratory housekeeping activities, including equipment cleaning, glassware maintenance, and waste disposal. Collaborate with Production, Quality Assurance, Engineering, and other departments to support product quality and manufacturing operations. Follow all laboratory safety procedures and quality requirements. Growth &amp; Development Opportunities With training, this role will expand into: HPLC, GC, LC, and additional instrumental analytical testing. Method development and method transfer activities. Instrument calibration, qualification, and validation support (IQ/OQ/PQ). Stability testing programs. SOP development, review, and revision. Laboratory troubleshooting and continuous improvement initiatives. Required Qualifications Bachelor's degree in Chemistry, Biochemistry, Biology, Microbiology, Chemical Engineering, Pharmaceutical Sciences, or another related scientific discipline. Laboratory experience through academic coursework, undergraduate research, internships, co-ops, or industry experience. Understanding of basic analytical chemistry principles and laboratory practices. Experience with sample preparation, solution preparation, and laboratory documentation. Strong attention to detail and organizational skills. Ability to accurately record observations, test results, and laboratory activities. Effective verbal and written communication skills. Ability to work independently and as part of a team in a fast-paced environment. Proficiency with Microsoft Office applications, including Excel, Wo</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Chain Analyst</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>East Peoria, Illinois, 61611, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2347,12 +2337,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2362,12 +2352,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006211353/Supply-Chain-Analyst</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2375,22 +2365,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-14T04:46:20+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>048251fc65475b88aad8</t>
+          <t>2acf8accb8cab7cf4980</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Supply Chain Analyst Job Description This role serves as a line-side planner supporting eight manufacturing value streams, including large wheel loaders, compactors, and motor graders. The supply chain analyst coordinates material flow, manages changes to product configurations, and ensures accurate production data by handling bills of materials, manufacturing execution system updates, kitting activities, and validation tasks. The position requires strong mechanical aptitude, solid computer skills, and the ability to work closely with production teams in a fast-paced manufacturing environment. Responsibilities Act as a line-side planner supporting all eight value streams, including large wheel loaders, compactors, and motor graders. Manage and maintain bills of materials (BOM) to ensure accuracy and reflect current product configurations. Perform updates in the manufacturing execution system (MES) to align with engineering and production changes. Coordinate and oversee kitting activities to ensure correct and timely delivery of parts to the production line. Conduct validation tasks to confirm that BOM changes, MES updates, and kitting processes meet quality and production requirements. Provide technical and process-related support to production teams, extending beyond electronics to broader mechanical and supply chain topics. Collaborate with engineering and operations to implement changes efficiently and minimize disruption to production. Use computer-based tools and systems to track, analyze, and report on material flow, inventory status, and production readiness. Identify and escalate issues related to material availability, configuration changes, or process deviations, and support resolution activities. Contribute to continuous improvement initiatives focused on enhancing supply chain efficiency and line-side planning effectiveness. Essential Skills Demonstrated mechanical aptitude, with the ability to understand mechanical components and assemblies. Supply chain knowledge and experience in planning, material coordination, or related functions. Strong computer skills, including proficiency with production, planning, or data entry systems. Ability to work effectively in a manufacturing environment supporting multiple value streams. Attention to detail when managing BOM changes, MES updates, and kitting activities. Strong communication skills to collaborate with production, engineering, and other stakeholders. Open to candidates with any engineering degree or equivalent technical education. Additional Skills &amp; Qualifications Manufacturing experience is a strong plus, particularly in environments with complex mechanical products. Experience working with bills of materials (BOM) and manufacturing execution systems (MES) is beneficial. Prior exposure to line-side planning, kitting, or material coordination in a production setting is advantageous. Experience in an engineering discipline, such as mechanical or related fields, is preferred. Experienc</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2392,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2417,12 +2407,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2016-02-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2437,7 +2427,7 @@
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2450,17 +2440,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9bf4a4e2dae5cc85a155</t>
+          <t>42d3008393a735c10ebf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2462,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Data Analyst R Programming</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2487,12 +2477,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-01-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2507,7 +2497,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -2520,17 +2510,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21e4d98805199fb268c1</t>
+          <t>dd7b5f57e42a3e48d371</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2532,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Data Architect ( Hadoop / Spark )</t>
+          <t>Database Administrator (NoSQL / Oracle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2557,12 +2547,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2577,7 +2567,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J31" t="b">
@@ -2590,17 +2580,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>067704edcb00e117f37a</t>
+          <t>eb910a182e0aacee19cf</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2602,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Data Architect With Azure</t>
+          <t>IVR Business Analyst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2627,12 +2617,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2016-03-29</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2647,7 +2637,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -2660,17 +2650,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>5e42a504d189fe30c4fa</t>
+          <t>29d3945c6149cb7d27ce</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2672,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Kronos Analyst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2702,7 +2692,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2730,17 +2720,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2acf8accb8cab7cf4980</t>
+          <t>48ab717cae2854563a90</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2742,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
+          <t>Oracle eBS Techno Functional Analyst</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2767,12 +2757,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2016-02-12</t>
+          <t>2016-12-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2787,7 +2777,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -2800,17 +2790,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>42d3008393a735c10ebf</t>
+          <t>c46f1d2e683e01fd3d10</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2812,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Report developer/analyst/consultant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2837,12 +2827,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2016-01-25</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2857,7 +2847,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2870,17 +2860,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>dd7b5f57e42a3e48d371</t>
+          <t>05b173f523c68702bbf4</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2882,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Database Administrator (NoSQL / Oracle)</t>
+          <t>System Analyst (BI/DWH)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2912,7 +2902,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-03-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2927,7 +2917,7 @@
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -2940,17 +2930,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>eb910a182e0aacee19cf</t>
+          <t>e765218d0ec589c265ea</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2952,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IVR Business Analyst</t>
+          <t>Workforce Management Analyst</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2982,7 +2972,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2997,7 +2987,7 @@
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3010,49 +3000,49 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>29d3945c6149cb7d27ce</t>
+          <t>0d140e426844c92e6ab8</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kronos Analyst</t>
+          <t>Analyst, Compensation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Houston, TX, 77002, US</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3062,12 +3052,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
+          <t>https://www.apexsystems.com/job/3045990_usa/analyst-compensation</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3075,54 +3065,54 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>48ab717cae2854563a90</t>
+          <t>4f7bc38cce2da78131f1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Analyst, Compensation\nLocation: Houston, Texas (Hybrid)\n \nRole Overview\nWe are seeking a Compensation Analyst to support the administration and analysis of employee compensation programs. This role involves working with base pay, incentive compensation, market pricing, job evaluations, and compensation reporting. The analyst will partner with HR and business stakeholders to ensure compensation programs are administered accurately and are aligned with market data and company guidelines.\n \nKey Responsibilities\nAdminister compensation programs including salary administration, incentive plans, market pricing, and job evaluations.Review and process compensation transactions such as promotions, salary adjustments, job changes, and incentive awards.Conduct market benchmarking and compensation analyses using survey data and internal tools.Evaluate new and revised positions, perform job pricing, and develop compensation recommendations.Support compensation studies and prepare reports for HR and business leaders.Respond to compensation-related inquiries and data requests from cross-functional teams.Maintain compensation and position data within HRIS systems, including SAP.Ensure compliance with compensation regulations, including FLSA and Equal Pay Act requirements.Support employee recognition and incentive programs.\nRequired Qualifications\nEducation: A Bachelor's degree in Human Resources, Business Administration, Finance, or a related field is required.\n \nExperience: A minimum of 2 years of demonstrated experience in compensation administration is required. This includes experience with base salary administration, market surveys, job pricing techniques, job evaluation, variable pay programs, and regulatory compliance.\n \nTechnical Skills: Strong analytical and reporting skills are necessary. Experience with HRIS systems, with a preference for SAP, and advanced Excel skills are required.\n \nPreferred Qualifications\nA Certified Compensation Professional (CCP) certification or progress toward certification.Experience supporting compensation programs in a large corporate environment.Experience in the energy, utility, or a regulated industry.\nWork Environment\nThis role involves the ability to exert up to 10 pounds of force occasionally and operate a personal computer for extended periods. The work environment is an office setting, and the position requires the ability to work with moderate daily pressure to meet frequent deadlines. Occasional overtime and travel may be necessary. The successful candidate may be required to remain in the service area during emergency events.\n Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excelle</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oracle eBS Techno Functional Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Saint Paul, MN, 55102, US</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2016-12-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3132,12 +3122,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
+          <t>https://www.apexsystems.com/job/3045809_usa/business-analyst</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3145,54 +3135,54 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>c46f1d2e683e01fd3d10</t>
+          <t>e112986d9d0744246aee</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
+          <t>Business AnalystLocation: Saint Paul, Minnesota (Partial Remote) Role OverviewWe are seeking one Business Analyst. This role operates in a fast-paced, agile environment focused on data science, AI, and digital B2B/B2C applications. You will be part of a cross-functional development team, working alongside a Product Owner and Scrum Master on an emerging digital solution that is in the early stages of its lifecycle, focused on improvements and enhancements based on initial feedback. Key ResponsibilitiesCreate and manage user stories, organize ADO boards, and help manage the product backlog using Azure DevOps.Collaborate with product owners, engineering, UI, and data science teams.Transform ambiguous and evolving needs into well-structured requirement sets.Gather, document, and translate business needs into clear functional and non-functional requirements.Manage dependencies across UI, engineering, data science, modeling, and product teams within a multi-workstream agile environment.Understand and document APIs.Required QualificationsExperience writing user stories and managing backlogs in Azure DevOps (ADO).Proven ability to work effectively in an agile environment with multiple workstreams.Ability to work in a fast-paced, collaborative setting.Must be able to come onsite to Saint Paul, MN or Naperville, IL as needed for PI Planning and workshops.Preferred QualificationsExperience with B2B web application solutions, digital products, or writing stories for mobile applications.Knowledge of food safety in Food RetailExperience in AI, Business Intelligence, or Data Science.Skilled at collaborating with customers to refine and clarify requirements.Experience with digital product roadmaps, working with APIs, integrating data streams, and leveraging AI modeling.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disabil</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Report developer/analyst/consultant</t>
+          <t>Business Analyst 2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Portland, OR, 97204, US</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3202,12 +3192,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
+          <t>https://www.apexsystems.com/job/3046372_usa/business-analyst-2</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3215,39 +3205,39 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>05b173f523c68702bbf4</t>
+          <t>0722cb440dd023798007</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
+          <t>Business Analyst 2Location: Remote Role OverviewThe main function of a Business Analyst is to perform business analysis on all aspects of technology and business improvement projects, focusing on stakeholder analysis, requirement development and management, and Acceptance testing. This role will assist and/or lead the identification and clarification of innovative business solutions related to divisional strategic goals, in alignment with corporate strategy. The position involves creating reports and communicating effectively with stakeholders. Key ResponsibilitiesAssist and/or lead identification and clarification of innovative business solutions.Utilize appropriate analysis tools and techniques to deliver cost-effective solutions which meet business needs and improve efficiencies.Participate in developing both the Business Analysis Practice and Business Analysis Framework to support the definition and delivery of business value.Assess and document business value propositions and maintain a focus on the value proposition throughout each project.Foster partnerships with customers and business partners to ensure their needs as stakeholders are identified and represented.Establish and document business processes.Set up project and work breakdown structures.Track project budgets and expenditures, monitoring transaction controls and costs against budgets.Create reports and communicate with stakeholders.Required QualificationsExperience: 2-4+ years of progressive experience in business analysis, preferably in employee benefits, financial services, or technology delivery. Experience with Fieldglass is required. Education: A Bachelor’s degree in Business or a related field is required. Skills:Demonstrated communication, facilitation, and collaboration skills.Verbal and written communication skills, problem-solving skills, attention to detail, and interpersonal skills.Ability to work independently and manage one’s time.Leadership and mentoring skills to provide support and constructive performance feedback.Knowledge of design techniques and principles involved in the production of drawings and models. Preferred QualificationsAchievement of or progress toward: Fellow, Life Management Institute (FLMI), Certified Business Analysis Professional (CBAP), or Certification of Competency in Business Analysis (CCBA).Project Management Professional (PMP), certification in Process or Performance Management, or certification in Quality Assurance/Testing is desirable.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place t</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>System Analyst (BI/DWH)</t>
+          <t>Business Financial Operations Analyst</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Charlotte, NC, 28217, US</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3257,12 +3247,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2016-03-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3272,12 +3262,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
+          <t>https://www.apexsystems.com/job/3046125_usa/business-financial-operations-analyst</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -3285,39 +3275,39 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>e765218d0ec589c265ea</t>
+          <t>fde9bada61f9a913c715</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>We are seeking a highly organized and proactive Business Operations Manager to support a team of senior leaders, including Directors, GVPs, and SVPs, in managing financial operations, budget reporting, and business planning activities. This individual will serve as a central point of coordination across multiple leaders and organizations, ensuring financial information, supporting documentation, and reporting deliverables are accurate, complete, and delivered on time.The ideal candidate thrives in a fast-paced environment with competing priorities and numerous stakeholders. They possess exceptional organizational skills, strong financial acumen, advanced Excel capabilities, and a demonstrated ability to drive work forward through persistent follow-up and stakeholder engagement.A critical component of this role is identifying opportunities to streamline reporting, budgeting, and operational processes through the use of AI tools, with preference for experience leveraging Claude (or Kiro) to improve productivity, automate repetitive work, and enhance decision-making.Key ResponsibilitiesPartner directly with Directors, GVPs, and SVPs to organize, manage, and maintain budget-related information across multiple business areas.Coordinate collection, validation, and consolidation of financial data, supporting documentation, budget inputs, invoices, purchase orders, and reporting requirements.Develop recurring budget reports, executive summaries, and financial updates tailored to individual leadership stakeholders.Track key financial milestones, deliverables, and deadlines, ensuring leadership teams provide required information on time.Establish and maintain structure around financial planning, reporting, and operational processes.Drive cross-functional coordination among stakeholders to resolve discrepancies, close reporting gaps, and maintain data accuracy.Translate detailed financial information into concise, executive-ready insights and recommendations.Identify opportunities to improve efficiency through process optimization and AI-enabled workflows.Leverage AI tools, including Claude and other generative AI platforms, to streamline reporting, documentation, analysis, and business operations workflows.Independently manage multiple competing priorities while maintaining a high level of accuracy and attention to detail.Required Qualifications5+ years of experience in Business Operations, Financial Operations, Business Analysis, Program Management, or a related field.Experience supporting senior executives and managing deliverables across multiple stakeholders and organizations.Demonstrated experience coordinating budgets, financial planning activities, forecasting processes, or operational finance functions.Advanced Microsoft Excel skills, including complex formulas, pivot tables, reporting, and data analysis.Strong organizational, communication, and stakeholder management skills.Proven ability to drive actions to completion through follow-up, accountab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Workforce Management Analyst</t>
+          <t>CAD MSH Patient Drug Adherence Data Scientist (Contract)_Forge</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Mississauga, ON, L5N 0H1, CA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3327,12 +3317,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3342,12 +3332,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
+          <t>https://www.apexsystems.com/job/3046092_usa/cad-msh-patient-drug-adherence-data-scientist-contractforge</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3355,22 +3345,22 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0d140e426844c92e6ab8</t>
+          <t>8860afd023dcb2a4d805</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Senior Analyst, Data &amp; Insights / Data Product OwnerJob DescriptionJob SummaryReporting to the Director, Strategic Insights, the Data Product Owner will lead cross-functional analytics, reporting, and data science initiatives that support McKesson Specialty Health business lines. This role serves as a strategic partner to business, technology, operations, and leadership teams by translating complex business needs into scalable data products, actionable insights, and measurable business outcomes.This role combines product ownership, advanced analytics, machine learning, business intelligence, and stakeholder engagement. The successful candidate will own the roadmap and lifecycle of analytics products, guide reporting and dashboard development, support predictive modeling and experimentation, and drive adoption of data-driven decision-making across the organization.Key ResponsibilitiesData Product Ownership &amp; Roadmap Management· Define and manage the vision, roadmap, backlog, and lifecycle of analytics and data products.· Translate business needs into clear product requirements, user stories, KPIs, success measures, and delivery priorities.· Lead cross-functional delivery across business stakeholders, analytics teams, technology partners, vendors, data governance, privacy, and operations.· Drive product adoption, change management, documentation, issue resolution, and continuous improvement for reporting and analytical solutions.· Ensure analytics products are scalable, reliable, business-aligned, and governed appropriately for a regulated healthcare environment.Advanced Analytics, Data Science &amp; Experimentation· Design, develop, validate, and monitor predictive models, machine learning solutions, and advanced analytical frameworks.· Apply statistical methods, segmentation, forecasting, hypothesis testing, and A/B testing to evaluate business initiatives and interventions.· Identify AI/ML opportunities and partner with appropriate teams to assess feasibility, business value, compliance needs, and implementation approach.· Perform exploratory analysis, feature engineering, model evaluation, and performance monitoring to support explainable and actionable insights.· Translate analytical findings into practical recommendations that improve operational performance, customer value, and decision quality.Reporting, Business Intelligence &amp; Insight Delivery· Design, develop, and manage dashboards, scorecards, recurring reports, and self-serve analytics products.· Establish KPI frameworks, reporting standards, data definitions, and measurement methodologies across assigned business areas.· Use SQL, Python, Snowflake, Salesforce, Azure, and BI tools to extract, transform, analyze, and visualize complex datasets.· Create compelling data visualizations and executive-ready narratives for both technical and non-technical audiences.· Support forecasting, operational planning, product demos, RFPs, business cases, and strategic decision-making through trusted analyt</t>
         </is>
       </c>
     </row>
@@ -3382,17 +3372,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Analyst, Compensation</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, 77002, US</t>
+          <t>Birmingham, AL, 35243, US</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3417,7 +3407,7 @@
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045990_usa/analyst-compensation</t>
+          <t>https://www.apexsystems.com/job/3046060_usa/data-analyst</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -3430,17 +3420,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4f7bc38cce2da78131f1</t>
+          <t>3d3754c05091e7d7cb07</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Analyst, Compensation\nLocation: Houston, Texas (Hybrid)\n \nRole Overview\nWe are seeking a Compensation Analyst to support the administration and analysis of employee compensation programs. This role involves working with base pay, incentive compensation, market pricing, job evaluations, and compensation reporting. The analyst will partner with HR and business stakeholders to ensure compensation programs are administered accurately and are aligned with market data and company guidelines.\n \nKey Responsibilities\nAdminister compensation programs including salary administration, incentive plans, market pricing, and job evaluations.Review and process compensation transactions such as promotions, salary adjustments, job changes, and incentive awards.Conduct market benchmarking and compensation analyses using survey data and internal tools.Evaluate new and revised positions, perform job pricing, and develop compensation recommendations.Support compensation studies and prepare reports for HR and business leaders.Respond to compensation-related inquiries and data requests from cross-functional teams.Maintain compensation and position data within HRIS systems, including SAP.Ensure compliance with compensation regulations, including FLSA and Equal Pay Act requirements.Support employee recognition and incentive programs.\nRequired Qualifications\nEducation: A Bachelor's degree in Human Resources, Business Administration, Finance, or a related field is required.\n \nExperience: A minimum of 2 years of demonstrated experience in compensation administration is required. This includes experience with base salary administration, market surveys, job pricing techniques, job evaluation, variable pay programs, and regulatory compliance.\n \nTechnical Skills: Strong analytical and reporting skills are necessary. Experience with HRIS systems, with a preference for SAP, and advanced Excel skills are required.\n \nPreferred Qualifications\nA Certified Compensation Professional (CCP) certification or progress toward certification.Experience supporting compensation programs in a large corporate environment.Experience in the energy, utility, or a regulated industry.\nWork Environment\nThis role involves the ability to exert up to 10 pounds of force occasionally and operate a personal computer for extended periods. The work environment is an office setting, and the position requires the ability to work with moderate daily pressure to meet frequent deadlines. Occasional overtime and travel may be necessary. The successful candidate may be required to remain in the service area during emergency events.\n Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excelle</t>
+          <t>Data Analytics AnalystLocation: Birmingham, ALTravel: Up to 50% (primarily within the regional generation fleet)OverviewWe are seeking a detail-oriented Data Analytics Analyst I to support the management, integration, and optimization of critical asset and maintenance data across a growing generation portfolio. This role plays a key part in ensuring operational readiness for new generation projects and existing power generation assets by supporting data governance, equipment hierarchy development, maintenance strategy implementation, and asset management processes.The ideal candidate combines strong analytical skills with the ability to collaborate across engineering, operations, maintenance, and project teams to ensure asset data is accurate, standardized, and effectively integrated into enterprise systems.Key ResponsibilitiesSupport generation project teams and operating facilities with the development and maintenance of equipment hierarchies, preventive maintenance programs, job plans, and inventory data.Coordinate the onboarding of new generation assets and updates to existing assets within enterprise asset management systems.Gather, validate, and analyze technical equipment data for construction projects, acquisitions, modernization efforts, and major capital initiatives.Ensure data quality, consistency, and adherence to established equipment identification and data governance standards.Partner with subject matter experts, plant personnel, and project managers to verify equipment information and maintenance requirements.Assist in the development and implementation of maintenance strategies that support the long-term reliability and operation of generation assets.Perform routine analysis of technical and operational data to identify trends, opportunities for improvement, and areas requiring corrective action.Support standardization efforts and promote best practices across multiple facilities and project teams.Participate in benchmarking and like-unit comparisons to identify lessons learned and drive continuous improvement initiatives.Provide field support as needed to address questions related to asset data, maintenance programs, and equipment structures.Required QualificationsBachelor's degree in Engineering, Business, Computer Science, Data Science, Information Systems, or a related technical discipline preferred.Equivalent combination of education and relevant experience may be considered.Proficiency with Microsoft Office applications, including Excel, Word, and PowerPoint.Strong analytical, organizational, and problem-solving skills.Ability to manage multiple priorities and projects in a fast-paced environment.Excellent written and verbal communication skills.Demonstrated ability to collaborate effectively across functional teams.Ability to travel to operational sites and conduct field walkthroughs of industrial equipment.Preferred QualificationsExperience working with asset management, maintenance, or operational data.Experience integra</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3442,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, 55102, US</t>
+          <t>Greenwood Village, CO, 80111, US</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3487,7 +3477,7 @@
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045809_usa/business-analyst</t>
+          <t>https://www.apexsystems.com/job/3043401_usa/data-engineer</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -3495,22 +3485,22 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-12T18:33:39+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>e112986d9d0744246aee</t>
+          <t>6b7f5cde84910ff73522</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Business AnalystLocation: Saint Paul, Minnesota (Partial Remote) Role OverviewWe are seeking one Business Analyst. This role operates in a fast-paced, agile environment focused on data science, AI, and digital B2B/B2C applications. You will be part of a cross-functional development team, working alongside a Product Owner and Scrum Master on an emerging digital solution that is in the early stages of its lifecycle, focused on improvements and enhancements based on initial feedback. Key ResponsibilitiesCreate and manage user stories, organize ADO boards, and help manage the product backlog using Azure DevOps.Collaborate with product owners, engineering, UI, and data science teams.Transform ambiguous and evolving needs into well-structured requirement sets.Gather, document, and translate business needs into clear functional and non-functional requirements.Manage dependencies across UI, engineering, data science, modeling, and product teams within a multi-workstream agile environment.Understand and document APIs.Required QualificationsExperience writing user stories and managing backlogs in Azure DevOps (ADO).Proven ability to work effectively in an agile environment with multiple workstreams.Ability to work in a fast-paced, collaborative setting.Must be able to come onsite to Saint Paul, MN or Naperville, IL as needed for PI Planning and workshops.Preferred QualificationsExperience with B2B web application solutions, digital products, or writing stories for mobile applications.Knowledge of food safety in Food RetailExperience in AI, Business Intelligence, or Data Science.Skilled at collaborating with customers to refine and clarify requirements.Experience with digital product roadmaps, working with APIs, integrating data streams, and leveraging AI modeling.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disabil</t>
+          <t>Data Engineer\nLocation: Greenwood Village, Colorado (Remote)\n \nRole Overview\nThis role is for a Data Engineer to design, build, and maintain the ETL pipelines and data infrastructure that feed a data lake, anomaly detection models, and AI agents. The position focuses on constructing robust, scalable data pipelines using Spark/Scala, ensuring data quality and availability across a growing portfolio of network data sources. The goal is to enable downstream consumers such as data scientists, agents, and dashboards to access reliable, well-structured data.\n \nKey Responsibilities\nDesign, develop, and maintain scalable ETL pipelines using Apache Spark (Scala) to ingest, transform, and load network data into the data lake.Onboard new data sources (network telemetry, syslogs, SNMP traps, device configuration data, ticketing systems) by building ingestion pipelines.Implement monitoring and alerting solutions to ensure data pipeline reliability and performance.Develop and manage deployment pipelines for continuous integration and delivery of data engineering solutions.Manage and optimize data storage solutions, including distributed file systems, relational databases, and external sources accessed via API.Implement data quality checks, validation rules, and automated testing to ensure pipeline reliability and data integrity.Optimize pipeline performance for large-scale data processing across batch and mini-batch processing patterns.Manage and evolve data schemas, partitioning strategies, and storage formats.Support data backfills and recovery when upstream issues or schema changes require reprocessing.Collaborate with data scientists and agent developers to deliver datasets that support anomaly detection models and AI agent workflows.\nRequired Qualifications\nExpert-level experience in building and maintaining ETL pipelines for Big Data.Programming experience with Python and/or Scala.Experience with large-scale data processing with Spark.Experience with AWS services: S3, Glue, Athena, and EMR, including working with EMR as the operating system.Strong understanding of relational databases and SQL.Knowledge of data architecture, data warehousing, partitioning strategies, and columnar storage formats (e.g., Parquet).Experience with workflow orchestration tools, with a preference for Airflow.Proficiency with Linux-based operating systems and shell scripting.Experience with Git-based version control and collaborative development workflows.\nPreferred Qualifications\nExperience with streaming or mini-batch data processing (Spark Streaming, structured streaming, or similar).Experience with Apache Kafka or similar messaging/streaming platforms.Experience with NoSQL databases.Experience in the telecommunications industry or other large-scale network operations environments.Familiarity with network data sources: telemetry, syslogs, SNMP traps, device configuration data.Experience with data integration via REST APIs and cloud SDKs (e.g., boto3).Experience wri</t>
         </is>
       </c>
     </row>
@@ -3522,17 +3512,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Business Analyst 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portland, OR, 97204, US</t>
+          <t>Denver, CO, 80237, US</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3542,7 +3532,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3557,7 +3547,7 @@
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046372_usa/business-analyst-2</t>
+          <t>https://www.apexsystems.com/job/3045667_usa/data-engineer</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -3570,17 +3560,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0722cb440dd023798007</t>
+          <t>e33d9978d04463291091</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Business Analyst 2Location: Remote Role OverviewThe main function of a Business Analyst is to perform business analysis on all aspects of technology and business improvement projects, focusing on stakeholder analysis, requirement development and management, and Acceptance testing. This role will assist and/or lead the identification and clarification of innovative business solutions related to divisional strategic goals, in alignment with corporate strategy. The position involves creating reports and communicating effectively with stakeholders. Key ResponsibilitiesAssist and/or lead identification and clarification of innovative business solutions.Utilize appropriate analysis tools and techniques to deliver cost-effective solutions which meet business needs and improve efficiencies.Participate in developing both the Business Analysis Practice and Business Analysis Framework to support the definition and delivery of business value.Assess and document business value propositions and maintain a focus on the value proposition throughout each project.Foster partnerships with customers and business partners to ensure their needs as stakeholders are identified and represented.Establish and document business processes.Set up project and work breakdown structures.Track project budgets and expenditures, monitoring transaction controls and costs against budgets.Create reports and communicate with stakeholders.Required QualificationsExperience: 2-4+ years of progressive experience in business analysis, preferably in employee benefits, financial services, or technology delivery. Experience with Fieldglass is required. Education: A Bachelor’s degree in Business or a related field is required. Skills:Demonstrated communication, facilitation, and collaboration skills.Verbal and written communication skills, problem-solving skills, attention to detail, and interpersonal skills.Ability to work independently and manage one’s time.Leadership and mentoring skills to provide support and constructive performance feedback.Knowledge of design techniques and principles involved in the production of drawings and models. Preferred QualificationsAchievement of or progress toward: Fellow, Life Management Institute (FLMI), Certified Business Analysis Professional (CBAP), or Certification of Competency in Business Analysis (CCBA).Project Management Professional (PMP), certification in Process or Performance Management, or certification in Quality Assurance/Testing is desirable.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place t</t>
+          <t>Data Engineer\nLocation: Denver, Colorado (Onsite)\n \nRole Overview\nOur engineering teams are adept at solving complex problems with leading-edge technology. This role involves working in a fast-paced environment to deliver intelligence and defense data, handling data integration for a system that serves numerous users worldwide. The position focuses on creating new data feeds, maintaining existing feeds, operations monitoring, and managing data outages through scripting and modern technologies.\n \nKey Responsibilities\nConfigure and maintain data ingest workflows (ETL) across multiple production systems.Install, configure, and update a wide array of COTS/GOTS software applications.Support and troubleshoot diverse IT infrastructure hardware platforms and protocols.Work with software development and systems administration staff to monitor and troubleshoot production systems.Generate and maintain systems documentation and diagrams.Troubleshoot network issues and establish new connectivity.Monitor and maintain a variety of databases.Create new data feeds and maintain hundreds of existing integrated data pipelines.\nRequired Qualifications\nEducation: A Bachelor’s degree or equivalent is required.\n \nExperience: A minimum of 3 years of experience with software development programs is required.\n \nTechnical Skills:\nScripting skills in Python and Bash.Experience developing in a Linux/Unix/RHEL environment.Experience with Commercial Cloud Systems (AWS – EC2, RDS, S3).Familiarity with engineering management tools such as JIRA/Confluence.Proficiency with RDBMS databases like PostgreSQL, Oracle, or MySQL.Experience with Git version-control system and CI/CD tools such as Docker, Kubernetes, Helm, and GitLab Runners.Knowledge of common data/configuration formats including Delimited, JSON, GeoJSON, and YAML.Experience with common API/interfaces such as REST, SFTP, Kafka, AMQ, and Socket.\nCertifications: Must be able to obtain a DoD 8570 level IAT-II qualification (such as Security+) within 6 months of hire and maintain it throughout employment.\n \nWork Authorization: Candidates must be a US Citizen.\n \nPreferred Qualifications\nExperience with AWS services such as Diode, Flink, and ArgoCD.Familiarity with monitoring tools like Grafana and Kibana.An understanding of compiled languages, including Java.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By appl</t>
         </is>
       </c>
     </row>
@@ -3592,17 +3582,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Business Financial Operations Analyst</t>
+          <t>Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28217, US</t>
+          <t>New York, NY, 10018, US</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3627,7 +3617,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046125_usa/business-financial-operations-analyst</t>
+          <t>https://www.apexsystems.com/job/3046150_usa/data-engineer---data-engineer-iii</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -3640,17 +3630,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>fde9bada61f9a913c715</t>
+          <t>7928fa9372e07280d384</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>We are seeking a highly organized and proactive Business Operations Manager to support a team of senior leaders, including Directors, GVPs, and SVPs, in managing financial operations, budget reporting, and business planning activities. This individual will serve as a central point of coordination across multiple leaders and organizations, ensuring financial information, supporting documentation, and reporting deliverables are accurate, complete, and delivered on time.The ideal candidate thrives in a fast-paced environment with competing priorities and numerous stakeholders. They possess exceptional organizational skills, strong financial acumen, advanced Excel capabilities, and a demonstrated ability to drive work forward through persistent follow-up and stakeholder engagement.A critical component of this role is identifying opportunities to streamline reporting, budgeting, and operational processes through the use of AI tools, with preference for experience leveraging Claude (or Kiro) to improve productivity, automate repetitive work, and enhance decision-making.Key ResponsibilitiesPartner directly with Directors, GVPs, and SVPs to organize, manage, and maintain budget-related information across multiple business areas.Coordinate collection, validation, and consolidation of financial data, supporting documentation, budget inputs, invoices, purchase orders, and reporting requirements.Develop recurring budget reports, executive summaries, and financial updates tailored to individual leadership stakeholders.Track key financial milestones, deliverables, and deadlines, ensuring leadership teams provide required information on time.Establish and maintain structure around financial planning, reporting, and operational processes.Drive cross-functional coordination among stakeholders to resolve discrepancies, close reporting gaps, and maintain data accuracy.Translate detailed financial information into concise, executive-ready insights and recommendations.Identify opportunities to improve efficiency through process optimization and AI-enabled workflows.Leverage AI tools, including Claude and other generative AI platforms, to streamline reporting, documentation, analysis, and business operations workflows.Independently manage multiple competing priorities while maintaining a high level of accuracy and attention to detail.Required Qualifications5+ years of experience in Business Operations, Financial Operations, Business Analysis, Program Management, or a related field.Experience supporting senior executives and managing deliverables across multiple stakeholders and organizations.Demonstrated experience coordinating budgets, financial planning activities, forecasting processes, or operational finance functions.Advanced Microsoft Excel skills, including complex formulas, pivot tables, reporting, and data analysis.Strong organizational, communication, and stakeholder management skills.Proven ability to drive actions to completion through follow-up, accountab</t>
+          <t>Data Engineer - Data Engineer IIILocation: New York, New York (Onsite)COMPENSATION: $68 - $78 HOURLY Role OverviewAs a Data Engineer, you will solve complex data problems and support critical projects. You will partner with stakeholders across the business and with the Data Engineering team to deliver new features or migrate legacy features to a modern, cloud-based platform. This role involves collaboration with teams across the business, providing opportunities to learn about the fashion industry and e-commerce. Key ResponsibilitiesArchitect, design, and implement next-generation data pipelines and BI solutions built on AWS.Build and optimize ETL processes to improve data quality, reliability, and freshness.Leverage AI-powered developer and data tools to boost productivity and code quality.Partner with business stakeholders to translate their needs into scalable data solutions.Collaborate with the Science team to build data foundations for AI solutions and bring them into production.Improve the team's operational excellence through monitoring, automation, and error reduction.Work EnvironmentWe are seeking a candidate available to be in person at our New York office.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access</t>
         </is>
       </c>
     </row>
@@ -3662,17 +3652,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAD MSH Patient Drug Adherence Data Scientist (Contract)_Forge</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mississauga, ON, L5N 0H1, CA</t>
+          <t>Charlotte, NC, 28255, US</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3697,7 +3687,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046092_usa/cad-msh-patient-drug-adherence-data-scientist-contractforge</t>
+          <t>https://www.apexsystems.com/job/3046011_usa/data-engineer-ii</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3710,17 +3700,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8860afd023dcb2a4d805</t>
+          <t>543e7ac4ae4bde57a7a1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data &amp; Insights / Data Product OwnerJob DescriptionJob SummaryReporting to the Director, Strategic Insights, the Data Product Owner will lead cross-functional analytics, reporting, and data science initiatives that support McKesson Specialty Health business lines. This role serves as a strategic partner to business, technology, operations, and leadership teams by translating complex business needs into scalable data products, actionable insights, and measurable business outcomes.This role combines product ownership, advanced analytics, machine learning, business intelligence, and stakeholder engagement. The successful candidate will own the roadmap and lifecycle of analytics products, guide reporting and dashboard development, support predictive modeling and experimentation, and drive adoption of data-driven decision-making across the organization.Key ResponsibilitiesData Product Ownership &amp; Roadmap Management· Define and manage the vision, roadmap, backlog, and lifecycle of analytics and data products.· Translate business needs into clear product requirements, user stories, KPIs, success measures, and delivery priorities.· Lead cross-functional delivery across business stakeholders, analytics teams, technology partners, vendors, data governance, privacy, and operations.· Drive product adoption, change management, documentation, issue resolution, and continuous improvement for reporting and analytical solutions.· Ensure analytics products are scalable, reliable, business-aligned, and governed appropriately for a regulated healthcare environment.Advanced Analytics, Data Science &amp; Experimentation· Design, develop, validate, and monitor predictive models, machine learning solutions, and advanced analytical frameworks.· Apply statistical methods, segmentation, forecasting, hypothesis testing, and A/B testing to evaluate business initiatives and interventions.· Identify AI/ML opportunities and partner with appropriate teams to assess feasibility, business value, compliance needs, and implementation approach.· Perform exploratory analysis, feature engineering, model evaluation, and performance monitoring to support explainable and actionable insights.· Translate analytical findings into practical recommendations that improve operational performance, customer value, and decision quality.Reporting, Business Intelligence &amp; Insight Delivery· Design, develop, and manage dashboards, scorecards, recurring reports, and self-serve analytics products.· Establish KPI frameworks, reporting standards, data definitions, and measurement methodologies across assigned business areas.· Use SQL, Python, Snowflake, Salesforce, Azure, and BI tools to extract, transform, analyze, and visualize complex datasets.· Create compelling data visualizations and executive-ready narratives for both technical and non-technical audiences.· Support forecasting, operational planning, product demos, RFPs, business cases, and strategic decision-making through trusted analyt</t>
+          <t>Data Engineer IILocation: Charlotte, North Carolina (Hybrid)Duration: 12 months Role OverviewWe are seeking a Data Engineer II to help design, build, and maintain a centralized performance and analytics repository. This role involves integrating data from multiple technology platforms and operational systems. The position is responsible for developing scalable data pipelines, transforming complex datasets, and creating reusable data structures to support reporting, analytics, and operational decision-making. Key ResponsibilitiesDesign, develop, and maintain data ingestion and transformation pipelines.Integrate data from multiple platforms, databases, APIs, and operational systems.Create and maintain data models, schemas, tables, views, and collections.Build and optimize solutions using PostgreSQL, MongoDB, or similar databases.Develop processes that ensure data quality, accuracy, consistency, and reliability.Transform raw and semi-structured data into curated, analytics-ready datasets.Partner with stakeholders to define data requirements and technical solutions.Support dashboard, reporting, and visualization initiatives by providing optimized datasets.Troubleshoot data issues, identify root causes, and implement corrective actions.Participate in testing, code reviews, deployment activities, and production support.Document data flows, transformations, and technical solutions.Contribute to Agile planning, estimation, and delivery activities.Required QualificationsExperience: 3+ years of experience in data engineering, ETL, or data integration roles. Experience building and maintaining automated data pipelines and working with large-scale operational or analytical datasets. Technical Skills: Strong SQL skills and experience designing relational database solutions. Experience with PostgreSQL, SQL Server, or similar database technologies. Experience with MongoDB or other NoSQL database platforms. Proficiency in Python, Java, Spark, or similar data processing technologies. Familiarity with REST APIs, file-based ingestion, and system integrations. Experience supporting dashboards and reporting platforms such as Grafana, Tableau, or Power BI. Knowledge: Knowledge of data modeling, schema design, and data warehouse concepts. Understanding of performance tuning, indexing, and query optimization. Familiarity with Agile development methodologies and CI/CD practices. Preferred QualificationsExperience working on Big Data Technologies.Cloudera Admin / Dev Certification.Certification in Cloud, Docker-Container, or Openshift Technologies.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds B</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3722,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, 35243, US</t>
+          <t>Atlanta, GA, 30308, US</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3767,7 +3757,7 @@
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046060_usa/data-analyst</t>
+          <t>https://www.apexsystems.com/job/3045202_usa/data-engineer-sr</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -3780,17 +3770,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3d3754c05091e7d7cb07</t>
+          <t>77142cddb1e72169aadb</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Data Analytics AnalystLocation: Birmingham, ALTravel: Up to 50% (primarily within the regional generation fleet)OverviewWe are seeking a detail-oriented Data Analytics Analyst I to support the management, integration, and optimization of critical asset and maintenance data across a growing generation portfolio. This role plays a key part in ensuring operational readiness for new generation projects and existing power generation assets by supporting data governance, equipment hierarchy development, maintenance strategy implementation, and asset management processes.The ideal candidate combines strong analytical skills with the ability to collaborate across engineering, operations, maintenance, and project teams to ensure asset data is accurate, standardized, and effectively integrated into enterprise systems.Key ResponsibilitiesSupport generation project teams and operating facilities with the development and maintenance of equipment hierarchies, preventive maintenance programs, job plans, and inventory data.Coordinate the onboarding of new generation assets and updates to existing assets within enterprise asset management systems.Gather, validate, and analyze technical equipment data for construction projects, acquisitions, modernization efforts, and major capital initiatives.Ensure data quality, consistency, and adherence to established equipment identification and data governance standards.Partner with subject matter experts, plant personnel, and project managers to verify equipment information and maintenance requirements.Assist in the development and implementation of maintenance strategies that support the long-term reliability and operation of generation assets.Perform routine analysis of technical and operational data to identify trends, opportunities for improvement, and areas requiring corrective action.Support standardization efforts and promote best practices across multiple facilities and project teams.Participate in benchmarking and like-unit comparisons to identify lessons learned and drive continuous improvement initiatives.Provide field support as needed to address questions related to asset data, maintenance programs, and equipment structures.Required QualificationsBachelor's degree in Engineering, Business, Computer Science, Data Science, Information Systems, or a related technical discipline preferred.Equivalent combination of education and relevant experience may be considered.Proficiency with Microsoft Office applications, including Excel, Word, and PowerPoint.Strong analytical, organizational, and problem-solving skills.Ability to manage multiple priorities and projects in a fast-paced environment.Excellent written and verbal communication skills.Demonstrated ability to collaborate effectively across functional teams.Ability to travel to operational sites and conduct field walkthroughs of industrial equipment.Preferred QualificationsExperience working with asset management, maintenance, or operational data.Experience integra</t>
+          <t>Data Engineer Sr\nLocation: Atlanta, GA (Onsite)\n \nRole Overview\nThe Data Engineer is responsible for designing, building, and supporting scalable data platforms, data products, application integrations, and analytics solutions that enable business decision-making across Power Delivery. This role develops and maintains enterprise data pipelines, integrates operational systems with cloud-based lakehouse platforms, and supports both low-code and pro-code application development using Microsoft Power Platform, OutSystems, and Databricks. The successful candidate will partner with business stakeholders, data analysts, application developers, and technology teams to deliver trusted, governed, and reusable data assets.\n \nKey Responsibilities\nDesign, build, and support enterprise data pipelines using ETL and ELT methodologies.Develop scalable ingestion frameworks for structured, semi-structured, and streaming data.Build and maintain Databricks notebooks, workflows, and data pipelines.Ingest data from source systems using Azure Data Factory, Kafka, CDC technologies, APIs, files, and database sources.Implement data quality checks, monitoring, and exception handling.Support Bronze, Silver, and Gold data architectures within the Databricks Lakehouse.Design and maintain Delta Lake tables and data products.Build and enhance business applications using Microsoft Power Apps, Power Automate, Power Platform, and OutSystems.Implement CI/CD practices using GitHub and Azure DevOps.Maintain documentation, lineage, and metadata for enterprise data assets.\nRequired Qualifications\nEducation: Bachelor's degree in Computer Science, Information Systems, Data Analytics, Engineering, or a related technical discipline.\n \nExperience: 3-7 years of experience in data engineering, analytics engineering, or software development, including building enterprise data pipelines and integrations, and working with cloud-based data platforms.\n \nTechnical Skills:\nData Engineering: ETL/ELT design, data ingestion frameworks, data pipeline orchestration, Data Warehousing concepts, Data Lake and Lakehouse architectures (Medallion architecture).Databricks: Databricks Workflows, PySpark, Spark SQL, Delta Lake, Unity Catalog, and Data Products.Cloud &amp; Integration: Azure Data Factory, APIs, Kafka, CDC technologies, and SQL Server.Development: Python, SQL, GitHub, and Azure DevOps.Business Applications: Power Apps, Power Automate, Power Platform, and OutSystems.\nPreferred Qualifications\nUtility industry experience.Power Delivery domain knowledge.Experience supporting Transmission or Distribution Analytics.Real-time data streaming experience.Knowledge of AI/ML enablement on Databricks.Experience with Power BI integration and Direct Query architectures.\nMust be authorized to work in the US without sponsorship.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovat</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3792,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Visualization Specialist</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, 80111, US</t>
+          <t>Richmond, VA, 23219, US</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3822,7 +3812,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3837,7 +3827,7 @@
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3043401_usa/data-engineer</t>
+          <t>https://www.apexsystems.com/job/3046209_usa/data-visualization-specialist</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -3845,22 +3835,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-12T18:33:39+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>6b7f5cde84910ff73522</t>
+          <t>d4969320cc96dd1de9b0</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Data Engineer\nLocation: Greenwood Village, Colorado (Remote)\n \nRole Overview\nThis role is for a Data Engineer to design, build, and maintain the ETL pipelines and data infrastructure that feed a data lake, anomaly detection models, and AI agents. The position focuses on constructing robust, scalable data pipelines using Spark/Scala, ensuring data quality and availability across a growing portfolio of network data sources. The goal is to enable downstream consumers such as data scientists, agents, and dashboards to access reliable, well-structured data.\n \nKey Responsibilities\nDesign, develop, and maintain scalable ETL pipelines using Apache Spark (Scala) to ingest, transform, and load network data into the data lake.Onboard new data sources (network telemetry, syslogs, SNMP traps, device configuration data, ticketing systems) by building ingestion pipelines.Implement monitoring and alerting solutions to ensure data pipeline reliability and performance.Develop and manage deployment pipelines for continuous integration and delivery of data engineering solutions.Manage and optimize data storage solutions, including distributed file systems, relational databases, and external sources accessed via API.Implement data quality checks, validation rules, and automated testing to ensure pipeline reliability and data integrity.Optimize pipeline performance for large-scale data processing across batch and mini-batch processing patterns.Manage and evolve data schemas, partitioning strategies, and storage formats.Support data backfills and recovery when upstream issues or schema changes require reprocessing.Collaborate with data scientists and agent developers to deliver datasets that support anomaly detection models and AI agent workflows.\nRequired Qualifications\nExpert-level experience in building and maintaining ETL pipelines for Big Data.Programming experience with Python and/or Scala.Experience with large-scale data processing with Spark.Experience with AWS services: S3, Glue, Athena, and EMR, including working with EMR as the operating system.Strong understanding of relational databases and SQL.Knowledge of data architecture, data warehousing, partitioning strategies, and columnar storage formats (e.g., Parquet).Experience with workflow orchestration tools, with a preference for Airflow.Proficiency with Linux-based operating systems and shell scripting.Experience with Git-based version control and collaborative development workflows.\nPreferred Qualifications\nExperience with streaming or mini-batch data processing (Spark Streaming, structured streaming, or similar).Experience with Apache Kafka or similar messaging/streaming platforms.Experience with NoSQL databases.Experience in the telecommunications industry or other large-scale network operations environments.Familiarity with network data sources: telemetry, syslogs, SNMP traps, device configuration data.Experience with data integration via REST APIs and cloud SDKs (e.g., boto3).Experience wri</t>
+          <t>Data Visualization Specialist\nLocation: Richmond, Virginia (Remote)\n \nRole Overview\nWe are looking for a Data Visualization Specialist to join our team and help transform the way we build and deliver our applications. As a Data Visualization Specialist, you will analyze and investigate data, generate dashboards and reports using Tableau, participate in web development, and partner with business lines to ensure data consistency and accuracy.\n \nKey Responsibilities\nParticipate in the design, development, and validation of metrics, reports, analyses, and dashboards to drive key business decisions using Tableau.Design and develop intuitive dashboards and data visualization products using Tableau and other business intelligence tools.Learn new data visualization tools to analyze results, evaluate performance, and project future trends.Champion processes and procedures across the organization.Translate business requirements into technical requirements to ensure solutions meet business needs.Explore, extract, cleanse, and combine data from multiple sources and systems.Continually improve data quality, build monitoring tools, and issue alerts.Collaborate cross-functionally to gather requirements, design, and execute solutions.Lead dashboard demo sessions, develop training materials, and produce dashboard documentation.\nRequired Qualifications\nExperience: 3+ years of professional work experience. Candidates should have a robust portfolio outlining previous projects.\n \nTechnical Skills: Extensive experience building visualizations and dashboards. Experience with UI development using Javascript, HTML, and CSS. Proficiency with Tableau, PowerBI, Quicksight or similar reporting tools is required. Knowledge of information design principles and data visualization methods is necessary.\n \nCompany Overview &amp; Culture\nOur organization is a nationwide team delivering technology solutions and support. When you join our team, you will become part of a culture that welcomes differences, cares about our communities, and empowers each other to lead from where we are to make things better. We provide challenging and purposeful careers in a variety of fields and opportunities to grow.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliat</t>
         </is>
       </c>
     </row>
@@ -3872,17 +3862,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Disaster Recovery - Senior Analyst</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, 80237, US</t>
+          <t>Chicago, IL, 60606, US</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3907,7 +3897,7 @@
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045667_usa/data-engineer</t>
+          <t>https://www.apexsystems.com/job/3041163_usa/disaster-recovery---senior-analyst</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -3920,17 +3910,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>e33d9978d04463291091</t>
+          <t>01c26c3c036cb9e8784c</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Data Engineer\nLocation: Denver, Colorado (Onsite)\n \nRole Overview\nOur engineering teams are adept at solving complex problems with leading-edge technology. This role involves working in a fast-paced environment to deliver intelligence and defense data, handling data integration for a system that serves numerous users worldwide. The position focuses on creating new data feeds, maintaining existing feeds, operations monitoring, and managing data outages through scripting and modern technologies.\n \nKey Responsibilities\nConfigure and maintain data ingest workflows (ETL) across multiple production systems.Install, configure, and update a wide array of COTS/GOTS software applications.Support and troubleshoot diverse IT infrastructure hardware platforms and protocols.Work with software development and systems administration staff to monitor and troubleshoot production systems.Generate and maintain systems documentation and diagrams.Troubleshoot network issues and establish new connectivity.Monitor and maintain a variety of databases.Create new data feeds and maintain hundreds of existing integrated data pipelines.\nRequired Qualifications\nEducation: A Bachelor’s degree or equivalent is required.\n \nExperience: A minimum of 3 years of experience with software development programs is required.\n \nTechnical Skills:\nScripting skills in Python and Bash.Experience developing in a Linux/Unix/RHEL environment.Experience with Commercial Cloud Systems (AWS – EC2, RDS, S3).Familiarity with engineering management tools such as JIRA/Confluence.Proficiency with RDBMS databases like PostgreSQL, Oracle, or MySQL.Experience with Git version-control system and CI/CD tools such as Docker, Kubernetes, Helm, and GitLab Runners.Knowledge of common data/configuration formats including Delimited, JSON, GeoJSON, and YAML.Experience with common API/interfaces such as REST, SFTP, Kafka, AMQ, and Socket.\nCertifications: Must be able to obtain a DoD 8570 level IAT-II qualification (such as Security+) within 6 months of hire and maintain it throughout employment.\n \nWork Authorization: Candidates must be a US Citizen.\n \nPreferred Qualifications\nExperience with AWS services such as Diode, Flink, and ArgoCD.Familiarity with monitoring tools like Grafana and Kibana.An understanding of compiled languages, including Java.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By appl</t>
+          <t>Disaster Recovery - Senior Analyst\nLocation: Chicago, Illinois (Remote)\n \nRole Overview\nWe are seeking a Disaster Recovery Senior Analyst to function as a program manager, leading efforts in standardizing and building governance practices for evolving DR standards. This role is pivotal in the transition to a more stable environment with a focus on zero downtime through modernization and investment. You will interface with numerous cross-functional teams to ensure the resilience and reliability of systems in a hybrid architecture.\n \nKey Responsibilities\nLead CMDB and Discovery enablement by enhancing Application Impact Assessments (Tier, RTO, RPO, business function) and configuring automated discovery in ServiceNow for On-Prem and AWS environments.Enable and validate dependency mapping via Dynatrace to support "blast radius" analysis and remediate data quality issues within the CMDB, including missing, stale, or incorrect CI relationships.Review and remediate Disaster Recovery and CMDB documentation to align with governance and audit standards, ensuring it supports audit reviews and leadership oversight.Define and document the On-Prem (NextGen) DR Standard, ensuring it aligns with modern resiliency principles and hybrid architecture.Document SRE-aligned DR practices, as well as DevOps and automation practices.Support monthly and quarterly DR metrics reporting, covering test outcomes, risks, and overall coverage.Identify recurring CMDB and DR issues, recommend corrective actions, and support updates to DR templates, workflows, and ServiceNow processes.Collaborate with DR, Architecture, SRE, and platform teams in an advisory and enablement capacity.\nRequired Qualifications\nTechnical Skills: Experience with ServiceNow for CMDB and discovery, Dynatrace for dependency mapping, and familiarity with AWS and On-Prem environments. Proficient in application assessment and understanding of next-generation DR principles (active/active, active/hot).\n \nPreferred Qualifications\nCertifications are considered beneficial but are not required.\nWork Environment\nThis role will interface with internal teams, including a team of five consultants and three full-time employees (two analysts, one engineer), touching every cross-functional team.This position is ideally based in Chicago; some travel may be required for candidates located elsewhere.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3932,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer III</t>
+          <t>ETRM Support Analyst</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, 10018, US</t>
+          <t>Houston, TX, 77079, US</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3962,7 +3952,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3977,7 +3967,7 @@
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046150_usa/data-engineer---data-engineer-iii</t>
+          <t>https://www.apexsystems.com/job/3045630_usa/etrm-support-analyst</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -3990,17 +3980,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>7928fa9372e07280d384</t>
+          <t>b7a24853e2b54f3b88e0</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Engineer IIILocation: New York, New York (Onsite)COMPENSATION: $68 - $78 HOURLY Role OverviewAs a Data Engineer, you will solve complex data problems and support critical projects. You will partner with stakeholders across the business and with the Data Engineering team to deliver new features or migrate legacy features to a modern, cloud-based platform. This role involves collaboration with teams across the business, providing opportunities to learn about the fashion industry and e-commerce. Key ResponsibilitiesArchitect, design, and implement next-generation data pipelines and BI solutions built on AWS.Build and optimize ETL processes to improve data quality, reliability, and freshness.Leverage AI-powered developer and data tools to boost productivity and code quality.Partner with business stakeholders to translate their needs into scalable data solutions.Collaborate with the Science team to build data foundations for AI solutions and bring them into production.Improve the team's operational excellence through monitoring, automation, and error reduction.Work EnvironmentWe are seeking a candidate available to be in person at our New York office.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access</t>
+          <t>ETRM Support AnalystLocation: Houston, Texas (Onsite)Schedule: 9/80 Contract: 12+ Months on W2. Can extend Role OverviewThe Trade Floor ETRM Support Analyst provides functional business and operational support for Triple Point Commodity XL (TPT-XL). The role partners directly with Front Office, Middle Office, Scheduling, Logistics, Risk, Settlements, Accounting, and Operations users to maintain reliable trading processes. Responsibilities include incident triage, application troubleshooting, controlled configuration and reference-data maintenance, daily process monitoring, and user guidance. Key ResponsibilitiesServe as the primary Level 1/Level 2 support contact for TPXL users across trading, scheduling, logistics, risk, settlements, accounting, and operations.Troubleshoot and resolve functional and data issues involving trade capture, pricing, valuation, positions, risk reporting, scheduling, inventory, and settlements.Support traders, schedulers, and operations personnel during market hours by assessing business impact, communicating status, and restoring service.Configure and maintain TPXL pricing setups, contracts, counterparties, books, portfolios, products, market data, and other business reference data.Monitor daily business processes, trade interfaces, batch jobs, workflows, reports, and end-of-day or month-end activities.Analyze recurring incidents, identify root causes, and recommend sustainable process or application improvements.Own incidents, service requests, and problem tickets through closure, maintaining accurate priorities and user communications.Partner with business users, vendors, and application development teams to resolve defects, test fixes, and implement enhancements.Create and maintain runbooks, knowledge articles, support procedures, and functional documentation.Provide user coaching and training on TPXL workflows, controls, and application functionality.Required QualificationsEducation: Bachelor’s degree in Business, Finance, Information Technology, Computer Science, Management Information Systems, Engineering, or equivalent practical experience. Experience: Five or more years of experience in TPXL support, ETRM/CTRM application support, commodity operations, trading system business analysis, or trade-floor production support. Demonstrated experience supporting business-critical commodity trading processes is necessary. Technical Skills: Hands-on experience supporting and configuring Triple Point Commodity XL. Strong understanding of physical and financial commodity trading processes and workflows is required. Working knowledge of the trade lifecycle, including deal capture, pricing, position management, risk reporting, scheduling, settlements, and invoicing is also necessary. Experience with service management tools like ServiceNow or Jira is needed. Preferred QualificationsExperience supporting natural gas, power, LNG, crude, refined products, or NGL trading workflows.Knowledge of nominations, scheduling, actualiza</t>
         </is>
       </c>
     </row>
@@ -4012,27 +4002,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28255, US</t>
+          <t>Orlando, FL, 32801, US</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FullTime</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4047,7 +4037,7 @@
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046011_usa/data-engineer-ii</t>
+          <t>https://www.apexsystems.com/job/3045943_usa/financial-analyst</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -4060,17 +4050,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>543e7ac4ae4bde57a7a1</t>
+          <t>4c71f50026d724a07523</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Data Engineer IILocation: Charlotte, North Carolina (Hybrid)Duration: 12 months Role OverviewWe are seeking a Data Engineer II to help design, build, and maintain a centralized performance and analytics repository. This role involves integrating data from multiple technology platforms and operational systems. The position is responsible for developing scalable data pipelines, transforming complex datasets, and creating reusable data structures to support reporting, analytics, and operational decision-making. Key ResponsibilitiesDesign, develop, and maintain data ingestion and transformation pipelines.Integrate data from multiple platforms, databases, APIs, and operational systems.Create and maintain data models, schemas, tables, views, and collections.Build and optimize solutions using PostgreSQL, MongoDB, or similar databases.Develop processes that ensure data quality, accuracy, consistency, and reliability.Transform raw and semi-structured data into curated, analytics-ready datasets.Partner with stakeholders to define data requirements and technical solutions.Support dashboard, reporting, and visualization initiatives by providing optimized datasets.Troubleshoot data issues, identify root causes, and implement corrective actions.Participate in testing, code reviews, deployment activities, and production support.Document data flows, transformations, and technical solutions.Contribute to Agile planning, estimation, and delivery activities.Required QualificationsExperience: 3+ years of experience in data engineering, ETL, or data integration roles. Experience building and maintaining automated data pipelines and working with large-scale operational or analytical datasets. Technical Skills: Strong SQL skills and experience designing relational database solutions. Experience with PostgreSQL, SQL Server, or similar database technologies. Experience with MongoDB or other NoSQL database platforms. Proficiency in Python, Java, Spark, or similar data processing technologies. Familiarity with REST APIs, file-based ingestion, and system integrations. Experience supporting dashboards and reporting platforms such as Grafana, Tableau, or Power BI. Knowledge: Knowledge of data modeling, schema design, and data warehouse concepts. Understanding of performance tuning, indexing, and query optimization. Familiarity with Agile development methodologies and CI/CD practices. Preferred QualificationsExperience working on Big Data Technologies.Cloudera Admin / Dev Certification.Certification in Cloud, Docker-Container, or Openshift Technologies.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds B</t>
+          <t>Apex Systems is sourcing for a Financial Analyst along with one of our clients based in Orlando, FL. Please see details below and apply if you are interested!Job Title: Financial AnalystLocation: (Remote)Employment Type: Direct HireSalary: $82,000-112,000 Role OverviewThis position is responsible for conducting in-depth analysis of client-reported electronic data to ensure it is accurate and timely in accordance with treaty guidelines. This role requires a blend of reinsurance knowledge, financial analysis, and data-driven problem-solving. The position involves monitoring and communicating client issues and unusual reporting trends to appropriate stakeholders, and preparing quarterly Statutory, IFRS, and Solvency II financial reports for assigned accounts. Operating with minimal daily direction from a manager is expected. Key ResponsibilitiesDevelop an understanding of reinsurance treaty structures, terms, and guidelines to determine operational expectations.Conduct detailed analysis of client-reported data to validate accuracy against treaty requirements.Independently investigate reporting inconsistencies or errors and liaise directly with clients to understand and resolve data discrepancies.Calculate and analyze Experience Refunds and Loss Carryforwards to ensure alignment with treaty provisions.Accurately record details of all client reporting across multiple business systems and analyze trend reports for reasonability.Communicate actual or potential financial impacts and business risks to stakeholders across finance, actuarial, and operations teams.Prepare and analyze quarterly Statutory, IFRS, and Solvency II financial reports for assigned reinsurance treaties.Prepare detailed financial workpapers, schedules, and supporting documentation for internal and external auditors.Independently analyze and identify client reporting inconsistencies to implement corrections and propose procedures to improve processing inefficiencies.Required QualificationsEducation:A college degree from an accredited institution in Accounting, Finance, Business, or a related field is required. Experience:A minimum of 5 years of experience in Life, Health, or Property &amp; Casualty (re)insurance is required, with a background in reinsurance accounting, financial close cycles, or financial analysis. Candidates must have advanced business knowledge of (re)insurance concepts. Technical Skills:Advanced Microsoft Excel skills are required, including the ability to build and create models, pivot tables, advanced formulas, and macros.Competency using Hyperion Reporting is necessary.Excellent verbal, written, and interpersonal skills for establishing and maintaining professional client, reinsurer, and internal relationships are required.Strong organizational and analytical skills with attention to detail are essential. Preferred QualificationsKnowledge of Health and Special Risk reinsurance practices and principles.Experience with Statutory accounting (STAT), GAAP, and IFRS.Abilit</t>
         </is>
       </c>
     </row>
@@ -4082,17 +4072,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, 30308, US</t>
+          <t>Dearborn, MI, 48120, US</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4117,7 +4107,7 @@
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045202_usa/data-engineer-sr</t>
+          <t>https://www.apexsystems.com/job/3046112_usa/gcp-data-engineer</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -4130,17 +4120,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>77142cddb1e72169aadb</t>
+          <t>72b79700bf28240279f8</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Data Engineer Sr\nLocation: Atlanta, GA (Onsite)\n \nRole Overview\nThe Data Engineer is responsible for designing, building, and supporting scalable data platforms, data products, application integrations, and analytics solutions that enable business decision-making across Power Delivery. This role develops and maintains enterprise data pipelines, integrates operational systems with cloud-based lakehouse platforms, and supports both low-code and pro-code application development using Microsoft Power Platform, OutSystems, and Databricks. The successful candidate will partner with business stakeholders, data analysts, application developers, and technology teams to deliver trusted, governed, and reusable data assets.\n \nKey Responsibilities\nDesign, build, and support enterprise data pipelines using ETL and ELT methodologies.Develop scalable ingestion frameworks for structured, semi-structured, and streaming data.Build and maintain Databricks notebooks, workflows, and data pipelines.Ingest data from source systems using Azure Data Factory, Kafka, CDC technologies, APIs, files, and database sources.Implement data quality checks, monitoring, and exception handling.Support Bronze, Silver, and Gold data architectures within the Databricks Lakehouse.Design and maintain Delta Lake tables and data products.Build and enhance business applications using Microsoft Power Apps, Power Automate, Power Platform, and OutSystems.Implement CI/CD practices using GitHub and Azure DevOps.Maintain documentation, lineage, and metadata for enterprise data assets.\nRequired Qualifications\nEducation: Bachelor's degree in Computer Science, Information Systems, Data Analytics, Engineering, or a related technical discipline.\n \nExperience: 3-7 years of experience in data engineering, analytics engineering, or software development, including building enterprise data pipelines and integrations, and working with cloud-based data platforms.\n \nTechnical Skills:\nData Engineering: ETL/ELT design, data ingestion frameworks, data pipeline orchestration, Data Warehousing concepts, Data Lake and Lakehouse architectures (Medallion architecture).Databricks: Databricks Workflows, PySpark, Spark SQL, Delta Lake, Unity Catalog, and Data Products.Cloud &amp; Integration: Azure Data Factory, APIs, Kafka, CDC technologies, and SQL Server.Development: Python, SQL, GitHub, and Azure DevOps.Business Applications: Power Apps, Power Automate, Power Platform, and OutSystems.\nPreferred Qualifications\nUtility industry experience.Power Delivery domain knowledge.Experience supporting Transmission or Distribution Analytics.Real-time data streaming experience.Knowledge of AI/ML enablement on Databricks.Experience with Power BI integration and Direct Query architectures.\nMust be authorized to work in the US without sponsorship.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovat</t>
+          <t>Role: GCP Data EngineerLocation: Hybrid - 4 days/week in our SE Michigan officeDuration: 12+ monthsDescription:The Data Engineer is responsible for designing, building, and maintaining scalable data solutions that support enterprise analytics, machine learning, and business intelligence initiatives. This role develops and optimizes data infrastructure, pipelines, and platforms that enable the efficient collection, storage, processing, and analysis of large volumes of structured and unstructured data. The ideal candidate will possess strong expertise in cloud-based data engineering, data modeling, pipeline development, and modern data platforms, while partnering closely with business and technology stakeholders to deliver reliable, high-performing data solutions. Key ResponsibilitiesCollaborate with business and technology stakeholders to understand current and future data requirements and translate them into scalable technical solutions.Design, develop, and maintain reliable, efficient, and scalable data infrastructure supporting data collection, storage, transformation, and analytics.Build and optimize end-to-end data pipelines, workflows, and data models to ensure accurate and efficient data processing.Design, implement, and support enterprise data platforms, including data warehouses, data lakes, and lakehouse architectures.Develop tools, frameworks, scripts, and automation capabilities that improve data engineering efficiency and reduce manual effort.Create and maintain robust data integration solutions across multiple systems and sources.Ensure data quality, performance, reliability, and scalability through monitoring, testing, and continuous optimization.Partner with data scientists, analysts, and application teams to support advanced analytics and machine learning initiatives.Identify opportunities to improve data architecture, pipeline performance, cost optimization, and operational efficiency.Implement data governance, security, and best practices across the data ecosystem. Required QualificationsData Engineering &amp; Cloud Platforms5+ years of professional experience in Data Engineering.Hands-on experience designing, developing, and maintaining modern data architectures and data platforms.Strong experience with Google Cloud Platform (GCP) services and cloud-native data solutions.Advanced knowledge of BigQuery for data warehousing, analytics, and large-scale data processing.Programming &amp; AutomationStrong proficiency in Python for data engineering, automation, and data pipeline development.Experience developing reusable frameworks, scripts, and automation solutions.Proficiency using GitHub and modern source control practices.Data Architecture &amp; ModelingExperience designing and implementing: Data WarehousesData LakesLakehouse ArchitecturesStrong understanding of data modeling concepts and relational database design.Experience building scalable ETL/ELT pipelines and data integration solutions.Analytics &amp; Machine Learning EnablementExperience s</t>
         </is>
       </c>
     </row>
@@ -4152,17 +4142,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Data Visualization Specialist</t>
+          <t>IAM Business Analyst</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, 23219, US</t>
+          <t>Atlanta, GA, 30303, US</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4187,7 +4177,7 @@
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046209_usa/data-visualization-specialist</t>
+          <t>https://www.apexsystems.com/job/3046284_usa/iam-business-analyst</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -4200,17 +4190,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>d4969320cc96dd1de9b0</t>
+          <t>dd7ad9e0f4e232c52b72</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Data Visualization Specialist\nLocation: Richmond, Virginia (Remote)\n \nRole Overview\nWe are looking for a Data Visualization Specialist to join our team and help transform the way we build and deliver our applications. As a Data Visualization Specialist, you will analyze and investigate data, generate dashboards and reports using Tableau, participate in web development, and partner with business lines to ensure data consistency and accuracy.\n \nKey Responsibilities\nParticipate in the design, development, and validation of metrics, reports, analyses, and dashboards to drive key business decisions using Tableau.Design and develop intuitive dashboards and data visualization products using Tableau and other business intelligence tools.Learn new data visualization tools to analyze results, evaluate performance, and project future trends.Champion processes and procedures across the organization.Translate business requirements into technical requirements to ensure solutions meet business needs.Explore, extract, cleanse, and combine data from multiple sources and systems.Continually improve data quality, build monitoring tools, and issue alerts.Collaborate cross-functionally to gather requirements, design, and execute solutions.Lead dashboard demo sessions, develop training materials, and produce dashboard documentation.\nRequired Qualifications\nExperience: 3+ years of professional work experience. Candidates should have a robust portfolio outlining previous projects.\n \nTechnical Skills: Extensive experience building visualizations and dashboards. Experience with UI development using Javascript, HTML, and CSS. Proficiency with Tableau, PowerBI, Quicksight or similar reporting tools is required. Knowledge of information design principles and data visualization methods is necessary.\n \nCompany Overview &amp; Culture\nOur organization is a nationwide team delivering technology solutions and support. When you join our team, you will become part of a culture that welcomes differences, cares about our communities, and empowers each other to lead from where we are to make things better. We provide challenging and purposeful careers in a variety of fields and opportunities to grow.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliat</t>
+          <t>IAM Business AnalystLocation: Atlanta, Georgia or Charlotte, NC (Onsite) Role OverviewWe are seeking an IAM Business Analyst to support critical identity and access management initiatives. This role will define and document IAM processes, develop operational runbooks, and build implementation playbooks. The analyst will be responsible for data analysis, mapping privileged users and access, and performing gap analysis to identify risks and inconsistencies. Key ResponsibilitiesDefine and document IAM lifecycle processes, including provisioning, rotation, and revocation.Develop operational runbooks for onboarding, support, and recovery procedures.Build and publish IAM playbooks that provide implementation guidance.Identify and map privileged users, roles, and access entitlements.Compile, merge, and normalize datasets from IAM, application, and system sources.Map users to systems and classify control planes and platforms.Perform gap analysis, risk scoring, and identification of inconsistencies.Deduplicate data and resolve mismatches across various data sources.Inventory authentication methods and categorize applications based on findings.Engage with stakeholders to drive alignment across multiple teams.Required QualificationsA Bachelor's Degree is not required for this position. Technical Skills:IAM Process and Lifecycle ManagementBusiness Analysis and Requirements ManagementIAM Data Analysis and ReconciliationAccess Governance and Entitlement AnalysisRisk Analysis and Gap AssessmentPlaybook and Runbook DevelopmentStakeholder EngagementPreferred QualificationsIAM Domain ExpertiseExperience with IAM Repositories and Data HubsKnowledge of Zero Trust and Modern AuthenticationData Governance ExperienceReporting and Dashboard DevelopmentExperience with Audit and Regulatory requirementsProject Delivery ExperienceEverforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits</t>
         </is>
       </c>
     </row>
@@ -4222,17 +4212,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Disaster Recovery - Senior Analyst</t>
+          <t>IT Analyst – Desktop Governance &amp; Compliance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, 60606, US</t>
+          <t>Pensacola, FL, 32526, US</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4257,7 +4247,7 @@
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3041163_usa/disaster-recovery---senior-analyst</t>
+          <t>https://www.apexsystems.com/job/3046000_usa/it-analyst--desktop-governance--compliance</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -4270,17 +4260,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>01c26c3c036cb9e8784c</t>
+          <t>c4794178e9dee2599320</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Disaster Recovery - Senior Analyst\nLocation: Chicago, Illinois (Remote)\n \nRole Overview\nWe are seeking a Disaster Recovery Senior Analyst to function as a program manager, leading efforts in standardizing and building governance practices for evolving DR standards. This role is pivotal in the transition to a more stable environment with a focus on zero downtime through modernization and investment. You will interface with numerous cross-functional teams to ensure the resilience and reliability of systems in a hybrid architecture.\n \nKey Responsibilities\nLead CMDB and Discovery enablement by enhancing Application Impact Assessments (Tier, RTO, RPO, business function) and configuring automated discovery in ServiceNow for On-Prem and AWS environments.Enable and validate dependency mapping via Dynatrace to support "blast radius" analysis and remediate data quality issues within the CMDB, including missing, stale, or incorrect CI relationships.Review and remediate Disaster Recovery and CMDB documentation to align with governance and audit standards, ensuring it supports audit reviews and leadership oversight.Define and document the On-Prem (NextGen) DR Standard, ensuring it aligns with modern resiliency principles and hybrid architecture.Document SRE-aligned DR practices, as well as DevOps and automation practices.Support monthly and quarterly DR metrics reporting, covering test outcomes, risks, and overall coverage.Identify recurring CMDB and DR issues, recommend corrective actions, and support updates to DR templates, workflows, and ServiceNow processes.Collaborate with DR, Architecture, SRE, and platform teams in an advisory and enablement capacity.\nRequired Qualifications\nTechnical Skills: Experience with ServiceNow for CMDB and discovery, Dynatrace for dependency mapping, and familiarity with AWS and On-Prem environments. Proficient in application assessment and understanding of next-generation DR principles (active/active, active/hot).\n \nPreferred Qualifications\nCertifications are considered beneficial but are not required.\nWork Environment\nThis role will interface with internal teams, including a team of five consultants and three full-time employees (two analysts, one engineer), touching every cross-functional team.This position is ideally based in Chicago; some travel may be required for candidates located elsewhere.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process</t>
+          <t>IT Analyst – Desktop Governance &amp; ComplianceLocation: Pensacola, FL or Vienna, VA (Hybrid) Role OverviewWe are seeking a skilled IT Analyst for a Desktop Governance and Compliance role. This position supports operational efficiency, stability, and security across a diverse end-user computing environment. The analyst will focus on governance, risk, and compliance activities, including elevated access controls, audit readiness, remediation support, and evidence management. Key ResponsibilitiesSupport elevated access governance activities, including recurring reviews, entitlement validation, recertifications, exception tracking, and evidence collection.Review access and control-related requests against business needs, security requirements, and policy standards.Develop and maintain compliance reporting, dashboards, Standard Operating Procedures, and governance reference materials.Use Excel, pivot tables, and reporting tools to analyze data, validate controls, and support risk-based decisions.Support projects and process improvements through planning, tracking, and implementation.Build effective relationships with team members, management, and business partners.Demonstrate a strong technical aptitude for desktop infrastructure and communicate technical requirements effectively.Perform other duties as assigned.Required QualificationsEducation: A Bachelor’s degree in Business Administration, Information Technology, Risk Management, or a related field, or an equivalent combination of education, training, and experience is required. Experience: Candidates must have over 5 years of IT experience in formulating and supporting desktop infrastructure technical solutions for access governance, privileged access administration, risk remediation, audit support, compliance reporting, and control validation within end-user computing operations. Experience is also required in supporting privileged access management, workstation elevated-access provisioning, entitlement management, recertification processes, ServiceNow, MyIT, and related reporting tools. Additional experience includes supporting projects, facilitating meetings, driving process improvement, and working within Systems Development Life Cycle and agile methodologies. Skills: Applicants should possess strong communication, documentation, planning, and time management skills. Strong research, analytical, and problem-solving abilities are necessary, including proficiency with Excel and pivot tables. Candidates must have a keen attention to detail and be self-motivated professionals capable of working independently and collaboratively. Preferred QualificationsPMP or similar project management certification.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportuni</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4282,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ETRM Support Analyst</t>
+          <t>IT Business Analyst III</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, 77079, US</t>
+          <t>Addison, TX, 75001, US</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4312,7 +4302,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4327,7 +4317,7 @@
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045630_usa/etrm-support-analyst</t>
+          <t>https://www.apexsystems.com/job/3045945_usa/it-business-analyst-iii</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -4340,17 +4330,17 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>b7a24853e2b54f3b88e0</t>
+          <t>0334db74dc84984b1593</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ETRM Support AnalystLocation: Houston, Texas (Onsite)Schedule: 9/80 Contract: 12+ Months on W2. Can extend Role OverviewThe Trade Floor ETRM Support Analyst provides functional business and operational support for Triple Point Commodity XL (TPT-XL). The role partners directly with Front Office, Middle Office, Scheduling, Logistics, Risk, Settlements, Accounting, and Operations users to maintain reliable trading processes. Responsibilities include incident triage, application troubleshooting, controlled configuration and reference-data maintenance, daily process monitoring, and user guidance. Key ResponsibilitiesServe as the primary Level 1/Level 2 support contact for TPXL users across trading, scheduling, logistics, risk, settlements, accounting, and operations.Troubleshoot and resolve functional and data issues involving trade capture, pricing, valuation, positions, risk reporting, scheduling, inventory, and settlements.Support traders, schedulers, and operations personnel during market hours by assessing business impact, communicating status, and restoring service.Configure and maintain TPXL pricing setups, contracts, counterparties, books, portfolios, products, market data, and other business reference data.Monitor daily business processes, trade interfaces, batch jobs, workflows, reports, and end-of-day or month-end activities.Analyze recurring incidents, identify root causes, and recommend sustainable process or application improvements.Own incidents, service requests, and problem tickets through closure, maintaining accurate priorities and user communications.Partner with business users, vendors, and application development teams to resolve defects, test fixes, and implement enhancements.Create and maintain runbooks, knowledge articles, support procedures, and functional documentation.Provide user coaching and training on TPXL workflows, controls, and application functionality.Required QualificationsEducation: Bachelor’s degree in Business, Finance, Information Technology, Computer Science, Management Information Systems, Engineering, or equivalent practical experience. Experience: Five or more years of experience in TPXL support, ETRM/CTRM application support, commodity operations, trading system business analysis, or trade-floor production support. Demonstrated experience supporting business-critical commodity trading processes is necessary. Technical Skills: Hands-on experience supporting and configuring Triple Point Commodity XL. Strong understanding of physical and financial commodity trading processes and workflows is required. Working knowledge of the trade lifecycle, including deal capture, pricing, position management, risk reporting, scheduling, settlements, and invoicing is also necessary. Experience with service management tools like ServiceNow or Jira is needed. Preferred QualificationsExperience supporting natural gas, power, LNG, crude, refined products, or NGL trading workflows.Knowledge of nominations, scheduling, actualiza</t>
+          <t>IT Business Analyst IIILocation: Addison, TX/ Charlotte NC/ Jacksonville FL (Onsite)Duration: 12 months Role OverviewThis position is for a Business Analyst who will serve as the primary interface with business partners, solution architects, and cross-organizational technology teams. The analyst will examine current processes and systems, evaluating the business model and its integration with technology. The role involves working with stakeholders to understand their needs, analyze issues, capture requirements, and collaborate with the development team to refine these into executable specifications within an Agile Scrum framework. Key ResponsibilitiesAct as the primary interface with business partners to elicit requirements, document process flows, and define strategies for technical solutions.Analyze current processes and systems, assessing the business model and its integration with technology.Collaborate with the Product Owner to evaluate features, write user stories, and document business rules.Work with developers to ensure acceptance criteria for user stories are understood and applied, and review technical designs to identify enablers and dependencies.Document detailed functional and technical requirements for business needs.Provide support to UAT and SIT testers to clarify requirements and assess defects.Work with testers to ensure that test plans and scripts satisfy the requirements.Analyze existing capabilities to identify gaps and opportunities for improvement.Facilitate discussions and help resolve conflicts. Required QualificationsExperience: A minimum of 5 years of experience as a Business Analyst, working closely with business partners to elicit requirements and document processes. At least 3 years of practical agile experience is required. Technical Skills: Working knowledge of agile tools such as JIRA. Functional Skills:Proven analytical skills with experience converting business needs into epics and stories.Experience in refining business processes.Ability to work effectively with both technical and business team members.Excellent oral and written communication skills.Self-motivated with the ability to work with minimal supervision.Experience in a Product Owner capacity or working closely with a Product Owner to define business needs.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls</t>
         </is>
       </c>
     </row>
@@ -4362,27 +4352,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Jr. Business Analyst</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Orlando, FL, 32801, US</t>
+          <t>Lansing, MI, 48933, US</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FullTime</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4397,7 +4387,7 @@
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045943_usa/financial-analyst</t>
+          <t>https://www.apexsystems.com/job/3045854_usa/jr-business-analyst</t>
         </is>
       </c>
       <c r="J57" t="b">
@@ -4410,17 +4400,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>4c71f50026d724a07523</t>
+          <t>d6747ac10fe311640159</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Apex Systems is sourcing for a Financial Analyst along with one of our clients based in Orlando, FL. Please see details below and apply if you are interested!Job Title: Financial AnalystLocation: (Remote)Employment Type: Direct HireSalary: $82,000-112,000 Role OverviewThis position is responsible for conducting in-depth analysis of client-reported electronic data to ensure it is accurate and timely in accordance with treaty guidelines. This role requires a blend of reinsurance knowledge, financial analysis, and data-driven problem-solving. The position involves monitoring and communicating client issues and unusual reporting trends to appropriate stakeholders, and preparing quarterly Statutory, IFRS, and Solvency II financial reports for assigned accounts. Operating with minimal daily direction from a manager is expected. Key ResponsibilitiesDevelop an understanding of reinsurance treaty structures, terms, and guidelines to determine operational expectations.Conduct detailed analysis of client-reported data to validate accuracy against treaty requirements.Independently investigate reporting inconsistencies or errors and liaise directly with clients to understand and resolve data discrepancies.Calculate and analyze Experience Refunds and Loss Carryforwards to ensure alignment with treaty provisions.Accurately record details of all client reporting across multiple business systems and analyze trend reports for reasonability.Communicate actual or potential financial impacts and business risks to stakeholders across finance, actuarial, and operations teams.Prepare and analyze quarterly Statutory, IFRS, and Solvency II financial reports for assigned reinsurance treaties.Prepare detailed financial workpapers, schedules, and supporting documentation for internal and external auditors.Independently analyze and identify client reporting inconsistencies to implement corrections and propose procedures to improve processing inefficiencies.Required QualificationsEducation:A college degree from an accredited institution in Accounting, Finance, Business, or a related field is required. Experience:A minimum of 5 years of experience in Life, Health, or Property &amp; Casualty (re)insurance is required, with a background in reinsurance accounting, financial close cycles, or financial analysis. Candidates must have advanced business knowledge of (re)insurance concepts. Technical Skills:Advanced Microsoft Excel skills are required, including the ability to build and create models, pivot tables, advanced formulas, and macros.Competency using Hyperion Reporting is necessary.Excellent verbal, written, and interpersonal skills for establishing and maintaining professional client, reinsurer, and internal relationships are required.Strong organizational and analytical skills with attention to detail are essential. Preferred QualificationsKnowledge of Health and Special Risk reinsurance practices and principles.Experience with Statutory accounting (STAT), GAAP, and IFRS.Abilit</t>
+          <t>The Business Analyst is responsible for gathering and documenting clear, unambiguous, and testable business requirements from the client, and understanding the business requirements thoroughly in order to communicate business need and system functionality to technical and non-technical stakeholders, project team members, and the user community. The Business Analyst serves as the ScrumMaster (heavy usage of Monday.com and/or JIRA tool) on campaign finance related projects and coordinates with the PMO’s Project Manager for artifacts/documentation needed on projects. This position has on-site/in person workdays of Tuesday/Wednesday (no exceptions). The Business Analyst is responsible for working with the project team and stakeholders to examine existing and future-state business processes, data, and systems. This information is used to guide the gathering of business requirements as they relate to the desired system functionality. This position includes creating test plans with the business area, and ensuring repeatable processes are in place beyond the lifecycle of the current project. Job Fit: The ideal candidate for this role will have a mentor/teaching type of background to ensure the future long-term success of the business area, helping to solidify an Agile mindset with their vendor and shoring up long-term transition from project mode to maintenance mode. ResponsibilitiesResponsible for documenting business requirements that are clear, unambiguous, testable, and satisfy the business need in accordance with standard templates and adherence to policies, standards, and guidelines. Creating Test plans with the business, ensuring repeatable processes are in place beyond the lifecycle of the current project. Documenting repeatable steps/processes (technical documentation) for the business area to refer to as part of maintenance planning. Responsible for facilitating requirement gathering meetings to identify impacted business processes and document the project business requirements. Attendees include relevant project team members and stakeholders as identified in the Communication Plan.Responsible for adhering to the project schedule by developing and maintaining the project backlog during Agile projects and working with the product owner to set priority throughout the duration of project.Responsible for understanding project scope and actively monitoring requirements process to maintain adherence to the objectives set for the project.Responsible for understanding high-level information governance objectives and ensuring appropriate Stakeholder inclusion and/or awareness regarding data requirements.Responsible for appropriate resolution of critical IT issues as it pertains to the BA role.Responsible for understanding project specific benefits and related impact of changes to project scope or business requirements.Ensures SEM (system engineering methodology) deliverables for the project that are a responsibility of the BA are completed, reviewed, an</t>
         </is>
       </c>
     </row>
@@ -4432,17 +4422,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Manufacturing Analyst 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, 48120, US</t>
+          <t>Palmdale, CA, 93550, US</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4452,7 +4442,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4467,7 +4457,7 @@
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046112_usa/gcp-data-engineer</t>
+          <t>https://www.apexsystems.com/job/3044545_usa/manufacturing-analyst-1</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -4480,17 +4470,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>72b79700bf28240279f8</t>
+          <t>553d01a264e0e332c14d</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Role: GCP Data EngineerLocation: Hybrid - 4 days/week in our SE Michigan officeDuration: 12+ monthsDescription:The Data Engineer is responsible for designing, building, and maintaining scalable data solutions that support enterprise analytics, machine learning, and business intelligence initiatives. This role develops and optimizes data infrastructure, pipelines, and platforms that enable the efficient collection, storage, processing, and analysis of large volumes of structured and unstructured data. The ideal candidate will possess strong expertise in cloud-based data engineering, data modeling, pipeline development, and modern data platforms, while partnering closely with business and technology stakeholders to deliver reliable, high-performing data solutions. Key ResponsibilitiesCollaborate with business and technology stakeholders to understand current and future data requirements and translate them into scalable technical solutions.Design, develop, and maintain reliable, efficient, and scalable data infrastructure supporting data collection, storage, transformation, and analytics.Build and optimize end-to-end data pipelines, workflows, and data models to ensure accurate and efficient data processing.Design, implement, and support enterprise data platforms, including data warehouses, data lakes, and lakehouse architectures.Develop tools, frameworks, scripts, and automation capabilities that improve data engineering efficiency and reduce manual effort.Create and maintain robust data integration solutions across multiple systems and sources.Ensure data quality, performance, reliability, and scalability through monitoring, testing, and continuous optimization.Partner with data scientists, analysts, and application teams to support advanced analytics and machine learning initiatives.Identify opportunities to improve data architecture, pipeline performance, cost optimization, and operational efficiency.Implement data governance, security, and best practices across the data ecosystem. Required QualificationsData Engineering &amp; Cloud Platforms5+ years of professional experience in Data Engineering.Hands-on experience designing, developing, and maintaining modern data architectures and data platforms.Strong experience with Google Cloud Platform (GCP) services and cloud-native data solutions.Advanced knowledge of BigQuery for data warehousing, analytics, and large-scale data processing.Programming &amp; AutomationStrong proficiency in Python for data engineering, automation, and data pipeline development.Experience developing reusable frameworks, scripts, and automation solutions.Proficiency using GitHub and modern source control practices.Data Architecture &amp; ModelingExperience designing and implementing: Data WarehousesData LakesLakehouse ArchitecturesStrong understanding of data modeling concepts and relational database design.Experience building scalable ETL/ELT pipelines and data integration solutions.Analytics &amp; Machine Learning EnablementExperience s</t>
+          <t>Manufacturing Analyst 1Location: Palmdale, California (Onsite) Role OverviewThis organization is seeking a Manufacturing Analyst to join a team of qualified, diverse individuals. This position involves supporting production, business, and other processes in a team-based manufacturing environment. The role includes performing activities in various cross-functional areas, including production planning and control, quality management, systems, manufacturing, equipment and facilities engineering, material management, and process reengineering. Key ResponsibilitiesTrack daily costs and administer earned value management activities.Maintain visibility charts and provide weekly and monthly status reports.Close and document tool orders for assembly tooling.Oversee the validation of incoming materials against the bill of material.Develop internal tooling packages.Liaise with support organizations to negotiate schedules.Order and record chemical usage, ensuring proper inventory within tracking systems.Manage tool control and accountability activities, including inventory, audits, and asset management.Handle technical administrative tasks such as certification compliance, meeting support, and team engagement.Required QualificationsEducation: A Bachelor's degree with 3 years of experience, a Master's Degree with 1 year of experience, or 7 years of relevant experience in lieu of a degree. Experience: Experience in a manufacturing environment.Cost account management experience. Technical Skills: Intermediate to Advanced Microsoft Suite capabilities (Excel, PowerPoint, Word). Must be highly detail-oriented, organized, proactive, and a skilled communicator. Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee st</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4492,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IAM Business Analyst</t>
+          <t>Member Account Protection Analyst</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, 30303, US</t>
+          <t>Anaheim, CA, 92807, US</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4537,7 +4527,7 @@
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046284_usa/iam-business-analyst</t>
+          <t>https://www.apexsystems.com/job/3046147_usa/member-account-protection-analyst</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -4550,17 +4540,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>dd7ad9e0f4e232c52b72</t>
+          <t>5a3a7c9c2c0570efa20f</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>IAM Business AnalystLocation: Atlanta, Georgia or Charlotte, NC (Onsite) Role OverviewWe are seeking an IAM Business Analyst to support critical identity and access management initiatives. This role will define and document IAM processes, develop operational runbooks, and build implementation playbooks. The analyst will be responsible for data analysis, mapping privileged users and access, and performing gap analysis to identify risks and inconsistencies. Key ResponsibilitiesDefine and document IAM lifecycle processes, including provisioning, rotation, and revocation.Develop operational runbooks for onboarding, support, and recovery procedures.Build and publish IAM playbooks that provide implementation guidance.Identify and map privileged users, roles, and access entitlements.Compile, merge, and normalize datasets from IAM, application, and system sources.Map users to systems and classify control planes and platforms.Perform gap analysis, risk scoring, and identification of inconsistencies.Deduplicate data and resolve mismatches across various data sources.Inventory authentication methods and categorize applications based on findings.Engage with stakeholders to drive alignment across multiple teams.Required QualificationsA Bachelor's Degree is not required for this position. Technical Skills:IAM Process and Lifecycle ManagementBusiness Analysis and Requirements ManagementIAM Data Analysis and ReconciliationAccess Governance and Entitlement AnalysisRisk Analysis and Gap AssessmentPlaybook and Runbook DevelopmentStakeholder EngagementPreferred QualificationsIAM Domain ExpertiseExperience with IAM Repositories and Data HubsKnowledge of Zero Trust and Modern AuthenticationData Governance ExperienceReporting and Dashboard DevelopmentExperience with Audit and Regulatory requirementsProject Delivery ExperienceEverforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits</t>
+          <t>Member Account Protection AnalystLocation: Anaheim, California (Hybrid)Contract: Through 10/31/26Role OverviewOur organization is seeking a Member Account Protection Analyst to support fraud prevention, investigations, and dispute resolution activities. This individual will review fraud alerts, investigate suspicious account activity, manage card-related fraud claims, and support payment network investigations. The role is responsible for minimizing fraud losses while ensuring compliance with regulatory requirements and internal procedures. Key ResponsibilitiesReview and investigate fraud alerts and suspicious account activity.Manage ATM, debit card, and credit card fraud claims.Support ACH and person-to-person payment investigations.Assist with Regulation E dispute processing.Independently manage a pipeline of fraud cases and disputes.Maintain compliance with regulatory requirements and internal procedures.Provide a high level of customer service.Required QualificationsExperience in banking or credit union environments.Experience with ATM, debit card, and credit card fraud claims or investigations.Demonstrated experience in fraud investigations, claims, or disputes.Strong communication and customer service skills.Preferred QualificationsExperience with Zelle investigations.Experience with FDR, First Track, and/or Fiserv systems.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions</t>
         </is>
       </c>
     </row>
@@ -4572,17 +4562,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IT Analyst – Desktop Governance &amp; Compliance</t>
+          <t>Operations Support Analyst - ATM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pensacola, FL, 32526, US</t>
+          <t>Saint Louis, MO, 63101-2510, US</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4592,7 +4582,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4607,7 +4597,7 @@
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046000_usa/it-analyst--desktop-governance--compliance</t>
+          <t>https://www.apexsystems.com/job/3046305_usa/operations-support-analyst---atm</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -4620,17 +4610,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>c4794178e9dee2599320</t>
+          <t>c6f5e933e9fefe3054d1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>IT Analyst – Desktop Governance &amp; ComplianceLocation: Pensacola, FL or Vienna, VA (Hybrid) Role OverviewWe are seeking a skilled IT Analyst for a Desktop Governance and Compliance role. This position supports operational efficiency, stability, and security across a diverse end-user computing environment. The analyst will focus on governance, risk, and compliance activities, including elevated access controls, audit readiness, remediation support, and evidence management. Key ResponsibilitiesSupport elevated access governance activities, including recurring reviews, entitlement validation, recertifications, exception tracking, and evidence collection.Review access and control-related requests against business needs, security requirements, and policy standards.Develop and maintain compliance reporting, dashboards, Standard Operating Procedures, and governance reference materials.Use Excel, pivot tables, and reporting tools to analyze data, validate controls, and support risk-based decisions.Support projects and process improvements through planning, tracking, and implementation.Build effective relationships with team members, management, and business partners.Demonstrate a strong technical aptitude for desktop infrastructure and communicate technical requirements effectively.Perform other duties as assigned.Required QualificationsEducation: A Bachelor’s degree in Business Administration, Information Technology, Risk Management, or a related field, or an equivalent combination of education, training, and experience is required. Experience: Candidates must have over 5 years of IT experience in formulating and supporting desktop infrastructure technical solutions for access governance, privileged access administration, risk remediation, audit support, compliance reporting, and control validation within end-user computing operations. Experience is also required in supporting privileged access management, workstation elevated-access provisioning, entitlement management, recertification processes, ServiceNow, MyIT, and related reporting tools. Additional experience includes supporting projects, facilitating meetings, driving process improvement, and working within Systems Development Life Cycle and agile methodologies. Skills: Applicants should possess strong communication, documentation, planning, and time management skills. Strong research, analytical, and problem-solving abilities are necessary, including proficiency with Excel and pivot tables. Candidates must have a keen attention to detail and be self-motivated professionals capable of working independently and collaboratively. Preferred QualificationsPMP or similar project management certification.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportuni</t>
+          <t>Operations Support Analyst - ATM\nLocation: Saint Louis, Missouri (Onsite)\n \nRole Overview\nWe are seeking an Operations Support Analyst for an ATM Operations Level 1 support role. This position is responsible for the day-to-day operations of the technology platform, focusing on problem and incident management, release deployment, application monitoring, and service analytics. The analyst will identify potential production failure scenarios, create incident and enhancement tickets, and communicate with internal operations teams.\n \nKey Responsibilities\nProvide phone queue support for ATM operational issues, comprising approximately 75% of daily activities.Perform technical recovery of ATMs, accounting for about 25% of daily tasks.Take ownership of escalations, performing troubleshooting, analysis, and resolution using query and programming skills.Identify ATM production failure scenarios and create incident, enhancement, or problem tickets.Perform analytical, technical, and administrative work to support new and existing equipment and software.Interpret, evaluate, and resolve issues related to the functional operation of technology products.Navigate multiple applications simultaneously to support operational needs.\n \nRequired Qualifications\nExperience:\nExperience in a technical support, helpdesk, ATM servicing, or electronic banking operational role.Proven ability to troubleshoot issues to maintain network stability.Strong customer service skills with excellent verbal and written communication.\nTechnical Skills:\nProficiency with the Microsoft Office Suite.Familiarity with Jira and Splunk is beneficial.\n \nPreferred Qualifications\nPrevious knowledge of ATM systems.Experience with root cause analysis and troubleshooting.Proficiency with telephone systems, as the majority of the day will be spent on telecom support.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of</t>
         </is>
       </c>
     </row>
@@ -4642,12 +4632,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IT Business Analyst III</t>
+          <t>Order Analyst IV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Addison, TX, 75001, US</t>
+          <t>Houston, TX, 77046, US</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4677,7 +4667,7 @@
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045945_usa/it-business-analyst-iii</t>
+          <t>https://www.apexsystems.com/job/3043997_usa/order-analyst-iv</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -4690,17 +4680,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>0334db74dc84984b1593</t>
+          <t>f2a07af249fdd58c0ced</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>IT Business Analyst IIILocation: Addison, TX/ Charlotte NC/ Jacksonville FL (Onsite)Duration: 12 months Role OverviewThis position is for a Business Analyst who will serve as the primary interface with business partners, solution architects, and cross-organizational technology teams. The analyst will examine current processes and systems, evaluating the business model and its integration with technology. The role involves working with stakeholders to understand their needs, analyze issues, capture requirements, and collaborate with the development team to refine these into executable specifications within an Agile Scrum framework. Key ResponsibilitiesAct as the primary interface with business partners to elicit requirements, document process flows, and define strategies for technical solutions.Analyze current processes and systems, assessing the business model and its integration with technology.Collaborate with the Product Owner to evaluate features, write user stories, and document business rules.Work with developers to ensure acceptance criteria for user stories are understood and applied, and review technical designs to identify enablers and dependencies.Document detailed functional and technical requirements for business needs.Provide support to UAT and SIT testers to clarify requirements and assess defects.Work with testers to ensure that test plans and scripts satisfy the requirements.Analyze existing capabilities to identify gaps and opportunities for improvement.Facilitate discussions and help resolve conflicts. Required QualificationsExperience: A minimum of 5 years of experience as a Business Analyst, working closely with business partners to elicit requirements and document processes. At least 3 years of practical agile experience is required. Technical Skills: Working knowledge of agile tools such as JIRA. Functional Skills:Proven analytical skills with experience converting business needs into epics and stories.Experience in refining business processes.Ability to work effectively with both technical and business team members.Excellent oral and written communication skills.Self-motivated with the ability to work with minimal supervision.Experience in a Product Owner capacity or working closely with a Product Owner to define business needs.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls</t>
+          <t>Senior Division Order AnalystLocation: Houston, Texas (Onsite 3 days/week) Role OverviewWe are seeking a seasoned Division Order Analyst for a role based in Houston, TX. The position involves facilitating the distribution of proceeds from oil and gas sales and the collection of well expenses. This role is focused on maintenance items within the EOR region and requires a candidate who can navigate complex title structures. Key ResponsibilitiesFacilitate the distribution of proceeds from oil and gas sales and the collection of well expenses.Determine the relative ownership of the company, working interest partners, and royalty holders by analyzing title documents.Maintain and update ownership records for the assigned EOR region.Handle maintenance items related to the EOR asset.Required QualificationsOwnership maintenanceComplex title analysisRevenue and royalty ownership calculationsWorking Interest and ORRI ownershipUnitized and EOR propertiesAdvanced Excel reporting and analysisEverforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access to certification prep and a library of technical and leadership courses/books/seminars once you have 6+ months of tenure, and certification discounts and other perks to associations that inclu</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4702,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jr. Business Analyst</t>
+          <t>Post Market Analyst</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lansing, MI, 48933, US</t>
+          <t>Burlingame, CA, 94010, US</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4747,7 +4737,7 @@
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045854_usa/jr-business-analyst</t>
+          <t>https://www.apexsystems.com/job/3045581_usa/post-market-analyst</t>
         </is>
       </c>
       <c r="J62" t="b">
@@ -4760,17 +4750,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>d6747ac10fe311640159</t>
+          <t>bd67c2345ef96be8792b</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>The Business Analyst is responsible for gathering and documenting clear, unambiguous, and testable business requirements from the client, and understanding the business requirements thoroughly in order to communicate business need and system functionality to technical and non-technical stakeholders, project team members, and the user community. The Business Analyst serves as the ScrumMaster (heavy usage of Monday.com and/or JIRA tool) on campaign finance related projects and coordinates with the PMO’s Project Manager for artifacts/documentation needed on projects. This position has on-site/in person workdays of Tuesday/Wednesday (no exceptions). The Business Analyst is responsible for working with the project team and stakeholders to examine existing and future-state business processes, data, and systems. This information is used to guide the gathering of business requirements as they relate to the desired system functionality. This position includes creating test plans with the business area, and ensuring repeatable processes are in place beyond the lifecycle of the current project. Job Fit: The ideal candidate for this role will have a mentor/teaching type of background to ensure the future long-term success of the business area, helping to solidify an Agile mindset with their vendor and shoring up long-term transition from project mode to maintenance mode. ResponsibilitiesResponsible for documenting business requirements that are clear, unambiguous, testable, and satisfy the business need in accordance with standard templates and adherence to policies, standards, and guidelines. Creating Test plans with the business, ensuring repeatable processes are in place beyond the lifecycle of the current project. Documenting repeatable steps/processes (technical documentation) for the business area to refer to as part of maintenance planning. Responsible for facilitating requirement gathering meetings to identify impacted business processes and document the project business requirements. Attendees include relevant project team members and stakeholders as identified in the Communication Plan.Responsible for adhering to the project schedule by developing and maintaining the project backlog during Agile projects and working with the product owner to set priority throughout the duration of project.Responsible for understanding project scope and actively monitoring requirements process to maintain adherence to the objectives set for the project.Responsible for understanding high-level information governance objectives and ensuring appropriate Stakeholder inclusion and/or awareness regarding data requirements.Responsible for appropriate resolution of critical IT issues as it pertains to the BA role.Responsible for understanding project specific benefits and related impact of changes to project scope or business requirements.Ensures SEM (system engineering methodology) deliverables for the project that are a responsibility of the BA are completed, reviewed, an</t>
+          <t>Apex Systems is seeking a Post Market Complaint Analyst to support a clients Hearing Enhancement and wearable technology programs. This role will focus on post-market surveillance (PMS), complaint investigations, and customer quality activities supporting regulated products. The ideal candidate will have experience handling product complaints, conducting root cause investigations, supporting CAPA activities, and working within a Quality Management System in a regulated environment.Logistical Details:Contract Length: 12 monthsPay Rate: $35-$40/hrLocation: Burlingame, CA (onsite, relocation considered)ResponsibilitiesReview, triage, investigate, and document customer and product complaints.Support post-market surveillance (PMS) activities for Hearing Enhancement products.Manage and track first-party store complaints and customer escalations.Assist with complaint trend analysis and reporting.Support CAPA investigations and root cause analysis activities.Maintain complaint records and documentation in accordance with quality system requirements.Partner with Quality, Engineering, Product, and Operations teams to ensure timely complaint resolution.Support SOP, work instruction, and quality record updates as needed.Assist with audits and quality compliance initiatives.Required Qualifications1-4 years of experience in Quality, Complaint Handling, Customer Quality, Product Quality, or Post Market Surveillance.Experience investigating product complaints or customer escalations.Familiarity with CAPA and root cause analysis methodologies.Experience working with quality systems, document management systems, or complaint management tools.Strong organizational and communication skills.Experience supporting consumer electronics, medical devices, wearables, or technology products preferred.Preferred QualificationsKnowledge of ISO 13485 and/or FDA quality regulations.Experience supporting regulated products.Experience with data analysis and trend reporting.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy p</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4772,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Manufacturing Analyst 1</t>
+          <t>Post Market Analyst Lead</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Palmdale, CA, 93550, US</t>
+          <t>Burlingame, CA, 94010, US</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4802,7 +4792,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4817,7 +4807,7 @@
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3044545_usa/manufacturing-analyst-1</t>
+          <t>https://www.apexsystems.com/job/3045582_usa/post-market-analyst-lead</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -4830,17 +4820,17 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>553d01a264e0e332c14d</t>
+          <t>8cd6b009e669aad1a2b8</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Manufacturing Analyst 1Location: Palmdale, California (Onsite) Role OverviewThis organization is seeking a Manufacturing Analyst to join a team of qualified, diverse individuals. This position involves supporting production, business, and other processes in a team-based manufacturing environment. The role includes performing activities in various cross-functional areas, including production planning and control, quality management, systems, manufacturing, equipment and facilities engineering, material management, and process reengineering. Key ResponsibilitiesTrack daily costs and administer earned value management activities.Maintain visibility charts and provide weekly and monthly status reports.Close and document tool orders for assembly tooling.Oversee the validation of incoming materials against the bill of material.Develop internal tooling packages.Liaise with support organizations to negotiate schedules.Order and record chemical usage, ensuring proper inventory within tracking systems.Manage tool control and accountability activities, including inventory, audits, and asset management.Handle technical administrative tasks such as certification compliance, meeting support, and team engagement.Required QualificationsEducation: A Bachelor's degree with 3 years of experience, a Master's Degree with 1 year of experience, or 7 years of relevant experience in lieu of a degree. Experience: Experience in a manufacturing environment.Cost account management experience. Technical Skills: Intermediate to Advanced Microsoft Suite capabilities (Excel, PowerPoint, Word). Must be highly detail-oriented, organized, proactive, and a skilled communicator. Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee st</t>
+          <t>Apex Systems is seeking a Post Market Complaint Lead to support wearable technology initiatives. This individual will serve as a key resource for complaint management, post-market surveillance (PMS), complaint trending, and customer quality activities supporting regulated consumer technology products.The Complaint Lead will focus on Hearing Enhancement complaint management and serve as a primary quality contact for complaint investigations, PMS reporting, and issue escalation activities. This role requires a strong understanding of complaint handling processes, root cause investigations, CAPA, and quality system compliance.Additional DetailsJob Title: Post Market Compliant LeadContract Length: 12 monthsPay Rate: $40-$50/hrLocation: Burlingame, CA (onsite, relocation considered)ResponsibilitiesLead complaint handling and post-market surveillance activities for Hearing Enhancement products.Review, triage, investigate, and resolve product complaints from initiation through closure.Manage and oversee first-party (1P) store complaint activities.Conduct complaint trending analysis and provide reports to quality leadership.Drive root cause investigations and support CAPA development.Maintain complaint records and ensure compliance with quality system requirements.Support SOP development, process improvements, and quality documentation updates.Partner closely with Engineering, Product, Human Factors, Risk Management, and Regulatory teams.Provide expertise related to complaint management, PMS, and associated quality processes.Required Qualifications2-5+ years of experience in Complaint Handling, Post Market Surveillance, Customer Quality, Product Quality, or regulated quality systems.Experience conducting complaint investigations and root cause analysis.Experience supporting CAPA and quality process improvement activities.Strong understanding of quality documentation and compliance requirements.Experience presenting complaint trends, metrics, and quality insights.Ability to work independently and manage multiple priorities.Preferred QualificationsExperience supporting wearables, hearing enhancement products, consumer electronics, or medical devices.Knowledge of ISO 13485, FDA Quality System Regulations, or regulated product environments.Experience with complaint management systems, PLM tools, or eQMS platforms.Familiarity with risk management and human factors activities.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as p</t>
         </is>
       </c>
     </row>
@@ -4852,17 +4842,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Member Account Protection Analyst</t>
+          <t>QA Testing Analyst (Python)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anaheim, CA, 92807, US</t>
+          <t>Columbus, OH, 43219, US</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4872,7 +4862,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4887,7 +4877,7 @@
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046147_usa/member-account-protection-analyst</t>
+          <t>https://www.apexsystems.com/job/3045421_usa/qa-testing-analyst-python</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4900,17 +4890,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>5a3a7c9c2c0570efa20f</t>
+          <t>d7e183b6db9caf8441eb</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Member Account Protection AnalystLocation: Anaheim, California (Hybrid)Contract: Through 10/31/26Role OverviewOur organization is seeking a Member Account Protection Analyst to support fraud prevention, investigations, and dispute resolution activities. This individual will review fraud alerts, investigate suspicious account activity, manage card-related fraud claims, and support payment network investigations. The role is responsible for minimizing fraud losses while ensuring compliance with regulatory requirements and internal procedures. Key ResponsibilitiesReview and investigate fraud alerts and suspicious account activity.Manage ATM, debit card, and credit card fraud claims.Support ACH and person-to-person payment investigations.Assist with Regulation E dispute processing.Independently manage a pipeline of fraud cases and disputes.Maintain compliance with regulatory requirements and internal procedures.Provide a high level of customer service.Required QualificationsExperience in banking or credit union environments.Experience with ATM, debit card, and credit card fraud claims or investigations.Demonstrated experience in fraud investigations, claims, or disputes.Strong communication and customer service skills.Preferred QualificationsExperience with Zelle investigations.Experience with FDR, First Track, and/or Fiserv systems.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions</t>
+          <t>QA Testing Analyst (Python)\nLocation: Columbus, OH (Onsite)\n \nRole Overview\nWe are looking for an experienced QA Automation Engineer with strong hands-on experience in Python, Pytest, and API automation testing. The candidate will be responsible for analyzing requirements, developing and maintaining automation test scripts, executing functional and integration tests, analyzing failures, managing defects, and supporting software releases. The candidate should have experience across the complete automation-testing lifecycle and should be capable of working independently with development, business, and testing teams.\n \nKey Responsibilities\nAnalyze business, functional, and technical requirements and create appropriate test scenarios and test cases.Design, develop, and maintain automated test scripts using Python and Pytest.Develop and maintain reusable automation-framework components, fixtures, utilities, and test data.Perform REST API testing and automate API test cases.Validate API requests, responses, status codes, headers, JSON/XML payloads, and error scenarios.Perform functional, integration, regression, system, and end-to-end testing.Test APIs routed through an API gateway and validate integrations with downstream systems.Validate authentication and authorization scenarios, including OAuth, JWT, bearer tokens, and 401/403 responses.Identify, document, track, and retest defects.Collaborate with developers, business analysts, product owners, and other testing-team members.\nRequired Qualifications\nEducation: Bachelor’s degree in computer science, Information Systems, Engineering, or a related field, or equivalent professional experience.\n \nExperience: Minimum five years of hands-on automation-testing experience.\n \nTechnical Skills: Strong programming experience in Python and hands-on experience with Pytest. Experience developing and maintaining automation frameworks, along with REST API testing and automation experience using libraries such as requests. Hands-on experience with Postman or SoapUI, JSON/XML validation, and CI/CD platforms like Jenkins. Experience with test-reporting tools such as Allure or Pytest HTML. Experience with API gateway, downstream-system integration testing, SQL, database validation, and Git or another source-control system is required.\n \nPreferred Qualifications\nExperience with JMeter or another performance-testing tool.Knowledge of TDD or ATDD practices.Experience testing cloud-based or containerized applications.Experience with microservices and complex system integrations.Relevant testing certifications are an added advantage.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is r</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4912,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Operations Support Analyst - ATM</t>
+          <t>QMS Analyst</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Louis, MO, 63101-2510, US</t>
+          <t>Burlingame, CA, 94010, US</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4942,7 +4932,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4957,7 +4947,7 @@
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046305_usa/operations-support-analyst---atm</t>
+          <t>https://www.apexsystems.com/job/3045579_usa/qms-analyst</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -4970,17 +4960,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>c6f5e933e9fefe3054d1</t>
+          <t>3aa197b7523dd3f618ef</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Operations Support Analyst - ATM\nLocation: Saint Louis, Missouri (Onsite)\n \nRole Overview\nWe are seeking an Operations Support Analyst for an ATM Operations Level 1 support role. This position is responsible for the day-to-day operations of the technology platform, focusing on problem and incident management, release deployment, application monitoring, and service analytics. The analyst will identify potential production failure scenarios, create incident and enhancement tickets, and communicate with internal operations teams.\n \nKey Responsibilities\nProvide phone queue support for ATM operational issues, comprising approximately 75% of daily activities.Perform technical recovery of ATMs, accounting for about 25% of daily tasks.Take ownership of escalations, performing troubleshooting, analysis, and resolution using query and programming skills.Identify ATM production failure scenarios and create incident, enhancement, or problem tickets.Perform analytical, technical, and administrative work to support new and existing equipment and software.Interpret, evaluate, and resolve issues related to the functional operation of technology products.Navigate multiple applications simultaneously to support operational needs.\n \nRequired Qualifications\nExperience:\nExperience in a technical support, helpdesk, ATM servicing, or electronic banking operational role.Proven ability to troubleshoot issues to maintain network stability.Strong customer service skills with excellent verbal and written communication.\nTechnical Skills:\nProficiency with the Microsoft Office Suite.Familiarity with Jira and Splunk is beneficial.\n \nPreferred Qualifications\nPrevious knowledge of ATM systems.Experience with root cause analysis and troubleshooting.Proficiency with telephone systems, as the majority of the day will be spent on telecom support.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of</t>
+          <t>Apex Systems is seeking a Quality System Analyst to support a clients Hearing Enhancement and wearable technology programs. This role will focus on post-market surveillance (PMS), complaint investigations, and customer quality activities supporting regulated products. The ideal candidate will have experience handling product complaints, conducting root cause investigations, supporting CAPA activities, and working within a Quality Management System in a regulated environment.Job Title: Quality System AnalystContract Length: 12 monthsPay Rate: $35-$40/hrLocation: Burlingame, CA (onsite, relocation considered)Job Overview:As Quality System Analyst, you will take on a critical role in bringing medical device compliance to our AR/VR products. You will work side-by-side with quality, engineering and business teams that are leading innovation in this exciting new product category.The Quality System Analyst will support product programs by executing / implementing Standard Operating Procedures, Work Instructions, and Records from product concept through obsolescence. The Quality System Analyst has knowledge and experience working in regulated environments (i.e. ISO 13485, US FDA QSR/820) and sufficient knowledge and experience to be able to operate with minimal supervision. You are flexible, responsive, detail oriented, hands-on and able to manage competing demands.Responsibilities:● Support Labs Quality Management System quality system needs, including the execution of processes such as document management, CSV processing, nonconformance, CAPA, supplier qualification and monitoring, process monitoring, internal audits and medical device product complaint management.● Create and release complaint quality system SOPs, WI, Templates and records based to support business needs for new product introduction and product sustainment.● Ensure documentation and data related to the requirements of the Quality System are controlled in a manner which ensures integrity and accessibility● Collaboratively communicate quality system requirements between Operations, Supply Chain and Engineering to facilitate compliance to applicable medical devices standards● Maintenance of all applicable records such as validation reports, test reports, exit reviews, test results, as defined by applicable regulations and standards● Support audits by external bodies for licensure and accreditation documents submission● Manage and organize complex projects and priorities, solve problems that impact release progress and provide detailed information to cross functional teams● Support the implementation of new eQMSMinimum Qualifications● 5+ years of related experience in a high tech, fast paced, consumer electronics environment managing medical device Quality Management System documentation and resulting records● Experience with Teamcenter or related PLM/Document Management systems● Experience working on a regulated Medical Device environment● Familiarity with Google Suite● Familiarity with</t>
         </is>
       </c>
     </row>
@@ -4992,27 +4982,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Order Analyst IV</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, 77046, US</t>
+          <t>Mississauga, ON, L4Z 1S1, CA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FullTime</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5027,7 +5017,7 @@
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3043997_usa/order-analyst-iv</t>
+          <t>https://www.apexsystems.com/job/3045452_usa/senior-data-architect</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -5040,17 +5030,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>f2a07af249fdd58c0ced</t>
+          <t>87b29a66fb6b651a6da0</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Senior Division Order AnalystLocation: Houston, Texas (Onsite 3 days/week) Role OverviewWe are seeking a seasoned Division Order Analyst for a role based in Houston, TX. The position involves facilitating the distribution of proceeds from oil and gas sales and the collection of well expenses. This role is focused on maintenance items within the EOR region and requires a candidate who can navigate complex title structures. Key ResponsibilitiesFacilitate the distribution of proceeds from oil and gas sales and the collection of well expenses.Determine the relative ownership of the company, working interest partners, and royalty holders by analyzing title documents.Maintain and update ownership records for the assigned EOR region.Handle maintenance items related to the EOR asset.Required QualificationsOwnership maintenanceComplex title analysisRevenue and royalty ownership calculationsWorking Interest and ORRI ownershipUnitized and EOR propertiesAdvanced Excel reporting and analysisEverforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access to certification prep and a library of technical and leadership courses/books/seminars once you have 6+ months of tenure, and certification discounts and other perks to associations that inclu</t>
+          <t>Senior Data ArchitectLocation: Mississauga/Toronto (Hybrid)Type: Permanent, Full‑Time Position SummaryThe Senior Data Architect is responsible for designing, implementing, and governing enterprise‑level data solutions that support multiple concurrent initiatives. This role provides architectural leadership across the full data lifecycle, including discovery, modeling, integration, governance, and performance optimization - while ensuring that all solutions are scalable, secure, and aligned to organizational standards. Key ResponsibilitiesData Architecture &amp; DesignLead end‑to‑end data architecture activities including requirements analysis, conceptual/logical/physical modeling, and solution design.Develop scalable architectures for modern data platforms, including cloud-based data warehouses and relational databases.Produce high‑quality architecture documentation, data models, and DDL artifacts.Data Integration &amp; EngineeringDefine and support ETL/ELT patterns that ensure quality, integrity, and performance across data pipelines.Collaborate with development, DBA, and engineering teams to enable seamless integration across systems.Optimize data structures, queries, pipelines, and storage strategies.Governance, Quality &amp; SecurityEmbed data governance principles into all designs, including metadata, lineage, standards, access, and data residency requirements.Ensure solutions comply with organizational security and quality expectations.Review and approve data‑related production changes to safeguard operational stability.Cross‑Functional CollaborationWork closely with project managers, developers, business analysts, architects, and leadership to deliver cohesive end‑to‑end solutions.Participate in planning, estimation, solution reviews, and technical governance forums.Communicate complex technical concepts clearly to both technical and non‑technical stakeholders.Strategic &amp; Enterprise ContributionContribute to the definition and refinement of enterprise data architecture standards, patterns, and best practices.Support continuous improvement of data platform capabilities and architectural maturity.Required Qualifications7+ years of experience in data architecture or related disciplines.Strong SQL skills and expertise in designing logical and physical data models.Hands‑on experience with cloud-based data warehouse platforms.Experience with modern ETL/ELT integration tools.Understanding of data governance, data quality frameworks, and data residency requirements.Experience supporting or enabling data for analytics, machine learning, or AI initiatives.Excellent communication, documentation, and stakeholder engagement skills.Experience with tools such as Snowflake and experience in Cloud Data ArchitectureExperience with AWS or Azure Preferred QualificationsExperience with PostgreSQL or additional relational database technologies.Certifications such as TOGAF, CDP, Snowflake certifications, or cloud architect credentials.Experience operating within large, mult</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5052,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Post Market Analyst</t>
+          <t>Senior Data Engineer / ETL Developer - NC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Burlingame, CA, 94010, US</t>
+          <t>Charlotte, NC, 28202, US</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5097,7 +5087,7 @@
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045581_usa/post-market-analyst</t>
+          <t>https://www.apexsystems.com/job/3045999_usa/senior-data-engineer--etl-developer---nc</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -5110,17 +5100,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>bd67c2345ef96be8792b</t>
+          <t>0799ec4b6ac4fe1619f5</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Apex Systems is seeking a Post Market Complaint Analyst to support a clients Hearing Enhancement and wearable technology programs. This role will focus on post-market surveillance (PMS), complaint investigations, and customer quality activities supporting regulated products. The ideal candidate will have experience handling product complaints, conducting root cause investigations, supporting CAPA activities, and working within a Quality Management System in a regulated environment.Logistical Details:Contract Length: 12 monthsPay Rate: $35-$40/hrLocation: Burlingame, CA (onsite, relocation considered)ResponsibilitiesReview, triage, investigate, and document customer and product complaints.Support post-market surveillance (PMS) activities for Hearing Enhancement products.Manage and track first-party store complaints and customer escalations.Assist with complaint trend analysis and reporting.Support CAPA investigations and root cause analysis activities.Maintain complaint records and documentation in accordance with quality system requirements.Partner with Quality, Engineering, Product, and Operations teams to ensure timely complaint resolution.Support SOP, work instruction, and quality record updates as needed.Assist with audits and quality compliance initiatives.Required Qualifications1-4 years of experience in Quality, Complaint Handling, Customer Quality, Product Quality, or Post Market Surveillance.Experience investigating product complaints or customer escalations.Familiarity with CAPA and root cause analysis methodologies.Experience working with quality systems, document management systems, or complaint management tools.Strong organizational and communication skills.Experience supporting consumer electronics, medical devices, wearables, or technology products preferred.Preferred QualificationsKnowledge of ISO 13485 and/or FDA quality regulations.Experience supporting regulated products.Experience with data analysis and trend reporting.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy p</t>
+          <t>Job Title: Senior Data Engineer / ETL DeveloperLocations: Charlotte, NCWork Arrangement: Fully onsite, 5 days per weekContract: 12 months, with potential conversionBill Rate: $53/hr- $57/hrNote: We are not able to consider C2C or third-party submissions Role OverviewThis is a hands-on Senior Data Engineer / ETL Developer role supporting the Home Lending Data &amp; Insights team. The selected consultant will support the Core Downstream application, which receives and processes mortgage application data. This role focuses on consolidating data from multiple repositories, cleansing and transforming it, and delivering trusted data assets to business consumers while combining traditional enterprise ETL development with cloud modernization initiatives. Key ResponsibilitiesBuild and maintain scalable batch and near real-time data pipelines.Develop ETL solutions using Ab Initio, Python, PySpark, SQL, and PL/SQL.Review technical designs and convert solution blueprints into reusable code.Integrate, cleanse, normalize, and transform data from multiple mortgage-related systems.Partner with Product Owners, Architects, Engineers, and business stakeholders.Support migration and modernization initiatives from legacy platforms to Google Cloud.Build, schedule, orchestrate, and deploy solutions through enterprise CI/CD pipelines.Support monitoring, operational excellence, root cause analysis, and production reliability.Required Qualifications4+ years of Data Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, training, military experience, or education.4+ years of PL/SQL and SQL skills with proven experience in Oracle, Teradata, Python and/or BigQuery, including complex query development, tuning, and debugging.4+ years of Ab Initio skills with proven experience to build complex graphs, Psets, and perform performance tuning.3+ years of programming skills in Python; hands-on PySpark for distributed data processing.3+ years of ETL/ETL design, data warehousing concepts, and data modeling best practices.Preferred QualificationsFinancial Services or Mortgage industry experience.Production operations experience: monitoring, SLAs, incident response, root cause analysis, and performance optimization.Experience working in hybrid environments (on-prem + cloud) and supporting data migration/modernization initiatives.Experience with scheduling/orchestration in Autosys and Airflow-based orchestration (Cloud Composer direction).Experience with Git-based workflows, code reviews, and automated testing practices for data pipelines.Experience with Harness, Jenkins, and uDeploy based CICD environments.Practical experience using AI-assisted coding tools in daily development.Ab Initio development/maintenance experience and/or hands-on migration of Ab Initio graphs to modern Spark/SQL patterns.Experience with Dataplex and broader data governance concepts.Experience with Informatica Data Quality implementation patterns.Experience</t>
         </is>
       </c>
     </row>
@@ -5132,17 +5122,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Post Market Analyst Lead</t>
+          <t>Senior Database Administrator &amp; Data Modeler</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Burlingame, CA, 94010, US</t>
+          <t>Toronto, ON, M5H 4C7, CA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5152,7 +5142,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5167,7 +5157,7 @@
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045582_usa/post-market-analyst-lead</t>
+          <t>https://www.apexsystems.com/job/3045662_usa/senior-database-administrator--data-modeler</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -5180,17 +5170,17 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>8cd6b009e669aad1a2b8</t>
+          <t>2e1804568b815c466cef</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Apex Systems is seeking a Post Market Complaint Lead to support wearable technology initiatives. This individual will serve as a key resource for complaint management, post-market surveillance (PMS), complaint trending, and customer quality activities supporting regulated consumer technology products.The Complaint Lead will focus on Hearing Enhancement complaint management and serve as a primary quality contact for complaint investigations, PMS reporting, and issue escalation activities. This role requires a strong understanding of complaint handling processes, root cause investigations, CAPA, and quality system compliance.Additional DetailsJob Title: Post Market Compliant LeadContract Length: 12 monthsPay Rate: $40-$50/hrLocation: Burlingame, CA (onsite, relocation considered)ResponsibilitiesLead complaint handling and post-market surveillance activities for Hearing Enhancement products.Review, triage, investigate, and resolve product complaints from initiation through closure.Manage and oversee first-party (1P) store complaint activities.Conduct complaint trending analysis and provide reports to quality leadership.Drive root cause investigations and support CAPA development.Maintain complaint records and ensure compliance with quality system requirements.Support SOP development, process improvements, and quality documentation updates.Partner closely with Engineering, Product, Human Factors, Risk Management, and Regulatory teams.Provide expertise related to complaint management, PMS, and associated quality processes.Required Qualifications2-5+ years of experience in Complaint Handling, Post Market Surveillance, Customer Quality, Product Quality, or regulated quality systems.Experience conducting complaint investigations and root cause analysis.Experience supporting CAPA and quality process improvement activities.Strong understanding of quality documentation and compliance requirements.Experience presenting complaint trends, metrics, and quality insights.Ability to work independently and manage multiple priorities.Preferred QualificationsExperience supporting wearables, hearing enhancement products, consumer electronics, or medical devices.Knowledge of ISO 13485, FDA Quality System Regulations, or regulated product environments.Experience with complaint management systems, PLM tools, or eQMS platforms.Familiarity with risk management and human factors activities.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as p</t>
+          <t>Summary: We are in search of an experienced Senior Database Administrator &amp; Data Modeler to spearhead a critical new development project involving the rewrite of a legacy system for a prominent financial client. This role demands expertise in analyzing existing databases, deciphering complex logic, and crafting new, performance-driven data models aligned with evolving business needs. The ideal candidate will play a pivotal role in ensuring the creation of robust, auditable, and compliant data controls within the system.Responsibilities:· Conduct in-depth analysis of the existing database architecture, decipher complex logic, and understand legacy data models.· Collaborate closely with business stakeholders to elicit, understand, and translate evolving business requirements into effective and scalable database solutions.· Design and create new data models aligned with iterative business needs, ensuring optimal performance and adherence to best practices.· Lead the development of database schemas, tables, procedures, and controls to ensure data integrity, performance, and auditability.· Implement rigorous data controls, ensuring compliance with regulatory standards and internal security policies.· Work iteratively, adapting, and refining data models based on evolving business requirements throughout the development lifecycle.· Provide mentorship and guidance to the development team, ensuring alignment with best data modeling practices.· Collaborate effectively with cross-functional teams in an Agile environment, utilizing tools like Jira, Confluence, and Gliffy for documentation and workflows. Requirements:· Bachelor's degree in computer science, Information Technology, or related field.· 8-10 years of extensive experience in SQL Server DBA, data modeling, and management, focusing on large-scale development projects, particularly in financial environments.· Expertise in:o Data migration, ETL (Extract Transform Load), and integration services, including SSIS.o Reporting services like SSRS and Tableau for visualization/report creation.o Data analysis, data quality, and proficient data modeling.o Test automation tools and techniques for SQL databases.o Microsoft Full Stack technologies: .NET, C#, ASP.NET, MVC, and Web API.o Control-M is a plus.· Proven record of accomplishment in:o Designing and implementing high-performance, auditable data models aligned with evolving business needs.o Understanding and implementing data controls, regulatory compliance, and security measures in financial systems.· Advantageous:o Familiarity with cloud databases and full-stack technologies (such as .NET, C#).· Excellent analytical, problem-solving, and proactive communication skills, coupled with a collaborative approach.· Strong organizational and time management skills.· Ability to work in a high-pressure, deadline-driven environment.· Demonstrated experience in applying DevSecOps best practices within an Agile software development environmentThis role presents a uni</t>
         </is>
       </c>
     </row>
@@ -5202,17 +5192,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QA Testing Analyst (Python)</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant - NC, MN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, 43219, US</t>
+          <t>Charlotte, NC, 28277, US</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5222,7 +5212,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5237,7 +5227,7 @@
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045421_usa/qa-testing-analyst-python</t>
+          <t>https://www.apexsystems.com/job/3046156_usa/senior-power-bi--gcp-data-analytics-consultant---nc-mn</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -5250,17 +5240,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>d7e183b6db9caf8441eb</t>
+          <t>26fd44882744fc38daec</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>QA Testing Analyst (Python)\nLocation: Columbus, OH (Onsite)\n \nRole Overview\nWe are looking for an experienced QA Automation Engineer with strong hands-on experience in Python, Pytest, and API automation testing. The candidate will be responsible for analyzing requirements, developing and maintaining automation test scripts, executing functional and integration tests, analyzing failures, managing defects, and supporting software releases. The candidate should have experience across the complete automation-testing lifecycle and should be capable of working independently with development, business, and testing teams.\n \nKey Responsibilities\nAnalyze business, functional, and technical requirements and create appropriate test scenarios and test cases.Design, develop, and maintain automated test scripts using Python and Pytest.Develop and maintain reusable automation-framework components, fixtures, utilities, and test data.Perform REST API testing and automate API test cases.Validate API requests, responses, status codes, headers, JSON/XML payloads, and error scenarios.Perform functional, integration, regression, system, and end-to-end testing.Test APIs routed through an API gateway and validate integrations with downstream systems.Validate authentication and authorization scenarios, including OAuth, JWT, bearer tokens, and 401/403 responses.Identify, document, track, and retest defects.Collaborate with developers, business analysts, product owners, and other testing-team members.\nRequired Qualifications\nEducation: Bachelor’s degree in computer science, Information Systems, Engineering, or a related field, or equivalent professional experience.\n \nExperience: Minimum five years of hands-on automation-testing experience.\n \nTechnical Skills: Strong programming experience in Python and hands-on experience with Pytest. Experience developing and maintaining automation frameworks, along with REST API testing and automation experience using libraries such as requests. Hands-on experience with Postman or SoapUI, JSON/XML validation, and CI/CD platforms like Jenkins. Experience with test-reporting tools such as Allure or Pytest HTML. Experience with API gateway, downstream-system integration testing, SQL, database validation, and Git or another source-control system is required.\n \nPreferred Qualifications\nExperience with JMeter or another performance-testing tool.Knowledge of TDD or ATDD practices.Experience testing cloud-based or containerized applications.Experience with microservices and complex system integrations.Relevant testing certifications are an added advantage.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is r</t>
+          <t>Client: Financial ServicesJob Title: Systems Architect 4 – ContingentRole: Senior Power BI &amp; GCP Data Analytics ConsultantLocations: Charlotte, NC preferred; Minneapolis, MN secondaryEngagement: Full-time ContractorDuration: 6 Months, with Possible ExtensionStart Date: ImmediateBill Rate: $69 - $74Top Requirements5+ years of hands-on Power BI development3+ years of Google Cloud Platform and BigQuery experienceAdvanced Power BI, DAX, Power Query, SQL, and data-modeling skillsETL/ELT, data integration, and scalable analytics-pipeline experienceExecutive dashboard, KPI, and operational reporting experiencePlussesHuman-in-the-Loop analyticsAI Operations or Process Intelligence experienceStatistical Process Control and control-chart developmentPython and API integrationData governance and metadata managementProcess mining or workflow analyticsLean, Six Sigma, or Operational Excellence experienceFinancial-services or other regulated-industry experienceJob SummaryIn this contingent resource assignment, you will consult on complex initiatives with broad impact and large-scale planning for Systems Architecture. This role will design and deliver enterprise analytics, reporting, data-ingestion, and operational-control solutions that support business intelligence, process intelligence, and Human-in-the-Loop programs.The Senior Power BI &amp; GCP Data Analytics Consultant will translate enterprise data into actionable insights through executive dashboards, KPI frameworks, automated GCP pipelines, and Statistical Process Control reporting. The consultant will work across business, engineering, product, data governance, and process-management teams to deliver scalable, governed, and reliable analytics capabilities.Day-to-Day ResponsibilitiesPower BI &amp; Executive ReportingDesign, develop, and maintain enterprise-grade Power BI dashboards and scorecardsCreate executive, operational, and strategic reporting solutionsBuild complex:Data ModelsSemantic LayersDAX MeasuresCalculationsPower Query TransformationsDevelop interactive visualizations highlighting performance trends, risks, exceptions, and improvement opportunitiesOptimize dashboard performance, user experience, and data-refresh processesEstablish reporting standards, governance, and technical documentationPrepare monthly and quarterly business review packagesGCP Data EngineeringDesign and optimize data-ingestion pipelines on Google Cloud PlatformDevelop ETL and ELT processes using data from:Enterprise ApplicationsAPIsOperational SystemsThird-Party SourcesBuild analytical datasets, reporting marts, and curated data assetsUse BigQuery and cloud-native services for scalable analyticsPerform data transformation, quality validation, reconciliation, and monitoringOptimize storage and processing architectures for performance and scalabilityKPI &amp; Performance AnalyticsPartner with stakeholders to define KPI frameworks and metric standardsDevelop executive scorecards and operational-health dashboardsDefine leading and lagg</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5262,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QMS Analyst</t>
+          <t>Senior Unconventional Analytics Engineer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Burlingame, CA, 94010, US</t>
+          <t>Spring, TX, 77389, US</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5307,7 +5297,7 @@
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045579_usa/qms-analyst</t>
+          <t>https://www.apexsystems.com/job/3046017_usa/senior-unconventional-analytics-engineer</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -5320,49 +5310,49 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>3aa197b7523dd3f618ef</t>
+          <t>617af8d54f95bd8a9540</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Apex Systems is seeking a Quality System Analyst to support a clients Hearing Enhancement and wearable technology programs. This role will focus on post-market surveillance (PMS), complaint investigations, and customer quality activities supporting regulated products. The ideal candidate will have experience handling product complaints, conducting root cause investigations, supporting CAPA activities, and working within a Quality Management System in a regulated environment.Job Title: Quality System AnalystContract Length: 12 monthsPay Rate: $35-$40/hrLocation: Burlingame, CA (onsite, relocation considered)Job Overview:As Quality System Analyst, you will take on a critical role in bringing medical device compliance to our AR/VR products. You will work side-by-side with quality, engineering and business teams that are leading innovation in this exciting new product category.The Quality System Analyst will support product programs by executing / implementing Standard Operating Procedures, Work Instructions, and Records from product concept through obsolescence. The Quality System Analyst has knowledge and experience working in regulated environments (i.e. ISO 13485, US FDA QSR/820) and sufficient knowledge and experience to be able to operate with minimal supervision. You are flexible, responsive, detail oriented, hands-on and able to manage competing demands.Responsibilities:● Support Labs Quality Management System quality system needs, including the execution of processes such as document management, CSV processing, nonconformance, CAPA, supplier qualification and monitoring, process monitoring, internal audits and medical device product complaint management.● Create and release complaint quality system SOPs, WI, Templates and records based to support business needs for new product introduction and product sustainment.● Ensure documentation and data related to the requirements of the Quality System are controlled in a manner which ensures integrity and accessibility● Collaboratively communicate quality system requirements between Operations, Supply Chain and Engineering to facilitate compliance to applicable medical devices standards● Maintenance of all applicable records such as validation reports, test reports, exit reviews, test results, as defined by applicable regulations and standards● Support audits by external bodies for licensure and accreditation documents submission● Manage and organize complex projects and priorities, solve problems that impact release progress and provide detailed information to cross functional teams● Support the implementation of new eQMSMinimum Qualifications● 5+ years of related experience in a high tech, fast paced, consumer electronics environment managing medical device Quality Management System documentation and resulting records● Experience with Teamcenter or related PLM/Document Management systems● Experience working on a regulated Medical Device environment● Familiarity with Google Suite● Familiarity with</t>
+          <t>Senior Unconventional Analytics EngineerLocation: Spring, TX (On-Site)Organization: Unconventional ResourcesAbout the RoleWe are seeking a Senior Unconventional Analytics Engineer to ensure data-driven decision making are intuitive and reliable across our Unconventional organization.Over the past two years, our team has developed forecasting, economic, and operational analytics solutions leveraging Databricks, ComboCurve, and Spotfire. While these tools provide significant value, their effectiveness depends on consistent, trusted, and easily accessible data.This role will focus on building and managing the data products that power our forecasting, economics, planning, and operational workflows. The successful candidate will work closely with reservoir engineers, production engineers, planners, economists, and data professionals to ensure critical business data is reliable, governed, automated, and readily available for analytics and decision support.Key ResponsibilitiesData Product OwnershipDesign, develop, and maintain analytics-ready data products supporting forecasting, economics, planning, drilling, completions, and production workflows.Establish trusted datasets and business logic that serve as authoritative sources for key analytical processes.Partner with business stakeholders to prioritize data product enhancements and new capabilities.Databricks Data EngineeringDevelop scalable data pipelines and transformation processes within Databricks using SQL and Python.Integrate data from operational, corporate, and third-party sources into a unified analytical environment.Optimize data models and architectures to improve performance, usability, and scalability.Implement automated workflows that reduce manual data preparation and spreadsheet-based processes.ComboCurve Integration &amp; EnablementSupport and enhance data flows feeding ComboCurve forecasting and economic workflows.Ensure forecasting and economic analyses are based on consistent, validated, and auditable datasets.Collaborate with engineers and economists to streamline data preparation and model execution.Improve traceability and transparency of inputs used in forecasting and economic evaluations.Spotfire Analytics EnablementDevelop and maintain curated datasets optimized for Spotfire dashboards and self-service analytics.Partner with stakeholders to improve data accessibility and visualization capabilities.Ensure consistency between Spotfire reporting, ComboCurve outputs, and enterprise data sources.Enable users to gain insights quickly through well-designed analytical data structures.Data Quality &amp; GovernanceEstablish data quality standards, validation rules, and monitoring processes.Identify and resolve data inconsistencies across systems and workflows.Develop business metadata, documentation, lineage, and governance practices.Promote a culture of data accountability and continuous improvement.Required QualificationsTechnical ExpertiseBachelor's degree in Engineering, Computer Science,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mississauga, ON, L4Z 1S1, CA</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FullTime</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5377,7 +5367,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045452_usa/senior-data-architect</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131997/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -5385,54 +5375,54 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>87b29a66fb6b651a6da0</t>
+          <t>50fd2fdb0dc885a55d37</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Senior Data ArchitectLocation: Mississauga/Toronto (Hybrid)Type: Permanent, Full‑Time Position SummaryThe Senior Data Architect is responsible for designing, implementing, and governing enterprise‑level data solutions that support multiple concurrent initiatives. This role provides architectural leadership across the full data lifecycle, including discovery, modeling, integration, governance, and performance optimization - while ensuring that all solutions are scalable, secure, and aligned to organizational standards. Key ResponsibilitiesData Architecture &amp; DesignLead end‑to‑end data architecture activities including requirements analysis, conceptual/logical/physical modeling, and solution design.Develop scalable architectures for modern data platforms, including cloud-based data warehouses and relational databases.Produce high‑quality architecture documentation, data models, and DDL artifacts.Data Integration &amp; EngineeringDefine and support ETL/ELT patterns that ensure quality, integrity, and performance across data pipelines.Collaborate with development, DBA, and engineering teams to enable seamless integration across systems.Optimize data structures, queries, pipelines, and storage strategies.Governance, Quality &amp; SecurityEmbed data governance principles into all designs, including metadata, lineage, standards, access, and data residency requirements.Ensure solutions comply with organizational security and quality expectations.Review and approve data‑related production changes to safeguard operational stability.Cross‑Functional CollaborationWork closely with project managers, developers, business analysts, architects, and leadership to deliver cohesive end‑to‑end solutions.Participate in planning, estimation, solution reviews, and technical governance forums.Communicate complex technical concepts clearly to both technical and non‑technical stakeholders.Strategic &amp; Enterprise ContributionContribute to the definition and refinement of enterprise data architecture standards, patterns, and best practices.Support continuous improvement of data platform capabilities and architectural maturity.Required Qualifications7+ years of experience in data architecture or related disciplines.Strong SQL skills and expertise in designing logical and physical data models.Hands‑on experience with cloud-based data warehouse platforms.Experience with modern ETL/ELT integration tools.Understanding of data governance, data quality frameworks, and data residency requirements.Experience supporting or enabling data for analytics, machine learning, or AI initiatives.Excellent communication, documentation, and stakeholder engagement skills.Experience with tools such as Snowflake and experience in Cloud Data ArchitectureExperience with AWS or Azure Preferred QualificationsExperience with PostgreSQL or additional relational database technologies.Certifications such as TOGAF, CDP, Snowflake certifications, or cloud architect credentials.Experience operating within large, mult</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / ETL Developer - NC</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28202, US</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5447,7 +5437,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045999_usa/senior-data-engineer--etl-developer---nc</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131996/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -5455,54 +5445,54 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0799ec4b6ac4fe1619f5</t>
+          <t>1739427c8572b9e16c54</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Job Title: Senior Data Engineer / ETL DeveloperLocations: Charlotte, NCWork Arrangement: Fully onsite, 5 days per weekContract: 12 months, with potential conversionBill Rate: $53/hr- $57/hrNote: We are not able to consider C2C or third-party submissions Role OverviewThis is a hands-on Senior Data Engineer / ETL Developer role supporting the Home Lending Data &amp; Insights team. The selected consultant will support the Core Downstream application, which receives and processes mortgage application data. This role focuses on consolidating data from multiple repositories, cleansing and transforming it, and delivering trusted data assets to business consumers while combining traditional enterprise ETL development with cloud modernization initiatives. Key ResponsibilitiesBuild and maintain scalable batch and near real-time data pipelines.Develop ETL solutions using Ab Initio, Python, PySpark, SQL, and PL/SQL.Review technical designs and convert solution blueprints into reusable code.Integrate, cleanse, normalize, and transform data from multiple mortgage-related systems.Partner with Product Owners, Architects, Engineers, and business stakeholders.Support migration and modernization initiatives from legacy platforms to Google Cloud.Build, schedule, orchestrate, and deploy solutions through enterprise CI/CD pipelines.Support monitoring, operational excellence, root cause analysis, and production reliability.Required Qualifications4+ years of Data Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, training, military experience, or education.4+ years of PL/SQL and SQL skills with proven experience in Oracle, Teradata, Python and/or BigQuery, including complex query development, tuning, and debugging.4+ years of Ab Initio skills with proven experience to build complex graphs, Psets, and perform performance tuning.3+ years of programming skills in Python; hands-on PySpark for distributed data processing.3+ years of ETL/ETL design, data warehousing concepts, and data modeling best practices.Preferred QualificationsFinancial Services or Mortgage industry experience.Production operations experience: monitoring, SLAs, incident response, root cause analysis, and performance optimization.Experience working in hybrid environments (on-prem + cloud) and supporting data migration/modernization initiatives.Experience with scheduling/orchestration in Autosys and Airflow-based orchestration (Cloud Composer direction).Experience with Git-based workflows, code reviews, and automated testing practices for data pipelines.Experience with Harness, Jenkins, and uDeploy based CICD environments.Practical experience using AI-assisted coding tools in daily development.Ab Initio development/maintenance experience and/or hands-on migration of Ab Initio graphs to modern Spark/SQL patterns.Experience with Dataplex and broader data governance concepts.Experience with Informatica Data Quality implementation patterns.Experience</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Senior Database Administrator &amp; Data Modeler</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Toronto, ON, M5H 4C7, CA</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5517,7 +5507,7 @@
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3045662_usa/senior-database-administrator--data-modeler</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131995/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -5525,39 +5515,39 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2e1804568b815c466cef</t>
+          <t>d61a9673a94652c8948d</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Summary: We are in search of an experienced Senior Database Administrator &amp; Data Modeler to spearhead a critical new development project involving the rewrite of a legacy system for a prominent financial client. This role demands expertise in analyzing existing databases, deciphering complex logic, and crafting new, performance-driven data models aligned with evolving business needs. The ideal candidate will play a pivotal role in ensuring the creation of robust, auditable, and compliant data controls within the system.Responsibilities:· Conduct in-depth analysis of the existing database architecture, decipher complex logic, and understand legacy data models.· Collaborate closely with business stakeholders to elicit, understand, and translate evolving business requirements into effective and scalable database solutions.· Design and create new data models aligned with iterative business needs, ensuring optimal performance and adherence to best practices.· Lead the development of database schemas, tables, procedures, and controls to ensure data integrity, performance, and auditability.· Implement rigorous data controls, ensuring compliance with regulatory standards and internal security policies.· Work iteratively, adapting, and refining data models based on evolving business requirements throughout the development lifecycle.· Provide mentorship and guidance to the development team, ensuring alignment with best data modeling practices.· Collaborate effectively with cross-functional teams in an Agile environment, utilizing tools like Jira, Confluence, and Gliffy for documentation and workflows. Requirements:· Bachelor's degree in computer science, Information Technology, or related field.· 8-10 years of extensive experience in SQL Server DBA, data modeling, and management, focusing on large-scale development projects, particularly in financial environments.· Expertise in:o Data migration, ETL (Extract Transform Load), and integration services, including SSIS.o Reporting services like SSRS and Tableau for visualization/report creation.o Data analysis, data quality, and proficient data modeling.o Test automation tools and techniques for SQL databases.o Microsoft Full Stack technologies: .NET, C#, ASP.NET, MVC, and Web API.o Control-M is a plus.· Proven record of accomplishment in:o Designing and implementing high-performance, auditable data models aligned with evolving business needs.o Understanding and implementing data controls, regulatory compliance, and security measures in financial systems.· Advantageous:o Familiarity with cloud databases and full-stack technologies (such as .NET, C#).· Excellent analytical, problem-solving, and proactive communication skills, coupled with a collaborative approach.· Strong organizational and time management skills.· Ability to work in a high-pressure, deadline-driven environment.· Demonstrated experience in applying DevSecOps best practices within an Agile software development environmentThis role presents a uni</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant - NC, MN</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28277, US</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5567,12 +5557,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5587,7 +5577,7 @@
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046156_usa/senior-power-bi--gcp-data-analytics-consultant---nc-mn</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131994/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -5595,54 +5585,54 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>26fd44882744fc38daec</t>
+          <t>5e2f686de97e73e9af36</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Client: Financial ServicesJob Title: Systems Architect 4 – ContingentRole: Senior Power BI &amp; GCP Data Analytics ConsultantLocations: Charlotte, NC preferred; Minneapolis, MN secondaryEngagement: Full-time ContractorDuration: 6 Months, with Possible ExtensionStart Date: ImmediateBill Rate: $69 - $74Top Requirements5+ years of hands-on Power BI development3+ years of Google Cloud Platform and BigQuery experienceAdvanced Power BI, DAX, Power Query, SQL, and data-modeling skillsETL/ELT, data integration, and scalable analytics-pipeline experienceExecutive dashboard, KPI, and operational reporting experiencePlussesHuman-in-the-Loop analyticsAI Operations or Process Intelligence experienceStatistical Process Control and control-chart developmentPython and API integrationData governance and metadata managementProcess mining or workflow analyticsLean, Six Sigma, or Operational Excellence experienceFinancial-services or other regulated-industry experienceJob SummaryIn this contingent resource assignment, you will consult on complex initiatives with broad impact and large-scale planning for Systems Architecture. This role will design and deliver enterprise analytics, reporting, data-ingestion, and operational-control solutions that support business intelligence, process intelligence, and Human-in-the-Loop programs.The Senior Power BI &amp; GCP Data Analytics Consultant will translate enterprise data into actionable insights through executive dashboards, KPI frameworks, automated GCP pipelines, and Statistical Process Control reporting. The consultant will work across business, engineering, product, data governance, and process-management teams to deliver scalable, governed, and reliable analytics capabilities.Day-to-Day ResponsibilitiesPower BI &amp; Executive ReportingDesign, develop, and maintain enterprise-grade Power BI dashboards and scorecardsCreate executive, operational, and strategic reporting solutionsBuild complex:Data ModelsSemantic LayersDAX MeasuresCalculationsPower Query TransformationsDevelop interactive visualizations highlighting performance trends, risks, exceptions, and improvement opportunitiesOptimize dashboard performance, user experience, and data-refresh processesEstablish reporting standards, governance, and technical documentationPrepare monthly and quarterly business review packagesGCP Data EngineeringDesign and optimize data-ingestion pipelines on Google Cloud PlatformDevelop ETL and ELT processes using data from:Enterprise ApplicationsAPIsOperational SystemsThird-Party SourcesBuild analytical datasets, reporting marts, and curated data assetsUse BigQuery and cloud-native services for scalable analyticsPerform data transformation, quality validation, reconciliation, and monitoringOptimize storage and processing architectures for performance and scalabilityKPI &amp; Performance AnalyticsPartner with stakeholders to define KPI frameworks and metric standardsDevelop executive scorecards and operational-health dashboardsDefine leading and lagg</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Senior Unconventional Analytics Engineer</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spring, TX, 77389, US</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5657,7 +5647,7 @@
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3046017_usa/senior-unconventional-analytics-engineer</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131993/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -5665,39 +5655,39 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>617af8d54f95bd8a9540</t>
+          <t>da60c6db3c8bf52b3c59</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Senior Unconventional Analytics EngineerLocation: Spring, TX (On-Site)Organization: Unconventional ResourcesAbout the RoleWe are seeking a Senior Unconventional Analytics Engineer to ensure data-driven decision making are intuitive and reliable across our Unconventional organization.Over the past two years, our team has developed forecasting, economic, and operational analytics solutions leveraging Databricks, ComboCurve, and Spotfire. While these tools provide significant value, their effectiveness depends on consistent, trusted, and easily accessible data.This role will focus on building and managing the data products that power our forecasting, economics, planning, and operational workflows. The successful candidate will work closely with reservoir engineers, production engineers, planners, economists, and data professionals to ensure critical business data is reliable, governed, automated, and readily available for analytics and decision support.Key ResponsibilitiesData Product OwnershipDesign, develop, and maintain analytics-ready data products supporting forecasting, economics, planning, drilling, completions, and production workflows.Establish trusted datasets and business logic that serve as authoritative sources for key analytical processes.Partner with business stakeholders to prioritize data product enhancements and new capabilities.Databricks Data EngineeringDevelop scalable data pipelines and transformation processes within Databricks using SQL and Python.Integrate data from operational, corporate, and third-party sources into a unified analytical environment.Optimize data models and architectures to improve performance, usability, and scalability.Implement automated workflows that reduce manual data preparation and spreadsheet-based processes.ComboCurve Integration &amp; EnablementSupport and enhance data flows feeding ComboCurve forecasting and economic workflows.Ensure forecasting and economic analyses are based on consistent, validated, and auditable datasets.Collaborate with engineers and economists to streamline data preparation and model execution.Improve traceability and transparency of inputs used in forecasting and economic evaluations.Spotfire Analytics EnablementDevelop and maintain curated datasets optimized for Spotfire dashboards and self-service analytics.Partner with stakeholders to improve data accessibility and visualization capabilities.Ensure consistency between Spotfire reporting, ComboCurve outputs, and enterprise data sources.Enable users to gain insights quickly through well-designed analytical data structures.Data Quality &amp; GovernanceEstablish data quality standards, validation rules, and monitoring processes.Identify and resolve data inconsistencies across systems and workflows.Develop business metadata, documentation, lineage, and governance practices.Promote a culture of data accountability and continuous improvement.Required QualificationsTechnical ExpertiseBachelor's degree in Engineering, Computer Science,</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CompuGain</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
+          <t>Entry-level Healthcare Analyst</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rockville Pike</t>
+          <t>Englewood, Colorado, United States</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5707,12 +5697,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5722,12 +5712,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070131992/entry-level-healthcare-analyst</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -5735,22 +5725,22 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>52176647527c6698e6d4</t>
+          <t>d00b31e4784f93e29d99</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Entry-level Healthcare Analyst Position Overview Cognizant is helping healthcare leaders make the shift—with practical insights, more automation and efficiency, innovative products and services, and modern infrastructure which drives better outcomes at a lower cost. When you join as an Entry-Level Healthcare Analyst, you will have the opportunity to work on complex emerging technology and business projects to shape the next phase of innovation in the healthcare industry. You will assist in designing and developing fully functional software products catering to healthcare and aligning with user needs and business goals. You will serve as part of a team to bridge development and operations functions, automate and streamline operations processes while working collaboratively with software engineering to deploy and operate our systems by resolving issues in our dev/test/production environments. Qualifications Bachelor’s degree or equivalent. Preferred majors include Computer Science, Computer Engineering, Software Engineering, Information Systems, Decision Sciences, Data Analytics/Data Science. Internship or academic experience with programming languages like Java, .NET, C#, and PL/SQL. Internship or academic experience and/or certifications using cloud services: Azure, AWS, GCP, etc. Interested in data – Data Science, Data Analytics, Databases, large data sets, or data mining. Excited to work within the Healthcare domain. Self-motivated individuals with strong analytical, troubleshooting and problem-solving skills with the passion and appetite to learn newer technologies. Work within the organization to establish and grow best practices and procedures with a focus on improving the ability of the organization to meet requirements. Strong interpersonal and communication skills. Ability to work collaboratively with global project teams. Location(s) New hires will be deployed to Cognizant office in Englewood, CO, Plano, TX, or Mesa, AZ where you will work alongside other experienced Cognizant associates delivering technology solutions. Applicants must be willing to relocate. Please note that this role will be remote/hybrid which will require associates to be in the office at least two days a week. Start Date(s) New hires will largely start in June 2026 . While we will attempt to honor candidate summer start date preferences, business needs and position availability will determine final start date assignment. Exact summer start dates will be communicated with enough time for you to plan effectively. Why Choose Us? Cognizant delivers solutions that draw upon the full power and scale of our associates. You will be supported by high-caliber experts and employ some of the most advanced and patented capabilities. Our associate’s diverse backgrounds offer varied perspectives and fuel new ways of thinking. We encourage lively discussions which inspire better results for our clients. Salary and Other Compensation: Applications are accepted on an ongoing basis. T</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5752,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5782,7 +5772,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5797,7 +5787,7 @@
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -5810,34 +5800,34 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>406d96610632ccfd5711</t>
+          <t>52176647527c6698e6d4</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>CompuGain</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Automotive Service Parts Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Rockville Pike</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5847,7 +5837,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5857,12 +5852,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/automotive-service-parts-analyst/5879824</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J78" t="b">
@@ -5870,22 +5865,22 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-13T07:13:41+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>f8bcdffdf9e7ac1affb3</t>
+          <t>406d96610632ccfd5711</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Automotive Service Parts Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Automotive Service Parts Analyst Reference Number: 5879824 Published Date: 08/11/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Service Parts Analyst Our client, in Auburn Hills, MI is seeking a dealer/diagnostic support - Service Parts Analyst to join their team. As a Service Parts analyst, you play a critical role in supporting vehicle launch readiness by managing the creation, maintenance, and release of service parts across multiple vehicle programs. This full-time onsite contract position ensures timely and accurate part setup using various internal systems and collaborates cross-functionally to resolve issues impacting service part availability and accuracy. This is a long term contract position. Job Title: Service Parts Analyst Location: Auburn Hills, MI Pay Range: $32.41 What’s the Job? Create, maintain, and release service parts to support vehicle launch timing rM Manage a high volume of part setups annually:Approximately 8,000–10,000 new part setups per year.Approximately 2,000–2,500 engineering change updates per year. Coordinate service parts release activities within the SBOM system. Support vehicle launch programs and ensure adherence to project timelines and KPIs. Manage service part updates related to Platform variants and model variations. Mid-Cycle Actions (MCAs), including styling updates and product enhancements. What’s Needed? High school diploma or GED 3+ years of experience in automotive service parts or as an automotive technician Computer proficient-PC literacy with Windows, Google, Microsoft Office Suite SBOM and EBOM Power BI dashboards Familiarity with Bill of Materials What’s in it fo</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5892,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming</t>
+          <t>Automotive Service Parts Analyst</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5912,7 +5907,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5927,7 +5922,7 @@
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/education/boardcertifiedbehavioranalystbcbaleadbehavioralprogramming/5879008</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/automotive-service-parts-analyst/5879824</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -5935,22 +5930,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-13T07:13:41+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>7378132d3f3081dc1693</t>
+          <t>f8bcdffdf9e7ac1affb3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming Reference Number: 5879008 Published Date: 08/10/2026 Job Type: Permanent Industry: Education Hours: Full Time APPLY NOW SAVE SHARE Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming Pay Rate: $72-82K Annual Salary Schedule: Monday-Friday, 7:30 AM-3:30 PM Assignment Length: Direct-Hire | 200-Day School Year Position We are seeking an experienced and passionate Board Certified Behavior Analyst (BCBA) to join a dedicated educational team and lead behavioral programming within a specialized K-5 autism and behavioral support program. This is a critical hiring need for a qualified individual who wants to make a meaningful impact not only on students' lives, but also on the development of educators, behavioral health professionals, and an expanding program. This opportunity offers competitive compensation, comprehensive benefits, and temporary housing assistance for qualified candidates. This is far more than a traditional BCBA role. You'll serve as a behavioral leader, mentor, coach, and collaborator in a relationship-centered educational environment where your expertise directly influences student success, staff development, and program growth . If you're passionate about evidence-based practices, trauma-informed care, autism services , and shaping the next generation of behavioral health professionals , this could be the career opportunity you've been looking for. Some of the Perks: Meaningful impact on the lives of children with autism and behavioral needs Consistent school-year schedule with excellent work-life balance Opportunity to mentor futu</t>
+          <t>Automotive Service Parts Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Automotive Service Parts Analyst Reference Number: 5879824 Published Date: 08/11/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Service Parts Analyst Our client, in Auburn Hills, MI is seeking a dealer/diagnostic support - Service Parts Analyst to join their team. As a Service Parts analyst, you play a critical role in supporting vehicle launch readiness by managing the creation, maintenance, and release of service parts across multiple vehicle programs. This full-time onsite contract position ensures timely and accurate part setup using various internal systems and collaborates cross-functionally to resolve issues impacting service part availability and accuracy. This is a long term contract position. Job Title: Service Parts Analyst Location: Auburn Hills, MI Pay Range: $32.41 What’s the Job? Create, maintain, and release service parts to support vehicle launch timing rM Manage a high volume of part setups annually:Approximately 8,000–10,000 new part setups per year.Approximately 2,000–2,500 engineering change updates per year. Coordinate service parts release activities within the SBOM system. Support vehicle launch programs and ensure adherence to project timelines and KPIs. Manage service part updates related to Platform variants and model variations. Mid-Cycle Actions (MCAs), including styling updates and product enhancements. What’s Needed? High school diploma or GED 3+ years of experience in automotive service parts or as an automotive technician Computer proficient-PC literacy with Windows, Google, Microsoft Office Suite SBOM and EBOM Power BI dashboards Familiarity with Bill of Materials What’s in it fo</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5957,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Credit Analyst</t>
+          <t>Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5977,7 +5972,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5992,7 +5987,7 @@
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/credit-analyst/5876680</t>
+          <t>https://www.manpower.com/en/job/education/boardcertifiedbehavioranalystbcbaleadbehavioralprogramming/5879008</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -6000,22 +5995,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-13T18:35:16+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>eb7055df9c90f5595b0b</t>
+          <t>7378132d3f3081dc1693</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Credit Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Credit Analyst Reference Number: 5876680 Published Date: 08/11/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Join the Manpower Team Supporting Acushnet Company! We're hiring a Credit Analyst to support Acushnet Company, the organization behind industry-leading brands like Titleist and FootJoy. This position offers the opportunity to contribute to a globally recognized company while building your experience in credit analysis and financial risk management. If you're analytical, detail-oriented, and looking for an opportunity to grow your finance career, we'd love to hear from you. What's In It for You? Competitive pay at $32 per hour Hybrid flexibility - office is in Fairhaven, MA Full-time schedule with consistent hours Weekly pay through Manpower Opportunity to support a globally recognized organization Build valuable experience in credit analysis and finance Potential for contract extension based on business needs and performance What You'll Do As a Credit Analyst, you'll play a key role in managing credit risk and supporting the company's financial operations by: Managing a portfolio of customer accounts throughout the order-to-cash process Reviewing financial statements, credit reports, and supporting data to assess creditworthiness Establishing and maintaining appropriate credit limits Monitoring customer accounts and addressing delinquent balances Negotiating payment solutions and helping reduce financial risk Processing new customer credit applications and maintaining accurate account records Collaborating with Sales, Customer Service, and Finance teams to support efficient credit and collection activities What We're Looking</t>
+          <t>Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming Reference Number: 5879008 Published Date: 08/10/2026 Job Type: Permanent Industry: Education Hours: Full Time APPLY NOW SAVE SHARE Board Certified Behavior Analyst (BCBA) – Lead Behavioral Programming Pay Rate: $72-82K Annual Salary Schedule: Monday-Friday, 7:30 AM-3:30 PM Assignment Length: Direct-Hire | 200-Day School Year Position We are seeking an experienced and passionate Board Certified Behavior Analyst (BCBA) to join a dedicated educational team and lead behavioral programming within a specialized K-5 autism and behavioral support program. This is a critical hiring need for a qualified individual who wants to make a meaningful impact not only on students' lives, but also on the development of educators, behavioral health professionals, and an expanding program. This opportunity offers competitive compensation, comprehensive benefits, and temporary housing assistance for qualified candidates. This is far more than a traditional BCBA role. You'll serve as a behavioral leader, mentor, coach, and collaborator in a relationship-centered educational environment where your expertise directly influences student success, staff development, and program growth . If you're passionate about evidence-based practices, trauma-informed care, autism services , and shaping the next generation of behavioral health professionals , this could be the career opportunity you've been looking for. Some of the Perks: Meaningful impact on the lives of children with autism and behavioral needs Consistent school-year schedule with excellent work-life balance Opportunity to mentor futu</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6022,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst</t>
+          <t>Credit Analyst</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6037,7 +6032,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6057,7 +6052,7 @@
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/credit-analyst/5876680</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -6070,17 +6065,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>f177712205fd7fd46f19</t>
+          <t>eb7055df9c90f5595b0b</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 08/11/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
+          <t>Credit Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Credit Analyst Reference Number: 5876680 Published Date: 08/11/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Join the Manpower Team Supporting Acushnet Company! We're hiring a Credit Analyst to support Acushnet Company, the organization behind industry-leading brands like Titleist and FootJoy. This position offers the opportunity to contribute to a globally recognized company while building your experience in credit analysis and financial risk management. If you're analytical, detail-oriented, and looking for an opportunity to grow your finance career, we'd love to hear from you. What's In It for You? Competitive pay at $32 per hour Hybrid flexibility - office is in Fairhaven, MA Full-time schedule with consistent hours Weekly pay through Manpower Opportunity to support a globally recognized organization Build valuable experience in credit analysis and finance Potential for contract extension based on business needs and performance What You'll Do As a Credit Analyst, you'll play a key role in managing credit risk and supporting the company's financial operations by: Managing a portfolio of customer accounts throughout the order-to-cash process Reviewing financial statements, credit reports, and supporting data to assess creditworthiness Establishing and maintaining appropriate credit limits Monitoring customer accounts and addressing delinquent balances Negotiating payment solutions and helping reduce financial risk Processing new customer credit applications and maintaining accurate account records Collaborating with Sales, Customer Service, and Finance teams to support efficient credit and collection activities What We're Looking</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6087,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lease Admin Analyst</t>
+          <t>Hybrid Financial Analyst</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6102,7 +6097,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6122,7 +6117,7 @@
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/lease-admin-analyst/5867194</t>
+          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -6130,22 +6125,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-13T07:13:41+00:00</t>
+          <t>2026-08-13T18:35:16+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>6bba874c85b3b6d0a5d9</t>
+          <t>f177712205fd7fd46f19</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Lease Admin Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Lease Admin Analyst Reference Number: 5867194 Published Date: 08/13/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the commercial real estate sector, is seeking a Lease Admin Analyst to join their team. As a Lease Admin Analyst, you will be part of the Property &amp; Facilities Management department supporting global data center portfolios. The ideal candidate will demonstrate strong attention to detail, proactive communication skills, and a self-motivated approach, which will align successfully in the organization. Job Title: Lease Admin Analyst Location: San Jose, CA Pay Range: $32-33hr. Shift: Days9:00an-6pm What's the Job? Conduct reconciliations for small to medium-sized clients to ensure operating expenses follow lease terms Review and process invoices, purchase orders, and contractual documents related to lease agreements Coordinate accounts payable activities, validate invoices, and resolve billing discrepancies Maintain and track industry certificates to ensure portfolio compliance Support contract reviews and generate reports for lease asset management teams What's Needed? Minimum of 3 to 5 years of experience in commercial real estate lease administration or related roles Experience reviewing invoices, purchase orders, and contracts within a property management or data center environment Proficiency with spreadsheets, including creating formulas, running reports, and managing detailed data Strong organizational skills and ability to work independently as a self-starter Excellent communication skills to effectively speak to your resume and work collaboratively What's in it for me? Opp</t>
+          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 08/11/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6152,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Logistics Analyst</t>
+          <t>Lease Admin Analyst</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6187,7 +6182,7 @@
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/lease-admin-analyst/5867194</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -6200,17 +6195,17 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>55a327dd3e52a4c3c560</t>
+          <t>6bba874c85b3b6d0a5d9</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 08/12/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
+          <t>Lease Admin Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Lease Admin Analyst Reference Number: 5867194 Published Date: 08/13/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the commercial real estate sector, is seeking a Lease Admin Analyst to join their team. As a Lease Admin Analyst, you will be part of the Property &amp; Facilities Management department supporting global data center portfolios. The ideal candidate will demonstrate strong attention to detail, proactive communication skills, and a self-motivated approach, which will align successfully in the organization. Job Title: Lease Admin Analyst Location: San Jose, CA Pay Range: $32-33hr. Shift: Days9:00an-6pm What's the Job? Conduct reconciliations for small to medium-sized clients to ensure operating expenses follow lease terms Review and process invoices, purchase orders, and contractual documents related to lease agreements Coordinate accounts payable activities, validate invoices, and resolve billing discrepancies Maintain and track industry certificates to ensure portfolio compliance Support contract reviews and generate reports for lease asset management teams What's Needed? Minimum of 3 to 5 years of experience in commercial real estate lease administration or related roles Experience reviewing invoices, purchase orders, and contracts within a property management or data center environment Proficiency with spreadsheets, including creating formulas, running reports, and managing detailed data Strong organizational skills and ability to work independently as a self-starter Excellent communication skills to effectively speak to your resume and work collaboratively What's in it for me? Opp</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6217,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Manufacturing Data &amp; AI Engineer</t>
+          <t>Logistics Analyst</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6252,7 +6247,7 @@
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/manufacturingdataaiengineer/401527</t>
+          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -6265,17 +6260,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>07e110011c12492112f7</t>
+          <t>55a327dd3e52a4c3c560</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Manufacturing Data &amp; AI Engineer | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Manufacturing Data &amp; AI Engineer Reference Number: 401527 Published Date: 08/10/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in manufacturing and autonomous vehicle production, is seeking a Manufacturing Data &amp; AI Engineer to join their team. As a Manufacturing Data &amp; AI Engineer, you will be part of the Manufacturing Operations supporting data architecture, analytics, and AI-enabled solutions. The ideal candidate will have strong problem-solving skills, collaboration abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Manufacturing Data &amp; AI Engineer Location: Foster City, CA Pay Range: $73/hour + Benefits What's the Job? Design, develop, and maintain scalable data pipelines, ETL processes, and data warehouse solutions supporting manufacturing reporting and analytics. Build and manage curated data models and datasets that provide trusted manufacturing performance metrics. Integrate data from enterprise and manufacturing systems such as SAP HANA, SAP MES, and operational databases. Identify operational challenges and collaborate with stakeholders to develop AI-enabled solutions and automation opportunities. Develop and optimize Python-based data processing solutions and advanced SQL queries for complex datasets analysis. What's Needed? Bachelor's degree in Computer Science, Data Science, Engineering, or related technical field. 4–6 years of experience in Data Engineering, Analytics Engineering, or Software Engineering with significant data responsibilities. Proficiency in SQL, Python, data modeling, ETL development, and enterprise-scale data war</t>
+          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 08/12/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
         </is>
       </c>
     </row>
@@ -6287,12 +6282,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Planning Analyst</t>
+          <t>Manufacturing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, ITALY</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6302,12 +6297,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6322,7 +6312,7 @@
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/planning-analyst/5877372</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/manufacturingdataaiengineer/401527</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -6335,17 +6325,17 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>d9837c263591e088eb82</t>
+          <t>07e110011c12492112f7</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Planning Analyst – Pay Rate: $70 - $75k Our client in Cleveland, OH is looking for and experienced and motivated Planning Analyst to join their team. This individual will facilitate the demand planning process and is responsible for management of the daily and weekly demand planning functions. Don’t wait… apply today! What's in it for you? Payrate: $70k - $75k Healthcare benefits 10 Paid Holidays Paid Time off 4% 401k Match Tuition Assistance Employer Funded HSA Tickets to Sporting Events Annual Golf Outing Hot Dog &amp; Taco Trucks ...and more! What will you be doing? Works in coordination with the team on the annual &amp; monthly EGI forecast development. Assists in the monthly S&amp;OP process, facilitates demand planning meetings and executes any new actions related to the demand plan. Provides short-term demand plan updates in weekly S&amp;OE meetings. Provides reports that analyzes customer item forecast to actual customer demand. Performs root cause analysis of demand issues to determine best solutions. Manages and executes various ad-hoc requests. What do you bring? Bachelor Degree in Business, Analytics, Communication or related area of study. 2+ years of analytical experience. ERP and MRP systems experience. High Level of Proficiency in Excel and PowerPoint. Skilled and experienced in demand planning and/or supply chain functions. Why should you choose Manpower? Free training to upgrade your skills, including a free college tuition program Medical, dental, vision, 401k Weekly pay with direct deposit 24/7 Manpower customer care support Dedicated Career Partner to help you achieve your career goals Voted #1 best places to work by Glassdoor 2021 Are you Interested? Stop your job search and apply today! A recruiter will be in touch within 24 hours. Share this job with friends and family and earn dollars with every successful hire. ManpowerGroup recognizes the importance of providing an accessible and barrier-free environment. We are committed to creating a welcoming, fair and inclusive environment by offering equal opportunity to access our services. At ManpowerGroup, we are committed to providing accommodations, and will work with you to meet your needs.</t>
+          <t>Manufacturing Data &amp; AI Engineer | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Manufacturing Data &amp; AI Engineer Reference Number: 401527 Published Date: 08/10/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in manufacturing and autonomous vehicle production, is seeking a Manufacturing Data &amp; AI Engineer to join their team. As a Manufacturing Data &amp; AI Engineer, you will be part of the Manufacturing Operations supporting data architecture, analytics, and AI-enabled solutions. The ideal candidate will have strong problem-solving skills, collaboration abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Manufacturing Data &amp; AI Engineer Location: Foster City, CA Pay Range: $73/hour + Benefits What's the Job? Design, develop, and maintain scalable data pipelines, ETL processes, and data warehouse solutions supporting manufacturing reporting and analytics. Build and manage curated data models and datasets that provide trusted manufacturing performance metrics. Integrate data from enterprise and manufacturing systems such as SAP HANA, SAP MES, and operational databases. Identify operational challenges and collaborate with stakeholders to develop AI-enabled solutions and automation opportunities. Develop and optimize Python-based data processing solutions and advanced SQL queries for complex datasets analysis. What's Needed? Bachelor's degree in Computer Science, Data Science, Engineering, or related technical field. 4–6 years of experience in Data Engineering, Analytics Engineering, or Software Engineering with significant data responsibilities. Proficiency in SQL, Python, data modeling, ETL development, and enterprise-scale data war</t>
         </is>
       </c>
     </row>
@@ -6357,12 +6347,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Portfolio Analyst</t>
+          <t>Planning Analyst</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Cleveland, OH, ITALY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6372,7 +6362,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6387,7 +6382,7 @@
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/portfolio-analyst/5880074</t>
+          <t>https://www.manpower.com/en/job/business-operations/planning-analyst/5877372</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -6400,17 +6395,17 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>f77ac6ead1d5cb115b1b</t>
+          <t>d9837c263591e088eb82</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Portfolio Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Portfolio Analyst Reference Number: 5880074 Published Date: 08/11/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the energy and infrastructure sector, is seeking a Portfolio Analyst to join their team. As a Portfolio Analyst, you will be part of the Business Services department supporting project and program management initiatives. The ideal candidate will have strong communication skills, analytical thinking, and a proactive approach, which will align successfully in the organization. Job Title: Portfolio Analyst Location: White Plains, NY Pay Range: Shift: Monday through Friday, 7.5-hour workday with a 0.5-hour unpaid lunch What's the Job? Assist in reviewing project and program progress from initiation to closeout, ensuring alignment with organizational strategies and financial targets. Oversee and guide project teams in developing comprehensive business cases and maintaining governance standards. Prepare portfolio-level analysis and reporting on financial control, resource utilization, risk, and benefits, comparing planned versus actual performance. Lead reviews of significant initiatives and provide recommendations on project continuation, modification, or discontinuation. Develop monthly and ad hoc status reports, highlighting issues, conflicts, and key milestone movements to stakeholders. What's Needed? 5-10 years of experience in construction, engineering, or related fields with a focus on project or portfolio management. Bachelor’s degree in business administration, finance, engineering, or a related field; Master’s degree preferred. Proficiency with Microsoft Office Suite, including</t>
+          <t>Planning Analyst – Pay Rate: $70 - $75k Our client in Cleveland, OH is looking for and experienced and motivated Planning Analyst to join their team. This individual will facilitate the demand planning process and is responsible for management of the daily and weekly demand planning functions. Don’t wait… apply today! What's in it for you? Payrate: $70k - $75k Healthcare benefits 10 Paid Holidays Paid Time off 4% 401k Match Tuition Assistance Employer Funded HSA Tickets to Sporting Events Annual Golf Outing Hot Dog &amp; Taco Trucks ...and more! What will you be doing? Works in coordination with the team on the annual &amp; monthly EGI forecast development. Assists in the monthly S&amp;OP process, facilitates demand planning meetings and executes any new actions related to the demand plan. Provides short-term demand plan updates in weekly S&amp;OE meetings. Provides reports that analyzes customer item forecast to actual customer demand. Performs root cause analysis of demand issues to determine best solutions. Manages and executes various ad-hoc requests. What do you bring? Bachelor Degree in Business, Analytics, Communication or related area of study. 2+ years of analytical experience. ERP and MRP systems experience. High Level of Proficiency in Excel and PowerPoint. Skilled and experienced in demand planning and/or supply chain functions. Why should you choose Manpower? Free training to upgrade your skills, including a free college tuition program Medical, dental, vision, 401k Weekly pay with direct deposit 24/7 Manpower customer care support Dedicated Career Partner to help you achieve your career goals Voted #1 best places to work by Glassdoor 2021 Are you Interested? Stop your job search and apply today! A recruiter will be in touch within 24 hours. Share this job with friends and family and earn dollars with every successful hire. ManpowerGroup recognizes the importance of providing an accessible and barrier-free environment. We are committed to creating a welcoming, fair and inclusive environment by offering equal opportunity to access our services. At ManpowerGroup, we are committed to providing accommodations, and will work with you to meet your needs.</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6417,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Remote Data Analyst</t>
+          <t>Portfolio Analyst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6432,7 +6427,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6452,7 +6447,7 @@
       </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-/5879174</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/portfolio-analyst/5880074</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -6465,17 +6460,17 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>b8bb41fbf34c4234c974</t>
+          <t>f77ac6ead1d5cb115b1b</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Remote Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst Reference Number: 5879174 Published Date: 08/11/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the legal and restructuring sector, is seeking a Remote CA ONLY Data Analyst to join their team. As a Remote CA ONLY Data Analyst, you will be part of the Corporate Restructuring department supporting various operational and administrative functions. The ideal candidate will demonstrate attention to detail, strong communication skills, and adaptability, which will align successfully in the organization. Job Title: Remote CA ONLY Data Analyst Location: Remote (El Segundo, CA) Pay Range:$28.00hr to $30.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status and claims Assist with preparing claim and solicitation binders for court submission Manage and log case voicemails, perform internet research for creditor information Coordinate, input, and review ballots, address changes, and proofs of claim What's Needed? Ability to quickly learn and navigate proprietary software and applications Solid attention to detail and accuracy in work Strong written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training preferred What's in it for me? Remote work opportunity with flexible hours Weekly pay every Friday Potential for overtime and career growth True contract-to-hire opportunity with the possibility of direct employment Competitive</t>
+          <t>Portfolio Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Portfolio Analyst Reference Number: 5880074 Published Date: 08/11/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the energy and infrastructure sector, is seeking a Portfolio Analyst to join their team. As a Portfolio Analyst, you will be part of the Business Services department supporting project and program management initiatives. The ideal candidate will have strong communication skills, analytical thinking, and a proactive approach, which will align successfully in the organization. Job Title: Portfolio Analyst Location: White Plains, NY Pay Range: Shift: Monday through Friday, 7.5-hour workday with a 0.5-hour unpaid lunch What's the Job? Assist in reviewing project and program progress from initiation to closeout, ensuring alignment with organizational strategies and financial targets. Oversee and guide project teams in developing comprehensive business cases and maintaining governance standards. Prepare portfolio-level analysis and reporting on financial control, resource utilization, risk, and benefits, comparing planned versus actual performance. Lead reviews of significant initiatives and provide recommendations on project continuation, modification, or discontinuation. Develop monthly and ad hoc status reports, highlighting issues, conflicts, and key milestone movements to stakeholders. What's Needed? 5-10 years of experience in construction, engineering, or related fields with a focus on project or portfolio management. Bachelor’s degree in business administration, finance, engineering, or a related field; Master’s degree preferred. Proficiency with Microsoft Office Suite, including</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6482,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract</t>
+          <t>Remote Data Analyst</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6497,7 +6492,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6517,7 +6512,7 @@
       </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/seniordatascientistpythonsqlmachinelearningforecastingoneyearcontract/406621</t>
+          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-/5879174</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -6530,17 +6525,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>edad17fb99483f99400b</t>
+          <t>b8bb41fbf34c4234c974</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract Reference Number: 406621 Published Date: 08/11/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a global leader in energy technology and industrial engineering solutions, is seeking a Senior Data Scientist to join their team. As a Senior Data Scientist, you will be part of the Data &amp; Analytics organization supporting Engineering, Operations, Program Management, and Business Strategy teams. The ideal candidate will have strong analytical thinking, excellent stakeholder communication skills, and a collaborative, solution-oriented mindset that will align successfully within the organization. Job Title: Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting Location: Greenville, SC Pay Range: $52.61/hour What's the Job? Develop machine learning, forecasting, and predictive analytics solutions that support business and operational decision-making. Build scenario-planning and "what-if" models to evaluate resource capacity, project execution, costs, and business forecasts. Analyze and integrate data from multiple enterprise platforms, including ERP, CRM, business intelligence, financial, and project management systems. Collaborate with business leaders, engineers, and data teams to translate complex business challenges into data-driven solutions. Create executive reporting, dashboards, and AI-powered analytical tools that provide actionable insights and improve operational performance. What's Needed? Strong experience using Python for data analysis, statist</t>
+          <t>Remote Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst Reference Number: 5879174 Published Date: 08/11/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the legal and restructuring sector, is seeking a Remote CA ONLY Data Analyst to join their team. As a Remote CA ONLY Data Analyst, you will be part of the Corporate Restructuring department supporting various operational and administrative functions. The ideal candidate will demonstrate attention to detail, strong communication skills, and adaptability, which will align successfully in the organization. Job Title: Remote CA ONLY Data Analyst Location: Remote (El Segundo, CA) Pay Range:$28.00hr to $30.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status and claims Assist with preparing claim and solicitation binders for court submission Manage and log case voicemails, perform internet research for creditor information Coordinate, input, and review ballots, address changes, and proofs of claim What's Needed? Ability to quickly learn and navigate proprietary software and applications Solid attention to detail and accuracy in work Strong written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training preferred What's in it for me? Remote work opportunity with flexible hours Weekly pay every Friday Potential for overtime and career growth True contract-to-hire opportunity with the possibility of direct employment Competitive</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6547,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Senior Treasury Analyst - Hybrid</t>
+          <t>Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6562,12 +6557,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6582,7 +6577,7 @@
       </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/management/senior-treasury-analyst-hybrid/5858337</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/seniordatascientistpythonsqlmachinelearningforecastingoneyearcontract/406621</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -6595,17 +6590,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>c6a0e86a16702c328364</t>
+          <t>edad17fb99483f99400b</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Senior Treasury Analyst - Hybrid | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Treasury Analyst - Hybrid Reference Number: 5858337 Published Date: 08/12/2026 Job Type: Permanent Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Our client, a mission-driven research and nonprofit organization , is seeking a Senior Investment &amp; Treasury Analyst to join their team. As a Senior Investment &amp; Treasury Analyst, you will be part of the Finance Department supporting the Treasury and Investment Operations teams . The ideal candidate will have strong analytical skills , attention to detail , and excellent communication abilities which will align successfully in the organization. Job Title: Senior Investment &amp; Treasury Analyst Location: North Side, Cook County, IL (Hybrid) Pay Range: $80,000 – $110,000 (depending on experience) + Bonus What’s the Job? Monitor and analyze investment portfolio performance and prepare reporting materials Build financial models, including forecasts, scenario and sensitivity analysis Support treasury operations such as cash management, banking, and wire transfers Assist with audits, tax filings (990 series), and compliance initiatives Collaborate cross-functionally with finance, accounting, and legal teams What’s Needed? Bachelor’s degree in Finance, Accounting, or related field 5+ years of experience in treasury, investments, or financial analysis Strong financial modeling and advanced Excel skills Knowledge of investment portfolio management and treasury operations CPA, CMA, or CTP certification preferred What’s in it for me? Competitive compensation with bonus eligibility Comprehensive health, dental, and vision benefits Generous retirement contributions and 401(k) match Collaborative and mission-driven work</t>
+          <t>Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting | One year contract Reference Number: 406621 Published Date: 08/11/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a global leader in energy technology and industrial engineering solutions, is seeking a Senior Data Scientist to join their team. As a Senior Data Scientist, you will be part of the Data &amp; Analytics organization supporting Engineering, Operations, Program Management, and Business Strategy teams. The ideal candidate will have strong analytical thinking, excellent stakeholder communication skills, and a collaborative, solution-oriented mindset that will align successfully within the organization. Job Title: Senior Data Scientist | Python, SQL, Machine Learning &amp; Forecasting Location: Greenville, SC Pay Range: $52.61/hour What's the Job? Develop machine learning, forecasting, and predictive analytics solutions that support business and operational decision-making. Build scenario-planning and "what-if" models to evaluate resource capacity, project execution, costs, and business forecasts. Analyze and integrate data from multiple enterprise platforms, including ERP, CRM, business intelligence, financial, and project management systems. Collaborate with business leaders, engineers, and data teams to translate complex business challenges into data-driven solutions. Create executive reporting, dashboards, and AI-powered analytical tools that provide actionable insights and improve operational performance. What's Needed? Strong experience using Python for data analysis, statist</t>
         </is>
       </c>
     </row>
@@ -6617,27 +6612,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Warranty Data Administration Analyst</t>
+          <t>Senior Treasury Analyst - Hybrid</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, ITALY</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6652,7 +6642,7 @@
       </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/warranty-data-administration-analyst/405692</t>
+          <t>https://www.manpower.com/en/job/management/senior-treasury-analyst-hybrid/5858337</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -6665,34 +6655,34 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>6f9485c053cd0b52b9bd</t>
+          <t>c6a0e86a16702c328364</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Our client, a leading commercial vehicle manufacturing company , is seeking a Warranty Data Administration Analyst to join their team. As a Warranty Data Administration Analyst, you will be part of the Warranty Operations Department supporting the Warranty Analysis, Service Engineering, and Supplier Quality Teams . The ideal candidate will have strong analytical skills , attention to detail , and effective communication skills which will align successfully in the organization. Job Title: Warranty Data Administration Analyst Location: Detroit, MI Pay Range: $25.00 - $29.00/hour What's the Job? Analyze warranty claims data and develop reports, metrics, and dashboards to evaluate business performance and warranty trends. Investigate technical warranty issues by reviewing service documentation, diagnostic information, and component design details. Support failure analysis activities through examination and testing of failed engine and exhaust aftertreatment system components. Collaborate with dealerships, repair facilities, suppliers, and internal teams to resolve warranty claim issues and coordinate inspections. Prepare technical documentation, findings, and recommendations to support warranty evaluations and appeals. What's Needed? Bachelor's degree in Engineering, Data Analytics, Business, or a related technical field. Experience analyzing warranty, service, automotive, manufacturing, or technical data. Strong analytical and problem-solving skills with the ability to interpret large data sets. Proficiency with reporting tools, Microsoft Excel, and data visualization platforms such as Power BI or Tableau. Excellent communication skills with the ability to work cross-functionally with internal and external stakeholders. What's in it for me? Opportunity to support a global leader in commercial vehicle manufacturing. Exposure to advanced vehicle systems, engineering teams, and warranty operations. Collaborative and innovative work environment. Professional development and career growth opportunities. Competitive compensation and comprehensive benefits package. If this is a role that interests you and you'd like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis, Talent Solutions, and Jefferson Wells ManpowerGroup® (NYSE: MAN), the leading global workforce solutions company, helps organizations transform in a fast-changing world of work by sourcing, assessing, developing, and managing the talent that enables them to win. We develop innovative solutions for hundreds of thousands of organizations every year, providing them with skilled talent while finding meaningful, sustainable employment for millions of people across a wide range of industries and skills. Our expert family of brands – Manpower, Experis, Talent Solutions, and Jefferson Wells – creates substantial value for candidates and clients across</t>
+          <t>Senior Treasury Analyst - Hybrid | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Treasury Analyst - Hybrid Reference Number: 5858337 Published Date: 08/12/2026 Job Type: Permanent Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Our client, a mission-driven research and nonprofit organization , is seeking a Senior Investment &amp; Treasury Analyst to join their team. As a Senior Investment &amp; Treasury Analyst, you will be part of the Finance Department supporting the Treasury and Investment Operations teams . The ideal candidate will have strong analytical skills , attention to detail , and excellent communication abilities which will align successfully in the organization. Job Title: Senior Investment &amp; Treasury Analyst Location: North Side, Cook County, IL (Hybrid) Pay Range: $80,000 – $110,000 (depending on experience) + Bonus What’s the Job? Monitor and analyze investment portfolio performance and prepare reporting materials Build financial models, including forecasts, scenario and sensitivity analysis Support treasury operations such as cash management, banking, and wire transfers Assist with audits, tax filings (990 series), and compliance initiatives Collaborate cross-functionally with finance, accounting, and legal teams What’s Needed? Bachelor’s degree in Finance, Accounting, or related field 5+ years of experience in treasury, investments, or financial analysis Strong financial modeling and advanced Excel skills Knowledge of investment portfolio management and treasury operations CPA, CMA, or CTP certification preferred What’s in it for me? Competitive compensation with bonus eligibility Comprehensive health, dental, and vision benefits Generous retirement contributions and 401(k) match Collaborative and mission-driven work</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Technical Data Analyst</t>
+          <t>Warranty Data Administration Analyst</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US</t>
+          <t>Detroit, MI, ITALY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6702,12 +6692,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>["full-time"]</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6717,12 +6707,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/6bbcbfc19115ac640Xx62A~~</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/warranty-data-administration-analyst/405692</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -6730,22 +6720,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-13T21:32:27+00:00</t>
+          <t>2026-08-13T07:13:41+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>1ad3e91e4f974b917412</t>
+          <t>6f9485c053cd0b52b9bd</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Need a Strong Technical Data Analyst. Location – Mountain View, CA ONLY EX-INTUIT CANDIDATES • 5+ years of work experience involving quantitative data analysis • Technical undergraduate degree (Engineering, Computer Science, Statistics, Analytics etc.) or equivalent experience • Advanced SQL skills to get the data you need from a data warehouse and perform data segmentation and aggregation from scratch. • Data query and data processing tools/systems (e.g., relational, NoSQL, stream processing) • Familiarity with AWS (Redshift, Athena, and AWS core concepts) • Familiarity with Data modeling and schema design • Proficient in analytical and data modeling tools, such as Python, R, or PyCharm • Self-starter who attacks the problem with excellent critical-thinking skills, creativity, and end-to-end quantitative and qualitative analysis • Excellent written and verbal communication skills with the ability to present complex technical information in a clear and concise manner to executives and non-technical leaders • High level of professionalism, passion, strong organization, time management and task prioritization skills with attention to detail and bias to action • Inquisitive, curious, and bias towards learning and continuous improvement • Ability to grasp quickly and get up to speed on instrumentation, clickstream data, data architecture, and complex business system interactions such as Salesforce, Amazon Connect, EWFM preferred • Ability to operate effectively in a fast-paced environment with minimal hand-holding. Demonstrates strong self-directed learning—able to get up to speed by digging into documentation, conducting independent research, and proactively reaching out across teams to ask the right questions and drive clarity."</t>
+          <t>Our client, a leading commercial vehicle manufacturing company , is seeking a Warranty Data Administration Analyst to join their team. As a Warranty Data Administration Analyst, you will be part of the Warranty Operations Department supporting the Warranty Analysis, Service Engineering, and Supplier Quality Teams . The ideal candidate will have strong analytical skills , attention to detail , and effective communication skills which will align successfully in the organization. Job Title: Warranty Data Administration Analyst Location: Detroit, MI Pay Range: $25.00 - $29.00/hour What's the Job? Analyze warranty claims data and develop reports, metrics, and dashboards to evaluate business performance and warranty trends. Investigate technical warranty issues by reviewing service documentation, diagnostic information, and component design details. Support failure analysis activities through examination and testing of failed engine and exhaust aftertreatment system components. Collaborate with dealerships, repair facilities, suppliers, and internal teams to resolve warranty claim issues and coordinate inspections. Prepare technical documentation, findings, and recommendations to support warranty evaluations and appeals. What's Needed? Bachelor's degree in Engineering, Data Analytics, Business, or a related technical field. Experience analyzing warranty, service, automotive, manufacturing, or technical data. Strong analytical and problem-solving skills with the ability to interpret large data sets. Proficiency with reporting tools, Microsoft Excel, and data visualization platforms such as Power BI or Tableau. Excellent communication skills with the ability to work cross-functionally with internal and external stakeholders. What's in it for me? Opportunity to support a global leader in commercial vehicle manufacturing. Exposure to advanced vehicle systems, engineering teams, and warranty operations. Collaborative and innovative work environment. Professional development and career growth opportunities. Competitive compensation and comprehensive benefits package. If this is a role that interests you and you'd like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis, Talent Solutions, and Jefferson Wells ManpowerGroup® (NYSE: MAN), the leading global workforce solutions company, helps organizations transform in a fast-changing world of work by sourcing, assessing, developing, and managing the talent that enables them to win. We develop innovative solutions for hundreds of thousands of organizations every year, providing them with skilled talent while finding meaningful, sustainable employment for millions of people across a wide range of industries and skills. Our expert family of brands – Manpower, Experis, Talent Solutions, and Jefferson Wells – creates substantial value for candidates and clients across</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6795,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6875,7 +6865,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6945,7 +6935,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7015,7 +7005,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7085,7 +7075,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7155,7 +7145,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7225,7 +7215,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7295,7 +7285,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7365,7 +7355,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7435,7 +7425,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7505,7 +7495,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7575,7 +7565,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -7645,7 +7635,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7715,7 +7705,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7785,7 +7775,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7855,7 +7845,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7925,7 +7915,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7995,7 +7985,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8065,7 +8055,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8135,7 +8125,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8205,7 +8195,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8275,7 +8265,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8345,7 +8335,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -8415,7 +8405,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -8485,7 +8475,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -8555,7 +8545,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8625,7 +8615,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -8695,7 +8685,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8765,7 +8755,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -8835,7 +8825,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -8905,7 +8895,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -8975,7 +8965,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9045,7 +9035,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9110,7 +9100,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9175,7 +9165,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -9192,27 +9182,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>278 results for Data Engineer jobs</t>
+          <t>Accounts Receivable &amp; Collections Analyst - Order to Cash (OTC)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Louisville, KY, 40223, USA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9222,12 +9217,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
+          <t>https://www.roseint.com/Jobs/Analyst-KY-Louisville-Rose-International-Job-505704.html</t>
         </is>
       </c>
       <c r="J127" t="b">
@@ -9235,22 +9230,22 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-08-13T18:35:16+00:00</t>
+          <t>2026-08-13T21:32:27+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>c015a1404fcb6f47b483</t>
+          <t>384d96a9f99f4d92f71b</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>278 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Permanent talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2026 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 278 results for Data Engineer jobs Data Engineer Erlanger, KY onsite Temporary / Contract 38 - 44 USD / Hourly We are looking for a detail-focused Engineer/Analyst to join a Long-term Contract assignment supporting technical data quality and material information management in northern Kentucky. In this role, you will help maintain accurate, standardized data for raw materials and packaging components so teams can move product development, supplier onboarding, and manufacturing activities forward efficiently. This position works closely with research, quality, procurement, operations, and master data partners to strengthen consistency across systems and improve the reliability of material records. This role will be onsite 4 days a week and 1 day remote. Must be comfortable working in a lab/plant manufacturing setting. YOU MUST LIVE IN KY or OH to be considered. No option for remote work. Responsibilities: • Manage the collection, review, and entry of technical specifications for raw materials and packaging components within designated data and specification platforms. • Verify that material records are complete, accurate, and aligned with company standards, compliance expectations, and approved documentation. • Apply consistent naming structures, formatting rules, and data standards to improve usability across regional and enterprise systems. • Investigate missing, conflicting, or outdated information in material specifications and resolve issues through coordination with cross-functional stakeholders. • Maintain material master records and ensure proper connections between specification data, system entries, and related documentation. • Build, revise, and validate bills of materials to support production readiness, product updates, supplier changes, and ongoing improvement efforts. • Partner with master data, procurement, operations, and technical teams to enhance data governance practices and streamline data management processes. • Monitor assigned project activities and data deliverables to help keep timelines on track and support broader documentation standardization efforts. 2026-08-10T00:00:00Z Data Engineer Kalamazoo, MI remote Permanent / Full Time 150000 - 225000 USD / Yearly We are looking for a senio</t>
+          <t>Required/Preferred Educationâ¢ Bachelors degree in Business, Accounting, Finance or other relevant fieldsRequired/Preferred CertificationsN/ARequirements, Required/Preferred Soft Skillsâ¢ 0-3+ years of relevant working experience in a similar role inâ¢ Accounts Receivableâ¢ Creditâ¢ Collectionsâ¢ Billingâ¢ General knowledge of accounting principles a plusâ¢ Strong knowledge of Microsoft Office -Excel &amp; Wordâ¢ Strong communication skills - oral, written, interpersonalâ¢ Strong Analytical and problem-solving skillsâ¢ Ability to multi-task, prioritize and deal with ambiguityâ¢ Flexibility with work scheduleâ¢ Demonstrated the ability to be a team player and possess strong work ethic and integrityâ¢ Ability to operate in a fast paced environment and meet critical deadlinesâ¢ Demonstrate excellent organizational skillsâ¢ Demonstrate strong interpersonal skillsâ¢ Collections experience a plusâ¢ Language skill a plusâ¢ Experience in media industry a plusâ¢ Ability to adapt to organizational transformationâ¢ ERP or financial system experience a plus (SAP, Oracle a +)Job SummaryThe Collection Analyst is responsible for managing a substantial portfolio of Ad Sales for Local TV Stations, including identifying and resolving discrepancies, maintaining a consistent payment pattern, and fostering strong client relationships. The role requires the use of various collection methods and techniques to optimize cash flow and minimize bad debt risk. As a key player within the organization, the Collector directly impacts Client financial results. This position is part of the Order to Cash team, based in Louisville.Responsibilitiesâ¢ Oversee Ad Sales TV Stations Collections portfolio varying from â¢ Contacting customers for the prompt collections and resolution of the aged receivables using various collection methods,â¢ Keeping adequate records of all contact made with customersâ¢ Performing timely follow-up on accounts ensuring customers pay within payment termsâ¢ Managing &amp; resolving high volume of customer discrepancies (ensuring proper communication with ad sales, &amp; stakeholders)â¢ Meeting cash collection targets (KPIâs such as Cash targets, Aging, DSO, % of Overdue)â¢ Providing leadership with periodic cash forecast projectionsâ¢ Working closely with other departments / functions to understand the specific issues causing payment delays; also directly involved in determining the most appropriate course of action (account credit holds, payment plans)â¢ Preparing routine reports for the management teamâ¢ Organize and participate in the periodic aging reviews with Managementâ¢ Supporting customerâs ad-hoc requests (statement of accounts, invoice copies, backup documentation, accounts reconciliations, etc.)â¢ Working closely with various departments, playing an active role during month end close activitiesâ¢ Ensuring that Accounts Receivable ledgers are properly managedâ¢ Supporting the Cash Application team in the account reconci</t>
         </is>
       </c>
     </row>
@@ -9262,27 +9257,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Accounts Receivable &amp; Collections Analyst - Order to Cash (OTC)</t>
+          <t>NEW JOB OPENING FINANCIAL ANALYST - FP&amp;A, FINANCIAL MODELING &amp; REPORTING IN NEW YORK, NY, USA!</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Louisville, KY, 40223, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9297,7 +9287,7 @@
       </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Analyst-KY-Louisville-Rose-International-Job-505704.html</t>
+          <t>https://www.roseint.com/Jobs/Financial-Analyst-NY-New-York-Rose-International-Job-505670.html</t>
         </is>
       </c>
       <c r="J128" t="b">
@@ -9305,22 +9295,22 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-08-13T21:32:27+00:00</t>
+          <t>2026-08-13T15:43:44+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>384d96a9f99f4d92f71b</t>
+          <t>c0de0a57e0780739960f</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Required/Preferred Educationâ¢ Bachelors degree in Business, Accounting, Finance or other relevant fieldsRequired/Preferred CertificationsN/ARequirements, Required/Preferred Soft Skillsâ¢ 0-3+ years of relevant working experience in a similar role inâ¢ Accounts Receivableâ¢ Creditâ¢ Collectionsâ¢ Billingâ¢ General knowledge of accounting principles a plusâ¢ Strong knowledge of Microsoft Office -Excel &amp; Wordâ¢ Strong communication skills - oral, written, interpersonalâ¢ Strong Analytical and problem-solving skillsâ¢ Ability to multi-task, prioritize and deal with ambiguityâ¢ Flexibility with work scheduleâ¢ Demonstrated the ability to be a team player and possess strong work ethic and integrityâ¢ Ability to operate in a fast paced environment and meet critical deadlinesâ¢ Demonstrate excellent organizational skillsâ¢ Demonstrate strong interpersonal skillsâ¢ Collections experience a plusâ¢ Language skill a plusâ¢ Experience in media industry a plusâ¢ Ability to adapt to organizational transformationâ¢ ERP or financial system experience a plus (SAP, Oracle a +)Job SummaryThe Collection Analyst is responsible for managing a substantial portfolio of Ad Sales for Local TV Stations, including identifying and resolving discrepancies, maintaining a consistent payment pattern, and fostering strong client relationships. The role requires the use of various collection methods and techniques to optimize cash flow and minimize bad debt risk. As a key player within the organization, the Collector directly impacts Client financial results. This position is part of the Order to Cash team, based in Louisville.Responsibilitiesâ¢ Oversee Ad Sales TV Stations Collections portfolio varying from â¢ Contacting customers for the prompt collections and resolution of the aged receivables using various collection methods,â¢ Keeping adequate records of all contact made with customersâ¢ Performing timely follow-up on accounts ensuring customers pay within payment termsâ¢ Managing &amp; resolving high volume of customer discrepancies (ensuring proper communication with ad sales, &amp; stakeholders)â¢ Meeting cash collection targets (KPIâs such as Cash targets, Aging, DSO, % of Overdue)â¢ Providing leadership with periodic cash forecast projectionsâ¢ Working closely with other departments / functions to understand the specific issues causing payment delays; also directly involved in determining the most appropriate course of action (account credit holds, payment plans)â¢ Preparing routine reports for the management teamâ¢ Organize and participate in the periodic aging reviews with Managementâ¢ Supporting customerâs ad-hoc requests (statement of accounts, invoice copies, backup documentation, accounts reconciliations, etc.)â¢ Working closely with various departments, playing an active role during month end close activitiesâ¢ Ensuring that Accounts Receivable ledgers are properly managedâ¢ Supporting the Cash Application team in the account reconci</t>
+          <t>Financial Analyst - FP&amp;A, Financial Modeling &amp; Reporting - New York, NY | Onsite, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING FINANCIAL ANALYST - FP&amp;A, FINANCIAL MODELING &amp; REPORTING IN NEW YORK, NY, USA! Date Posted: 08/13/2026 Hiring Organization: Rose International Position Number: 505670 Industry: Media and Entertainment Job Title: Financial Analyst - FP&amp;A, Financial Modeling &amp; Reporting Job Location: New York, NY, USA, 10036 Work Model: Onsite Shift: 9 am - 6 pm EST Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 6 Min Hourly Rate($): 35.00 Max Hourly Rate($): 40.00 Must Have Skills/Attributes: Analytical Skills, Financial Modeling, Forecasting, Google Docs/Sheet/Slide, Google Workspace Experience Desired: Experience in finance, accounting, (1+ yrs); Advanced Google Workspace suite skills, particularly Sheets and Slides (2 yrs); Experience with Excel fundamental formulas, VLOOKUP (2 yrs) Required Minimum Education: Bachelorâs Degree **C2C is not available** Job Description Required Education â¢ Bachelorâs degree Required Experience: â¢ 1+ years of work experience in finance, accounting, or a similar quantitative role Required Qualifications: â¢ A willingness and quick ability to learn new software â¢ Excellent communication and presentation skills - be able to handle and synthesize large datasets to deliver critical insights in an easy-to-digest format for management and external partners â¢ Ability to work independently in a fast-paced environment Preferred Qualifications: â¢ Media, entertainment, and/or technology with AI (Claude) experience a plus Required Technical Skills: â¢ Experience with fundamental formulas, VLOOKUP. â¢ Advanced Google Workspace suite skills, particularly Sheets and Slides â¢ Strong financial modeling, forecasting, and analytical skills Job Overview: â¢ The Financial Analyst will play a key role in tracking, analyzing, and reporting on financial data to support business planning and decision-making. â¢ This role is part of the Financial Planning &amp; Analysis team. Our team is collaborative, passionate and aims to drive business decisions on all levels through high quality, accurate, timely, relevant data, analysis, and insights. â¢ This position will primarily support all areas, with a focus on SG&amp;A and Marketing costs and help with KPI metrics pacing reporting. â¢ The ideal candidate will be an effective communicator and have a solid background with PO requests, cash payments, and data ingestion. Responsibilities: â¢ Processing poâs and invoices, assisting with payments, general FP&amp;A support, pulling reports as needed. â¢ Will assist in updating presentation decks to be presented to leadership and handling large datasets. â¢ Working in Google Sheets (or Excel). ? Purchase Orders: Creating and managing purchase orders, ensuring accuracy and proper coding, while tracking status through approval and fulfillment. ? Cash Payme</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9322,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ICS and OT Security Analyst</t>
+          <t>NEW JOB OPENING IT DISASTER RECOVERY &amp; BUSINESS CONTINUITY ANALYST IN REMOTE, USA!</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9347,12 +9337,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TEMP TO HIRE</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9367,7 +9352,7 @@
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Compliance-Analyst-Remote-Rose-International-Job-505654.html</t>
+          <t>https://www.roseint.com/Jobs/Analyst-Remote-Rose-International-Job-505683.html</t>
         </is>
       </c>
       <c r="J129" t="b">
@@ -9375,22 +9360,22 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-08-12T21:30:11+00:00</t>
+          <t>2026-08-13T15:43:44+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>0f9ecfb928bc0ae26625</t>
+          <t>d285ce7db73c44f1a64e</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Required Education:â¢ Bachelors Degree in related field is required. Master's degree in Computer Science, Network Engineering, Cybersecurity, or a related field is preferred. Required Skills:â¢ 5+ years of hands-on security experience â¢ ICS/OT Security: Understanding of OT security principles, network segmentation, and defense-in-depth strategies for industrial environments, including working knowledge of industrial communication protocols including Modbus (RS485 and TCP/IP), BACnet, Profibus, and associated gateway architectures. â¢ Ability to assess protocol-level security risks and identify misconfigurations â¢ Network &amp; Logical Security Fundamentals: Foundational knowledge of firewall rule management, network segmentation principles, and access control models as applied to OT/IT convergence environments â¢ Knowledge of basic vulnerability assessment frameworks (CVE/CVSS scoring, NVD), firmware analysis and patch management â¢ Documentation and Process Discipline: Ability to create clear, structured documentation including decision trees, runbooks, and standard operating proceduresâ¢ Communication and Escalation Judgment: Clear written communication for security assessments and recommendations. Strong ability to distinguish between items that can be resolved independently vs. those requiring SME escalationPreferred Skills:â¢ ICS/OT Security: Experience with industrial control systems in critical infrastructure environments (data centers, power generation, manufacturing, or facilities management) â¢ Familiarity with Supervisory Control and Data Acquisition or building automation systems used in power distribution, cooling, and environmental monitoring â¢ Experience working on or managing projects that have enterprise-wide impact and/or multi-organization cross functional stakeholders â¢ Basic scripting ability (Python, PowerShell, or Bash) or familiarity with AI-agents for developing workflow and process automationOverview:The IDC Security &amp; Compliance team is seeking a Contingent Worker (CW) with Industrial Control Systems (ICS) and Operational Technology (OT) expertise to support the Facilities Ecosystem program within Client eta's Infrastructure Data Center (IDC) Organization. This CW will work with the Facilities Subject Matter Expert (SME) to serve as the first line of review and triage for Facilities security operational workstreams including network integrity, security and compliance, conducting firmware and vulnerability reviews, reviewing firewall exception requests and security intake processing.This is a high-volume operational role requiring an individual who can rapidly assess technical security requests, apply structured decision frameworks, maintain accurate documentation, and manage multiple workstreams. The role is structured in two phases: initial operational execution with process documentation, followed by automation development and capacity building. Responsibility: â¢ Review incoming security intake requests,</t>
+          <t>IT Disaster Recovery &amp; Business Continuity Analyst - Remote, USA | Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING IT DISASTER RECOVERY &amp; BUSINESS CONTINUITY ANALYST IN REMOTE, USA! Date Posted: 08/13/2026 Hiring Organization: Rose International Position Number: 505683 Industry: Aerospace Job Title: IT Disaster Recovery &amp; Business Continuity Analyst Job Location: Remote, USA Work Model: Remote Work Model Details: Minimum 50-mile proximity to a client office Shift: Monday - Thursday 10 hours a day Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 12 Min Hourly Rate($): 50.00 Max Hourly Rate($): 57.97 Must Have Skills/Attributes: Analytical Skills, Disaster Recovery, Incident Management, Infrastructure, Network Fundamentals Experience Desired: IT infrastructure experience, including operating systems, networking, and storage solutions (5+ yrs); Hands-on experience in IT operations with a strong understanding of technical systems and processes (5+ yrs); Experience with IT Disaster Recovery planning and exercise development (3-5+ yrs); Proficiency with data visualization tools, Microsoft Office, and project management software. (3+ yrs); Proven ability to handle Business Continuity and Disaster Recovery events and crises (3+ yrs) Preferred Education: Bachelorâs Degree **C2C is not available** Job Description Preferred Education: â¢ Bachelorsâ degree in related discipline Required Qualifications: â¢ IT infrastructure experience, including operating systems, networking, and storage solutions â¢ Hands-on experience in IT operations with a strong understanding of technical systems and processes â¢ Proven ability to prioritize and manage multiple tasks and projects simultaneously â¢ Excellent written and verbal communication skills with the ability to collaborate effectively with technical and non-technical stakeholders â¢ Knowledge and experience with incident management, including problem-solving and resolution techniques â¢ U.S. Citizenship is required Preferred Qualifications: â¢ Experience with IT Disaster Recovery planning and exercise development â¢ Proven ability to handle Business Continuity and Disaster Recovery events and crises â¢ Proficiency with data visualization tools, Microsoft Office, and project management software. â¢ Crisis management experience in a corporate setting â¢ Understanding of Disaster Recovery and Business Continuity principles, including risk management and compliance â¢ Familiarity with Systems Administration, Engineering, and Testing principles and practices Job Summary: We are seeking a motivated and detail-oriented Disaster Recovery Analyst to support IT Disaster Recovery and Business Continuity initiatives. This role will be responsible for planning, organizing, and controlling scheduled initiatives while gathering relevant facts and data to support decision-making. The Disaster Recovery Analyst will integrate EO IT Disaster Recover</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9387,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING BUSINESS SYSTEMS ANALYST WITH CX &amp; SYSTEMS INTEGRATION IN Remote, USA!</t>
+          <t>NEW JOB OPENING SENIOR CLINICAL BUSINESS ANALYST - CLINICAL UX &amp; IT SERVICE MANAGEMENT IN FREDERICTON, NB, CANADA!</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9412,7 +9397,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9432,7 +9417,7 @@
       </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Systems-Analyst-Remote-Rose-International-Job-505618.html</t>
+          <t>https://www.roseint.com/Jobs/Data-Governance-Lead-NB-Fredericton-Rose-International-Job-505644.html</t>
         </is>
       </c>
       <c r="J130" t="b">
@@ -9440,22 +9425,22 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-08-12T18:33:39+00:00</t>
+          <t>2026-08-12T21:30:11+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>c87e8e91b5496fa3a52f</t>
+          <t>738d21f33952749af52e</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Business Systems Analyst With CX &amp; Systems Integration - Remote, USA | Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING BUSINESS SYSTEMS ANALYST WITH CX &amp; SYSTEMS INTEGRATION IN Remote, USA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505618 Job Title: Business Systems Analyst With CX &amp; Systems Integration Job Location: Remote, USA Work Model: Remote Shift: Standard business hours Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 24.00 Max Hourly Rate($): 28.00 Must Have Skills/Attributes: Business system analyst, Documentation, Requirement Analysis, Requirements Gathering Experience Desired: Business Analysis &amp; Requirements Gathering (2-4 yrs); Google CES/CEP &amp; Contact Center Exp IVR, virtual agents, chat, routing, and agent Desktop (2-4 yrs); Data Analysis &amp; Process Improvement (2-4 yrs); Systems Integration &amp; Systems Thinking (2-4 yrs) Required Minimum Education: Bachelorâs Degree **C2C is not available** Job Description ***Only qualified Business Systems Analyst candidates located within the US will be considered, as this position is fully remote.*** Required Education: â¢ Bachelor's degree in a relevant field Required Skills, Experience, &amp; Abilities: â¢ Two to four years of experience as a business analyst. â¢ Business Acumen: Understand the business objective behind each request and connect requirements to customer experience, revenue, operational efficiency, risk reduction, and strategic outcomes. â¢ Systems Thinking: Analyze end-to-end impacts across platforms, teams, upstream inputs, downstream outputs, integrations, data flows, and operational processes. â¢ Technical Curiosity: Ask strong questions, understand system behavior, learn enough technical detail to challenge assumptions, and translate between business and technology teams. â¢ Facilitation &amp; Stakeholder Management: Lead productive working sessions, draw out requirements from multiple viewpoints, manage competing priorities, and drive alignment across business, product, technology, operations, and vendor teams. â¢ Critical Thinking &amp; Problem Framing: Break vague asks into clear problems, identify root causes, surface options, and recommend practical solutions. â¢ Backlog &amp; Prioritization Discipline: Create well-structured Jira epics, features, and user stories, support grooming, and help sequence work based on value, risk, dependencies, and readiness. â¢ Operational Readiness Awareness: Ensure requirements account for training, communications, reporting, support procedures, compliance needs, launch readiness, and post-production support. â¢ AI &amp; Automation Enablement: Use AI responsibly to accelerate requirements discovery, process mapping, documentation, gap identification, and quality checks while validating outputs against approved source materials. â¢ Ownership &amp; Execution Discipline: Drive work forward with minimal oversight, track de</t>
+          <t>Senior Clinical Business Analyst - Clinical UX &amp; IT Service Management - Fredericton, NB, Canada | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR CLINICAL BUSINESS ANALYST - CLINICAL UX &amp; IT SERVICE MANAGEMENT IN FREDERICTON, NB, CANADA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505644 Industry: Government Job Title: Senior Clinical Business Analyst - Clinical UX &amp; IT Service Management Job Location: Fredericton, NB, Canada, E3B 5X4 Work Model: Hybrid Work Model Details: Primarily remote, Onsite once every month Shift: Monday to Friday (8 AM-5 PM) Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 25 Min Hourly Rate($): 65.00 Max Hourly Rate($): 80.00 Must Have Skills/Attributes: Clinical, Incident Management, ITIL, Project Management, Project Plans, Requirements Gathering, Service Desk Support, User Experience Nice To Have Skills/Attributes: Cerner, EPIC Experience Desired: Demonstrated experience in a formal Project Management capacity (3+ yrs); Experience leading process improvement, service transformation, or technology adoption initiatives (3+ yrs); Demonstrated experience redesigning and streamlining an IT or clinical Service Desk function (3+ yrs); Experience engaging directly with front-line clinicians or end users in a healthcare setting (3+ yrs); Experience applying ITIL-aligned practices to redesign or streamline a Service Desk operation (3+ yrs); Experience supporting or participating in a Clinical Information System (CIS) implementation (1+ yrs); Project Management experience leading multi-stakeholder initiatives in a complex organization (3+ yrs) Required Minimum Education: Bachelorâs Degree Required Certifications/Licenses: ITIL Foundation certification (v3 or v4) or equivalent hands-on application of ITIL practices Preferred Certifications/Licenses: PMP, CAPM, PRINCE2, or ITIL Practitioner/higher **C2C is not available** Job Description Required Education: â¢ A bachelor's level university degree in Business, Healthcare, Information Technology, or a related discipline. An equivalent combination of education and experience may be considered Required Certifications: â¢ ITIL Foundation certification (v3 or v4) or higher. Candidates without formal certification but with a minimum of two (2) years of demonstrated hands-on application of ITIL practices (Incident, Request, Problem, and Knowledge Management) may be considered equivalent Preferred Certifications: â¢ Formal Project Management and/or Service Management certification (e.g., PMP, CAPM, PRINCE2, or ITIL Practitioner/higher) Required Skills: â¢ A minimum of three (3) years of demonstrated experience in a formal Project Management capacity, leading process improvement, service transformation, or technology adoption initiatives from planning through to closure (charters, schedules, RAID logs, status reporting) (3+ Years) â¢ A minimum of three (3) years o</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9452,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING FINANCIAL ANALYST - FP&amp;A, FINANCIAL MODELING &amp; REPORTING IN NEW YORK, NY, USA!</t>
+          <t>NEW JOB OPENING SENIOR SOFTWARE TEST ANALYST DEVSECOPS QA IN LANSING, MI, USA!</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9477,7 +9462,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9497,7 +9482,7 @@
       </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Financial-Analyst-NY-New-York-Rose-International-Job-505670.html</t>
+          <t>https://www.roseint.com/Jobs/Software-Quality-Analyst-MI-Lansing-Rose-International-Job-505635.html</t>
         </is>
       </c>
       <c r="J131" t="b">
@@ -9505,22 +9490,22 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-08-13T15:43:44+00:00</t>
+          <t>2026-08-12T21:30:11+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>c0de0a57e0780739960f</t>
+          <t>6db78f7bb726c4a30449</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Financial Analyst - FP&amp;A, Financial Modeling &amp; Reporting - New York, NY | Onsite, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING FINANCIAL ANALYST - FP&amp;A, FINANCIAL MODELING &amp; REPORTING IN NEW YORK, NY, USA! Date Posted: 08/13/2026 Hiring Organization: Rose International Position Number: 505670 Industry: Media and Entertainment Job Title: Financial Analyst - FP&amp;A, Financial Modeling &amp; Reporting Job Location: New York, NY, USA, 10036 Work Model: Onsite Shift: 9 am - 6 pm EST Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 6 Min Hourly Rate($): 35.00 Max Hourly Rate($): 40.00 Must Have Skills/Attributes: Analytical Skills, Financial Modeling, Forecasting, Google Docs/Sheet/Slide, Google Workspace Experience Desired: Experience in finance, accounting, (1+ yrs); Advanced Google Workspace suite skills, particularly Sheets and Slides (2 yrs); Experience with Excel fundamental formulas, VLOOKUP (2 yrs) Required Minimum Education: Bachelorâs Degree **C2C is not available** Job Description Required Education â¢ Bachelorâs degree Required Experience: â¢ 1+ years of work experience in finance, accounting, or a similar quantitative role Required Qualifications: â¢ A willingness and quick ability to learn new software â¢ Excellent communication and presentation skills - be able to handle and synthesize large datasets to deliver critical insights in an easy-to-digest format for management and external partners â¢ Ability to work independently in a fast-paced environment Preferred Qualifications: â¢ Media, entertainment, and/or technology with AI (Claude) experience a plus Required Technical Skills: â¢ Experience with fundamental formulas, VLOOKUP. â¢ Advanced Google Workspace suite skills, particularly Sheets and Slides â¢ Strong financial modeling, forecasting, and analytical skills Job Overview: â¢ The Financial Analyst will play a key role in tracking, analyzing, and reporting on financial data to support business planning and decision-making. â¢ This role is part of the Financial Planning &amp; Analysis team. Our team is collaborative, passionate and aims to drive business decisions on all levels through high quality, accurate, timely, relevant data, analysis, and insights. â¢ This position will primarily support all areas, with a focus on SG&amp;A and Marketing costs and help with KPI metrics pacing reporting. â¢ The ideal candidate will be an effective communicator and have a solid background with PO requests, cash payments, and data ingestion. Responsibilities: â¢ Processing poâs and invoices, assisting with payments, general FP&amp;A support, pulling reports as needed. â¢ Will assist in updating presentation decks to be presented to leadership and handling large datasets. â¢ Working in Google Sheets (or Excel). ? Purchase Orders: Creating and managing purchase orders, ensuring accuracy and proper coding, while tracking status through approval and fulfillment. ? Cash Payme</t>
+          <t>Senior Software Test Analyst DevSecOps QA - Lansing, MI | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR SOFTWARE TEST ANALYST DEVSECOPS QA IN LANSING, MI, USA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505635 Industry: Government/Staffing Job Title: Senior Software Test Analyst DevSecOps QA Job Location: Lansing, MI, USA, 48933 Work Model: Hybrid Work Model Details: On-site 2 days per week (Tue &amp; Wed) Shift: Mon-Fri 8:00 AM - 5:00 PM Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 40.00 Max Hourly Rate($): 43.00 Must Have Skills/Attributes: Documentation, Regression Testing, Test Cases, Testing, User Acceptance Testing Experience Desired: DevSecOps experience integrating QA/testing activities into modern software development &amp; deployment (5+ yrs); Must have experience using DevOps specifically managing test cases and test plans in DevOps (5+ yrs); Software testing experience with enterprise applications, including functional, integration UAT test (5+ yrs); Working with the customer developing acceptance criteria to support the development of existing user (5+ yrs); Testing large-scale application modernization projects ideally migrating legacy desktop technologies (5+ yrs); End-to-end test planning, including test strategy, test cases, scenarios, scripts, defect management (5+ yrs) Required Minimum Education: Bachelorâs Degree **C2C is not available** Job Description ***Only qualified Software Test Analyst candidates located near the Lansing MI area to be considered due to the position requiring an onsite presence*** REQUIRED EDUCATION: â¢ Bachelor's Degree REQUIRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ The candidate must have a minimum of five (5) years of professional experience in DevSecOps practices and technologies â¢ Must have experience using Microsoft DevOps specifically managing test cases and test plans in DevOps â¢ Must have experience working with the customer developing acceptance criteria to support the development of existing user concepts PREFERRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ Past experience as a tester or with testing tools is a plus This project focuses on modernizing Clientâs legacy desktop applications by transitioning them from outdated technologies, including VB6 and.NET 3.5, to a modern web-based platform. This position will serve as the Quality Assurance Analyst for Agency Services, supporting the client. The Test Analyst will assist with all testing activities within the Quality Assurance Team, facilitating communication with business test representatives and ensuring that critical test issues are addressed or escalated as needed. Additionally, the role involves producing reports, presentations, and meeting minutes related to quality assurance testing tasks and deliverables. JOB RESPONSIBILITIES: â¢ Develop maintain and execute comprehensi</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9517,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING IT DISASTER RECOVERY &amp; BUSINESS CONTINUITY ANALYST IN REMOTE, USA!</t>
+          <t>NEW JOB OPENING TAX ANALYST PROGRAMMER IN SAN DIEGO, CA, USA!</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9542,7 +9527,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9562,7 +9547,7 @@
       </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Analyst-Remote-Rose-International-Job-505683.html</t>
+          <t>https://www.roseint.com/Jobs/Tax-Analyst-CA-San-Diego-Rose-International-Job-505630.html</t>
         </is>
       </c>
       <c r="J132" t="b">
@@ -9570,22 +9555,22 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-08-13T15:43:44+00:00</t>
+          <t>2026-08-12T18:33:39+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>d285ce7db73c44f1a64e</t>
+          <t>8c184cd4f7299492cc2d</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>IT Disaster Recovery &amp; Business Continuity Analyst - Remote, USA | Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING IT DISASTER RECOVERY &amp; BUSINESS CONTINUITY ANALYST IN REMOTE, USA! Date Posted: 08/13/2026 Hiring Organization: Rose International Position Number: 505683 Industry: Aerospace Job Title: IT Disaster Recovery &amp; Business Continuity Analyst Job Location: Remote, USA Work Model: Remote Work Model Details: Minimum 50-mile proximity to a client office Shift: Monday - Thursday 10 hours a day Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 12 Min Hourly Rate($): 50.00 Max Hourly Rate($): 57.97 Must Have Skills/Attributes: Analytical Skills, Disaster Recovery, Incident Management, Infrastructure, Network Fundamentals Experience Desired: IT infrastructure experience, including operating systems, networking, and storage solutions (5+ yrs); Hands-on experience in IT operations with a strong understanding of technical systems and processes (5+ yrs); Experience with IT Disaster Recovery planning and exercise development (3-5+ yrs); Proficiency with data visualization tools, Microsoft Office, and project management software. (3+ yrs); Proven ability to handle Business Continuity and Disaster Recovery events and crises (3+ yrs) Preferred Education: Bachelorâs Degree **C2C is not available** Job Description Preferred Education: â¢ Bachelorsâ degree in related discipline Required Qualifications: â¢ IT infrastructure experience, including operating systems, networking, and storage solutions â¢ Hands-on experience in IT operations with a strong understanding of technical systems and processes â¢ Proven ability to prioritize and manage multiple tasks and projects simultaneously â¢ Excellent written and verbal communication skills with the ability to collaborate effectively with technical and non-technical stakeholders â¢ Knowledge and experience with incident management, including problem-solving and resolution techniques â¢ U.S. Citizenship is required Preferred Qualifications: â¢ Experience with IT Disaster Recovery planning and exercise development â¢ Proven ability to handle Business Continuity and Disaster Recovery events and crises â¢ Proficiency with data visualization tools, Microsoft Office, and project management software. â¢ Crisis management experience in a corporate setting â¢ Understanding of Disaster Recovery and Business Continuity principles, including risk management and compliance â¢ Familiarity with Systems Administration, Engineering, and Testing principles and practices Job Summary: We are seeking a motivated and detail-oriented Disaster Recovery Analyst to support IT Disaster Recovery and Business Continuity initiatives. This role will be responsible for planning, organizing, and controlling scheduled initiatives while gathering relevant facts and data to support decision-making. The Disaster Recovery Analyst will integrate EO IT Disaster Recover</t>
+          <t>Tax Analyst Programmer - San Diego, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING TAX ANALYST PROGRAMMER IN SAN DIEGO, CA, USA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505630 Industry: Software/Financial Services/IT Company Job Title: Tax Analyst Programmer Job Location: San Diego, CA, USA, 92129 Work Model: Hybrid Work Model Details: Hybrid: 3 days/week onsite Shift: Standard Business Hours Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 6 Min Hourly Rate($): 35.00 Max Hourly Rate($): 40.00 Must Have Skills/Attributes: Tax Analysis, Tax Preparation Experience Desired: Income tax preparation or analysis experience (3-7 yrs); Strong understanding of federal and state taxation (3-5+ yrs); In-depth utilization of tax preparation software (3-5+ yrs) Required Minimum Education: Bachelorâs Degree Preferred Education: Masterâs Degree Preferred Certifications/Licenses: Enrolled Agent and/or CPA **C2C is not available** Job Description ***Only qualified Tax Analyst Programmer candidates located near San Diego; CA will be considered due to the position requiring an on-site presence*** Required Education: Bachelor's degree in accounting, finance, or other business-related field. Preferred Education: MS in Accounting, MIS or Taxation and/or MBA highly desirable Preferred Certification: Certification in a tax-related field is highly desirable; Enrolled Agent and/or CPA is preferred Required Skills: â¢ 3-7 years of income tax preparation or analysis experience â¢ Previous in-depth utilization of tax preparation software is highly preferred (3-5+ years) â¢ Strong understanding of federal and state taxation, preferably in multiple tax categories: Individual, business, non-profit, estates and trusts, etc. (3-5+ years) â¢ Strong business analysis skills demonstrating strong business acumen â¢ Aptitude/ability to learn tax content development programming skills â¢ Positive "change agent" mindsets: leadership, optimism, innovation, continuous improvement of work processes â¢ Exhibits continuous learning approaches w/ expanding influence â¢ Consultative, customer-focused approach to problem solving â¢ Demonstrates increasingly influential product leadership and decision-making skills â¢ Ability to partner across teams and functions, and influence across boundaries â¢ Highly organized with strong attention to detail â¢ Superior computer skills, including proficiency in moderate to complex operations utilized in spreadsheet programs or other common computer applications â¢ Excellent written and verbal communication skills Duties: â¢ Tax Analyst Programmers develop requirements that are used to gather tax data, calculate tax scenarios and validate that the tax software complies with tax authority regulations. They may use specialized tools, templates and frameworks to: â¢ Interpret tax laws into logical requirements that are u</t>
         </is>
       </c>
     </row>
@@ -9597,22 +9582,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING SENIOR CLINICAL BUSINESS ANALYST - CLINICAL UX &amp; IT SERVICE MANAGEMENT IN FREDERICTON, NB, CANADA!</t>
+          <t>Senior BI Reporting Analyst - SQL &amp; Tableau</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>San Francisco, CA, 94105, USA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9627,7 +9617,7 @@
       </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Governance-Lead-NB-Fredericton-Rose-International-Job-505644.html</t>
+          <t>https://www.roseint.com/Jobs/Reporting-Analyst-CA-San-Francisco-Rose-International-Job-505662.html</t>
         </is>
       </c>
       <c r="J133" t="b">
@@ -9635,22 +9625,22 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-08-12T21:30:11+00:00</t>
+          <t>2026-08-13T18:35:16+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>738d21f33952749af52e</t>
+          <t>6b8b67e1fd120f422696</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Senior Clinical Business Analyst - Clinical UX &amp; IT Service Management - Fredericton, NB, Canada | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR CLINICAL BUSINESS ANALYST - CLINICAL UX &amp; IT SERVICE MANAGEMENT IN FREDERICTON, NB, CANADA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505644 Industry: Government Job Title: Senior Clinical Business Analyst - Clinical UX &amp; IT Service Management Job Location: Fredericton, NB, Canada, E3B 5X4 Work Model: Hybrid Work Model Details: Primarily remote, Onsite once every month Shift: Monday to Friday (8 AM-5 PM) Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 25 Min Hourly Rate($): 65.00 Max Hourly Rate($): 80.00 Must Have Skills/Attributes: Clinical, Incident Management, ITIL, Project Management, Project Plans, Requirements Gathering, Service Desk Support, User Experience Nice To Have Skills/Attributes: Cerner, EPIC Experience Desired: Demonstrated experience in a formal Project Management capacity (3+ yrs); Experience leading process improvement, service transformation, or technology adoption initiatives (3+ yrs); Demonstrated experience redesigning and streamlining an IT or clinical Service Desk function (3+ yrs); Experience engaging directly with front-line clinicians or end users in a healthcare setting (3+ yrs); Experience applying ITIL-aligned practices to redesign or streamline a Service Desk operation (3+ yrs); Experience supporting or participating in a Clinical Information System (CIS) implementation (1+ yrs); Project Management experience leading multi-stakeholder initiatives in a complex organization (3+ yrs) Required Minimum Education: Bachelorâs Degree Required Certifications/Licenses: ITIL Foundation certification (v3 or v4) or equivalent hands-on application of ITIL practices Preferred Certifications/Licenses: PMP, CAPM, PRINCE2, or ITIL Practitioner/higher **C2C is not available** Job Description Required Education: â¢ A bachelor's level university degree in Business, Healthcare, Information Technology, or a related discipline. An equivalent combination of education and experience may be considered Required Certifications: â¢ ITIL Foundation certification (v3 or v4) or higher. Candidates without formal certification but with a minimum of two (2) years of demonstrated hands-on application of ITIL practices (Incident, Request, Problem, and Knowledge Management) may be considered equivalent Preferred Certifications: â¢ Formal Project Management and/or Service Management certification (e.g., PMP, CAPM, PRINCE2, or ITIL Practitioner/higher) Required Skills: â¢ A minimum of three (3) years of demonstrated experience in a formal Project Management capacity, leading process improvement, service transformation, or technology adoption initiatives from planning through to closure (charters, schedules, RAID logs, status reporting) (3+ Years) â¢ A minimum of three (3) years o</t>
+          <t>Education:â¢ Undergraduate degree preferred; Computer Science/Management Information Systems or related field desiredRequired Skills:â¢ Strong analytical skills; knowledge of SQL and relational databases as well as BI tools such as Tableauâ¢ Microsoft experience: Word, ExcelJob Summary:Responsibilities:â¢ Disseminate information regarding tools, reports, or metadata enhancementsâ¢ Conduct or coordinate tests to ensure that intelligence is consistent with defined needsâ¢ Identify or monitor current and potential customers, using business intelligence toolsâ¢ Synthesize current business intelligence or trend data to support recommendations for actionâ¢ Maintain or update business intelligence tools, databases, dashboards, systems, or methodsâ¢ Manage timely flow of business intelligence information to usersâ¢ Identify and analyze industry or geographic trends with business strategy implicationsâ¢ Provide technical support for existing reports, dashboards, or other toolsâ¢ Maintain library of model documents, templates, or other reusable knowledge assetsâ¢ Create or review technical design documentation to ensure the accurate development of reporting solutionsâ¢ Communicate with customers, competitors, suppliers, professional organizations, or others to stay abreast of industry or business trendsâ¢ Document specifications for business intelligence or information technology (IT) reports, dashboards, or other outputsâ¢ Create business intelligence tools or systems, including design of related databases, spreadsheets, or outputsâ¢ Collect business intelligence data from available industry reports, public information, field reports, or purchased sourcesâ¢ Analyze technology trends to identify markets for future product development or to improve sales of existing productsâ¢ Analyze competitive market strategies through analysis of related product, market, or share trendsâ¢ Generate standard or custom reports summarizing business, financial, or economic data for review by executives, managers, clients, and other stakeholders**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -9662,22 +9652,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING SENIOR SOFTWARE TEST ANALYST DEVSECOPS QA IN LANSING, MI, USA!</t>
+          <t>Senior Financial Analyst</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9692,7 +9687,7 @@
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Software-Quality-Analyst-MI-Lansing-Rose-International-Job-505635.html</t>
+          <t>https://www.roseint.com/Jobs/Financial-Analyst-Remote-Rose-International-Job-505720.html</t>
         </is>
       </c>
       <c r="J134" t="b">
@@ -9700,22 +9695,22 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-08-12T21:30:11+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>6db78f7bb726c4a30449</t>
+          <t>91fa1a6db719c184d303</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Senior Software Test Analyst DevSecOps QA - Lansing, MI | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR SOFTWARE TEST ANALYST DEVSECOPS QA IN LANSING, MI, USA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505635 Industry: Government/Staffing Job Title: Senior Software Test Analyst DevSecOps QA Job Location: Lansing, MI, USA, 48933 Work Model: Hybrid Work Model Details: On-site 2 days per week (Tue &amp; Wed) Shift: Mon-Fri 8:00 AM - 5:00 PM Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 40.00 Max Hourly Rate($): 43.00 Must Have Skills/Attributes: Documentation, Regression Testing, Test Cases, Testing, User Acceptance Testing Experience Desired: DevSecOps experience integrating QA/testing activities into modern software development &amp; deployment (5+ yrs); Must have experience using DevOps specifically managing test cases and test plans in DevOps (5+ yrs); Software testing experience with enterprise applications, including functional, integration UAT test (5+ yrs); Working with the customer developing acceptance criteria to support the development of existing user (5+ yrs); Testing large-scale application modernization projects ideally migrating legacy desktop technologies (5+ yrs); End-to-end test planning, including test strategy, test cases, scenarios, scripts, defect management (5+ yrs) Required Minimum Education: Bachelorâs Degree **C2C is not available** Job Description ***Only qualified Software Test Analyst candidates located near the Lansing MI area to be considered due to the position requiring an onsite presence*** REQUIRED EDUCATION: â¢ Bachelor's Degree REQUIRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ The candidate must have a minimum of five (5) years of professional experience in DevSecOps practices and technologies â¢ Must have experience using Microsoft DevOps specifically managing test cases and test plans in DevOps â¢ Must have experience working with the customer developing acceptance criteria to support the development of existing user concepts PREFERRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ Past experience as a tester or with testing tools is a plus This project focuses on modernizing Clientâs legacy desktop applications by transitioning them from outdated technologies, including VB6 and.NET 3.5, to a modern web-based platform. This position will serve as the Quality Assurance Analyst for Agency Services, supporting the client. The Test Analyst will assist with all testing activities within the Quality Assurance Team, facilitating communication with business test representatives and ensuring that critical test issues are addressed or escalated as needed. Additionally, the role involves producing reports, presentations, and meeting minutes related to quality assurance testing tasks and deliverables. JOB RESPONSIBILITIES: â¢ Develop maintain and execute comprehensi</t>
+          <t>Required Education:â¢ Bachelor's degree in accounting or related financial discipline required. Preferred Education:â¢ An advanced degree in a financial discipline is preferred.Required Skills: â¢ 10+ years of Strong FP&amp;A experience (Opex management, budget cycles, project planning)â¢ Advanced Excelâ¢ Financial systems knowledge + ability to analyze/synthesize data for executives and business partnersPreferred Skills:â¢ Ability to work independently with minimal hand-holding (quick ramp-up)â¢ Comfort pulling from multiple data sourcesâ¢ Ability to thrive in a fast-paced environmentOverview:The main functions of a financial analyst are to gather and analyze financial information; will typically conduct quantitative analyses of information affecting investment programs of public or private institutions. A typical financial analyst is responsible for analyzing and communicating financial information for clients.We are looking for a detail-oriented FP&amp;A professional with 6+ years of experience in operational expenditure (Opex) budget management, ideally within a large-scale tech or media environment. This person will support client's 2027 Budget cycle, owning project-level planning, budget baseline development, and ongoing tracking of Opex spend. Day-to-day responsibilities:â¢ Monitoring actuals vs. plan, managing PO investment priorities, identifying and flagging areas of underrun, and serving as a first responder for Business Partner (BP) queries related to purchase orders (POs), cost center setup, contingent worker (CW) and headcount (HC) configurations, and general budget policy questions. â¢ Additionally, this person will be responsible for running, refreshing and maintaining weekly reports and dashboards to maintain canonical views of Headcount-related metrics â ensuring leadership and cross-functional partners always have access to accurate, up-to-date HC data for planning and decision-making. Pursuant to the California Fair Chance Act, Los Angeles County Fair Chance Ordinance for Employers, Los Angeles Fair Chance Initiative for Hiring Ordinance, and San Francisco Fair Chance Ordinance, qualified applicants will be considered for assignment with arrest and conviction records. Criminal history may have a direct, adverse, and negative relationship with some of the material job duties of this position. These include the duties and responsibilities listed above, as well as the abilities to adhere to company policies, exercise sound judgment, effectively manage stress and work safely and respectfully with others, exhibit trustworthiness, meet client expectations, standards, and accompanying requirements, and safeguard business operations and company reputation.**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -9727,22 +9722,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING TAX ANALYST PROGRAMMER IN SAN DIEGO, CA, USA!</t>
+          <t>Senior Power Platform &amp; Data Analyst</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Oakland, CA, 94612, USA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Tax-Analyst-CA-San-Diego-Rose-International-Job-505630.html</t>
+          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Oakland-Rose-International-Job-505617.html</t>
         </is>
       </c>
       <c r="J135" t="b">
@@ -9765,22 +9765,22 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-12T18:33:39+00:00</t>
+          <t>2026-08-14T00:27:47+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>8c184cd4f7299492cc2d</t>
+          <t>bc65d582f42446f2ca74</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Tax Analyst Programmer - San Diego, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING TAX ANALYST PROGRAMMER IN SAN DIEGO, CA, USA! Date Posted: 08/12/2026 Hiring Organization: Rose International Position Number: 505630 Industry: Software/Financial Services/IT Company Job Title: Tax Analyst Programmer Job Location: San Diego, CA, USA, 92129 Work Model: Hybrid Work Model Details: Hybrid: 3 days/week onsite Shift: Standard Business Hours Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 6 Min Hourly Rate($): 35.00 Max Hourly Rate($): 40.00 Must Have Skills/Attributes: Tax Analysis, Tax Preparation Experience Desired: Income tax preparation or analysis experience (3-7 yrs); Strong understanding of federal and state taxation (3-5+ yrs); In-depth utilization of tax preparation software (3-5+ yrs) Required Minimum Education: Bachelorâs Degree Preferred Education: Masterâs Degree Preferred Certifications/Licenses: Enrolled Agent and/or CPA **C2C is not available** Job Description ***Only qualified Tax Analyst Programmer candidates located near San Diego; CA will be considered due to the position requiring an on-site presence*** Required Education: Bachelor's degree in accounting, finance, or other business-related field. Preferred Education: MS in Accounting, MIS or Taxation and/or MBA highly desirable Preferred Certification: Certification in a tax-related field is highly desirable; Enrolled Agent and/or CPA is preferred Required Skills: â¢ 3-7 years of income tax preparation or analysis experience â¢ Previous in-depth utilization of tax preparation software is highly preferred (3-5+ years) â¢ Strong understanding of federal and state taxation, preferably in multiple tax categories: Individual, business, non-profit, estates and trusts, etc. (3-5+ years) â¢ Strong business analysis skills demonstrating strong business acumen â¢ Aptitude/ability to learn tax content development programming skills â¢ Positive "change agent" mindsets: leadership, optimism, innovation, continuous improvement of work processes â¢ Exhibits continuous learning approaches w/ expanding influence â¢ Consultative, customer-focused approach to problem solving â¢ Demonstrates increasingly influential product leadership and decision-making skills â¢ Ability to partner across teams and functions, and influence across boundaries â¢ Highly organized with strong attention to detail â¢ Superior computer skills, including proficiency in moderate to complex operations utilized in spreadsheet programs or other common computer applications â¢ Excellent written and verbal communication skills Duties: â¢ Tax Analyst Programmers develop requirements that are used to gather tax data, calculate tax scenarios and validate that the tax software complies with tax authority regulations. They may use specialized tools, templates and frameworks to: â¢ Interpret tax laws into logical requirements that are u</t>
+          <t>Required Education:â¢ BA/BS Degree in Marketing, Business, Computer Science, Engineering, Data Analytics, Information Systems, or other related field, or equivalent work experienceRequired Experience, Knowledge &amp; Skills:â¢ Prior utility experienceâ¢ Specific Power Apps domain knowledge (building, releasing, and maintaining Power Apps Solutions for teams) and other power platform skills such as Power BI, Power Automate, and Dataverse experienceâ¢ Cross functional requirements gathering and partnership experienceâ¢ 4 years of related work experience in data analysis, business intelligence, reporting, operations analytics, database management, automation, Power Apps development, or application developmentâ¢ Experience designing, building, deploying, and supporting Canvas or Model-Driven Power Apps in a business or enterprise environmentâ¢ Experience developing Power BI dashboards, enterprise reporting solutions, data models, or KPI scorecardsâ¢ Experience using Microsoft Power Platform technologies such as Power Apps, Power Automate, Dataverse, SharePoint Online, and Microsoft 365 is strongly preferredPreferred Experience, Knowledge &amp; Skills:â¢ Advanced data analysis, data processing, data visualization, and reporting skills with ability to translate complex data into actionable business insightsâ¢ Advanced Microsoft Excel and Access skills, including complex formulas, graphing, VBA, data manipulation, and reporting automationâ¢ Advanced skill writing SQL queries using Oracle, Business Objects, SQL Server, or related database technologiesâ¢ Proficiency with Power Apps, including Canvas apps, Model-Driven apps, forms, galleries, components, connectors, formulas, validation logic, role-based functionality, app testing, app deployment, app documentation, and user supportâ¢ Proficiency with Power BI, DAX, Power Query, data modeling, semantic models, star schema design, fact and dimension tables, data relationships, and dashboard designâ¢ Proficiency with Power Automate, SharePoint Online, Dataverse, Microsoft 365, Teams, Outlook, Excel, and workflow automation conceptsâ¢ Familiarity with Power Platform governance, application lifecycle management, environment strategy, security roles, permissions, solution packaging, release management, and maintainability practicesâ¢ Familiarity with ETL/ELT processes, REST APIs, data warehousing, data governance, data quality controls, and row-level securityâ¢ Familiarity with utility operations, compliance, risk management, audit, governance, or executive reporting environmentsâ¢ Knowledge of UNIX shell programming, base-SAS, Visual Basic, Perl, C, Azure Data Factory, Azure SQL, Synapse Analytics, Microsoft Fabric, or other data platforms is preferredâ¢ Strong organizational skills with ability to independently prioritize work, manage multiple projects, meet deadlines, and deliver high-quality work products with limited supervisionâ¢ Strong communication, presentation, facilitation, and stakeholde</t>
         </is>
       </c>
     </row>
@@ -9792,17 +9792,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Senior BI Reporting Analyst - SQL &amp; Tableau</t>
+          <t>Supply Chain Security &amp; Compliance Analyst</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Francisco, CA, 94105, USA</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Reporting-Analyst-CA-San-Francisco-Rose-International-Job-505662.html</t>
+          <t>https://www.roseint.com/Jobs/Compliance-Analyst-Remote-Rose-International-Job-505669.html</t>
         </is>
       </c>
       <c r="J136" t="b">
@@ -9840,34 +9840,34 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>6b8b67e1fd120f422696</t>
+          <t>930575c9f5057e27bcf9</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Education:â¢ Undergraduate degree preferred; Computer Science/Management Information Systems or related field desiredRequired Skills:â¢ Strong analytical skills; knowledge of SQL and relational databases as well as BI tools such as Tableauâ¢ Microsoft experience: Word, ExcelJob Summary:Responsibilities:â¢ Disseminate information regarding tools, reports, or metadata enhancementsâ¢ Conduct or coordinate tests to ensure that intelligence is consistent with defined needsâ¢ Identify or monitor current and potential customers, using business intelligence toolsâ¢ Synthesize current business intelligence or trend data to support recommendations for actionâ¢ Maintain or update business intelligence tools, databases, dashboards, systems, or methodsâ¢ Manage timely flow of business intelligence information to usersâ¢ Identify and analyze industry or geographic trends with business strategy implicationsâ¢ Provide technical support for existing reports, dashboards, or other toolsâ¢ Maintain library of model documents, templates, or other reusable knowledge assetsâ¢ Create or review technical design documentation to ensure the accurate development of reporting solutionsâ¢ Communicate with customers, competitors, suppliers, professional organizations, or others to stay abreast of industry or business trendsâ¢ Document specifications for business intelligence or information technology (IT) reports, dashboards, or other outputsâ¢ Create business intelligence tools or systems, including design of related databases, spreadsheets, or outputsâ¢ Collect business intelligence data from available industry reports, public information, field reports, or purchased sourcesâ¢ Analyze technology trends to identify markets for future product development or to improve sales of existing productsâ¢ Analyze competitive market strategies through analysis of related product, market, or share trendsâ¢ Generate standard or custom reports summarizing business, financial, or economic data for review by executives, managers, clients, and other stakeholders**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Certifications Required:TAPA FSR/TSR familiarity, C-TPAT, CTPAT validator experience, ASIS PSP or CPP, CFI (Certified Forensic Interviewer)Required Skills:â¢ Program management â Ability to manage multiple concurrent workstreams, track deliverables, and drive projects to completion across cross-functional teamsâ¢ Relationship building â Skilled at establishing trust and productive working relationships with diverse stakeholders including internal teams (IBOS, GSST, DEC, Sourcing) and external parties (carriers, vendors, 3P operators)â¢ Problem solving / adaptability â Demonstrated ability to think on their feet, solve problems in real-time, and adapt to rapidly changing operational environmentsâ¢ Communication â Clear and effective written and verbal communication for conveying security expectations, writing reports, and escalating issuesâ¢ Attention to detail â Ability to assess complex physical and operational security environments against documented standards and identify gapsâ¢ Industry: 3PL, freight brokerage, high-value electronics distribution, luxury goods, autonomous vehicles, pharma cold chain, tobacco or consumer electronics (both are theft-heavy and produce strong operators), hyperscale data center supply chain.Preferred skills:The following skills are beneficial but not required. The Logistics Security SME will provide hands-on training in these areas:â¢ Investigations â Experience conducting security investigations, gathering evidence, interviewing stakeholders, and producing findings reportsâ¢ Intelligence collection, analysis, and assessment â Familiarity with threat monitoring, open-source intelligence, and risk assessment methodologiesâ¢ Supply chain, logistics, and transportation security â Understanding of freight operations, carrier management, GPS tracking systems, chain-of-custody controls, and physical security for goods in transitâ¢ Hardware security â Familiarity with physical security controls for IT hardware assets, data bearing devices, and infrastructure equipmentâ¢ Data center security â Understanding of physical and logical security principles in data center environmentsâ¢ Data bearing device (DBD) security â Knowledge of sanitization requirements, handling procedures, and chain-of-custody for storage medOverview:The client's Security &amp; Compliance team is seeking a Contingent Worker (CW) to support the Supply Chain Security program within Client Infrastructure Data Centers (IDC) organization. This CW will work under the direction of the teamâs Logistics Security Subject Matter Expert (SME) to ensure that business teams across Client implement and adhere to IDC Security standards and requirements for transportation, warehousing, and manufacturing security.This is a hands-on role combining programmatic security work (~80%) with incident response (~20%), requiring an individual who can build relationships across cross-functional teams, manage multiple concurrent workstreams, remain</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst</t>
+          <t>Indirect Auto Credit Analyst</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Phoenix, Arizona, 85001, USA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Financial-Analyst-Remote-Rose-International-Job-505720.html</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006165749/Indirect-Auto-Credit-Analyst</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9905,54 +9905,54 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>91fa1a6db719c184d303</t>
+          <t>65129f2115e0b79bbb2e</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Required Education:â¢ Bachelor's degree in accounting or related financial discipline required. Preferred Education:â¢ An advanced degree in a financial discipline is preferred.Required Skills: â¢ 10+ years of Strong FP&amp;A experience (Opex management, budget cycles, project planning)â¢ Advanced Excelâ¢ Financial systems knowledge + ability to analyze/synthesize data for executives and business partnersPreferred Skills:â¢ Ability to work independently with minimal hand-holding (quick ramp-up)â¢ Comfort pulling from multiple data sourcesâ¢ Ability to thrive in a fast-paced environmentOverview:The main functions of a financial analyst are to gather and analyze financial information; will typically conduct quantitative analyses of information affecting investment programs of public or private institutions. A typical financial analyst is responsible for analyzing and communicating financial information for clients.We are looking for a detail-oriented FP&amp;A professional with 6+ years of experience in operational expenditure (Opex) budget management, ideally within a large-scale tech or media environment. This person will support client's 2027 Budget cycle, owning project-level planning, budget baseline development, and ongoing tracking of Opex spend. Day-to-day responsibilities:â¢ Monitoring actuals vs. plan, managing PO investment priorities, identifying and flagging areas of underrun, and serving as a first responder for Business Partner (BP) queries related to purchase orders (POs), cost center setup, contingent worker (CW) and headcount (HC) configurations, and general budget policy questions. â¢ Additionally, this person will be responsible for running, refreshing and maintaining weekly reports and dashboards to maintain canonical views of Headcount-related metrics â ensuring leadership and cross-functional partners always have access to accurate, up-to-date HC data for planning and decision-making. Pursuant to the California Fair Chance Act, Los Angeles County Fair Chance Ordinance for Employers, Los Angeles Fair Chance Initiative for Hiring Ordinance, and San Francisco Fair Chance Ordinance, qualified applicants will be considered for assignment with arrest and conviction records. Criminal history may have a direct, adverse, and negative relationship with some of the material job duties of this position. These include the duties and responsibilities listed above, as well as the abilities to adhere to company policies, exercise sound judgment, effectively manage stress and work safely and respectfully with others, exhibit trustworthiness, meet client expectations, standards, and accompanying requirements, and safeguard business operations and company reputation.**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Indirect Auto Underwriter | Credit Analyst 🕒 Schedule: 12:00 PM – 9:00 PM MT (weekends required) 📍 Location: Remote - MUST BE LOCATED IN: Colorado, Wyoming, Illinois, Texas, Arizona, Florida, Washington, Georgia, Virginia, OR Hawaii About the Role We’re seeking an experienced Indirect Auto Underwriter to independently review, analyze, and decision auto loan applications sourced through dealerships and credit unions. In this role, you’ll own credit decisions from start to finish while partnering closely with dealers and credit union representatives to maximize funding and approval rates. This position is ideal for underwriters who are confident decision‑makers and thrive in a fast‑paced, high‑volume environment. Key Responsibilities Review and underwrite indirect auto loan applications from dealer and credit union channels Analyze credit bureaus, income calculations, debt‑to‑income (DTI), and loan‑to‑value (LTV) ratios Make final credit decisions: approve, deny, or condition files for additional information Communicate directly with dealers and credit union partners to resolve stipulations and negotiate loan terms Document underwriting decisions clearly across multiple loan origination systems Monitor dealer productivity and support improved look‑to‑book and funding ratios Send completed loan packages to credit unions for final funding Support operational goals related to turnaround time, volume, and quality Mentor junior Credit Analysts as needed Required Qualifications Minimum 2 years of true indirect auto underwriting experience with decision‑making authority Strong experience breaking down credit bureaus, income calculations, LTV, and DTI Hands‑on experience with L360, CUDL, Ideal, Keystone Correlation, Loans PQ, and/or Meridian Link Comfortable working weekends and late shifts (12 PM – 9 PM MT) Strong documentation, communication, and relationship‑building skills Education High school diploma or equivalent required Associate’s or Bachelor’s degree preferred Why This Role Full underwriting autonomy and decision authority High visibility with credit unions and dealers Opportunity to directly influence funding and capture rates Fast‑paced, results‑driven environment with growth potential Pay and Benefits The pay range for this position is $27.00 - $32.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Ty</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Senior Power Platform &amp; Data Analyst</t>
+          <t>Lead Azure Fabric Data Engineer - Remote Position</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Oakland, CA, 94612, USA</t>
+          <t>Phoenix, Arizona, 85001, USA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Oakland-Rose-International-Job-505617.html</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006210958/Lead-Azure-Fabric-Data-Engineer-Remote-Position</t>
         </is>
       </c>
       <c r="J138" t="b">
@@ -9975,49 +9975,49 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-14T00:27:47+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>bc65d582f42446f2ca74</t>
+          <t>d6b506e44408fdaf87b9</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Required Education:â¢ BA/BS Degree in Marketing, Business, Computer Science, Engineering, Data Analytics, Information Systems, or other related field, or equivalent work experienceRequired Experience, Knowledge &amp; Skills:â¢ Prior utility experienceâ¢ Specific Power Apps domain knowledge (building, releasing, and maintaining Power Apps Solutions for teams) and other power platform skills such as Power BI, Power Automate, and Dataverse experienceâ¢ Cross functional requirements gathering and partnership experienceâ¢ 4 years of related work experience in data analysis, business intelligence, reporting, operations analytics, database management, automation, Power Apps development, or application developmentâ¢ Experience designing, building, deploying, and supporting Canvas or Model-Driven Power Apps in a business or enterprise environmentâ¢ Experience developing Power BI dashboards, enterprise reporting solutions, data models, or KPI scorecardsâ¢ Experience using Microsoft Power Platform technologies such as Power Apps, Power Automate, Dataverse, SharePoint Online, and Microsoft 365 is strongly preferredPreferred Experience, Knowledge &amp; Skills:â¢ Advanced data analysis, data processing, data visualization, and reporting skills with ability to translate complex data into actionable business insightsâ¢ Advanced Microsoft Excel and Access skills, including complex formulas, graphing, VBA, data manipulation, and reporting automationâ¢ Advanced skill writing SQL queries using Oracle, Business Objects, SQL Server, or related database technologiesâ¢ Proficiency with Power Apps, including Canvas apps, Model-Driven apps, forms, galleries, components, connectors, formulas, validation logic, role-based functionality, app testing, app deployment, app documentation, and user supportâ¢ Proficiency with Power BI, DAX, Power Query, data modeling, semantic models, star schema design, fact and dimension tables, data relationships, and dashboard designâ¢ Proficiency with Power Automate, SharePoint Online, Dataverse, Microsoft 365, Teams, Outlook, Excel, and workflow automation conceptsâ¢ Familiarity with Power Platform governance, application lifecycle management, environment strategy, security roles, permissions, solution packaging, release management, and maintainability practicesâ¢ Familiarity with ETL/ELT processes, REST APIs, data warehousing, data governance, data quality controls, and row-level securityâ¢ Familiarity with utility operations, compliance, risk management, audit, governance, or executive reporting environmentsâ¢ Knowledge of UNIX shell programming, base-SAS, Visual Basic, Perl, C, Azure Data Factory, Azure SQL, Synapse Analytics, Microsoft Fabric, or other data platforms is preferredâ¢ Strong organizational skills with ability to independently prioritize work, manage multiple projects, meet deadlines, and deliver high-quality work products with limited supervisionâ¢ Strong communication, presentation, facilitation, and stakeholde</t>
+          <t>Think of TEKsystems Global Services (TGS) as the growth solution for enterprises today. We unleash growth through technology, strategy, design, execution and operations with a customer-first mindset for bold business leaders. We deliver cloud, data and customer experience solutions. Our partnerships with leading cloud, design and business intelligence platforms fuel our expertise. We value deep relationships, dedication to serving others and inclusion. We drive positive outcomes for our people and our business, and we stay true to our commitments and act in harmony with our words. We exist to create significant opportunities for people to achieve fulfillment through career success. Ready to join us? Here’s what the opportunity supported through our TGS Talent Acquisition Team requires: Position Overview We are seeking a highly skilled Lead Data Engineer with strong expertise in Microsoft Fabric and Azure analytics ecosystem to design and deliver modern, scalable data platforms. The ideal candidate should be a good team player with 8 or more years of experience in data engineering with Microsoft technologies, deep hands-on expertise in Microsoft Azure Fabric platform (OneLake, Lakehouse, Data Factory pipelines, Synapse Data Engineering, Power BI), and preferably some experience with Azure AI/ML services. This role requires expertise in designing, developing, and deploying secure, scalable, and high-performance cloud-native analytics solutions, mentoring engineering teams, and close collaboration with architects, AI Engineers, Data Scientists, and business stakeholders to deliver impactful, data-driven solutions. This position will require up to 50% travel to customer sites as per project need. Essential Functions • Actively involved in requirement gathering workshops from customers, translating the functional requirements into technical solutions, and translating complex technical concepts into actionable insights for stakeholders • Actively participates in architectural discussions independently or under guidance/supervision from Practice Architect to design and develop effective, efficient, reliable, secure, scalable, and cost-optimized data engineering solutions as per the overall data management strategy • Design and implement modern data platform architectures using Microsoft Fabric, including: o OneLake-based data Lakehouse architectures o Data Factory pipelines within Fabric o Synapse Data Engineering and Data Warehousing experiences • Develop scalable data ingestion, transformation, and orchestration pipelines using Fabric-native tools and Azure services • Design high-performance Lakehouse and Warehouse models following best practices (medallion architecture, dimensional modeling) • Integrate Azure services such as Azure Data Factory, ADLS Gen2, Azure SQL, Databricks (optional) • Build interactive and scalable Power BI semantic models and reports integrated with Fabric • Implement CI/CD pipelines (Azure DevOps/GitHub) for data and analytic</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Supply Chain Security &amp; Compliance Analyst</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Chandler, Arizona, 85224, USA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Compliance-Analyst-Remote-Rose-International-Job-505669.html</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006220916/Production-Support-Analyst</t>
         </is>
       </c>
       <c r="J139" t="b">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-13T18:35:16+00:00</t>
+          <t>2026-08-14T09:46:59+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>930575c9f5057e27bcf9</t>
+          <t>3f0c61efac299216c3d3</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Certifications Required:TAPA FSR/TSR familiarity, C-TPAT, CTPAT validator experience, ASIS PSP or CPP, CFI (Certified Forensic Interviewer)Required Skills:â¢ Program management â Ability to manage multiple concurrent workstreams, track deliverables, and drive projects to completion across cross-functional teamsâ¢ Relationship building â Skilled at establishing trust and productive working relationships with diverse stakeholders including internal teams (IBOS, GSST, DEC, Sourcing) and external parties (carriers, vendors, 3P operators)â¢ Problem solving / adaptability â Demonstrated ability to think on their feet, solve problems in real-time, and adapt to rapidly changing operational environmentsâ¢ Communication â Clear and effective written and verbal communication for conveying security expectations, writing reports, and escalating issuesâ¢ Attention to detail â Ability to assess complex physical and operational security environments against documented standards and identify gapsâ¢ Industry: 3PL, freight brokerage, high-value electronics distribution, luxury goods, autonomous vehicles, pharma cold chain, tobacco or consumer electronics (both are theft-heavy and produce strong operators), hyperscale data center supply chain.Preferred skills:The following skills are beneficial but not required. The Logistics Security SME will provide hands-on training in these areas:â¢ Investigations â Experience conducting security investigations, gathering evidence, interviewing stakeholders, and producing findings reportsâ¢ Intelligence collection, analysis, and assessment â Familiarity with threat monitoring, open-source intelligence, and risk assessment methodologiesâ¢ Supply chain, logistics, and transportation security â Understanding of freight operations, carrier management, GPS tracking systems, chain-of-custody controls, and physical security for goods in transitâ¢ Hardware security â Familiarity with physical security controls for IT hardware assets, data bearing devices, and infrastructure equipmentâ¢ Data center security â Understanding of physical and logical security principles in data center environmentsâ¢ Data bearing device (DBD) security â Knowledge of sanitization requirements, handling procedures, and chain-of-custody for storage medOverview:The client's Security &amp; Compliance team is seeking a Contingent Worker (CW) to support the Supply Chain Security program within Client Infrastructure Data Centers (IDC) organization. This CW will work under the direction of the teamâs Logistics Security Subject Matter Expert (SME) to ensure that business teams across Client implement and adhere to IDC Security standards and requirements for transportation, warehousing, and manufacturing security.This is a hands-on role combining programmatic security work (~80%) with incident response (~20%), requiring an individual who can build relationships across cross-functional teams, manage multiple concurrent workstreams, remain</t>
+          <t>Job Description Strong Attention to Detail: Crucial for tasks like restarting the correct jobs, where a small error can have significant consequences. Independent and Teachable: Must be able to learn quickly, operate with minimal supervision, and adapt to new challenges. Strong Interpersonal Skills: Ability to communicate effectively and assertively with customers and stakeholders to enforce process. Strategic Thinker: Capable of seeing the bigger picture beyond routine tasks and contributing to the long-term improvement of the services. Experience: Experience in a production support or similar operational role is highly preferred. Experience following runbooks and handling operational tasks like monitoring dashboards and escalating issues is expected. Key Responsibilities 24/7 Production Support: Provide on-call support for critical applications, including weekends and holidays, as part of a follow-the-sun model with an existing team in India. Independent Operation: Act as the sole representative of the team during shifts, making decisions and responding to incidents independently. Compliance and Process Adherence: Enforce proper documentation and justification for all requests, pushing back on non-compliant asks that come through informal channels like Teams or email. Incident and Change Management: Handle day-to-day operational tasks, including monitoring queues, managing incidents and change requests, and performing deployments. Process Improvement and Automation: Proactively identify recurring issues, analyze root causes, and drive improvements to streamline processes and reduce manual intervention. The goal is to evolve the role by automating L1-type tasks. Customer Engagement: Meet with application owners to discuss recurring problems and advocate for bug fixes and stability improvements over new feature development. Skills Windows, System administrator, UNIX, linux, autosys, servicenow, splunk, grafana, ticketing, job scheduling, triage, incident Top Skills Details Windows,System administrator,UNIX,linux,autosys,servicenow,splunk,grafana,ticketing,job scheduling,triage,incident Additional Skills &amp; Qualifications NA Experience Level Entry Level Job Type &amp; Location This is a Contract position based out of Chandler, AZ. Pay and Benefits The pay range for this position is $69.25 - $69.25/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO,</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-14T09:46:59+00:00</t>
+          <t>2026-08-14T12:22:54+00:00</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">

--- a/output/data-ai-jobs.xlsx
+++ b/output/data-ai-jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N217"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vancouver, Washington, 98660, USA</t>
+          <t>Annapolis, Maryland, 21401, USA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006268186/Business-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006267663/Business-Analyst</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -565,22 +565,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14e5301c8bbd909e5fe6</t>
+          <t>f23928c645d5b3a7d52b</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Actalent is currently seeking a qualified Business Analyst for a position in Vancouver, WA. This assignment will support the Bonneville Power Administration’s (BPA’s) Transmission Field Services, Business Controls and Information (TFAI) team and specifically, the Asset Data Management (ADM) team. ADM is responsible for providing an accessible, reliable and comprehensive asset data register. The Business Analyst in this assignment will support new reports development for ADM stakeholders, along with quality assurance data analysis. This assignment will assist in achieving the team’s goals of providing accurate and complete data to enable improvements of asset management capabilities. RESPONSIBILITIES INCLUDE: Support the planning and development of a large and complex reporting environment. Provide recommendations for enhancements and support any implementations of this reporting environment; providing on-going training, guidance and technical management of the environment. Collaborate with the Transmission Asset Data Management (ADM) team, its customers and stakeholders to design, develop, recommend and coordinate reporting solutions. Communicate, coordinate and collaborate with business teams to translate ambiguous business problems into actionable requirements and to develop customer-focused analytics. Analyze data from multiple data sources to confirm data integrity, analyze root causes, uncover new patterns and answer key questions. Identify quality assurance/quality control issues and identify failure or maintenance trends. Present compiled information to ADM team for awareness and analysis. Gather and document reporting requirements and work with IT counterparts to develop reporting solutions. Perform routine testing to validate reporting upgrades and verify enhancements meet requirements and do not negatively impact the business. Keep abreast of Business Intelligence best practices, and identify and utilize them in reports, metrics and dashboard solutions. Provide basic end user instruction and support for utilizing reporting and analytics solutions. Collect, organize, and validate data and model results to establish data reporting completeness, accuracy and quality. Communicate technical information (supported systems data, reporting and analysis results, etc.) verbally and in writing to a wide variety of technical and business experts, as well as non-technical users, in both individual and group settings. Qualifications A degree in Information or Computer Technology, Information Technology, Business Management or a closely-related field is preferred. With an applicable Bachelor’s degree, 5 years of experience is required. With an applicable Associate’s degree, 7 years of experience is required. Without an applicable degree, 9 years of experience is required. Experience should be consistent with the specific requirements of business analysis and progressively more technical in nature. Demonstrated experience with report, information and d</t>
+          <t>Job Title: Business Analyst Job Description The Business Analyst plays a key role in translating business, user, and product needs into clear, actionable requirements that support software and platform development in a complex, compliance-driven environment. This position partners closely with product, engineering, and quality assurance teams to ensure requirements are technically sound, testable, and fully traceable across the system lifecycle. Responsibilities Elicit, analyze, and document business, user, and product requirements that capture functional, non-functional, and compliance-related needs. Partner with Product Owners, Engineering, and QA teams to ensure requirements are technically sound, testable, and interconnected across systems. Analyze how requirements impact one another and identify dependencies, constraints, and interactions within integrated system components. Ensure compliance-driven and policy-related requirements are accurately reflected and traceable throughout the system lifecycle. Support QA processes by linking requirements to test cases and validation criteria to achieve complete coverage and end-to-end traceability. Maintain organized, high-quality documentation across Jira, Confluence, and related collaboration and tracking tools. Facilitate requirement review sessions to confirm accuracy, resolve ambiguities, and promote shared understanding across delivery teams. Interpret data flows, system integrations, and functional dependencies to inform requirement design and impact analysis. Collaborate with stakeholders from both technical and business domains to align requirements with strategic objectives and user needs. Essential Skills Minimum of 5 years of experience as a Business Analyst or Systems Analyst supporting software or platform development. Bachelor’s degree in Business, Information Systems, or a related field, or equivalent professional experience. Proven experience in requirements gathering and documentation across business, user, and product domains. Strong understanding of how business, user, and product requirements interrelate within complex system environments. Technical fluency sufficient to interpret data flows, system integrations, and functional dependencies. Experience supporting QA workflows and maintaining requirements-to-test-case traceability. Exceptional analytical skills with the ability to break down complex problems and define clear, structured requirements. Strong communication skills with the ability to bridge technical and business audiences and facilitate collaborative discussions. Ability to ensure compliance and security-related requirements are incorporated into system design and documentation. Additional Skills &amp; Qualifications Proficiency with Jira and Confluence for requirements management, documentation, and collaboration. Experience supporting government programs or compliance-driven software delivery initiatives. Knowledge of NIST standards, FedRAMP requirements, or Departmen</t>
         </is>
       </c>
     </row>
@@ -592,27 +592,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Clinical Research Billing Compliance Analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vancouver, Washington, 98660, USA</t>
+          <t>New Haven, Connecticut, 06501, USA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006242425/Business-Systems-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006264842/Clinical-Research-Billing-Compliance-Analyst</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -635,22 +635,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>388dd6126817c61a07fc</t>
+          <t>26fb9a39607014c232de</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Actalent is currently seeking a qualified Business Systems Analyst for a position in Vancouver, WA. This Business Systems Analyst assignment is in the Transmission Technology System Development and Support (JDD) organization. This position performs systems analysis, interfacing with users to support functional requirements development, analysis of tools and serves as the primary liaison between Transmission Technology business units and the development team. Leads the elicitation, analysis, documentation, and validation of business and functional requirements for new and existing Operational Technology (OT) systems. Translate complex business needs into detailed technical specifications and user stories for system development and enhancement projects.. RESPONSIBILITIES INCLUDE: Work associated with this position will be directly related to business process support for systems change management, process and compliance requirements for the organization. Analyze system infrastructures, functional requirements, and technical capabilities for system acquisitions. Develop or review specifications, verifying that all essential requirements are documented. Distribute requirements to hardware and software configuration items or manual operations using appropriate modeling techniques including automated structured analysis tools. Review the logical top-level design for applications and information systems (including test plans and procedures). Verify that project software specifications, interface requirement specifications and software development plans are correct and of adequate scope. Review and validate that configuration management policies and procedures provide thorough requirements traceability through version release and adequate documentation to support system operation and maintenance. Code, test, install, and document detailed programs while applying applicable standards to all products. Prepare and conduct program presentations, in-house and client training, and functional education. Develop and present recommendations and support analysis for management decisions. Plan/recommend project operations’ schedules. Provide recommendations to BPA management for staffing requirements and resource allocations for projects. Prepare technical reports, documents, studies, and system documentation as required. Develop technical system concepts and designs to support proposal development and position papers. Attend meetings, conferences, and seminars to support the customer needs. Attendance also assists in maintaining currency of technical, procedural and acquisition knowledge. Monitor system performance to determine whether adjustments need to be made, and to determine where changes will need to be made in the future. Confer with system users to document and solve existing system problems. Communicate with management and co-workers by telephone, written form, e-mail, or in person. Support organizations change process and configuration management efforts</t>
+          <t>Clinical Research Billing Compliance Analyst Location: Remote (Candidates must NOT reside in: AK, CA, CT, MS, MO, MT, NV, NM, ND, SD, WY) Position Overview The Clinical Research Billing Compliance Analyst serves as a key liaison between clinical research teams and centralized billing offices. This role is responsible for ensuring accurate billing and compliance with Medicare (CMS) regulations, institutional policies, and clinical trial requirements. The analyst will review billing charges, assess compliance risks, and collaborate with cross-functional stakeholders to drive process improvements and maintain regulatory adherence. Key Responsibilities Conduct risk assessments for clinical trials with billable services using OnCore and protocol documentation Review and validate medical documentation, coding, and billing for accuracy (ICD-10, CPT-4, HCPCS, modifiers) in compliance with regulatory standards Evaluate billing charges from hospital and professional billing offices, ensuring proper designation and compliance alignment Identify discrepancies and collaborate with stakeholders (e.g., Office of Sponsored Projects) to resolve documentation and billing issues Review clinical trial encounters using systems such as OnCore and Epic Maintain detailed logs, dashboards, and audit reports; analyze trends and identify potential risk areas Develop and support corrective action plans with Principal Investigators and study teams Contribute to ongoing monitoring and enhancement of the Research Billing Compliance Program Generate reports and perform data analysis using clinical trial management tools Support training initiatives for research teams on billing compliance, coding accuracy, and regulatory guidelines Stay current with evolving CMS regulations and industry best practices; maintain CPC certification through CEUs Required Skills &amp; Qualifications Bachelor’s degree in a related field 3+ years of clinical research billing, charge review, or compliance experience Experience with clinical trial systems, protocol tracking, and reporting (OnCore required) Strong knowledge of protocols, ICFs, MCA, CTAs, and research billing compliance Proficiency in medical documentation review and coding (ICD-10, CPT, HCPCS) Strong analytical, problem-solving, and critical thinking skills Ability to manage multiple priorities independently in a fast-paced environment Excellent communication, stakeholder engagement, and collaboration skills Proficiency in Microsoft Office (Excel, Word, PowerPoint) Experience with coverage analysis; oncology experience a plus Experience with bridging clinical research and finance Strong presentation and conflict resolution skills Job Type &amp; Location This is a Permanent position based out of New Haven, CT. Pay and Benefits The pay range for this position is $70000.00 - $98000.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowle</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clinical Lab Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ankeny, Iowa, 50021, USA</t>
+          <t>Herndon, Virginia, 20170, USA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["OTHER"]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006260132/Clinical-Lab-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-005234473/Data-Engineer</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -705,22 +705,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1c3a1a11f9327f86bd59</t>
+          <t>2c3bb40f9ec572ed5611</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Clinical Lab Analyst (Overnight Shift) Job Description Responsibilities Perform newborn screening testing on blood spot specimens using immunoassay, enzyme assay, electrophoresis, high-performance liquid chromatography (HPLC), tandem mass spectrometry, and molecular methods. Operate, monitor, and perform daily operation and routine maintenance on laboratory instruments and equipment in accordance with established procedures. Perform calibration of laboratory instruments and assist in troubleshooting instrument and method performance issues. Document and review newborn screening test data, procedures, and results with a high level of accuracy and attention to detail. Release test data and reports for use by physicians, health care professionals, and newborn screening medical follow-up teams, ensuring timeliness and accuracy. Develop and maintain standard operating procedures and assist in preparing documentation for test verification and validation studies. Perform quality control and quality assurance procedures in accordance with established standard operating procedures and policies. Recognize basic problems in laboratory methods and performance, document issues, and assist in troubleshooting to resolve them. Assemble and organize quality control data for further analysis, recognize trends or problems, and participate in root cause analysis. Initiate and document corrective actions in response to identified quality issues and contribute to continuous improvement of laboratory processes. Rotate through three separate testing areas, performing assigned testing in one area per shift and moving to a different area on subsequent shifts. Follow all laboratory safety procedures and regulatory requirements while handling specimens, reagents, and equipment. Collaborate with a small overnight team to ensure continuous coverage and timely completion of newborn screening tests. Use downtime productively by engaging in additional training, cross-training in different testing areas, and enhancing technical knowledge. Essential Skills Bachelor’s degree in Chemistry, Biochemistry, Biology, Genetics, or a related field, or an equivalent combination of education and experience. Eligibility under Clinical Laboratory Improvement Amendments (CLIA) qualifications for high complexity testing, including at least 6 semesters of Biology and 6 semesters of Chemistry. At least 3 months of hands-on laboratory experience, which may include work performed in a laboratory setting during school, beyond standard coursework-only lab classes. Strong foundational knowledge in Chemistry, Biochemistry, Biology, and Genetics. Experience working in a laboratory environment, including handling biological specimens and using standard laboratory equipment. Ability to perform and interpret quality control and quality assurance procedures in alignment with laboratory policies. Attention to detail and strong documentation skills for recording test data, procedures, and results. Ability to r</t>
+          <t>Job Title: Data Engineer 🚨NO C2C🚨 *This will be a W2 contract Job Description Collaborate with Business Intelligence Engineering team members, engineering stakeholders, partner technical teams, and business stakeholders to gather business and functional requirements. Translate these requirements into a robust, scalable, and operable data infrastructure that integrates well within the overall AWS data architecture, leading to improved engineering decisions. Responsibilities Develop a deep understanding and awareness of operational data from the AWS fleet and build mechanisms for retrieving and aggregating such data for use by downstream business intelligence solutions. Develop a deep understanding of our vast data sources and provide continuous recommendations for their use to solve specific business problems. Take ownership of data reliability by performing deep-dives to find root causes of potential data anomalies and taking subsequent action to address these anomalies. Continuously optimize the performance of data queries and address extract, transform, and load (ETL) procedures. Insist on the highest standards by recognizing and adopting best practices in reporting and analysis, including data integrity, test design, analysis, validation, and documentation. Essential Skills Proficient in SQL. Experience in at least one modern scripting or programming language, such as Python, Java, Scala, or NodeJS. Experience with AWS technologies like Redshift, S3, AWS Glue, EMR, Kinesis, Lambda, and IAM roles and permissions. Additional Skills &amp; Qualifications 3+ years of experience in a related field. Bachelor’s degree in computer science, data engineering, or data analytics. Work Environment This position is onsite, requiring presence in the office 5 days a week. 🌟Additional Information: This is a W2 contract opportunity. No C2C. No relocation is offered/provided. Contract is currently set for 6 months. Pay rate is flexible based on experience. Benefits offered. Pay and Benefits The pay range for this position is $50.00 - $60.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Herndon,VA. Application Deadline This position is anticipated to close on Apr 30, 2025. About Actalent Actalent is a global leader in engineering and sciences services and talent solutions. We help visi</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Construction Project Analyst</t>
+          <t>Environmental Monitoring Analyst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bothell, Washington, 98011, USA</t>
+          <t>Raleigh, North Carolina, 27601, USA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006248158/Construction-Project-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006262189/Environmental-Monitoring-Analyst</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -775,22 +775,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3ea1e80f55ae77b92f87</t>
+          <t>22c9844ae229436a0a33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[Job Description] A reputable utility company in Bothell, WA, is currently hiring for a Construction Project Analyst. This position will require running a lot of reports from SAP and BEx queries. The analyst will require relying on system data to pull work, find what's missing, and perform analytical reporting. This position will need someone who is a self-starter, able to run reports to see what has or has not been done, and work with various leadership and stakeholders on the findings. Pay - $35/hr. - $45/hr. Location - Bothell, WA (Hybrid; Will be 50% On-site and 50% Remote) - Must be local in WA (Relocation will not be considered) . Contract Duration - 24-Month Contract (High Possibility for Conversion) [ Responsibilities] Run and manage a high volume of reports from SAP, Business Warehouse (BW), and Business Explorer (BEx) to support construction and communication projects. Rely on system data to identify required work, detect missing information, and perform detailed analytical reporting. Prepare and review wireless and wireline communication billing, ensuring accuracy and completeness. Prepare non-consumption billing and verify that all relevant charges are correctly captured. Coordinate research and resolution of billing issues, collaborating with internal teams and external stakeholders as needed. Manage and track annual rental fees, application fees, and pre-construction prepayments, ensuring they are correctly billed and recorded. Identify potential money leaks and revenue gaps by analyzing complex data sets and billing records. Communicate with clients regarding invoice status for communication-related jobs, providing updates and clarifying discrepancies. Support project managers by supplying timely reports, data insights, and billing information to help them manage their projects effectively. Review and manage pole topping fees and other project-related charges to ensure proper allocation and billing. Ensure data integrity across all reporting and billing processes, validating data sources and correcting inconsistencies. Utilize data to determine appropriate next steps for projects, billing resolutions, and process improvements. Navigate complex data structures and analyze information to determine proper allocation of costs and revenues. Create and maintain reporting, query reports, and BW reports to support ongoing project and financial analysis. Identify opportunities for process improvement and contribute to the automation of manual reporting and billing processes. Work directly with leadership and stakeholders to present findings, explain data-driven recommendations, and support decision-making. [Qualification Requirements] ***Must be residing in the state of WA and be comfortable submitting to a drug test (including THC screening) upon onboarding.*** 2–3+ years of experience in data analysis, preferably in a billing, financial, or project-oriented environment. (Non-negotiable) Strong reporting experience Auditing experience with</t>
+          <t>Environmental Monitoring Analyst Launch Your Career in Pharmaceutical Quality &amp; Microbiology Are you a recent science graduate looking to start a rewarding career in the pharmaceutical or biotechnology industry? The Environmental Monitoring Analyst role is an excellent opportunity to gain hands-on experience in Quality Control, Microbiology, and GMP manufacturing while contributing directly to the production of life-changing medicines. In this role, you'll receive extensive training and mentorship as you learn how pharmaceutical facilities maintain sterile manufacturing environments and ensure the highest standards of product quality and patient safety. You'll work alongside experienced professionals in Quality, Manufacturing, and Laboratory Operations, developing highly sought-after skills that can lead to future opportunities in Microbiology, Quality Assurance, Quality Control, Validation, and other pharmaceutical science careers. What You'll Do Perform environmental monitoring activities throughout pharmaceutical manufacturing and laboratory areas to ensure cleanroom and facility compliance. Collect viable and non-viable air, surface, water, and utility samples used to evaluate contamination control programs. Incubate and analyze microbiological samples, interpret results, and document findings in electronic quality systems. Learn and apply industry-leading Good Manufacturing Practices (GMPs) and aseptic techniques used in regulated pharmaceutical environments. Support routine monitoring of cleanrooms, water systems, compressed gases, and other critical utilities that help ensure product quality and patient safety. Maintain accurate electronic documentation in compliance with pharmaceutical data integrity standards. Collaborate with Quality, Manufacturing, and Laboratory teams to investigate observations and maintain a state of control within the facility. Participate in ongoing training programs designed to develop expertise in environmental monitoring, microbiology, and pharmaceutical quality systems. Contribute to a culture of quality, compliance, teamwork, and continuous improvement. Why This Role is Great for New Graduates Strong training program with hands-on mentorship from experienced scientists and quality professionals. Opportunity to apply classroom knowledge in microbiology, biology, chemistry, and pharmaceutical sciences in a real-world GMP environment. Exposure to pharmaceutical manufacturing, microbiology testing, contamination control, and quality systems. Build foundational industry experience that can lead to advancement in Quality Control, Quality Assurance, Microbiology, Validation, Manufacturing Sciences, and other life sciences career paths. Work for an organization focused on innovation, patient safety, and professional development. What We're Looking For Bachelor's degree in Biology, Microbiology, Chemistry, Pharmaceutical Sciences, Environmental Science, or a related scientific discipline. Recent graduates are encourag</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Methods Analyst</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vancouver, Washington, 98660, USA</t>
+          <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006256545/Financial-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006260242/Methods-Analyst</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -845,22 +845,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>c9c51be154044f8fde59</t>
+          <t>942cb0fca55851f107fe</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Actalent is currently seeking a qualified Financial Analyst for a position in Vancouver, WA. This Financial Analyst assignment will provide support and assistance to the Financial Integrity &amp; Analytics organization (TIBF), supporting the Transmission (T) Business Line for Bonneville Power Administration (BPA). This assignment will serve as a Financial Analyst for the Transmission capital and expense programs designated by the TIBF manager, Internal Operations Manager, Executive Manager or BFTE Project Manager (PM). In addition, this assignment will conduct financial analysis and forecasting of capital, expense, and reimbursable programs to validate compliance with BPA capitalization and expense policies. The Financial Analyst works with a variety of individuals and organizations across BPA, including Executives, Management, Finance, Project Managers, Account Executives, Customer Service Engineers (CSEs), and other Federal Agency Officials. ASSIGNMENT RESPONSIBILITIES Perform financial analysis and provide recommendations based on Federal Energy Regulatory Commission (FERC), Generally Accepted Accounting Principles (GAAP) and A-123 guidelines. Maintain/adhere to internal project analysis policies, processes (update standards, desk procedures), and procedures. Perform work order completion analysis based on the interpretation of FERC, GAAP, internal audit, and A-123 guidelines. With notice and approval from the applicable Project Manager (PM), place capital assets into plant in-service upon project completion, initiating the start of financial depreciation reported and monitored on BPA’s balance sheet. This requires close collaboration and coordination with the PM to properly assign FERC codes to major and minor assets, and to accurately retire assets, ending depreciation. Provide clear, presentable financial reporting data to a variety of stakeholders, such as finance, internal/external auditors, project managers, and executive management based on target dates set for monthly and yearly financial closing activities. Research, identify, track, and process monthly accruals, reversals, and re-accruals for Transmission following accounting guidelines. Recommend appropriate financial action, based on defined Office of Management Budget (OMB) A-123 policies, financial rules, regulations, policies, and procedures. Perform monthly analysis of past and present financial expenditures to estimate and support financial forecasts, and other ad hoc analysis as requested. Evaluate and analyze program costs, identify errors, and recommend appropriate corrective action, monitor until corrections have been completed. Alert the BPA manager of any errors or obstacles encountered. Work closely with Project/Program Manager(s) responsible for capital and expense programs by researching, forecasting, analyzing, extracting, tracking, reviewing, completing, and consolidating costs vs. estimates for major projects. Conduct data analysis and reporting for one or more of the</t>
+          <t>Job Title: Methods Analyst Job Description As a Methods Analyst, you will prepare, plan, and maintain work instructions, including product specifications, assembly manuals, PVA’s, and technique sheets that establish the information required to manufacture parts or assemblies. You will apply estimated standards for tool build times and set up, run, and assembly times to parts and assemblies. Additionally, you will analyze new and complex designs, recommend design changes, and show progressive manufacturing bills of material for parts and assemblies. Responsibilities Prepare, plan, and maintain work instructions including product specifications and assembly manuals. Apply estimated standards for tool build and assembly times. Analyze complex designs and recommend design changes. Issue instructions for tool design and fabrication. Generate requests, parts list, assembly sequence, and condition of supply information. Liaise with all departments to resolve technical problems and facilitate continuous improvement. Develop manufacturing plans based on product strategy. Develop resource plans and program schedules at and below the rate item level. Work in design build teams, providing process capability and produce ability commitments. Investigate discrepant parts and tools using lofted information. Collaborate with Production, Engineering, and Finance for root cause analysis and problem resolution. Essential Skills Methods analysis Continuous improvement Aerospace engineering Manufacturing engineering Preparation and maintenance of work instructions Manufacturing process knowledge Additional Skills &amp; Qualifications Degree in Aerospace, Mechanical, or Manufacturing Engineering 2+ years of manufacturing engineering experience, ideally in an aerospace environment Proficiency in root cause analysis, troubleshooting, and problem-solving Experience with Catia V5 Work Environment This is a union position, 100% on-site, with the requirement to work days, afternoons, and weekends as per the union agreement. Shifts include Days from 7am-3:30pm, Afternoons from 3pm-11:30pm, and Weekends with a 12-hour shift from 8am-8pm, including 8 hours on Friday and Monday. The role involves working closely with production to support root cause analysis on the production floor. Overtime is required and will be compensated in accordance with union rules under Local 673. Job Type &amp; Location This is a Permanent position based out of Mississauga, ON. Pay and Benefits The pay range for this position is $104251.00 - $104251.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Workplace Type This is a fully onsite position in Mississauga,ON. À propos d'Actalent Actalent est un leader mondial dans les services d’ingénierie et de sciences ainsi que dans les solutions de talents. Nous aidons</t>
         </is>
       </c>
     </row>
@@ -872,27 +872,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GIS Analyst</t>
+          <t>Product Support Analyst (Colorado)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, 63101, USA</t>
+          <t>Worthington, Ohio, 43085, USA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>["OTHER"]</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006249048/Product-Support-Analyst-Colorado</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -915,22 +915,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2bb0d66e462a56093e20</t>
+          <t>26a1a78934bae2efea02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
+          <t>Product Support Analyst – Aerospace Job Description This role serves as a customer-facing Product Support Analyst (PSA) embedded onsite with a key aerospace and defense customer in the Denver, Colorado area. You will act as the primary supportability liaison between the customer and engineering, logistics, and program teams based in Ohio. In this position, you support critical aircraft systems and sustainment programs, influence design and lifecycle decisions, and build strong relationships with highly technical customer organizations. The role is ideal for a technically minded professional who communicates clearly, learns complex systems quickly, and collaborates effectively with engineering and program teams. Extensive training, mentoring, and ongoing support are provided for individuals with strong communication skills, technical aptitude, and a willingness to learn. Responsibilities Serve as the primary Supportability Point of Contact (POC) for a major aerospace and defense customer, representing the organization’s product support capabilities onsite. Build and maintain strong relationships with customer engineering, maintenance, and program management teams to ensure effective collaboration and trust. Perform Product Support Analysis (PSA), Logistics Support Analysis (LSA), and supportability assessments to evaluate maintenance concepts, repair strategies, and lifecycle support requirements for aircraft systems. Develop maintenance concepts, support strategies, and sustainment recommendations using PSA and LSA methodologies to optimize system readiness and lifecycle cost. Develop and utilize computer-based models to conduct logistics analysis, functional evaluations, and maintenance planning activities in support of customer programs. Review engineering drawings, schematics, mechanical designs, specifications, and technical documentation to identify supportability impacts and maintenance requirements. Participate in engineering design reviews and collaborate with product development teams to provide supportability-focused recommendations and feedback. Communicate analysis results, findings, and recommendations clearly and professionally to engineering leadership, program managers, and customer stakeholders. Identify support resources, maintenance requirements, and sustainment strategies necessary to maintain system readiness and meet customer performance objectives. Coordinate with internal subject matter experts, engineering teams, and logistics personnel in Ohio to address customer needs and support program deliverables. Manage multiple assignments and priorities simultaneously while adapting to changing customer requirements and program schedules in a fast-paced environment. Function as a trusted onsite representative, building credibility with highly technical customer and engineering organizations through professionalism and technical competence. Support the development of maintenance plans, maintenance strategies, sustainment concepts,</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Geospatial Analyst</t>
+          <t>Purchasing Analyst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Collins, Colorado, 80521, USA</t>
+          <t>Manchester, Connecticut, 06040, USA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006248347/Geospatial-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006251817/Purchasing-Analyst</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -985,22 +985,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>cd25950e4ad21b547b03</t>
+          <t>1e4d6038902999d39bb1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Job Title: Geospatial Analyst / GIS Technician Job Description This Geospatial Analyst / GIS Technician role focuses on mining and managing geospatial data, maintaining large and complex file structures, and performing geometric corrections and orthorectification to ensure high-quality spatial data products. The position supports meaningful national security, intelligence, and defense missions, with daily work contributing to real-world operational outcomes and influencing critical decision-making. Responsibilities Conduct geospatial data mining to identify, extract, and organize relevant spatial information from multiple sources. Manage large geospatial file structures, ensuring data is well-organized, properly documented, and easily accessible for analysis and production. Perform geometric fixes on geospatial datasets to correct spatial inaccuracies and improve positional accuracy. Execute orthorectification tasks to produce accurate, georeferenced imagery suitable for analysis and operational use. Utilize ArcGIS and related geospatial tools to process, analyze, and visualize geospatial data. Apply strong computer skills to handle complex datasets, troubleshoot technical issues, and optimize workflows. Support geospatial and GEOINT missions that contribute to national security, intelligence, and defense objectives. Collaborate with analysts and technologists to ensure geospatial products meet operational requirements and support real-world outcomes. Maintain data integrity and quality control throughout the geospatial processing lifecycle. Essential Skills Proficiency with ArcGIS and related geospatial software tools. Experience performing orthorectification and geometric corrections on geospatial data and imagery. Strong computer skills, including working with large datasets and complex file structures. Background in geography or a related field, ideally supported by a geography degree. Ability to manage and organize large geospatial data repositories effectively. Capacity to support mission-focused geospatial work tied to national security, intelligence, and defense. Additional Skills &amp; Qualifications Geography degree or equivalent education in geospatial sciences, GIS, or a closely related discipline. Interest in supporting GEOINT missions and contributing to real-world operational outcomes. Ability to work independently in a remote or hybrid environment while maintaining high standards of quality and productivity. Strong attention to detail and commitment to data accuracy and integrity. Work Environment The role offers a flexible work environment with options for 100% remote, hybrid, or onsite work, based on candidate preference. The standard work schedule is Monday through Friday, 8:00 AM to 5:00 PM, with the option to work a 4x10 schedule consisting of four 10-hour days. Candidates must reside in Colorado, with a preference for those located in Northern Colorado or the Denver metro area. For any onsite or client-facing activities, the dre</t>
+          <t>Hiring for a Purchasing &amp; Quoting Analyst in Manchester! Position Summary The Purchasing &amp; Quoting Analyst is responsible for managing procurement and supplier sourcing activities that support aerospace manufacturing operations. This role plays a critical part in ensuring the timely acquisition of raw materials, components, and services needed to meet production schedules and customer commitments. Key Responsibilities Supplier Sourcing &amp; Quoting Issue Requests for Quote (RFQs) to suppliers for materials, components, and services. Analyze supplier quotations and evaluate proposals based on price, lead time, quality, capacity, and overall value. Identify and qualify new suppliers to support business requirements and mitigate supply chain risk. Support cost reduction and strategic sourcing initiatives. Purchasing &amp; Procurement Create, process, and manage purchase orders in the ERP/MRP system. Ensure purchase orders are accurate and align with production and inventory requirements. Monitor open purchase orders and maintain accurate purchasing records. Coordinate purchase order changes, revisions, and cancellations as needed. Supplier Management Develop and maintain strong working relationships with suppliers. Track supplier performance related to quality, delivery, responsiveness, and compliance. Resolve supplier-related issues including delivery delays, quality concerns, and documentation discrepancies. Escalate critical supplier performance issues and support corrective action efforts. Required Qualifications 3+ years of purchasing, procurement, sourcing, or supply chain experience in a manufacturing environment. Experience issuing RFQs, evaluating supplier quotes, and managing purchase orders. Knowledge of ERP and/or MRP systems. Strong understanding of procurement processes, supplier management, and inventory planning. Proficiency with Microsoft Office Suite, particularly Excel. Excellent communication, negotiation, and organizational skills. Preferred Qualifications Aerospace, aviation, defense, or other highly regulated manufacturing industry experience. Experience supporting precision manufacturing or metal fabrication operations. Familiarity with AS9100, ISO quality standards, or aerospace supplier requirements. Experience with supplier performance management and expediting activities. Work Environment This position operates within a fast-paced aerospace manufacturing environment and requires frequent interaction with suppliers, production personnel, engineering teams, and quality departments to ensure materials are available when needed and procurement processes are executed efficiently. Job Type &amp; Location This is a Permanent position based out of Manchester, CT. Pay and Benefits The pay range for this position is $62000.00 - $90000.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity,</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geospatial Analyst</t>
+          <t>Quality Control Analyst</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Collins, Colorado, 80521, USA</t>
+          <t>Holly Springs, North Carolina, 27540, USA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006242689/Geospatial-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006268343/Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1055,22 +1055,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>429f10eba16f06b1ba94</t>
+          <t>67560f09528fb1234dcf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Job Title: Geospatial Analyst / GIS Technician Job Description This Geospatial Analyst / GIS Technician role focuses on mining and managing geospatial data, maintaining large and complex file structures, and performing geometric corrections and orthorectification to ensure high-quality spatial data products. The position supports meaningful national security, intelligence, and defense missions, with daily work contributing to real-world operational outcomes and influencing critical decision-making. Responsibilities Conduct geospatial data mining to identify, extract, and organize relevant spatial information from multiple sources. Manage large geospatial file structures, ensuring data is well-organized, properly documented, and easily accessible for analysis and production. Perform geometric fixes on geospatial datasets to correct spatial inaccuracies and improve positional accuracy. Execute orthorectification tasks to produce accurate, georeferenced imagery suitable for analysis and operational use. Utilize ArcGIS and related geospatial tools to process, analyze, and visualize geospatial data. Apply strong computer skills to handle complex datasets, troubleshoot technical issues, and optimize workflows. Support geospatial and GEOINT missions that contribute to national security, intelligence, and defense objectives. Collaborate with analysts and technologists to ensure geospatial products meet operational requirements and support real-world outcomes. Maintain data integrity and quality control throughout the geospatial processing lifecycle. Essential Skills Proficiency with ArcGIS and related geospatial software tools. Experience performing orthorectification and geometric corrections on geospatial data and imagery. Strong computer skills, including working with large datasets and complex file structures. Background in geography or a related field, ideally supported by a geography degree. Ability to manage and organize large geospatial data repositories effectively. Capacity to support mission-focused geospatial work tied to national security, intelligence, and defense. Additional Skills &amp; Qualifications Geography degree or equivalent education in geospatial sciences, GIS, or a closely related discipline. Interest in supporting GEOINT missions and contributing to real-world operational outcomes. Ability to work independently in a remote or hybrid environment while maintaining high standards of quality and productivity. Strong attention to detail and commitment to data accuracy and integrity. Work Environment The role offers a flexible work environment with options for 100% remote, hybrid, or onsite work, based on candidate preference. The standard work schedule is Monday through Friday, 8:00 AM to 5:00 PM, with the option to work a 4x10 schedule consisting of four 10-hour days. Candidates must reside in Colorado, with a preference for those located in Northern Colorado or the Denver metro area. For any onsite or client-facing activities, the dre</t>
+          <t>Job Title: Quality Control Analyst Job Description The Quality Control Analyst works onsite in a GMP-regulated laboratory, performing raw material and product release testing to ensure that all samples meet established quality requirements. This role is available at multiple levels (I, II, or III), with level determined by the depth of experience. The analyst conducts chemistry-based testing, documents results in accordance with regulatory and corporate standards, and supports continuous improvement initiatives within the QC function. Responsibilities Perform raw material compendial chemistry testing for quality control samples in a GMP environment. Conduct product testing related to chemistry methods for quality control samples, ensuring accuracy and reliability of results. Execute GMP testing and associated laboratory tasks without errors, strictly following applicable standard operating procedures (SOPs) and protocols. Ensure all samples are tested according to established quality requirements and that reported results are valid, accurate, and fully documented. Comply with procedures designed to maintain adherence to legal regulations, health and safety standards, and regulatory requirements. Apply data integrity principles to all laboratory activities, ensuring that records are complete, consistent, and traceable. Participate in 6S lean lab operations to maintain an organized, efficient, and safe laboratory environment. Support preventive action and continuous improvement programs aimed at reducing costs and enhancing laboratory efficiency. Use laboratory information management systems (LIMS) to enter, manage, and retrieve test data and results. Operate analytical instruments and perform hands-on analytical testing in accordance with analytical methods and compendial standards. Essential Skills Bachelor's degree in a scientific discipline. Knowledge of Good Manufacturing Practices (GMPs) and their application in a laboratory environment. Strong understanding of laboratory documentation requirements and data integrity principles, including ALCOA. Experience with hands-on analytical testing and familiarity with analytical methods and related instrumentation. Experience using laboratory information management systems (LIMS), including GLIMS Labware. Experience testing with pharmaceutical compendia (USP/EP) or strong knowledge of compendial requirements. Ability to follow SOPs and protocols precisely and perform GMP testing without errors. Attention to detail and ability to generate accurate, valid, and compliant test results. Additional Skills &amp; Qualifications Understanding of GMP principles and their impact on product quality and regulatory compliance. Understanding of ALCOA data integrity principles (Attributable, Legible, Contemporaneous, Original, Accurate). Experience working with compendial testing standards such as USP and EP. Familiarity with 6S or lean laboratory practices and participation in continuous improvement initiatives. Ability</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grain Quality Analyst</t>
+          <t>Quality Control Analyst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ankeny, Iowa, 50021, USA</t>
+          <t>Cambridge, Massachusetts, 02138, USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006267367/Grain-Quality-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006244532/Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1125,22 +1125,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4292a3cdcfebb3902aad</t>
+          <t>b7661d3d978121194e46</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Job Title: Grain Quality Analyst Job Description We are seeking a dedicated Grain Quality Analyst to oversee the receipt, identification, and preparation of samples. The role requires ensuring incoming samples are labeled correctly, appropriate analytical methods are requested, and samples are prepared and analyzed according to ISO work instructions. Responsibilities Identify and prepare samples ensuring proper labeling and analysis requests. Analyze samples based on ISO work instructions. Prioritize analyses according to customer needs and lab capacity. Organize and coordinate projects within a high-throughput laboratory environment. Obtain and ensure integrity of analytical data. Function effectively in multi-discipline teams. Deliver laboratory results in an efficient manner. Essential Skills Experience in laboratory settings. Knowledge in chemistry, biology, GMP, and microbiology. Minimum of a bachelor's degree in a scientific or engineering field such as Chemistry, Chemical Engineering, Biochemistry, Biology, or a related field. At least three years of related industry experience. Additional Skills &amp; Qualifications Hands-on experience with total combustion analysis, elemental analysis, calorimetry, Gas Chromatography (GC), NIR Spectroscopy, NMR, total oil analysis, colorimetry, falling number, farinograph, wet chemical analyses. Experience with LIMS and the Microsoft Office Suite. Work Environment This position operates within a high-throughput laboratory environment, Monday through Friday on a 1st shift schedule. Job Type &amp; Location This is a Contract position based out of Ankeny, IA. Pay and Benefits The pay range for this position is $20.00 - $22.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Ankeny,IA. Application Deadline This position is anticipated to close on Sep 11, 2026. About Actalent Actalent is a global leader in engineering and sciences services and talent solutions. We help visionary companies advance their engineering and science initiatives through access to specialized experts who drive scale, inno</t>
+          <t>Job Title: Quality Control Analyst Job Description The Quality Control (QC) department is essential for ensuring compliance with cGMP operations through the inspection of components and raw materials, as well as quality testing of intermediate, stability, and final product samples. Various techniques, such as assay transfers and validation of new instrumentation, are utilized within the Quality Control Laboratory to maintain cGMP compliance. As a Quality Control Analyst, you will perform routine testing of raw materials, in-process, and final products in accordance with SOPs for product release and validation. Responsibilities Run and execute PCR and PCR techniques. Perform microbiological assays for in-process and final product samples. Conduct analytical methods for final bulk material/finished goods. Test and disposition of raw materials and perform environmental monitoring. Review QC data for compliance to procedures and specifications. Calculate and evaluate results. Participate in lab maintenance and administration duties. Initiate lab investigations and deviations. Provide lab support including glass washing and autoclaving. Demonstrate an understanding of CGMPs and their application to responsibilities. Follow accurate oral and written procedures for testing of in-process and final product samples. Essential Skills Proficiency in PCR techniques and testing. Experience in microbiology, biology, or similar life sciences. Understanding of quality control, microbiology, and qPCR. Familiarity with CGMPs and quality control procedures. Additional Skills &amp; Qualifications BS degree with 3+ years or MS degree with 2-4 years of experience in microbiology, biology, or a related field. Experience with QC bioassays, particularly utilizing PCR. Experience with microbiological testing, biological assays, or environmental monitoring. Work Environment This position operates on a first shift from Monday to Friday during the training period, which takes place in Cambridge. After 2-3 months of training, the schedule will change to Sunday through Thursday, with work locations in both Cambridge and Burlington. Job Type &amp; Location This is a Contract position based out of Cambridge, MA. Pay and Benefits The pay range for this position is $35.00 - $40.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Volunta</t>
         </is>
       </c>
     </row>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Product Complaint Analyst II</t>
+          <t>Senior Quality Control Analyst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, California, 92101, USA</t>
+          <t>Norwood, Massachusetts, 02062, USA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006243995/Product-Complaint-Analyst-II</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006244495/Senior-Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J11" t="b">
@@ -1195,22 +1195,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>daf58113adc61a302ddf</t>
+          <t>aa6aaace0e786e4d6416</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Product Complaint Analyst II Schedule: Monday-Friday | 8:00 AM - 5:00 PM | Hybrid after training (3 days remote, 2 days onsite) Overview We are seeking a detail-oriented Product Complaint Analyst II to join a growing Quality team supporting a high-priority complaint remediation and investigation initiative. This role is responsible for reviewing, investigating, documenting, and closing product complaints while ensuring compliance with FDA regulations, GMP requirements, and internal quality standards. The ideal candidate will have experience in complaint handling, quality systems, and regulated environments such as medical devices, IVD, pharmaceuticals, or biotechnology. Success in this role requires strong analytical skills, excellent documentation practices, and the ability to manage multiple investigations in a fast-paced environment. Key Responsibilities Review, evaluate, and investigate product complaints to determine reportability, impact, and required actions. Conduct thorough complaint investigations, including data gathering, root cause analysis, and documentation of findings. Complete and maintain complaint records in accordance with FDA, GMP, and company quality system requirements. Support risk assessments and quality decision-making related to customer complaints and product performance concerns. Collaborate with Quality Assurance, Regulatory Affairs, Manufacturing, Technical Support, and Operations teams to drive timely complaint resolution. Manage multiple complaint investigations simultaneously while meeting established timelines and quality objectives. Ensure documentation accuracy, completeness, and compliance throughout the complaint handling process. Contribute to complaint backlog reduction, remediation projects, and continuous improvement initiatives. Support quality system activities including CAPA, adverse event evaluation, trend analysis, and corrective action implementation as needed. Required Qualifications Bachelor's degree in Biology, Chemistry, Biotechnology, Life Sciences, Engineering, or a related scientific discipline preferred. Minimum 2-4 years of experience in complaint handling, quality assurance, quality systems, or regulated manufacturing environments. Experience conducting investigations and documenting findings within FDA-regulated industries. Working knowledge of GMPs, quality systems, complaint management processes, and regulatory compliance requirements. Strong written and verbal communication skills with exceptional attention to detail. Ability to prioritize competing responsibilities and manage a high-volume workload effectively. Proficiency with Microsoft Office applications, particularly Excel and Word. Preferred Qualifications Experience within medical device, IVD, biotechnology, pharmaceutical, or other highly regulated industries. Familiarity with complaint management and quality systems software such as Salesforce, TrackWise, MasterControl , or similar platforms. Experience supporting complaint r</t>
+          <t>Quality Control Associate II – Molecular Biology &amp; Bioassays Location: Norwood, MA Schedule: Monday - Friday first shift Experience Level: Intermediate About the Role We are seeking a motivated Quality Control Associate II to support molecular biology and bioassay testing within a regulated laboratory environment. This individual will play a key role in executing QC assays, maintaining laboratory operations, supporting investigations, and ensuring compliance with GMP quality standards. The ideal candidate will have experience in molecular biology techniques, mammalian cell culture, potency assays, and QC testing within a pharmaceutical, biotechnology, or life sciences setting. Key Responsibilities Perform routine quality control testing using molecular biology and bioassay methods, including: qPCR Mammalian cell-based potency assays DNA sequencing Protein analysis techniques Execute raw material, in-process, and drug product testing according to approved methods and procedures. Assist with troubleshooting assay performance, equipment issues, and laboratory investigations. Prepare reagents, standards, media, and other laboratory materials required for testing activities. Support general laboratory operations, including equipment maintenance, housekeeping, calibration activities, and logbook review. Author, revise, and maintain laboratory documentation, including SOPs, protocols, technical reports, and controlled records. Support quality system activities such as investigations, change controls, deviations, and CAPAs. Maintain accurate documentation in accordance with GMP requirements. Participate in internal and external audits and contribute to continuous improvement initiatives. Collaborate effectively with Quality, Manufacturing, Analytical Development, and other cross-functional teams. Required Qualifications Bachelor's degree in Biology, Molecular Biology, Biochemistry, Biotechnology, or a related Life Science discipline. 3-5 years of experience in a cGMP laboratory environment. Hands-on experience with mammalian cell culture and cell-based potency assays. Experience performing molecular biology techniques, including qPCR and sequencing. Experience with protein analysis methods such as ELISA and related biochemical assays. Strong understanding of GMP documentation practices and quality systems. Preferred Qualifications Experience with method development, optimization, qualification, or transfer activities. Experience supporting investigations, CAPAs, and change controls. Familiarity with raw material testing and release processes. Experience working with drug products in a regulated pharmaceutical or biotechnology environment. Technical Skills Mammalian Cell Culture Cell-Based Potency Assays qPCR DNA Sequencing ELISA Protein Analysis GMP Documentation Raw Material Testing Reagent Preparation Laboratory Equipment Calibration &amp; Maintenance Aseptic Technique Biological Safety Cabinet (BSC) Operations Job Type &amp; Location This is a Contract positi</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product Complaint Analyst II</t>
+          <t>Technical Business Analyst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, California, 92101, USA</t>
+          <t>Morrisville, North Carolina, 27560, USA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006249771/Product-Complaint-Analyst-II</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006247087/Technical-Business-Analyst</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1265,54 +1265,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6b4f1d03c76bf4d1361a</t>
+          <t>c131a87765d2a3504726</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Job Title: Product Complaint Analyst II Job Description The Product Complaint Analyst II will play a pivotal role in a high-priority initiative aimed at reviewing, investigating, and resolving product complaints within a regulated quality environment. This position requires the evaluation of incoming complaints, conducting thorough investigations, documenting findings, supporting risk assessments, and ensuring that complaint records comply with quality and compliance standards. Responsibilities Evaluate and analyze incoming product complaints. Conduct detailed investigations into product complaints. Document findings and support risk assessments. Ensure complaint records meet quality and compliance requirements. Collaborate with quality, regulatory, and operational teams to drive complaint closure. Handle high volumes of complaints while maintaining compliance and documentation accuracy. Perform complaint assessments and document investigations. Close complaint cases in a high-volume environment. Essential Skills Experience in complaint handling and investigation. Quality assurance knowledge. Experience in medical device, IVD, or regulated industries. Familiarity with quality and compliance processes. Understanding of GMP documentation and compliance. Experience with FDA-regulated environments. Additional Skills &amp; Qualifications Bachelor's Degree in a science-related discipline preferred. Strong written documentation and organizational skills. Ability to prioritize competing tasks and adapt to changing priorities. Experience with CAPA, complaint documentation, investigations, and quality processes. Experience with Salesforce, Trackwise, MasterControl, and adverse event reporting. Collaborative, team-oriented mindset with the ability to work independently. Work Environment The role operates Monday through Friday from 8:00 AM to 5:00 PM with a hybrid schedule. Initial onsite training is required, followed by a flexible schedule after the training period. The work environment is collaborative, focusing on quality and regulatory processes, with a fast-paced, high-volume workload centered on complaint closure activities. Team members are located across multiple regions and support functions. Job Type &amp; Location This is a Contract position based out of San Diego, CA. Pay and Benefits The pay range for this position is $36.25 - $45.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) R</t>
+          <t>Job Title: Business Analyst Job Description The Business Analyst plays a key role in translating business, user, and product needs into clear, actionable requirements that support software and platform development in a complex, compliance-driven environment. This position partners closely with product, engineering, and quality assurance teams to ensure requirements are technically sound, testable, and fully traceable across the system lifecycle. Responsibilities Elicit, analyze, and document business, user, and product requirements that capture functional, non-functional, and compliance-related needs. Partner with Product Owners, Engineering, and QA teams to ensure requirements are technically sound, testable, and interconnected across systems. Analyze how requirements impact one another and identify dependencies, constraints, and interactions within integrated system components. Ensure compliance-driven and policy-related requirements are accurately reflected and traceable throughout the system lifecycle. Support QA processes by linking requirements to test cases and validation criteria to achieve complete coverage and end-to-end traceability. Maintain organized, high-quality documentation across Jira, Confluence, and related collaboration and tracking tools. Facilitate requirement review sessions to confirm accuracy, resolve ambiguities, and promote shared understanding across delivery teams. Interpret data flows, system integrations, and functional dependencies to inform requirement design and impact analysis. Collaborate with stakeholders from both technical and business domains to align requirements with strategic objectives and user needs. Essential Skills Minimum of 5 years of experience as a Business Analyst or Systems Analyst supporting software or platform development. Bachelor’s degree in Business, Information Systems, or a related field, or equivalent professional experience. Proven experience in requirements gathering and documentation across business, user, and product domains. Strong understanding of how business, user, and product requirements interrelate within complex system environments. Technical fluency sufficient to interpret data flows, system integrations, and functional dependencies. Experience supporting QA workflows and maintaining requirements-to-test-case traceability. Exceptional analytical skills with the ability to break down complex problems and define clear, structured requirements. Strong communication skills with the ability to bridge technical and business audiences and facilitate collaborative discussions. Ability to ensure compliance and security-related requirements are incorporated into system design and documentation. Additional Skills &amp; Qualifications Proficiency with Jira and Confluence for requirements management, documentation, and collaboration. Experience supporting government programs or compliance-driven software delivery initiatives. Knowledge of NIST standards, FedRAMP requirements, or Departmen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Research Contracts Budgets Analyst</t>
+          <t>Data Lead — Data Governance / MDG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anaheim, California, 92801, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006266197/Research-Contracts-Budgets-Analyst</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/data-lead-data-governance-mdg/409871</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1335,39 +1335,39 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>672a1a45c42833c9a84b</t>
+          <t>51dd1f94c7ae7d93ab36</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Job Title: Research Contracts and Budgets Analyst (1-2 days onsite per week) Job Description The Research Contracts and Budgets Analyst (Grants and Contracts Administrator) analyzes clinical trial documents and partners with clinical teams to develop, negotiate, and manage comprehensive budgets that cover institutional research costs. This role works closely with pharmaceutical and medical device companies, clinical research organizations, and external vendors to negotiate study-specific budgets, contract payment terms, master agreements, master fee schedules, and vendor service agreements. The analyst also supports the training and development of junior Grants and Contracts Administrators. Responsibilities Coordinate study agreements from initiation to completion, including study contracts, Study Start-Up Agreements, Accelerated Start-Up Agreements, Service Agreements, Physician Agreements, Master Contracts, and Master Fee Schedules. Prepare and provide tracked changes to contracts that require legal review, submit documents for review, monitor progress, and partner with legal teams to finalize and prepare contracts for execution. Review clinical trial protocols and complete the internal Qualifying Clinical Trial (QCT) checklist, determining the appropriateness of a Coverage Analysis (CA) on a study-by-study basis and collecting Principal Investigator signatures as needed. Develop and negotiate financially feasible budgets that ensure full cost coverage of internal research expenses while adhering to strict project timelines. Collaborate with site teams to confirm resource and expense allocations within budgets, facilitate vendor cost estimates, and clearly document resources and payees for Clinical Trial Management System (CTMS) development. Apply a strong understanding of billing compliance, fair market value, coverage analysis, study essential documents, organizational policies and procedures, and internal quality controls in daily work. Review protocol amendments, protocol letters, and study communications to determine impacts on coverage analysis, contracts, and budgets, and implement necessary changes resulting from these amendments. Use Microsoft Office applications, primarily Excel, to support enhancements to budget templates and tools for improved efficiency and ease of use. Collaborate effectively with post-award teams to resolve issues, understand downstream impacts of finalized budgets and contracts, and support process improvements that streamline post-award workflows. Adapt to changes in standards and processes, support implementation of new practices, and contribute thoughtful ideas and feedback for improvements. Support special projects that require data analysis and data mining to inform decision-making and process optimization. Maintain complete, accurate, and organized files of all project documents and related documentation within internal platforms. Cultivate and maintain positive working relationships with internal stakehol</t>
+          <t>Data Lead — Data Governance / MDG | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Lead — Data Governance / MDG Reference Number: 409871 Published Date: 09/08/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the autonomous mobility sector, is seeking a Data Lead — Data Governance / MDG to join their team. As a Data Lead — Data Governance / MDG, you will be part of the Data Management Department supporting cross-functional teams involved in manufacturing operations and enterprise data initiatives. The ideal candidate will demonstrate strong analytical skills, proactive communication, and collaborative spirit, which will align successfully in the organization. Job Title: Data Lead — Data Governance / MDG Location: Foster City, CA Pay Range: $90-$95/hour+ Benefits What's the Job? Lead current-state assessment of existing data management processes, tools, workflows, controls, and governance practices. Conduct comprehensive gap analysis between current MDM capabilities and target-state MDG solutions, focusing on workflow, approvals, stewardship, and data quality. Evaluate SAP MDG and comparable platforms to determine fit with business needs and existing SAP landscape. Partner with cross-functional teams to define and develop a scalable data governance operating model aligned with enterprise goals. Create detailed roadmaps, executive documentation, and strategic recommendations to support phased implementation and continuous improvement. What's Needed? 8 to 10 years of experience in data management, data governance, or enterprise data roles, with a focus on SAP data processes. Strong understanding of data governance concepts including ownership, stewardship,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Senior Analyst, Quality Control Microbiology</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, Colorado, 80027, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006247188/Senior-Analyst-Quality-Control-Microbiology</t>
+          <t>https://www.manpower.com/en/job/business-operations/financial-analyst/5888049</t>
         </is>
       </c>
       <c r="J14" t="b">
@@ -1405,39 +1405,39 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>eb24e555ded2f22a3108</t>
+          <t>ff4d695254d2ce15734d</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Senior Analyst, Quality Control Microbiology Job Description The Senior Analyst, Quality Control Microbiology plays a key role in ensuring the quality and safety of advanced cell and gene therapy products by performing and reviewing a wide range of microbiological quality control activities in a cGMP-regulated environment. This position supports environmental monitoring, clean utility testing, microbiological qualification, and method and equipment qualification while contributing to a culture of integrity, collaboration, and continuous improvement. The role is ideal for a hands-on QC professional who thrives in a dynamic, mission-driven setting and is passionate about work that directly impacts patients’ lives. Responsibilities Perform and review routine Quality Control microbiology laboratory activities, including environmental monitoring, clean utility sampling and testing, microbiological material qualification and maintenance, microbial identification, raw material sampling and inspection, bioburden testing, endotoxin testing, compendial testing, and container closure integrity testing. Generate, revise, and maintain Quality Control documents in accordance with established document management processes, ensuring accuracy, compliance, and timely completion. With management oversight, execute qualification and validation activities for QC laboratory equipment, instruments, systems, and methods to ensure they remain in a validated and compliant state. Initiate and support microbial excursion investigations related to facility and personnel monitoring programs, including environmental monitoring, aseptic gowning, and utility monitoring, by collaborating closely with cross-functional partners such as Engineering, Manufacturing, and MSAT. Apply and advance Operational Excellence and LEAN principles within the QC laboratories to drive continuous improvement across programs, processes, and systems. Prepare, ship, and track samples to external testing laboratories, ensuring proper documentation, chain of custody, and timely delivery. Support on-the-floor GMP activities by executing laboratory work in compliance with cGMP and GDP requirements, including proper documentation and adherence to standard operating procedures. Perform organism qualification, media qualification, and high-throughput environmental monitoring work to support robust microbiological control programs. Shepherd document changes through the document management system, including drafting, revising, and coordinating approvals for QC procedures and related documents. Collaborate with team members and other departments to ensure work is executed predictably and can be effectively handed off, demonstrating proactive planning and clear communication. Contribute to additional duties within the Quality organization as needed, including supporting release testing, analytical QC platforms, Quality Assurance, and broader Quality Control initiatives for candidates with a growth mindset. Demons</t>
+          <t>Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Financial Analyst Reference Number: 5888049 Published Date: 09/08/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a dedicated Financial Analyst to join their team. As a Financial Analyst, you will be part of the finance department supporting operational and strategic decision-making. The ideal candidate will demonstrate analytical thinking, strong communication skills, and a proactive attitude, which will align successfully in the organization. Job Title: Financial Analyst Location: Houston, TX Shift: 8AM to 5PM or 7AM to 4PM What's the Job? Support financial reporting, planning, and forecasting activities within the manufacturing plant. Prepare management reports, budgets, and financial forecasts to guide business decisions. Analyze financial performance and profitability to identify areas for improvement. Assist in year-end and compliance reporting processes. Conduct ad hoc financial analysis using JDE/Oracle systems and provide actionable insights. What's Needed? Basic experience in financial analysis or related field. Strong analytical and problem-solving skills. Proficiency with financial systems such as JDE or Oracle. Excellent communication and teamwork abilities. Ability to work under general supervision and meet deadlines. What's in it for me? Opportunity to work in a dynamic manufacturing environment. Gain valuable experience in financial planning and analysis. Collaborate with cross-functional teams to support business growth. Develop your skills in financial reporting and systems. Be part of a supportive and inclusive workplace culture. Upon completi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Solutions Analyst</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006252325/Data-Scientist</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/senior-solutions-analyst/410014</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1475,54 +1475,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23e2a29dae901b9ef6cf</t>
+          <t>4213e06280137879c519</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist / Forward Deployed Engineer (No Sponsorship Available/Cannot Support C2C) Locations: Phoenix, AZ Overview Join a newly formed, executive-sponsored AI Transformation team focused on bringing AI solutions from concept to production across a large enterprise environment. This team operates at the intersection of business and technology, partnering directly with stakeholders to identify high-impact opportunities, rapidly prototype solutions, and deliver AI-powered applications that drive measurable business outcomes. This is an opportunity to work on greenfield AI initiatives, influence the future direction of enterprise AI adoption, and help establish best practices for how AI is implemented at scale. What You'll Do Partner directly with business stakeholders to understand challenges and identify AI-driven solutions. Translate ambiguous business requirements into technical architectures and production-ready applications. Design, develop, and deploy AI agents, copilots, and intelligent automation solutions. Rapidly prototype and iterate on solutions to validate business value. Build applications leveraging LLMs, agent frameworks, retrieval systems, and modern AI tooling. Drive projects from ideation through deployment and adoption. Collaborate with product, engineering, and program leadership to deliver measurable outcomes. Advise stakeholders on AI capabilities, limitations, and implementation strategies. Help define standards and best practices for enterprise AI development. Must Haves: 5+ years of software engineering experience. Hands-on experience building and deploying AI applications in production. Strong understanding of LLMs, agentic workflows, prompt/context engineering, and modern AI architectures (in an enterprise capacity) Experience developing AI agents from scratch and integrating external tools, APIs, and services. Experience with agent frameworks, orchestration platforms, MCPs, skills, harnesses, or similar AI ecosystems. Strong system design and architecture skills. Ability to decompose complex business problems into scalable technical solutions. Excellent communication and stakeholder management skills. Demonstrated ability to work in ambiguous, fast-moving environments. Preferred Qualifications Experience with coding agents, AI-assisted software development, or SDLC automation. Background in consulting, solution engineering, forward deployed engineering, or technical leadership roles Exposure to model routing, RAG architectures, vector databases, and enterprise AI platforms. Experience delivering customer-facing or business-facing AI solutions. Prior experience working closely with product teams. Alternate Profile: AI/ML Data Scientist Additional Qualifications Expertise in machine learning, predictive modeling, and statistical analysis. Experience designing and deploying anomaly detection systems. Strong Background in experimentation, model evaluation, and analytics. Ability to identify opportunities where t</t>
+          <t>Senior Solutions Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Solutions Analyst Reference Number: 410014 Published Date: 09/08/2026 Job Type: Permanent Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in manufacturing and supply chain operations, is seeking a Senior Solutions Analyst to join their team. As a Senior Solutions Analyst, you will be part of the IT and Operations support teams, focusing on optimizing business processes through Microsoft Dynamics 365 Business Central. The ideal candidate will demonstrate strong analytical skills, excellent communication, and a proactive approach to problem-solving, which will align successfully in the organization. Job Title: Senior Solutions Analyst Location: Cincinnati, Ohio - Onsite Role What's the Job? Lead and support end-to-end Microsoft Dynamics 365 Business Central (BC) initiatives across warehousing, manufacturing, and supply chain operations. Translate business requirements into clear functional specifications for BC configuration or development. Coordinate with internal developers, ISV partners, and Microsoft resources on custom development, AL extensions, and third-party integrations. Perform hands-on data analysis and validation using SQL to support testing, migration, and troubleshooting. Support change management, end-user training, and provide day-to-day troubleshooting for BC-related processes and systems. What's Needed? 5+ years of experience with Microsoft Dynamics 365 Business Central (or NAV) implementations or major enhancements. Experience with warehousing/distribution and manufacturing environments, including inventory management and production processes. Strong analytical skills with the ability to</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Epic Grand Central Analyst</t>
+          <t>Senior Treasury Analyst - Hybrid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006251260/Epic-Grand-Central-Analyst</t>
+          <t>https://www.manpower.com/en/job/management/senior-treasury-analyst-hybrid/5887310</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>66defb730d21a8c1e031</t>
+          <t>0bb449560a855fcd7fc4</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Epic Grand Central Analyst Location: Remote Duration: Contract Industry: Healthcare IT / Epic Inpatient Overview Our client is seeking an experienced Epic Grand Central Analyst to support critical bed charge build and charge testing initiatives within their Epic environment. This is a backfill opportunity supporting ongoing operational needs and ensuring the successful maintenance and optimization of charge-related workflows. The ideal candidate will have strong Epic Grand Central expertise, hands-on build experience, and experience supporting inpatient charging workflows in a healthcare setting. Key Responsibilities Design, build, and maintain Epic Grand Central functionality. Support bed charge build activities and related workflow optimization. Execute and coordinate charge testing efforts to ensure accurate revenue capture and billing outcomes. Analyze issues, troubleshoot defects, and implement solutions within the Grand Central application. Collaborate with operational, revenue cycle, and clinical stakeholders to validate charge workflows and system functionality. Participate in system upgrades, enhancement projects, and testing activities. Ensure system build aligns with organizational standards and Epic best practices. Required Qualifications Epic Grand Central Certification (required). Hands-on experience with bed charge build. Experience performing and coordinating charge testing activities. Healthcare IT experience supporting Epic applications. Strong analytical, troubleshooting, and communication skills. Ability to work independently in a remote environment. Preferred Qualifications Experience supporting large healthcare systems. Knowledge of inpatient revenue cycle workflows and charge capture processes. Previous experience with Epic implementation, optimization, or migration initiatives. Ideal Candidate The ideal consultant is a self-driven Epic Grand Central analyst with strong build and testing experience who can quickly contribute to ongoing charge-related initiatives. They understand the relationship between operational workflows and revenue integrity and can effectively partner with both technical and operational teams. Why Join? Fully remote opportunity Join a highly respected healthcare organization undergoing continued Epic growth and optimization Support meaningful initiatives that directly impact patient care and operational excellence Work within a large and sophisticated Epic environment Opportunity to contribute to ongoing system enhancements and optimization efforts Collaborative team culture with a strong commitment to innovation and healthcare excellence Job Type &amp; Location This is a Contract position based out of Phoenix, AZ. Pay and Benefits The pay range for this position is $55.00 - $85.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinen</t>
+          <t>Senior Treasury Analyst - Hybrid | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Senior Treasury Analyst - Hybrid Reference Number: 5887310 Published Date: 09/08/2026 Job Type: Permanent Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Our client, a mission-driven research and standards organization focused on safety, sustainability, and public impact, is seeking a Senior Treasury Analyst to join their team. As a Senior Treasury Analyst, you will be part of the Finance team supporting Accounting, Legal, Leadership, and external advisory partners. The ideal candidate will have strong analytical skills, exceptional attention to detail, and effective communication abilities that will align successfully within the organization. Job Title: Senior Treasury Analyst Location: North Side, Cook County, IL (Hybrid) Pay Range: $80,000 - $112,000 + (depending on experience) + Generous Bonus What's the Job? Monitor debt agreements, financing arrangements, loan covenants, and related compliance requirements. Support treasury operations including cash management, banking administration, liquidity monitoring, and wire transfers. Assist with federal, state, and local tax filings, regulatory compliance, and audit support activities. Coordinate investment portfolio reporting, reconciliations, and performance monitoring. Prepare management, Audit Committee, and Board materials while partnering cross-functionally on strategic initiatives. What's Needed? Bachelor's degree in Accounting, Finance, or a related field. Minimum of 5 years of direct treasury experience. Professional certification such as CPA, CTP, or CA preferred. Strong analytical and organizational skills with the ability to manage multiple priorities and deadlines. Excellent communication skills</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jr-Mid Level GCP Data Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>Stafford, Virginia, 22430, USA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006244691/Jr-Mid-Level-GCP-Data-Engineer</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006210438/Business-Analyst</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7fad2b52842395873bac</t>
+          <t>7d42058c21020cf57507</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Jr-Mid Level GCP DATA ENGINEER W2 ONLY - Cannot do C2C or provide sponsorship HYBRID IN PHOENIX, AZ Top Skills' Details 1. 3+ years of experience in Data Engineering including hands on experience working with Hadoop and Google Cloud Data Solutions 2. Experience with GCP Data Services: Big Query, Cloud Storage, Data Proc, Cloud Composer. Experience migrating on prem to GCP 3. 2+ years of real time processing with Kafka, Flink, and Spark Streaming 4. 3+ Years of data lake experience with Python Job Description We are seeking a midlevel Data Engineer with hands‑on expertise in Hadoop, PySpark, Python, and real‑time streaming technologies such as Kafka. This role supports a large‑scale migration of on‑prem data and processing workloads into Google Cloud Platform (GCP). The candidate will be responsible for designing, developing, and deploying data pipelines across both Hadoop and GCP environments in a highly collaborative team setting. The ideal individual is a hard‑core developer who can independently convert requirements into scalable technical designs, perform integration and production deployments, and follow enterprise change‑management and access‑management procedures. The team has an established Hadoop platform and is actively standing up a new GCP platform, making this a critical role for data movement, orchestration, and modernization. Build and support Spark‑based processing pipelines in Hadoop using PySpark and Python Develop and maintain real‑time streaming pipelines using Kafka Design and implement data flows using Spark Streaming and Flink Migrate data and workloads from on‑prem Hadoop to GCP Work extensively with BigQuery, Cloud Composer, Data Proc, and GCP Cloud Storage Translate business and technical requirements into architecture, design, and deployment deliverables Conduct integration testing, production deployments, and pipeline optimization Work closely with internal teams, architects, and stakeholders to support platform enablement Follow enterprise change‑management and access‑management processes Support a newly forming GCP data platform environment while maintaining the existing Hadoop environment Job Type &amp; Location This is a Contract position based out of Phoenix, AZ. Pay and Benefits The pay range for this position is $38.00 - $40.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Li</t>
+          <t>Description, qualifications, and duties: The Team provides focused agile software development and maintenance for a mission-critical application for the government. Today, the application is a client server application developed using Microsoft .NET that supports a database repository of DNA profiles from individuals, unsolved scene evidence, and missing persons. The software allows local, state, and national laboratories to compare DNA profiles electronically, thereby linking serial crimes to each other and identifying suspects by matching DNA profiles from scenes to individuals’ profiles. Additionally, the software is used to assist with the identification of unidentified human remains, missing persons and disaster victims. The team is seeking a proactive and detail-oriented Technical/ Operational Readiness Program Analyst to support our Project and Program Managers in the successful execution of a complex program. This role is critical in bridging the gap between project management and our technical teams working on cutting-edge solutions in Cloud environments. The ideal candidate will have technical experience and a passion for organization, enabling them to effectively track, document, and support the lifecycle of advanced software development, operational readiness, end user communications and integration projects. You will be a key individual contributor, responsible for providing analytical support, facilitating communication, and ensuring project objectives are met in a fast-paced, Agile environment. Skills Agile, confluence, DevSecOps, Program Management, Jira, GitLab, runbooks, rollback strategies, migration Top Skills Details Agile, confluence, DevSecOps, Program Management, Jira, GitLab, runbooks, rollback strategies, migration Additional Skills &amp; Qualifications Desired Skills • Ability to take initiative as a self-starter, ask clarifying questions, and take directions. • Strong written and verbal communication skills for technical, non-technical materials and end-user communications. • Federal Consulting Experience in a fast-paced, matrixed environment. • Experience supporting or coordinating projects in a technical domain, such as software development, cloud computing, or data analytics. • Familiarity with Agile development methodologies and DevSecOps frameworks (e.g., Jira, GitLab, Confluence). Experience Level Intermediate Level Job Type &amp; Location This is a Contract to Hire position based out of Stafford, VA. Pay and Benefits The pay range for this position is $50.00 - $57.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Ins</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1642,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Junior-Mid Level GCP Data Engineer</t>
+          <t>Business Analyst - Workday / HR Payroll</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler, Arizona, 85224, USA</t>
+          <t>Arlington, Virginia, 22201, USA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006244712/Junior-Mid-Level-GCP-Data-Engineer</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006241720/Business-Analyst-Workday-HR-Payroll</t>
         </is>
       </c>
       <c r="J18" t="b">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>dc2f5a30585c1a79f1ae</t>
+          <t>285ff76c3cbe7597df3e</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Jr-Mid Level GCP DATA ENGINEER W2 ONLY - Cannot do C2C or provide sponsorship HYBRID IN Chandler, AZ Top Skills' Details 1. 3+ years of experience in Data Engineering including hands on experience working with Hadoop and Google Cloud Data Solutions 2. Experience with GCP Data Services: Big Query, Cloud Storage, Data Proc, Cloud Composer. Experience migrating on prem to GCP 3. 2+ years of real time processing with Kafka, Flink, and Spark Streaming 4. 3+ Years of data lake experience with Python Job Description We are seeking a midlevel Data Engineer with hands‑on expertise in Hadoop, PySpark, Python, and real‑time streaming technologies such as Kafka. This role supports a large‑scale migration of on‑prem data and processing workloads into Google Cloud Platform (GCP). The candidate will be responsible for designing, developing, and deploying data pipelines across both Hadoop and GCP environments in a highly collaborative team setting. The ideal individual is a hard‑core developer who can independently convert requirements into scalable technical designs, perform integration and production deployments, and follow enterprise change‑management and access‑management procedures. The team has an established Hadoop platform and is actively standing up a new GCP platform, making this a critical role for data movement, orchestration, and modernization. Build and support Spark‑based processing pipelines in Hadoop using PySpark and Python Develop and maintain real‑time streaming pipelines using Kafka Design and implement data flows using Spark Streaming and Flink Migrate data and workloads from on‑prem Hadoop to GCP Work extensively with BigQuery, Cloud Composer, Data Proc, and GCP Cloud Storage Translate business and technical requirements into architecture, design, and deployment deliverables Conduct integration testing, production deployments, and pipeline optimization Work closely with internal teams, architects, and stakeholders to support platform enablement Follow enterprise change‑management and access‑management processes Support a newly forming GCP data platform environment while maintaining the existing Hadoop environment Job Type &amp; Location This is a Contract position based out of Chandler, AZ. Pay and Benefits The pay range for this position is $38.00 - $40.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available</t>
+          <t>Description Primary Responsibilities for this role include but are not limited to: • Creating business requirement documents, use cases, and process maps. • Designing solutions to support non-standard work that meets business needs, workflow changes, and/or process re-engineering. • Act as a liaison between business teams and technical teams to ensure mutual understanding. • Partner with the other Benefits &amp; EBS leads to ensure a common consistent process • Coordinate with SAP, operational, and business process SMEs across RTX • Leading the testing and validation of proposed solutions and ensuring that they meet business requirements. • Assist in training users and providing ongoing support for new or updated systems. • Foster relationships with all internal and external stakeholders and business partners • Assist project management with scheduling, resourcing, and change management activities. Required Skills, Knowledge and Experience: • Prior hands-on experience with the implementation, configuration, or support of timekeeping, payroll, and/or Workday software projects. o Specific knowledge / experience with Paid Time Off, Leave of Absence, Leave Accruals is desired • Must demonstrate expertise in analyzing business processes, gathering requirements, and translating them into actionable solutions • Experience working in cross-functional teams, managing timelines, and collaborating effectively with stakeholders to ensure the successful deployment of software solutions. • Effective written and verbal communication skills and the ability to effectively communicate complex concepts to both technical and non-technical stakeholders and external third parties Qualifications you must have • U.S. citizenship is required, as only U.S. citizens are authorized to access the financial management system due to government contractual requirements. • 10+ years' working experience and knowledge of Business Services business processes and technical system knowledge Skills Business analysis, HR and Payroll IT domain knowledge, Requirements gathering, Agile Top Skills Details Business analysis,HR and Payroll IT domain knowledge,Requirements gathering Additional Skills &amp; Qualifications Enterprise level experience. Must work in a fortune 500 environment Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Arlington, VA. Pay and Benefits The pay range for this position is $55.00 - $60.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following:</t>
         </is>
       </c>
     </row>
@@ -1712,17 +1712,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Power BI Reporting Analyst</t>
+          <t>Incident Analyst</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>Catonsville, Maryland, 21228, USA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006268303/Power-BI-Reporting-Analyst</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006217409/Incident-Analyst</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>e141f844ca747ef3dc94</t>
+          <t>383cc806b9a35c9c9f43</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Power BI Reporting Analyst 100% Remote | Monday-Friday | 8:00 AM-5:00 PM Competitive Pay + Career Growth Opportunity Are you passionate about turning data into actionable business insights? We're partnering with a growing organization seeking a Power BI Reporting Analyst to help drive operational performance and decision-making across a large customer experience organization. This is an opportunity to work directly with business leaders, contact center operations teams, and technical stakeholders to design impactful dashboards, develop KPI reporting, and provide the insights that drive strategic decisions. If you enjoy gathering requirements, solving business problems with data, and building reporting solutions that make a measurable impact, we'd love to hear from you. What You'll Do Partner with business stakeholders and contact center leadership to gather reporting requirements and understand operational needs. Design, develop, and maintain Power BI dashboards, scorecards, and reporting solutions. Create meaningful visualizations that help leaders make data-driven decisions. Build and maintain KPI reporting related to customer experience and operational performance. Collaborate with IT and data teams to identify, validate, and leverage data sources. Write SQL queries to extract, analyze, and validate data. Investigate data discrepancies and ensure reporting accuracy. Support ongoing dashboard enhancements and ad hoc reporting requests. Train end users and stakeholders on dashboard functionality and reporting capabilities. Document reporting requirements, processes, and reporting standards. Required Qualifications 3+ years of experience in reporting, analytics, business intelligence, or data analysis. Hands-on experience building and maintaining Power BI dashboards and reports. Experience gathering business requirements and translating them into reporting solutions. Strong SQL skills and experience working with large datasets. Strong understanding of data visualization best practices. Experience working directly with business stakeholders and leadership teams. Excellent communication, presentation, and documentation skills. Ability to balance multiple reporting priorities in a fast-paced environment. Preferred Qualifications Contact center, customer service, operations, or customer experience reporting experience. Familiarity with metrics such as: Service Level Average Handle Time (AHT) Customer Satisfaction (CSAT) First Call Resolution (FCR) Occupancy Abandonment Rate Volume Forecasting Experience with Power Platform tools. Exposure to data warehousing concepts. Experience coordinating projects or reporting initiatives. Experience with SharePoint or enterprise content management systems. Why Join? 100% remote opportunity. Work directly with senior leadership and influence business decisions. Build enterprise-level reporting solutions used across the customer experience organization. Join a stable, growth-focused company with strong career advan</t>
+          <t>Description The Technical Incident Management (TIM) Analyst is responsible for leading and coordinating the lifecycle of Priority 1-Priority 2 incident, ensuring rapid service restoration, effective stakeholder communication, and proactive identification of recurring service issues. The TIM Analyst serves as the central point of coordination during major incidents, partnering with Service Desk, Infrastructure, Application Support, Network Operations, and business stakeholders to minimize business disruption. Skills Incident management, Root cause analysis, Servicenow, Troubleshooting Additional Skills &amp; Qualifications Major Incident Coordination · Lead Priority 1-2 incidents, management activities from identification through resolution. · Coordinate technical bridge calls and engage appropriate resolver groups. · Drive timely escalation of incidents based on business impact and urgency. · Ensure clear ownership, accountability, and action tracking during incidents. · Facilitate service restoration while minimizing customer impact. Incident Communications · Issue initial incident notifications within established KPI targets. · Provide ongoing executive and stakeholder updates throughout the incident lifecycle. · Publish closure communications and incident summaries following restoration. · Maintain incident records within Ivanti and other service management platforms. · Ensure communication accuracy, consistency, and timeliness. Service Restoration &amp; Operational Excellence · Monitor active high-priority incidents and service-impacting alerts. · Identify workarounds and coordinate rapid response efforts. · Validate restoration activities and confirm service stability before incident closure. · Support intelligent routing and automation initiatives that improve incident response. Job Type &amp; Location This is a Contract position based out of Catonsville, MD. Pay and Benefits The pay range for this position is $30.00 - $35.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully remote position. Application Deadline This position is anticipated to close on Aug 19, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the</t>
         </is>
       </c>
     </row>
@@ -1782,27 +1782,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer/Forward Deployed Engineer</t>
+          <t>Lead AI Engineer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>Hanover, Maryland, 21076, USA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006263472/Senior-AI-Engineer-Forward-Deployed-Engineer</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006267868/Lead-AI-Engineer</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -1825,39 +1825,39 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>460772f93ea5ec5da64f</t>
+          <t>c6434b80178e4cdc70dd</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / Forward Deployed Engineer (No Sponsorship Available / Cannot Support C2C) Location: Hybrid in Phoenix, AZ (Tuesday-Thursday onsite) Compensation: $80-$85/hr W2 + Benefits Duration: 12-Month Contract-to-Hire Opportunity WHY JOIN? Join a newly formed, executive-sponsored AI Transformation organization. Build production AI applications with enterprise-wide impact Work directly with business stakeholders and Senior leadership Help shape AI adoption across a global organization Opportunity to convert into a long-term role with a world-class organization Overview: Join a newly formed, executive-sponsored AI Transformation team focused on bringing enterprise AI solutions from concept to production across a large global organization. This team operates at the intersection of business, product, and engineering, partnering directly with stakeholders to identify high-impact opportunities, rapidly prototype solutions, and deliver AI-powered applications that drive measurable business outcomes. We're looking for engineers who combine strong software development experience with modern AI expertise to solve business problems, build production-ready applications, and accelerate enterprise AI adoption. This is an opportunity to work on greenfield AI initiatives, influence how AI is deployed across the enterprise, and help define the future of agentic AI, intelligent automation, and AI-powered applications at scale. The ideal candidate thrives in ambiguity, enjoys working directly with business stakeholders, and can rapidly translate business challenges into scalable AI-powered solutions. Responsibilities: Partner directly with business stakeholders to understand challenges and identify opportunities for AI-driven transformation. Translate ambiguous business requirements into scalable technical architectures and production-ready solutions. Design, develop, and deploy AI-powered applications, agents, copilots, and intelligent automation workflows. Build production-grade solutions leveraging LLMs, AI agents, MCPs (Model Context Protocol), skills, tools, harnesses, and modern AI frameworks. Rapidly prototype and iterate on solutions to validate business value and gather stakeholder feedback. Evaluate multiple technical approaches and determine the most effective implementation strategy for a given business problem. Develop integrations with enterprise systems, APIs, databases, and business applications. Conduct solution demonstrations and communicate technical concepts to both technical and non-technical audiences. Collaborate closely with product, engineering, and business teams to drive adoption and measurable outcomes. Help establish standards and best practices for enterprise AI development, delivery, evaluation, and governance. Must Haves: 5+ years of software engineering, application development, or product engineering experience. Strong experience building and shipping production software using technologies such as Python, Java, Go, TypeSc</t>
+          <t>Description Think of TEKsystems Global Services (TGS) as the growth solution for enterprises today. We unleash growth through technology, strategy, design, execution and operations with a customer-first mindset for bold business leaders. We deliver cloud, data and customer experience solutions. Our partnerships with leading cloud, design and business intelligence platforms fuel our expertise. We value deep relationships, dedication to serving others and inclusion. We drive positive outcomes for our people and our business, and we stay true to our commitments and act in harmony with our words. We exist to create significant opportunity for people to achieve fulfillment through career success. Ready to join us? Here’s what the opportunity supported through our TGS Talent Acquisition Team requires: We are looking for a highly experienced Lead AI Engineer with expert-level proficiency in Python and machine learning to guide our AI initiatives and mentor a talented engineering team. As a technical leader, you will architect and oversee the development of innovative AI solutions, ensuring best practices and high standards across all projects. Key Responsibilities • Architect, design, and lead the development of advanced machine learning models and AI systems using Python. • Provide technical leadership and mentorship to a team of AI/ML engineers and data scientists. • Oversee end-to-end project lifecycles: from data collection and preprocessing, through model development, to deployment and monitoring. • Collaborate with product managers, business stakeholders, and engineering teams to define AI strategy and translate business objectives into technical solutions. • Establish and enforce best practices for coding, model validation, versioning, and reproducibility. • Review code, provide constructive feedback, and ensure high-quality deliverables. • Stay abreast of the latest research and advancements in AI/ML, and drive the adoption of new technologies and methodologies. • Present technical concepts and project progress to both technical and non-technical audiences. Required Skills &amp; Qualifications • 5+ years of experience in AI/ML engineering, with at least 2 years in a technical leadership or lead role. • Expert-level Python programming skills and deep familiarity with ML libraries (NumPy, pandas, scikit-learn, TensorFlow, LangChain, PyTorch, etc.). • Demonstrated experience architecting and deploying production-grade machine learning systems. • Strong understanding of data engineering, feature engineering, and big data tools. • Experience with cloud platforms (GCP preferred), containerization (Docker, Kubernetes), and MLOps practices. • Excellent communication, leadership, and team management skills. • Bachelor’s or Master’s degree in Computer Science, Engineering, or a related field. Nice to Have • Experience with NLP, computer vision, or generative AI models. • Familiarity with CI/CD pipelines and infrastructure automation for ML projects. • Knowled</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Operational Research Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Fort Meade, Maryland, 20755, USA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1882,67 +1882,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006268122/Operational-Research-Analyst-Data-Scientist</t>
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>9bf4a4e2dae5cc85a155</t>
+          <t>7216ef8d9c0717c37aee</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>**MUST HAVE ACTIVE TS/SCI Clearance Description We are currently seeking an Operations Research Analyst to join our team at Fort Meade, MD. As a cornerstone of strategic decision-making, an Operations Research Analyst leverages advanced analytical and mathematical expertise to optimize organizational processes and solve complex problems. In this role, you will collaborate with diverse teams to dissect intricate issues, forecast outcomes, and implement data-driven solutions that enhance efficiency and productivity. Our ideal candidate possesses a strong aptitude for quantitative analysis, critical thinking, and innovative problem-solving, combined with proficient communication skills to convey technical information effectively to stakeholders. Primary Responsibilities • Develop and apply probability models, statistical inference, simulations, optimization, data analysis, data visualization, and implement mathematical models to solve operational problems. • Introduce quantitative and qualitative analysis, data analytics, and data science to military decision-making processes. • Conduct analysis, assessments, and determine progress of Agency directives by developing measures of performance and measures of effectiveness. • Analyze data to identify trends, patterns, and insights. • Collaborate with cross-functional teams to gather and interpret data. • Create simulations and predictive models to forecast future outcomes. • Optimize resource allocation and logistical processes. • Conduct cost-benefit analysis to evaluate project feasibility. • Prepare and present reports to communicate analytical results and recommendations. • Use statistical software and programming languages to perform analyses. • Monitor the effectiveness of implemented solutions and recommend improvements. • Stay updated with the latest industry trends and analytical techniques. · This position requires an active DoD Clearance (Secret, Top Secret, Top Secret/SCI) or the ability to be obtain an (Interim Secret, Interim Top Secret) · Because an active or interim DoD clearance is required, U.S. Citizenship is required Job Type &amp; Location This is a Contract to Hire position based out of Fort Meade, MD. Pay and Benefits The pay range for this position is $75.00 - $80.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Data Analyst R Programming</t>
+          <t>Power BI Reporting Analyst</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Baltimore, Maryland, 21201, USA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1952,52 +1952,52 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006268328/Power-BI-Reporting-Analyst</t>
         </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>21e4d98805199fb268c1</t>
+          <t>a8f4b8758b4d7af0cf3c</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Power BI Reporting Analyst 100% Remote | Monday-Friday | 8:00 AM-5:00 PM Competitive Pay + Career Growth Opportunity Are you passionate about turning data into actionable business insights? We're partnering with a growing organization seeking a Power BI Reporting Analyst to help drive operational performance and decision-making across a large customer experience organization. This is an opportunity to work directly with business leaders, contact center operations teams, and technical stakeholders to design impactful dashboards, develop KPI reporting, and provide the insights that drive strategic decisions. If you enjoy gathering requirements, solving business problems with data, and building reporting solutions that make a measurable impact, we'd love to hear from you. What You'll Do Partner with business stakeholders and contact center leadership to gather reporting requirements and understand operational needs. Design, develop, and maintain Power BI dashboards, scorecards, and reporting solutions. Create meaningful visualizations that help leaders make data-driven decisions. Build and maintain KPI reporting related to customer experience and operational performance. Collaborate with IT and data teams to identify, validate, and leverage data sources. Write SQL queries to extract, analyze, and validate data. Investigate data discrepancies and ensure reporting accuracy. Support ongoing dashboard enhancements and ad hoc reporting requests. Train end users and stakeholders on dashboard functionality and reporting capabilities. Document reporting requirements, processes, and reporting standards. Required Qualifications 3+ years of experience in reporting, analytics, business intelligence, or data analysis. Hands-on experience building and maintaining Power BI dashboards and reports. Experience gathering business requirements and translating them into reporting solutions. Strong SQL skills and experience working with large datasets. Strong understanding of data visualization best practices. Experience working directly with business stakeholders and leadership teams. Excellent communication, presentation, and documentation skills. Ability to balance multiple reporting priorities in a fast-paced environment. Preferred Qualifications Contact center, customer service, operations, or customer experience reporting experience. Familiarity with metrics such as: Service Level Average Handle Time (AHT) Customer Satisfaction (CSAT) First Call Resolution (FCR) Occupancy Abandonment Rate Volume Forecasting Experience with Power Platform tools. Exposure to data warehousing concepts. Experience coordinating projects or reporting initiatives. Experience with SharePoint or enterprise content management systems. Why Join? 100% remote opportunity. Work directly with senior leadership and influence business decisions. Build enterprise-level reporting solutions used across the customer experience organization. Join a stable, growth-focused company with strong career advan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data Architect ( Hadoop / Spark )</t>
+          <t>Security Analyst</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Columbia, Maryland, 21044, USA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2022,35 +2022,35 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006228785/Security-Analyst</t>
         </is>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>067704edcb00e117f37a</t>
+          <t>8d695f020de6ce501228</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
+          <t>Description Position Overview The Information Security Analyst II (GRC) provides support for Governance, Risk, and Compliance activities aligned to NIST CSF, NIST SP 800-53, HIPAA Security Rule, and HITRUST CSF, PCI-DSS. The role supports risk assessments, audit readiness, control validation, and policy governance. Essential Duties and Responsibilities • Support compliance initiatives aligned to NIST, HIPAA, and HITRUST, PCI-DSS frameworks • Assist in maintaining control mappings and compliance documentation • Perform control testing and support evidence collection for audits • Support HITRUST certification readiness activities • Support enterprise cyber-risk management activities • Execute and oversee the third-party risk management process • Maintain and update the risk register and track remediation • Support responses to third-party security questionnaires. Support contract review tasks in support of Cyber and Data security language. • Assist with development and maintenance of security policies and standards • Maintain audit documentation repositories • Support reporting on compliance metrics and KPIs • Collaborate with cross-functional teams to address risk and compliance gaps Minimum Requirements • 3-5 years of experience in information security, risk, or compliance • Bachelor's degree in systems/ IT Security related field • Certified in CISSP, CISM or CRISC –ISACA preferred • Knowledge of NIST CSF, NIST 800-53, HIPAA, and HITRUST, PCI-DSS • Strong analytical, documentation, and communication skills • Ability to work collaboratively across teams. • Self-Driven – Ability to manage tasks and organize project work Skills hipaa compliance, hitrust, nist, information security, security Top Skills Details hipaa compliance,hitrust,nist Additional Skills &amp; Qualifications Security Analyst • Contract alignment • Implementing Security controls • Risk Management – 3rd party risk management program • Governance and Risk Management • HIPAA and HI-TRUST experience is highly desired Experience Level Intermediate Level Job Type &amp; Location This is a Contract to Hire position based out of Columbia, MD. Pay and Benefits The pay range for this position is $55.00 - $60.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Data Architect With Azure</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2016-03-29</t>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5e42a504d189fe30c4fa</t>
+          <t>9bf4a4e2dae5cc85a155</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Analyst R Programming</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2acf8accb8cab7cf4980</t>
+          <t>21e4d98805199fb268c1</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
+          <t>Data Architect ( Hadoop / Spark )</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2016-02-12</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>42d3008393a735c10ebf</t>
+          <t>067704edcb00e117f37a</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Data Architect With Azure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2016-01-25</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2320,17 +2320,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>dd7b5f57e42a3e48d371</t>
+          <t>5e42a504d189fe30c4fa</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Database Administrator (NoSQL / Oracle)</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2390,17 +2390,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>eb910a182e0aacee19cf</t>
+          <t>2acf8accb8cab7cf4980</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IVR Business Analyst</t>
+          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-02-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2460,17 +2460,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>29d3945c6149cb7d27ce</t>
+          <t>42d3008393a735c10ebf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kronos Analyst</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2016-01-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>48ab717cae2854563a90</t>
+          <t>dd7b5f57e42a3e48d371</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle eBS Techno Functional Analyst</t>
+          <t>Database Administrator (NoSQL / Oracle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2016-12-05</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J31" t="b">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>c46f1d2e683e01fd3d10</t>
+          <t>eb910a182e0aacee19cf</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Report developer/analyst/consultant</t>
+          <t>IVR Business Analyst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>05b173f523c68702bbf4</t>
+          <t>29d3945c6149cb7d27ce</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>System Analyst (BI/DWH)</t>
+          <t>Kronos Analyst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2016-03-21</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>e765218d0ec589c265ea</t>
+          <t>48ab717cae2854563a90</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Workforce Management Analyst</t>
+          <t>Oracle eBS Techno Functional Analyst</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2016-12-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -2810,49 +2810,49 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0d140e426844c92e6ab8</t>
+          <t>c46f1d2e683e01fd3d10</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Report developer/analyst/consultant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28262, US</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049612_usa/ai-engineer</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2875,54 +2875,54 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-04T18:05:42+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>300ddf8602f49da4c185</t>
+          <t>05b173f523c68702bbf4</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>AI Engineer\nLocation: Charlotte, NC (Partial Remote)\n \nRole Overview\nWe are seeking a Senior AI Engineer to design and build enterprise AI search solutions. This role focuses on creating systems that allow users to ask questions in plain language and receive answers from large collections of company documents and data. This is a highly technical, individual-contributor position centered on intelligent document search and knowledge retrieval platforms. The ideal candidate will have hands-on experience with Azure AI technologies, AI-powered search, RAG architecture, and Python development for production-grade AI applications.\n \nKey Responsibilities\nDesign, build, test, deploy, and continuously improve AI-driven search and document-intelligence solutions.Translate business requirements, epics, and user stories into technical designs, estimates, and implementation activities.Build and enhance solutions using Azure AI Search, retrieval-augmented generation (RAG) across multiple indexes, query orchestration, and prompt engineering.Configure and tune semantic, keyword, vector, and hybrid retrieval, including query rewriting, scoring profiles, and reranking.\n*Deploy and support scalable AI applications using Kubernetes-based container environments.\nIntegrate structured and unstructured content, document-processing tools, and metadata to improve indexing and retrieval.Provide technical guidance, conduct peer reviews, and share knowledge with other developers.Collaborate with product, architecture, security, and quality teams to resolve technical issues and prepare solutions for release.Apply secure document-handling practices during solution design and implementation.Document technical designs, implementation decisions, and operating considerations.\nRequired Qualifications\nEducation: A bachelor’s or master’s degree in Computer Science or a related field, an applicable professional certification, or equivalent experience is required.\n \nExperience: A minimum of five years of progressive experience developing solutions for complex system problems is required. At least three years of experience in AI, machine learning, cloud-based search, or document processing is necessary.\n \nTechnical Skills: Hands-on experience with Azure AI Search, Document Intelligence, Cognitive Services, retrieval-augmented generation, and hybrid retrieval is required. Experience with Kubernetes-based container deployment and Python development for AI pipelines is also required.\n \nPreferred Qualifications\nExperience with hybrid cloud AI solutions.Familiarity with Azure OpenAI, LangChain, or AI Foundry.Experience with multi-index query orchestration and vector databases such as FAISS, Weaviate, or Pinecone.Experience in RRF and reranking strategies.A background in natural language processing, document classification, or entity extraction.Working knowledge of export-control requirements.\nWork Environment\nThe role requires one day per week onsite with some flexibility.</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analyst - Background Check Specialist</t>
+          <t>System Analyst (BI/DWH)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, 07310, US</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2016-03-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049624_usa/analyst---background-check-specialist</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -2945,54 +2945,54 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0289c5fbc42948b0cfc0</t>
+          <t>e765218d0ec589c265ea</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Analyst - Background Check Specialist\nLocation: Jersey City, New Jersey (Onsite)\n \nRole Overview\nThe Background Check Specialist is responsible for administering and governing the end-to-end background screening process for employees and contingent workers in a highly regulated environment. This role supports compliant onboarding by initiating, monitoring, reviewing, and auditing background investigations to ensure adherence to company policies, regulatory requirements, and regional standards. This role sits within the Global HR Operations function and partners closely with Talent Acquisition, Procurement, Compliance, Legal, and Security.\n \nKey Responsibilities\nAdminister end-to-end background screening processes for employees and contingent workers using First Advantage and related HCM systems, ensuring adherence to company policy, governance standards, and regional requirements.Initiate, monitor, and track background screenings in alignment with onboarding timelines and service level agreements.Coordinate screening requirements based on worker type, role, geography, and regulatory obligations.Review and assess screening results, including criminal history, non-criminal findings, OFAC and sanctions screening, adverse media reviews, and fingerprinting.Apply established adjudication guidelines and escalation protocols and partner with stakeholders on escalated cases.Support adverse action processes in accordance with applicable regulations and company standards.Maintain accurate audit documentation and help keep process documentation and standard operating procedures current.Identify process gaps, control risks, and opportunities for operational improvement.Participate in quality assurance reviews and compliance audits through reporting, documentation, and process validation.\nRequired Qualifications\nEducation: Bachelor’s degree in Human Resources, Business Administration, Compliance, Criminal Justice, or a related field.\n \nExperience: 3+ years of experience in background screening, onboarding operations, compliance operations, or workforce administration.\n \nTechnical Skills: Familiarity with First Advantage or a similar background screening platform. Knowledge of applicable screening and employment regulations, including FCRA and related compliance requirements. Strong attention to detail and the ability to manage sensitive and confidential information.\n \nPreferred Qualifications\nExperience working in a regulated or compliance-driven environment.Experience with HRIS and onboarding technologies, including Fieldglass and Oracle.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, includ</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Apex Systems</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Architecture Design &amp; Engineering Analyst</t>
+          <t>Workforce Management Analyst</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, 02895, US</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3050168_usa/architecture-design--engineering-analyst</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3015,22 +3015,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>ad4e50cea65f89cc5983</t>
+          <t>0d140e426844c92e6ab8</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Job Title: Architecture, Design &amp; Engineering (AD&amp;E) Senior AnalystLocation: RemoteEmployment Type: ContractOverview: The AD&amp;E Senior Analyst will support the Senior Project Manager and Project Manager in delivering one or more projects within a broader program or business initiative. This role involves close collaboration with external consultants and internal teams to manage architectural and engineering design, documentation, and specifications across disciplines including architectural, mechanical, electrical, structural, civil, and environmental.This is a remote contract opportunity requiring strong design aesthetics, analytical thinking, and strategic decision-making. The ideal candidate will have a solid background in architecture, excellent project management skills, and the ability to communicate effectively with stakeholders, architects, engineers, and internal teams.Key Responsibilities:Support data management and project tools such as Microsoft Project/Server and TRIRIGA.Manage document storage, invoice processing, and general contractor bidding coordination.Contribute to ideation, sketching, 3D modeling, renderings, and postproduction work.Provide administrative support to the A/E Manager in planning and executing projects.Coordinate project documentation including contracts, permits, drawings, and specifications.Track project milestones and deliverables, providing updates to stakeholders.Organize project meetings, prepare agendas, and document minutes.Maintain accurate and timely project reports and presentations.Required Qualifications:3–5 years of experience in design, architecture, engineering, or related fields.Strong understanding of construction types, documents, specifications, and materials.Proficiency in reading and preparing technical drawings and documentation.Excellent communication, design, and problem-solving skills.Strong presentation skills and ability to influence stakeholders.Collaborative team player with a positive attitude and strong work ethic.Effective time management and ability to meet fast-paced project deadlines.Proficiency in AutoCAD, Revit (BIM), Excel, Word, Photoshop, and PowerPoint.Willingness to travel up to 15%.Education:Bachelor’s or technical degree in Architecture, Engineering, Construction, or Interior Design, or equivalent work experience.Professional license to practice architecture is not required.LEED Green Certification or other sustainability credentials preferred but not required.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work®</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -3042,17 +3042,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate Customer Success Data Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Toronto, ON, M5H 4B6, CA</t>
+          <t>Charlotte, NC, 28262, US</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049411_usa/associate-customer-success-data-analyst</t>
+          <t>https://www.apexsystems.com/job/3049612_usa/ai-engineer</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3085,22 +3085,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-09-04T18:05:42+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>d0fe71aac09d441a1398</t>
+          <t>300ddf8602f49da4c185</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Associate Customer Success Data Analyst About the RoleWe're looking for an Associate Data Analyst to join our team. In this role, you'll be the primary data resource for our Enterprise Customer Success Management team — fielding incoming data requests, building &amp; maintaining reports and dashboards, and helping CSMs get the information they need to support their retailer partners.This is a high-volume, reactive-support role. You'll work across a broad portfolio of retailers and will need to move quickly, communicate clearly with non-technical stakeholders, and produce clean, reliable outputs within structured SLAs. This role is execution-focused; success means that CSMs spend less time blocked on data.What You'll DoFulfill incoming CSM data requests via a Jira intake process — pulling retailer metrics, building one-off analyses, and delivering results in a clear, CSM-ready formatMaintain and update existing Mode reports and dashboards, including the weekly automated retailer report flowSupport CSMs with standard data pulls across key metrics: GMV trends, conversion funnel, cancellation rates, reorder rates, new guest activation, and campaign performanceTroubleshoot data discrepancies and flag anomalies to the appropriate analytics or engineering teamDocument recurring request patterns to inform future playbook and tooling developmentCommunicate proactively on request status, turnaround times, and any blockersMake &amp; document consistent improvements based on feedback to the existing process of receiving &amp; completing data requestsWhat You Bring2–4 years of experience in an analytical or data operations roleStrong SQL skills — you can write and modify queries independently, navigate unfamiliar schemas, and validate your own outputsComfort working in Mode, Tableau, or similar BI tools; ability to update existing reports without starting from scratchSolid Google Sheets / Excel skills, including pivot tables, lookups, and chart creationClear written and verbal communication — you can translate a data output into a plain-language summary for a non-technical audienceHigh responsiveness and strong prioritization instincts; you're comfortable in a fast-moving, request-driven environmentSelf starter; you’re comfortable reaching out to cross-functional teams to advocate for what you need to get the job done wellFamiliarity with eCommerce metrics and/or the grocery retail landscape is a plus, but not requiredAdditional InformationThe expected contract duration is 6 months, with the possibility of extension depending on business needs.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best</t>
+          <t>AI Engineer\nLocation: Charlotte, NC (Partial Remote)\n \nRole Overview\nWe are seeking a Senior AI Engineer to design and build enterprise AI search solutions. This role focuses on creating systems that allow users to ask questions in plain language and receive answers from large collections of company documents and data. This is a highly technical, individual-contributor position centered on intelligent document search and knowledge retrieval platforms. The ideal candidate will have hands-on experience with Azure AI technologies, AI-powered search, RAG architecture, and Python development for production-grade AI applications.\n \nKey Responsibilities\nDesign, build, test, deploy, and continuously improve AI-driven search and document-intelligence solutions.Translate business requirements, epics, and user stories into technical designs, estimates, and implementation activities.Build and enhance solutions using Azure AI Search, retrieval-augmented generation (RAG) across multiple indexes, query orchestration, and prompt engineering.Configure and tune semantic, keyword, vector, and hybrid retrieval, including query rewriting, scoring profiles, and reranking.\n*Deploy and support scalable AI applications using Kubernetes-based container environments.\nIntegrate structured and unstructured content, document-processing tools, and metadata to improve indexing and retrieval.Provide technical guidance, conduct peer reviews, and share knowledge with other developers.Collaborate with product, architecture, security, and quality teams to resolve technical issues and prepare solutions for release.Apply secure document-handling practices during solution design and implementation.Document technical designs, implementation decisions, and operating considerations.\nRequired Qualifications\nEducation: A bachelor’s or master’s degree in Computer Science or a related field, an applicable professional certification, or equivalent experience is required.\n \nExperience: A minimum of five years of progressive experience developing solutions for complex system problems is required. At least three years of experience in AI, machine learning, cloud-based search, or document processing is necessary.\n \nTechnical Skills: Hands-on experience with Azure AI Search, Document Intelligence, Cognitive Services, retrieval-augmented generation, and hybrid retrieval is required. Experience with Kubernetes-based container deployment and Python development for AI pipelines is also required.\n \nPreferred Qualifications\nExperience with hybrid cloud AI solutions.Familiarity with Azure OpenAI, LangChain, or AI Foundry.Experience with multi-index query orchestration and vector databases such as FAISS, Weaviate, or Pinecone.Experience in RRF and reranking strategies.A background in natural language processing, document classification, or entity extraction.Working knowledge of export-control requirements.\nWork Environment\nThe role requires one day per week onsite with some flexibility.</t>
         </is>
       </c>
     </row>
@@ -3112,17 +3112,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Analyst - Background Check Specialist</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, 78744, US</t>
+          <t>Jersey City, NJ, 07310, US</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049744_usa/business-analyst</t>
+          <t>https://www.apexsystems.com/job/3049624_usa/analyst---background-check-specialist</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3160,17 +3160,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3c0b89162daf98b4e88c</t>
+          <t>0289c5fbc42948b0cfc0</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Business Analyst\nLocation: Austin, Texas (Hybrid)\n \nRole Overview\nWe are seeking a Business Analyst for a contract role. The ideal candidate will produce, distribute, and manage technical project-related information, analyze business needs, and construct decision-support-based applications. This position involves assisting business and technical professionals in assessing various business areas and processes and ascertaining business area readiness for change.\n \nKey Responsibilities\nProduce, distribute, and manage technical project related information.Analyze needs and construct and implement decision-support based applications.Assist business and technical professionals in the analysis and assessment of a variety of business areas and processes.Ascertain business area readiness for change to new business processes and identifies appropriate implementation measures.Develop project team emails to update the team regarding changes, new processes, collaborate, and prepare for requirements discovery sessions.Conduct user story documentation with stakeholders and department executive staff.Act as a liaison between teams for application integrations, enhancements, and development using ITIL process.Work requires contact with developers, information systems analysts, end users, and department executives.Compose correspondence and technical documents.Maintain communication with team members and stakeholders.\nRequired Qualifications\nExperience: 4-7 years of experience in a Business Analyst role.\n \nTechnical Skills: Must have general experience creating user stories. Some technical writing experience is ideal.\n \nPreferred Qualifications\nExperience with Azure DevOps for creating user stories.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer</t>
+          <t>Analyst - Background Check Specialist\nLocation: Jersey City, New Jersey (Onsite)\n \nRole Overview\nThe Background Check Specialist is responsible for administering and governing the end-to-end background screening process for employees and contingent workers in a highly regulated environment. This role supports compliant onboarding by initiating, monitoring, reviewing, and auditing background investigations to ensure adherence to company policies, regulatory requirements, and regional standards. This role sits within the Global HR Operations function and partners closely with Talent Acquisition, Procurement, Compliance, Legal, and Security.\n \nKey Responsibilities\nAdminister end-to-end background screening processes for employees and contingent workers using First Advantage and related HCM systems, ensuring adherence to company policy, governance standards, and regional requirements.Initiate, monitor, and track background screenings in alignment with onboarding timelines and service level agreements.Coordinate screening requirements based on worker type, role, geography, and regulatory obligations.Review and assess screening results, including criminal history, non-criminal findings, OFAC and sanctions screening, adverse media reviews, and fingerprinting.Apply established adjudication guidelines and escalation protocols and partner with stakeholders on escalated cases.Support adverse action processes in accordance with applicable regulations and company standards.Maintain accurate audit documentation and help keep process documentation and standard operating procedures current.Identify process gaps, control risks, and opportunities for operational improvement.Participate in quality assurance reviews and compliance audits through reporting, documentation, and process validation.\nRequired Qualifications\nEducation: Bachelor’s degree in Human Resources, Business Administration, Compliance, Criminal Justice, or a related field.\n \nExperience: 3+ years of experience in background screening, onboarding operations, compliance operations, or workforce administration.\n \nTechnical Skills: Familiarity with First Advantage or a similar background screening platform. Knowledge of applicable screening and employment regulations, including FCRA and related compliance requirements. Strong attention to detail and the ability to manage sensitive and confidential information.\n \nPreferred Qualifications\nExperience working in a regulated or compliance-driven environment.Experience with HRIS and onboarding technologies, including Fieldglass and Oracle.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, includ</t>
         </is>
       </c>
     </row>
@@ -3182,17 +3182,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Architecture Design &amp; Engineering Analyst</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, 02109, US</t>
+          <t>Woonsocket, RI, 02895, US</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049658_usa/business-analyst</t>
+          <t>https://www.apexsystems.com/job/3050168_usa/architecture-design--engineering-analyst</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3230,17 +3230,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>355f3a04a1863ec7adb5</t>
+          <t>ad4e50cea65f89cc5983</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Apex Systems is a world class technology services business that incorporates industry insights and experience to deliver solutions that fulfill our clients’ digital visions.Apex has an opportunity for a Business Analyst. For applicants who are interested in this opportunity, send your updated resume to Gabriel Ortega, Account Manager, at gortega@apexsystems.com.Here are the details:Position: Business AnalystClient: Commonwealth of MA (EOHHS)Location: Boston, MA (Hybrid)Duration: Thru 6/30/27 (with possibility of extension)Pay rate: $50-$54/hourPROJECT SUMMARY: The EOHHS Information Technology Team (EHS-IT) supporting the Department of Developmental Services (DDS) within the Executive Office of Health and Human Services (EHS) is seeking to hire a highly motivated Business Analyst with experience documenting existing workflows and Business/Functional requirements related to Case Management and/or Healthcare applications. DDS supports individuals with intellectual and developmental disabilities including autism spectrum disorder, to enhance opportunities to become fully engaged members of their community. The Executive Office of Health and Human Services is comprised of 11 agencies and the MassHealth program. EOHHS seeks to promote the health, resilience, and independence of the nearly one in three residents of the Commonwealth we serve. Our public health programs touch every community in the Commonwealth. To know more about EOHHS please visit: https://www.mass.gov/orgs/executive-office-of-health-and-human-services POSITION SUMMARY: The Business Analyst will be integral to large projects for EOHHS applications that support investigations, quality management, operations, and legal business units for DDS as well as business processes related to these core functions including integrated systems. In this role under the direction of a Project Manager/Business Analyst (PM/BA), the Business Analyst will be involved in the modernization of EOHHS applications including Home and Community Services Information System (HCSIS) and Quality Enhancement License and Certification (QE5). HCSIS is the primary application for DDS to monitor the Center for Medicaid Services (CMS) including the individuals served under the four Acquired Brain Injury / Moving Forward Plan (ABI/MFP) residential and non-residential waiver programs administered by MassHealth/CMS. QE5 is the application DDS uses to monitor CMS provider qualification assurances. The primary work location for this role will be at 40 Broad St., Boston, Massachusetts 02109. The work schedule for this position is Monday thru Friday, 9:00AM to 5:00PM. The individual is expected to occasionally travel to the DDS area and regional Massachusetts offices. This position is expected to follow a hybrid model of reporting to work that combines in-office workdays and work from home days as needed. Responsibilities:· Participate in design sessions in prototyping new systems or major enhancements for the purpose of improving</t>
+          <t>Job Title: Architecture, Design &amp; Engineering (AD&amp;E) Senior AnalystLocation: RemoteEmployment Type: ContractOverview: The AD&amp;E Senior Analyst will support the Senior Project Manager and Project Manager in delivering one or more projects within a broader program or business initiative. This role involves close collaboration with external consultants and internal teams to manage architectural and engineering design, documentation, and specifications across disciplines including architectural, mechanical, electrical, structural, civil, and environmental.This is a remote contract opportunity requiring strong design aesthetics, analytical thinking, and strategic decision-making. The ideal candidate will have a solid background in architecture, excellent project management skills, and the ability to communicate effectively with stakeholders, architects, engineers, and internal teams.Key Responsibilities:Support data management and project tools such as Microsoft Project/Server and TRIRIGA.Manage document storage, invoice processing, and general contractor bidding coordination.Contribute to ideation, sketching, 3D modeling, renderings, and postproduction work.Provide administrative support to the A/E Manager in planning and executing projects.Coordinate project documentation including contracts, permits, drawings, and specifications.Track project milestones and deliverables, providing updates to stakeholders.Organize project meetings, prepare agendas, and document minutes.Maintain accurate and timely project reports and presentations.Required Qualifications:3–5 years of experience in design, architecture, engineering, or related fields.Strong understanding of construction types, documents, specifications, and materials.Proficiency in reading and preparing technical drawings and documentation.Excellent communication, design, and problem-solving skills.Strong presentation skills and ability to influence stakeholders.Collaborative team player with a positive attitude and strong work ethic.Effective time management and ability to meet fast-paced project deadlines.Proficiency in AutoCAD, Revit (BIM), Excel, Word, Photoshop, and PowerPoint.Willingness to travel up to 15%.Education:Bachelor’s or technical degree in Architecture, Engineering, Construction, or Interior Design, or equivalent work experience.Professional license to practice architecture is not required.LEED Green Certification or other sustainability credentials preferred but not required.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work®</t>
         </is>
       </c>
     </row>
@@ -3252,17 +3252,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Associate Customer Success Data Analyst</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, 78744, US</t>
+          <t>Toronto, ON, M5H 4B6, CA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049561_usa/business-analyst</t>
+          <t>https://www.apexsystems.com/job/3049411_usa/associate-customer-success-data-analyst</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>d1ec9bafa399330304f5</t>
+          <t>d0fe71aac09d441a1398</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Business Analyst\nLocation: Austin, Texas (Onsite)\n \nRole Overview\nWe are seeking a Business Analyst for a role within our organization. This position is intended to support divisional transitions.\n \nCompany Overview &amp; Culture\nOur client is a major state agency in Texas focused on transportation. As a Business Analyst, you will be part of a team supporting critical government infrastructure and services.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access to certification prep and a library of technical and leadership courses/books/seminars once you have 6+ months of tenure, and certification discounts and other perks to associations that include CompTIA and IIBA. Everforth Apex has a dedicated customer service team for our Consultants that can address questions around benefits and other resources, as well as a certified Career Coach. You can access a full list of our benefits, programs, support teams and resources within our ‘Welcome Packet’ as well, which an Everforth Apex team member can provide.Everforth Apex Systems is an equal opportunity employer. We do not discriminate or allow discrimination on the basis of race, color, religion, creed, sex (including pregnancy, childbirth, breastfeeding, or related medi</t>
+          <t>Associate Customer Success Data Analyst About the RoleWe're looking for an Associate Data Analyst to join our team. In this role, you'll be the primary data resource for our Enterprise Customer Success Management team — fielding incoming data requests, building &amp; maintaining reports and dashboards, and helping CSMs get the information they need to support their retailer partners.This is a high-volume, reactive-support role. You'll work across a broad portfolio of retailers and will need to move quickly, communicate clearly with non-technical stakeholders, and produce clean, reliable outputs within structured SLAs. This role is execution-focused; success means that CSMs spend less time blocked on data.What You'll DoFulfill incoming CSM data requests via a Jira intake process — pulling retailer metrics, building one-off analyses, and delivering results in a clear, CSM-ready formatMaintain and update existing Mode reports and dashboards, including the weekly automated retailer report flowSupport CSMs with standard data pulls across key metrics: GMV trends, conversion funnel, cancellation rates, reorder rates, new guest activation, and campaign performanceTroubleshoot data discrepancies and flag anomalies to the appropriate analytics or engineering teamDocument recurring request patterns to inform future playbook and tooling developmentCommunicate proactively on request status, turnaround times, and any blockersMake &amp; document consistent improvements based on feedback to the existing process of receiving &amp; completing data requestsWhat You Bring2–4 years of experience in an analytical or data operations roleStrong SQL skills — you can write and modify queries independently, navigate unfamiliar schemas, and validate your own outputsComfort working in Mode, Tableau, or similar BI tools; ability to update existing reports without starting from scratchSolid Google Sheets / Excel skills, including pivot tables, lookups, and chart creationClear written and verbal communication — you can translate a data output into a plain-language summary for a non-technical audienceHigh responsiveness and strong prioritization instincts; you're comfortable in a fast-moving, request-driven environmentSelf starter; you’re comfortable reaching out to cross-functional teams to advocate for what you need to get the job done wellFamiliarity with eCommerce metrics and/or the grocery retail landscape is a plus, but not requiredAdditional InformationThe expected contract duration is 6 months, with the possibility of extension depending on business needs.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, 63134, US</t>
+          <t>Austin, TX, 78744, US</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049033_usa/business-analyst</t>
+          <t>https://www.apexsystems.com/job/3049744_usa/business-analyst</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2e1c3871f5350b544eb2</t>
+          <t>3c0b89162daf98b4e88c</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Business AnalystLocation: St. Louis, Missouri (Remote) Role OverviewOur organization is seeking a skilled Business Systems Analyst to support application lifecycle management initiatives, including upgrades, migrations, and the remediation of end-of-life systems. This role requires technical acumen, healthcare application experience, and communication skills to bridge the gap between business needs and technical solutions. Key ResponsibilitiesGather and document business and technical requirements from IT teams and business units.Translate requirements into actionable insights for architects, infrastructure teams, and application analysts.Support application and operating system upgrades and migrations to standard platforms.Assist in the remediation of end-of-life applications and systems.Understand and analyze application stack components (e.g., server, workstation, cloud).Collaborate with cross-functional teams to ensure successful implementation of technical solutions.Participate in stakeholder communications and status updates.Required QualificationsExperience: 5–7+ years of experience in business systems analysis or a related technical role. Experience with cloud migrations and end-of-life system remediation is a plus. Technical Skills: Strong understanding of healthcare applications and workflows. Solid knowledge of application stack architecture (server, client, cloud). Experience with Google Workspace (Sheets, Docs, etc.). General Skills: Excellent verbal and written communication skills. Ability to work independently and manage time effectively. Preferred QualificationsBackground in technical analysis or application architecture.Advanced Excel/Google Sheets skills (formulas, Appsheet experience).Bachelor’s degree in Computer Science, Engineering, or a related technical field.Familiarity with Java, SQL, Visual Basic, or Google App Script. We are an equal opportunity employer and welcome applications from all qualified candidates regardless of race, color, religion, sex, sexual orientation, gender identity, national origin, disability, or veteran status. Apex uses a virtual recruiter as part of the application process. Click here for more details. If you have visited our website in search of information on employment opportunities or to apply for a position, and you require an accommodation in using our website for a search or application, please contact our Benefits Department at leaverequest@apexsystems.com or 804-523-8228.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the</t>
+          <t>Business Analyst\nLocation: Austin, Texas (Hybrid)\n \nRole Overview\nWe are seeking a Business Analyst for a contract role. The ideal candidate will produce, distribute, and manage technical project-related information, analyze business needs, and construct decision-support-based applications. This position involves assisting business and technical professionals in assessing various business areas and processes and ascertaining business area readiness for change.\n \nKey Responsibilities\nProduce, distribute, and manage technical project related information.Analyze needs and construct and implement decision-support based applications.Assist business and technical professionals in the analysis and assessment of a variety of business areas and processes.Ascertain business area readiness for change to new business processes and identifies appropriate implementation measures.Develop project team emails to update the team regarding changes, new processes, collaborate, and prepare for requirements discovery sessions.Conduct user story documentation with stakeholders and department executive staff.Act as a liaison between teams for application integrations, enhancements, and development using ITIL process.Work requires contact with developers, information systems analysts, end users, and department executives.Compose correspondence and technical documents.Maintain communication with team members and stakeholders.\nRequired Qualifications\nExperience: 4-7 years of experience in a Business Analyst role.\n \nTechnical Skills: Must have general experience creating user stories. Some technical writing experience is ideal.\n \nPreferred Qualifications\nExperience with Azure DevOps for creating user stories.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer</t>
         </is>
       </c>
     </row>
@@ -3392,17 +3392,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Business Systems Analyst IV</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Anaheim, CA, 92805, US</t>
+          <t>Boston, MA, 02109, US</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3047863_usa/business-systems-analyst-iv</t>
+          <t>https://www.apexsystems.com/job/3049658_usa/business-analyst</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>f4e1582aa0f5bb564558</t>
+          <t>355f3a04a1863ec7adb5</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Business Systems Analyst IV\nLocation: Anaheim, California (On-site)\n \nRole Overview\nThis position will function as an Integrations Developer/Analyst. The primary responsibility is the development and maintenance of applications integrations for department interfaces. Additional duties include supporting business applications through maintenance activities such as upgrade initiatives, development of applications, reports, and interfaces, user support, and application testing. The role involves interacting with business application owners to identify needs, assessing business process improvements, and providing technical and process guidelines.\n \nKey Responsibilities\nDevelop and maintain application programs, scripts, and system interfaces.Migrate integrations and applications to a similar integration platform such as MuleSoft or IBM Ace.Gather business requirements and document specifications for application and integration development.Develop and implement processes for application migration, testing, and support maintenance.Interact with business application owners to identify business and technology needs and assess process improvements.Provide technical and process guidelines in applications development and operations.Deliver production support for the integration platform and interfacing systems.Prioritize and assign completion dates for fixes and change orders with users and team members.Follow existing business processes and operational guidelines for user support and maintenance activities.Coordinate with staff and vendors for application support and issue resolution.Support 24x7 business operations and be available onsite during business hours.\nRequired Qualifications\nEducation: A college degree, preferably in Computer Science or Computer Engineering, is required.\n \nExperience:\nA minimum of three years of proven work experience as an applications developer.A minimum of two years of experience developing and maintaining integrations on platforms like Tibco BusinessWorks, MuleSoft, IBM Ace, or Koodisi.A minimum of two years of experience using message brokers such as Apache Kafka, Apache ActiveMQ, or IBM MQ.Experience as a primary contact for client and vendor requests.Experience in production support for business applications, including troubleshooting and issue resolution.Experience in applications development, version upgrades, and system implementation.\n \nTechnical Skills:\nApplication development experience using C#, .NET, Java, or another object-oriented programming language.Scripting experience or use of tools like Docker and Python for application containerization.Knowledge of maintaining reports using tools such as Cognos, Crystal Reports, Power BI, Business Objects, or Tableau.Experience with relational databases like Oracle and/or MS SQL Server.Hands-on programming experience with SQL, PL/SQL, or equivalent versions.Problem-solving, troubleshooting, and issue resolution skills.Verbal communication, interpersonal ski</t>
+          <t>Apex Systems is a world class technology services business that incorporates industry insights and experience to deliver solutions that fulfill our clients’ digital visions.Apex has an opportunity for a Business Analyst. For applicants who are interested in this opportunity, send your updated resume to Gabriel Ortega, Account Manager, at gortega@apexsystems.com.Here are the details:Position: Business AnalystClient: Commonwealth of MA (EOHHS)Location: Boston, MA (Hybrid)Duration: Thru 6/30/27 (with possibility of extension)Pay rate: $50-$54/hourPROJECT SUMMARY: The EOHHS Information Technology Team (EHS-IT) supporting the Department of Developmental Services (DDS) within the Executive Office of Health and Human Services (EHS) is seeking to hire a highly motivated Business Analyst with experience documenting existing workflows and Business/Functional requirements related to Case Management and/or Healthcare applications. DDS supports individuals with intellectual and developmental disabilities including autism spectrum disorder, to enhance opportunities to become fully engaged members of their community. The Executive Office of Health and Human Services is comprised of 11 agencies and the MassHealth program. EOHHS seeks to promote the health, resilience, and independence of the nearly one in three residents of the Commonwealth we serve. Our public health programs touch every community in the Commonwealth. To know more about EOHHS please visit: https://www.mass.gov/orgs/executive-office-of-health-and-human-services POSITION SUMMARY: The Business Analyst will be integral to large projects for EOHHS applications that support investigations, quality management, operations, and legal business units for DDS as well as business processes related to these core functions including integrated systems. In this role under the direction of a Project Manager/Business Analyst (PM/BA), the Business Analyst will be involved in the modernization of EOHHS applications including Home and Community Services Information System (HCSIS) and Quality Enhancement License and Certification (QE5). HCSIS is the primary application for DDS to monitor the Center for Medicaid Services (CMS) including the individuals served under the four Acquired Brain Injury / Moving Forward Plan (ABI/MFP) residential and non-residential waiver programs administered by MassHealth/CMS. QE5 is the application DDS uses to monitor CMS provider qualification assurances. The primary work location for this role will be at 40 Broad St., Boston, Massachusetts 02109. The work schedule for this position is Monday thru Friday, 9:00AM to 5:00PM. The individual is expected to occasionally travel to the DDS area and regional Massachusetts offices. This position is expected to follow a hybrid model of reporting to work that combines in-office workdays and work from home days as needed. Responsibilities:· Participate in design sessions in prototyping new systems or major enhancements for the purpose of improving</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Client Support Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, 77024, US</t>
+          <t>Austin, TX, 78744, US</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049737_usa/client-support-analyst</t>
+          <t>https://www.apexsystems.com/job/3049561_usa/business-analyst</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>68f1cdac03f96d5ed4d3</t>
+          <t>d1ec9bafa399330304f5</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Job Tittle: Client Support AnalystLocation: Houston, Texas (Onsite) Role OverviewWe are seeking a Client Support Analyst with a passion for the Natural Gas and Retail Energy market. This role serves as a critical post-deal liaison between our organization, Brokers, and the Sales Team. The ideal candidate will conduct thorough operational research, resolve complex inquiries, and ensure exceptional service delivery across all phases of the customer lifecycle following contract execution. This position requires strong analytical capabilities, excellent communication skills, and the ability to manage multiple priorities in a fast-paced environment. Key ResponsibilitiesSupport Channel Partners and the Sales Team by resolving post-deal inquiries and navigating operational challenges.Serve as the primary point of contact for brokers and sales representatives regarding enrollment issues, billing inquiries, regulatory complaints, tax exemptions, and early termination scenarios.Conduct complex operational and financial analyses to support informed decision-making within the business unit.Manage processes such as commission inquiries, enrollment rejections, billing resolutions, and market change communications.Act as a trusted advisor to internal and external stakeholders, ensuring adherence to service level agreements.Engage in proactive process improvement and cross-functional collaboration.Provide consistent communication with leadership on deliverables and status updates.Develop reports and dashboards for business performance tracking using tools such as Excel and Power BI.Required QualificationsEducation: A High School Diploma/GED or equivalent experience is required. Experience: A minimum of 2 years of relevant experience is required. Technical Skills: Proficiency with the Microsoft Office Suite is required. Preferred QualificationsA bachelor's degree in Business, Economics, Information Systems, or a related field.Experience in business analysis, data management, or process improvement.Experience with SQL.Knowledge of financial analysis.Effective written and verbal communication skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may</t>
+          <t>Business Analyst\nLocation: Austin, Texas (Onsite)\n \nRole Overview\nWe are seeking a Business Analyst for a role within our organization. This position is intended to support divisional transitions.\n \nCompany Overview &amp; Culture\nOur client is a major state agency in Texas focused on transportation. As a Business Analyst, you will be part of a team supporting critical government infrastructure and services.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (EAP) with up to 8 free counseling sessions, a corporate discount savings program and other discounts. In terms of professional development, Everforth Apex hosts an on-demand training program, provides access to certification prep and a library of technical and leadership courses/books/seminars once you have 6+ months of tenure, and certification discounts and other perks to associations that include CompTIA and IIBA. Everforth Apex has a dedicated customer service team for our Consultants that can address questions around benefits and other resources, as well as a certified Career Coach. You can access a full list of our benefits, programs, support teams and resources within our ‘Welcome Packet’ as well, which an Everforth Apex team member can provide.Everforth Apex Systems is an equal opportunity employer. We do not discriminate or allow discrimination on the basis of race, color, religion, creed, sex (including pregnancy, childbirth, breastfeeding, or related medi</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cyber Security Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, 33408, US</t>
+          <t>St. Louis, MO, 63134, US</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3040605_usa/cyber-security-analyst</t>
+          <t>https://www.apexsystems.com/job/3049033_usa/business-analyst</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>90e72f7485d9dd20d9f6</t>
+          <t>2e1c3871f5350b544eb2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SOC Analyst Tier 2Location: 100% REMOTE - someone must be in South FloridaNight Shift:Four 10-hour shifts – Thursday – Sunday, 10pm-8am EST. Must be onsite in Miami, FL for the first week for training – Training is M-F, 8am – 5pm EST. Role OverviewAn opportunity is available to grow your career as a cybersecurity professional at one of the leading clean energy companies. This position is for a Cybersecurity Analyst on the Threat Detection and Response team within the Advanced Cyberdefense Center. The ideal candidate will have experience in a Cybersecurity Operations Center, focusing on investigations and incident response in either cloud or industrial control system environments. Key ResponsibilitiesPerform Tier 1 and 2 incident response, managing a queue of incoming tickets from various sources.Investigate alerts, including those from Crowdstrike, and process the email queue for reported phishing attempts.Administer, operate, and monitor information security sensors, logging, alerting, and other detection mechanisms to identify and respond to threats.Work with assigned cybersecurity technology stacks, such as identity and access management, network intrusion detection, or host-based security tools.Collaborate with security architecture to identify, evaluate, and recommend new security technologies.Communicate ongoing cybersecurity activities, priorities, and risk measurements to multiple organizational levels.Provide guidance for security activities and requirements in the system development life cycle (SDLC) and application development efforts.Participate in organizational projects as required.Required QualificationsDemonstrated understanding of cyber fundamentals.Knowledge of networking principles.Experience with identifying and analyzing phishing attempts.Preferred QualificationsComfort reading and writing Splunk queries to perform searches.Experience with Crowdstrike.Experience with Tanium.Experience with Splunk Enterprise Security.Development experience.Work EnvironmentThe work schedule for this position is Thursday through Sunday, from 10:00 PM to 8:00 AM.Onboarding will occur during daytime hours, followed by a transition to the second shift for one to two weeks before moving to the third shift.Candidates must be local to South Florida.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-gen</t>
+          <t>Business AnalystLocation: St. Louis, Missouri (Remote) Role OverviewOur organization is seeking a skilled Business Systems Analyst to support application lifecycle management initiatives, including upgrades, migrations, and the remediation of end-of-life systems. This role requires technical acumen, healthcare application experience, and communication skills to bridge the gap between business needs and technical solutions. Key ResponsibilitiesGather and document business and technical requirements from IT teams and business units.Translate requirements into actionable insights for architects, infrastructure teams, and application analysts.Support application and operating system upgrades and migrations to standard platforms.Assist in the remediation of end-of-life applications and systems.Understand and analyze application stack components (e.g., server, workstation, cloud).Collaborate with cross-functional teams to ensure successful implementation of technical solutions.Participate in stakeholder communications and status updates.Required QualificationsExperience: 5–7+ years of experience in business systems analysis or a related technical role. Experience with cloud migrations and end-of-life system remediation is a plus. Technical Skills: Strong understanding of healthcare applications and workflows. Solid knowledge of application stack architecture (server, client, cloud). Experience with Google Workspace (Sheets, Docs, etc.). General Skills: Excellent verbal and written communication skills. Ability to work independently and manage time effectively. Preferred QualificationsBackground in technical analysis or application architecture.Advanced Excel/Google Sheets skills (formulas, Appsheet experience).Bachelor’s degree in Computer Science, Engineering, or a related technical field.Familiarity with Java, SQL, Visual Basic, or Google App Script. We are an equal opportunity employer and welcome applications from all qualified candidates regardless of race, color, religion, sex, sexual orientation, gender identity, national origin, disability, or veteran status. Apex uses a virtual recruiter as part of the application process. Click here for more details. If you have visited our website in search of information on employment opportunities or to apply for a position, and you require an accommodation in using our website for a search or application, please contact our Benefits Department at leaverequest@apexsystems.com or 804-523-8228.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the</t>
         </is>
       </c>
     </row>
@@ -3602,17 +3602,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Systems Analyst IV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, 33408, US</t>
+          <t>Anaheim, CA, 92805, US</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049386_usa/data-analyst</t>
+          <t>https://www.apexsystems.com/job/3047863_usa/business-systems-analyst-iv</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -3645,22 +3645,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-03T18:19:19+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>ea831ffc8b24983a72f6</t>
+          <t>f4e1582aa0f5bb564558</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Data Analyst\nLocation: Juno Beach, Florida (Remote)\n \nRole Overview\nThis role supports groundbreaking AI projects for a leading renewable energy developer. The position requires a candidate with a foundation in data science and technical skills in data engineering and front-end development. The focus will be on driving the development and implementation of solutions that optimize internal processes and SCADA operations for renewable power plants.\n \nKey Responsibilities\nDesign, develop, and maintain data pipelines and ETL processes.Ensure data quality and integrity across various sources and platforms.\n* Collaborate with IT to integrate data solutions within existing infrastructure.\nDevelop and implement machine learning models and algorithms to derive actionable insights.Perform data analysis and visualization to support business decisions.Conduct experiments and validations to iterate on model performance.Collaborate with UX/UI designers to develop user-friendly interfaces for AI-driven tools.Implement interactive web applications to visualize data and model outcomes.Integrate front-end applications with back-end services and databases.Manage projects related to SCADA integration, commissioning, startup, and testing.Work with internal resources and suppliers to determine project priorities and meet milestones.\n \nRequired Qualifications\nEducation: Bachelor’s degree in computer science, data science, engineering, mathematics, or a related field, or equivalent experience.\n \nExperience: Experience related to data analytics for renewable power plants is required. Experience with Agile methodology, software lifecycle, and scrum ceremonies is also necessary.\n \nTechnical Skills:\nProficiency in programming languages such as Python, R, or Scala for data analysis and machine learning.Experience with data processing frameworks like Apache Spark, Hadoop, or Kubernetes.Adept at using SQL and NoSQL databases.Familiarity with front-end technologies such as HTML, CSS, JavaScript, and frameworks like React or Angular.Understanding of RESTful APIs and web services integration.Knowledge of AI and machine learning frameworks such as TensorFlow, PyTorch, or Scikit-Learn.Experience with SCADA operations, Power BI, AWS Glue, Lambda, SNS, and SQS.\n \nPreferred Qualifications\nCertifications in AWS, Microsoft Power BI, Salesforce, IT Project Management (PMP, Agile, SAFe), or DevOps methodologies.Experience in the renewable energy industry.\n \nWork Environment\nThis position is remote but requires up to 30% travel.Driving will be required. A valid, non-restricted driver's license must be maintained.Ability to lift up to 20 pounds.Ability to work at a desk in front of a computer monitor for extended periods.Bending, stooping, and twisting may be required.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and c</t>
+          <t>Business Systems Analyst IV\nLocation: Anaheim, California (On-site)\n \nRole Overview\nThis position will function as an Integrations Developer/Analyst. The primary responsibility is the development and maintenance of applications integrations for department interfaces. Additional duties include supporting business applications through maintenance activities such as upgrade initiatives, development of applications, reports, and interfaces, user support, and application testing. The role involves interacting with business application owners to identify needs, assessing business process improvements, and providing technical and process guidelines.\n \nKey Responsibilities\nDevelop and maintain application programs, scripts, and system interfaces.Migrate integrations and applications to a similar integration platform such as MuleSoft or IBM Ace.Gather business requirements and document specifications for application and integration development.Develop and implement processes for application migration, testing, and support maintenance.Interact with business application owners to identify business and technology needs and assess process improvements.Provide technical and process guidelines in applications development and operations.Deliver production support for the integration platform and interfacing systems.Prioritize and assign completion dates for fixes and change orders with users and team members.Follow existing business processes and operational guidelines for user support and maintenance activities.Coordinate with staff and vendors for application support and issue resolution.Support 24x7 business operations and be available onsite during business hours.\nRequired Qualifications\nEducation: A college degree, preferably in Computer Science or Computer Engineering, is required.\n \nExperience:\nA minimum of three years of proven work experience as an applications developer.A minimum of two years of experience developing and maintaining integrations on platforms like Tibco BusinessWorks, MuleSoft, IBM Ace, or Koodisi.A minimum of two years of experience using message brokers such as Apache Kafka, Apache ActiveMQ, or IBM MQ.Experience as a primary contact for client and vendor requests.Experience in production support for business applications, including troubleshooting and issue resolution.Experience in applications development, version upgrades, and system implementation.\n \nTechnical Skills:\nApplication development experience using C#, .NET, Java, or another object-oriented programming language.Scripting experience or use of tools like Docker and Python for application containerization.Knowledge of maintaining reports using tools such as Cognos, Crystal Reports, Power BI, Business Objects, or Tableau.Experience with relational databases like Oracle and/or MS SQL Server.Hands-on programming experience with SQL, PL/SQL, or equivalent versions.Problem-solving, troubleshooting, and issue resolution skills.Verbal communication, interpersonal ski</t>
         </is>
       </c>
     </row>
@@ -3672,17 +3672,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Data Analyst (*Part Time)</t>
+          <t>Client Support Analyst</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Coppell, TX, 75019, US</t>
+          <t>Houston, TX, 77024, US</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049406_usa/data-analyst-part-time</t>
+          <t>https://www.apexsystems.com/job/3049737_usa/client-support-analyst</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9c13d41b1eb9bb5cddc6</t>
+          <t>68f1cdac03f96d5ed4d3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Data Analyst (*Part Time - estimated 20/25 hours per week*)Location: Coppell, Texas (Hybrid) Role OverviewThis role is responsible for executing periodical reporting and data gathering responsibilities. The position requires a self-starter with high attention to detail to perform daily reviews and ensure timely action on pending items. This is a hybrid role based in Texas. Key ResponsibilitiesMonitor and process the receipt of financials, including communicating with members regarding missing reports and facilitating extensions, waivers, or fines.Enter financial data accurately into the Automated Financial Reporting System (AFRS) and track it through the approval workflow.Oversee the production and review of daily surveillance emails and track related workflows to completion.Conduct daily reviews for items that require same-day action.Reconcile reporting and trackers to ensure reports are accurate and up to date.Perform other duties as assigned.Required QualificationsKnowledge: A background in financial reporting components, including Income Statements and Balance Sheets, is necessary. Knowledge of credit and financial statement analysis for various financial institutions is also required. Technical Skills: Proficiency in Microsoft Office applications such as Outlook, Word, and Excel is required. General Skills: Effective communication skills are required for this role. Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (</t>
+          <t>Job Tittle: Client Support AnalystLocation: Houston, Texas (Onsite) Role OverviewWe are seeking a Client Support Analyst with a passion for the Natural Gas and Retail Energy market. This role serves as a critical post-deal liaison between our organization, Brokers, and the Sales Team. The ideal candidate will conduct thorough operational research, resolve complex inquiries, and ensure exceptional service delivery across all phases of the customer lifecycle following contract execution. This position requires strong analytical capabilities, excellent communication skills, and the ability to manage multiple priorities in a fast-paced environment. Key ResponsibilitiesSupport Channel Partners and the Sales Team by resolving post-deal inquiries and navigating operational challenges.Serve as the primary point of contact for brokers and sales representatives regarding enrollment issues, billing inquiries, regulatory complaints, tax exemptions, and early termination scenarios.Conduct complex operational and financial analyses to support informed decision-making within the business unit.Manage processes such as commission inquiries, enrollment rejections, billing resolutions, and market change communications.Act as a trusted advisor to internal and external stakeholders, ensuring adherence to service level agreements.Engage in proactive process improvement and cross-functional collaboration.Provide consistent communication with leadership on deliverables and status updates.Develop reports and dashboards for business performance tracking using tools such as Excel and Power BI.Required QualificationsEducation: A High School Diploma/GED or equivalent experience is required. Experience: A minimum of 2 years of relevant experience is required. Technical Skills: Proficiency with the Microsoft Office Suite is required. Preferred QualificationsA bachelor's degree in Business, Economics, Information Systems, or a related field.Experience in business analysis, data management, or process improvement.Experience with SQL.Knowledge of financial analysis.Effective written and verbal communication skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may</t>
         </is>
       </c>
     </row>
@@ -3742,17 +3742,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Security Analyst</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Brighton, MN, 55112, US</t>
+          <t>Juno Beach, FL, 33408, US</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049248_usa/data-engineer</t>
+          <t>https://www.apexsystems.com/job/3040605_usa/cyber-security-analyst</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -3785,22 +3785,22 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-02T18:23:08+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>03ed326aff3cf2f837e8</t>
+          <t>90e72f7485d9dd20d9f6</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>We are currently seeking a Data Engineer to join our team. This role will support our data-driven decision-making processes by analyzing and visualizing complex datasets, implementing modern data management tools, and collaborating with cross-functional teams to derive actionable insights. The individual will work closely with business teams to understand data needs, manage and improve data pipelines, and drive the transformation of our data infrastructure to a modern, scalable platform. Additionally, this role will support our broader efforts in implementing machine learning and advanced analytics capabilities to enhance business decision-making.Essential Duties &amp; Responsibilities To include, but not limited to the following:Design, implement, and maintain data architecture to support business intelligence and reporting needs.Build and manage data pipelines to integrate, clean, and transform data across systems (ETL processes).Collaborate with business teams to understand data requirements and deliver scalable data solutions.Monitor data quality and optimize data flows to ensure accuracy, integrity, consistency, and compliance with organizational standards.Troubleshoot and resolve data-related issues promptly.Assist in migrating existing data infrastructure to modern, cloud-based platforms, ensuring scalability and reliability.Develop and implement business intelligence solutions, including reports, dashboards, and data visualizations.Create and maintain data models and database designs that align with business needs.Support machine learning initiatives by preparing data for analysis and modeling.Provide actionable recommendations based on data analysis to support executive and operational decision-making.Lead and participate in data governance and quality initiatives, adhering to best practices and standards.Develop training materials and conduct sessions to ensure effective use of data tools across teams.Stay abreast of emerging trends in data analytics and suggest ways to implement innovative solutions.QualificationsRequired:Bachelor’s degree in computer science, Data Science, Information Systems, or a related field (or equivalent experience).3+ years of experience in data engineering, or a similar role.Strong knowledge of data modeling, database design, and ETL processes.Advanced SQL skills for querying and data manipulation.Proficiency in the Microsoft Azure ecosystem, including Azure Data Factory, Azure Synapse Analytics, Azure Purview, and Azure SQL Database.Strong experience with Power BI for data visualization.Experience with data integration tools (e.g., Azure Data Factory, SSIS, or similar).Hands-on experience with business intelligence tools.Strong problem-solving skills and ability to work on complex technical challenges.Preferred:Familiarity with Databricks for data engineering and analytics.Knowledge of data governance, privacy, and cataloging principles.Familiarity with machine learning workflows and data preparation for predicti</t>
+          <t>SOC Analyst Tier 2Location: 100% REMOTE - someone must be in South FloridaNight Shift:Four 10-hour shifts – Thursday – Sunday, 10pm-8am EST. Must be onsite in Miami, FL for the first week for training – Training is M-F, 8am – 5pm EST. Role OverviewAn opportunity is available to grow your career as a cybersecurity professional at one of the leading clean energy companies. This position is for a Cybersecurity Analyst on the Threat Detection and Response team within the Advanced Cyberdefense Center. The ideal candidate will have experience in a Cybersecurity Operations Center, focusing on investigations and incident response in either cloud or industrial control system environments. Key ResponsibilitiesPerform Tier 1 and 2 incident response, managing a queue of incoming tickets from various sources.Investigate alerts, including those from Crowdstrike, and process the email queue for reported phishing attempts.Administer, operate, and monitor information security sensors, logging, alerting, and other detection mechanisms to identify and respond to threats.Work with assigned cybersecurity technology stacks, such as identity and access management, network intrusion detection, or host-based security tools.Collaborate with security architecture to identify, evaluate, and recommend new security technologies.Communicate ongoing cybersecurity activities, priorities, and risk measurements to multiple organizational levels.Provide guidance for security activities and requirements in the system development life cycle (SDLC) and application development efforts.Participate in organizational projects as required.Required QualificationsDemonstrated understanding of cyber fundamentals.Knowledge of networking principles.Experience with identifying and analyzing phishing attempts.Preferred QualificationsComfort reading and writing Splunk queries to perform searches.Experience with Crowdstrike.Experience with Tanium.Experience with Splunk Enterprise Security.Development experience.Work EnvironmentThe work schedule for this position is Thursday through Sunday, from 10:00 PM to 8:00 AM.Onboarding will occur during daytime hours, followed by a transition to the second shift for one to two weeks before moving to the third shift.Candidates must be local to South Florida.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-gen</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, 75240, US</t>
+          <t>Juno Beach, FL, 33408, US</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049431_usa/data-engineer-ii</t>
+          <t>https://www.apexsystems.com/job/3049386_usa/data-analyst</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-09-03T18:19:19+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>66cb57c02f9bc9dd8c81</t>
+          <t>ea831ffc8b24983a72f6</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Data Engineer II\nLocation: Dallas, Texas (Onsite)\n \nRole Overview\nWe are seeking a results-oriented Data Engineer to design and build scalable solutions. The selected candidate will bring industry best practices to address business problems, define metrics, and create systems that operate reliably at scale. This role involves working in a large and complex data warehouse environment.\n \nKey Responsibilities\nDevelop and support analytic technologies to provide timely and structured data access.Design and implement a platform using in-house reporting tools, model metadata, and build reports and dashboards.Collaborate with business customers to understand requirements and implement solutions for analytical and reporting needs.Work with one of the world's largest and most complex data warehouse environments.\nRequired Qualifications\nEducation: A Bachelor’s degree is required.\n \nExperience: A minimum of 3-5 years of data engineering experience is required. This includes experience with data modeling, data warehousing, building ETL pipelines, and operating large-scale data structures for business intelligence analytics.\n \nTechnical Skills:\nHigh proficiency in SQL and Data Analysis.Strong knowledge of Python.Demonstrated experience with ETL processes.\n \nPreferred Qualifications\nExperience with the AWS stack, including Redshift, S3, AWS Glue, EMR, Kinesis, FireHose, and Lambda.Experience with data modeling and data warehousing.Experience with non-relational databases or data stores.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure</t>
+          <t>Data Analyst\nLocation: Juno Beach, Florida (Remote)\n \nRole Overview\nThis role supports groundbreaking AI projects for a leading renewable energy developer. The position requires a candidate with a foundation in data science and technical skills in data engineering and front-end development. The focus will be on driving the development and implementation of solutions that optimize internal processes and SCADA operations for renewable power plants.\n \nKey Responsibilities\nDesign, develop, and maintain data pipelines and ETL processes.Ensure data quality and integrity across various sources and platforms.\n* Collaborate with IT to integrate data solutions within existing infrastructure.\nDevelop and implement machine learning models and algorithms to derive actionable insights.Perform data analysis and visualization to support business decisions.Conduct experiments and validations to iterate on model performance.Collaborate with UX/UI designers to develop user-friendly interfaces for AI-driven tools.Implement interactive web applications to visualize data and model outcomes.Integrate front-end applications with back-end services and databases.Manage projects related to SCADA integration, commissioning, startup, and testing.Work with internal resources and suppliers to determine project priorities and meet milestones.\n \nRequired Qualifications\nEducation: Bachelor’s degree in computer science, data science, engineering, mathematics, or a related field, or equivalent experience.\n \nExperience: Experience related to data analytics for renewable power plants is required. Experience with Agile methodology, software lifecycle, and scrum ceremonies is also necessary.\n \nTechnical Skills:\nProficiency in programming languages such as Python, R, or Scala for data analysis and machine learning.Experience with data processing frameworks like Apache Spark, Hadoop, or Kubernetes.Adept at using SQL and NoSQL databases.Familiarity with front-end technologies such as HTML, CSS, JavaScript, and frameworks like React or Angular.Understanding of RESTful APIs and web services integration.Knowledge of AI and machine learning frameworks such as TensorFlow, PyTorch, or Scikit-Learn.Experience with SCADA operations, Power BI, AWS Glue, Lambda, SNS, and SQS.\n \nPreferred Qualifications\nCertifications in AWS, Microsoft Power BI, Salesforce, IT Project Management (PMP, Agile, SAFe), or DevOps methodologies.Experience in the renewable energy industry.\n \nWork Environment\nThis position is remote but requires up to 30% travel.Driving will be required. A valid, non-restricted driver's license must be maintained.Ability to lift up to 20 pounds.Ability to work at a desk in front of a computer monitor for extended periods.Bending, stooping, and twisting may be required.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and c</t>
         </is>
       </c>
     </row>
@@ -3882,17 +3882,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Data Governance Analyst</t>
+          <t>Data Analyst (*Part Time)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Addison, TX, 75001, US</t>
+          <t>Coppell, TX, 75019, US</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049583_usa/data-governance-analyst</t>
+          <t>https://www.apexsystems.com/job/3049406_usa/data-analyst-part-time</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>a07be263f1f9283f435b</t>
+          <t>9c13d41b1eb9bb5cddc6</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Data Governance AnalystLocation: Addison, Texas (On-site)Employment Type: ContractContract Duration: 12 Months Role OverviewThis role is responsible for developing and delivering complex requirements to accomplish business goals. The position involves ensuring that software is developed to meet functional, non-functional, and compliance requirements. The ideal candidate will code solutions, perform unit tests, and ensure successful integration into the overall application/system with clear, robust, and well-tested interfaces. Key ResponsibilitiesDevelop and deliver complex requirements to meet business goals.Ensure software development meets functional, non-functional, and compliance standards.Code solutions, conduct unit tests, and ensure successful system integration.Collaborate with teams to improve the developer experience and advance technology platforms.Reduce risk and improve quality by aligning with enterprise architecture strategy.Drive accessibility of applications for teammates and customers.Perform root cause analysis and recommend remediation for data governance and quality issues.Design and recommend governance structures and control frameworks for data management.Required QualificationsEducation: A BA/BS degree or equivalent practical experience is required. Experience: 3-5 years of experience working with data management, data analytics, and/or governance is required. Technical Skills: Experience with PostgreSQL is strongly preferred. Proficiency in data analysis and data management is required. Preferred QualificationsAdvanced communication and influencing skills for a diverse audience, including senior management.Capability to evaluate business needs and risks broadly across the enterprise.Personal initiative to find opportunities, lead change, improve processes, and solve problems.Demonstrated ability to perform root cause analysis.Basic knowledge of automation and continuous delivery practices (DevOps).Working knowledge of Agile/Waterfall frameworks.Basic understanding of financial data and risk management principles.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed o</t>
+          <t>Data Analyst (*Part Time - estimated 20/25 hours per week*)Location: Coppell, Texas (Hybrid) Role OverviewThis role is responsible for executing periodical reporting and data gathering responsibilities. The position requires a self-starter with high attention to detail to perform daily reviews and ensure timely action on pending items. This is a hybrid role based in Texas. Key ResponsibilitiesMonitor and process the receipt of financials, including communicating with members regarding missing reports and facilitating extensions, waivers, or fines.Enter financial data accurately into the Automated Financial Reporting System (AFRS) and track it through the approval workflow.Oversee the production and review of daily surveillance emails and track related workflows to completion.Conduct daily reviews for items that require same-day action.Reconcile reporting and trackers to ensure reports are accurate and up to date.Perform other duties as assigned.Required QualificationsKnowledge: A background in financial reporting components, including Income Statements and Balance Sheets, is necessary. Knowledge of credit and financial statement analysis for various financial institutions is also required. Technical Skills: Proficiency in Microsoft Office applications such as Outlook, Word, and Excel is required. General Skills: Effective communication skills are required for this role. Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure. Everforth Apex also offers a HSA (Health Savings Account on the HDHP plan), a SupportLinc Employee Assistance Program (</t>
         </is>
       </c>
     </row>
@@ -3952,17 +3952,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Data Product Manager</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, 55101, US</t>
+          <t>New Brighton, MN, 55112, US</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049530_usa/data-product-manager</t>
+          <t>https://www.apexsystems.com/job/3049248_usa/data-engineer</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -3995,22 +3995,22 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-09-02T18:23:08+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>4ec7ef1500689b82668b</t>
+          <t>03ed326aff3cf2f837e8</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Program Manager - RemoteSample Tasks· Product Strategy &amp; Vision: o Define the vision and roadmap for data products (e.g., data platforms, analytics tools, ML infrastructure). o Identify high value opportunities by investigating the data landscape, pain points, and business needs. o Align data product strategy with organizational priorities and long-term data architecture, in partnership with the Enterprise Architecture team and various interested parties. o Connect data capabilities to business outcomes and organize efforts to achieve the business outcomes. o Align engineering, analytics, and business teams. Uses metrics to guide prioritization and product evolution.· Data Product Development: o Lead the end-to-end lifecycle of data products: requirements, design, development, testing, launch, and iteration. o Partner with data engineers and data scientists to build scalable pipelines, models, and data services. Ensure data quality, governance, lineage, and documentation standards are met. o Translate business logic into data transformations, metadata, and domain specific rules. Skilled in or adept at data architecture, modeling, and pipelines. o Ensures data products are reliable, governed, and scalable. · Interested Parties Management: o Serve as the primary liaison between technical teams at Minnesota IT Services (MNIT) and business partners across DCYF. o Communicate product value, roadmap, and use cases to leadership and cross-functional teams. o Prioritize incoming requests and balance competing needs across teams. · Analytics, Insights &amp; Measurement: o Define success metrics and measure product performance and adoption. o Ensure data products deliver actionable insights and support decision making. o Partner with analytics teams to design dashboards, KPIs, and reporting frameworks. · Governance, Compliance &amp; Ethical Data Use: o Uphold data governance, privacy, and ethical AI standards. o Ensure compliance with regulatory and organizational data policies. o Advocate for responsible data use across the human services space served by and supported through DCYF and MNIT DCYF. · Provide knowledge transferDesired Qualifications· Desired 4–7 years of experience in Data management, data analytics, data engineering, or related fields. · Demonstrated Product leadership skills and ability to work in ambiguity.· Strong understanding of data systems: pipelines, warehousing, modeling, metadata, governance.· Proficiency collaborating with data Architecture, data engineering and data science teams.· Ability to translate complex technical concepts into business-friendly language.· Strong communication, prioritization, and stakeholder management skills.· Experience with analytics tools (dbt, Looker, Tableau, Power BI, Google Analytics).· Understanding of large organizational data sharing constraints and data sharing agreements.· Experience with SQL, data lakes, data and data pipelines / ETL.· Significant experience with Databricks. · Familiarity with Java a</t>
+          <t>We are currently seeking a Data Engineer to join our team. This role will support our data-driven decision-making processes by analyzing and visualizing complex datasets, implementing modern data management tools, and collaborating with cross-functional teams to derive actionable insights. The individual will work closely with business teams to understand data needs, manage and improve data pipelines, and drive the transformation of our data infrastructure to a modern, scalable platform. Additionally, this role will support our broader efforts in implementing machine learning and advanced analytics capabilities to enhance business decision-making.Essential Duties &amp; Responsibilities To include, but not limited to the following:Design, implement, and maintain data architecture to support business intelligence and reporting needs.Build and manage data pipelines to integrate, clean, and transform data across systems (ETL processes).Collaborate with business teams to understand data requirements and deliver scalable data solutions.Monitor data quality and optimize data flows to ensure accuracy, integrity, consistency, and compliance with organizational standards.Troubleshoot and resolve data-related issues promptly.Assist in migrating existing data infrastructure to modern, cloud-based platforms, ensuring scalability and reliability.Develop and implement business intelligence solutions, including reports, dashboards, and data visualizations.Create and maintain data models and database designs that align with business needs.Support machine learning initiatives by preparing data for analysis and modeling.Provide actionable recommendations based on data analysis to support executive and operational decision-making.Lead and participate in data governance and quality initiatives, adhering to best practices and standards.Develop training materials and conduct sessions to ensure effective use of data tools across teams.Stay abreast of emerging trends in data analytics and suggest ways to implement innovative solutions.QualificationsRequired:Bachelor’s degree in computer science, Data Science, Information Systems, or a related field (or equivalent experience).3+ years of experience in data engineering, or a similar role.Strong knowledge of data modeling, database design, and ETL processes.Advanced SQL skills for querying and data manipulation.Proficiency in the Microsoft Azure ecosystem, including Azure Data Factory, Azure Synapse Analytics, Azure Purview, and Azure SQL Database.Strong experience with Power BI for data visualization.Experience with data integration tools (e.g., Azure Data Factory, SSIS, or similar).Hands-on experience with business intelligence tools.Strong problem-solving skills and ability to work on complex technical challenges.Preferred:Familiarity with Databricks for data engineering and analytics.Knowledge of data governance, privacy, and cataloging principles.Familiarity with machine learning workflows and data preparation for predicti</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Digital Data Analyst (Adobe/CJA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Various, MO, 99999, US</t>
+          <t>Dallas, TX, 75240, US</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049706_usa/digital-data-analyst-adobecja</t>
+          <t>https://www.apexsystems.com/job/3049431_usa/data-engineer-ii</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -4070,17 +4070,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>bdf8d14886ec0791b883</t>
+          <t>66cb57c02f9bc9dd8c81</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Apex Systems is hiring a Digital Data Analyst (CJA focus) for a large healthcare client.Location: Fully remote anywhere in the United States.**YOU MUST BE AUTHORIZED TO WORK IN THE US WITHOUT SPONSORSHIP.This is a 6-month contract with a possibility to extend or convert. Role OverviewThis position offers an opportunity to connect business objectives with site usage metrics. The role involves pioneering behavioral usage tracking and collaborating with product and business teams to demonstrate the impact of data-driven decisions. The work will help shape the future of the organization's digital landscape by creating experiences that meet and exceed member expectations. Key ResponsibilitiesCreate, modify, and update dashboards for assigned feature sets.Monitor dashboards, investigate anomalies or unexpected behavior, and communicate findings.Check new tracking in lower-level environments to ensure adherence to standards.Attend daily stand-ups with agile development teams.Participate in design reviews for new development work to understand the purpose and formulate measurements for success.Contribute to daily Data Analytics touch-bases to maintain internal alignment.Facilitate ad hoc design and requirements reviews with analytics team members.Engage in weekly discussions with the Analytics Launch Developer to coordinate with Agile Development Teams.Required QualificationsEducation: A bachelor's degree in Data Science, Business Analytics, or a related field is required. Experience: A minimum of 10 years of experience in behavioral analytics, specializing in Adobe Analytics and Customer Journey Analytics is required. Candidates must have experience with custom report and dashboard creation using Adobe Customer Journey Analytics workspaces, and extensive experience in tying digital analytics tracking requirements to business goals. Technical Skills: Proficiency in data visualization and the ability to critically evaluate designs to ensure alignment with business objectives and site performance are necessary. Strong analytical skills to interpret complex data sets are also required. Preferred QualificationsAdobe Customer Journey Analytics Business Practitioner Professional Certification.Background in the health care industry.Experience with user experience (UX) design principles.Familiarity with agile project management methodologies.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click</t>
+          <t>Data Engineer II\nLocation: Dallas, Texas (Onsite)\n \nRole Overview\nWe are seeking a results-oriented Data Engineer to design and build scalable solutions. The selected candidate will bring industry best practices to address business problems, define metrics, and create systems that operate reliably at scale. This role involves working in a large and complex data warehouse environment.\n \nKey Responsibilities\nDevelop and support analytic technologies to provide timely and structured data access.Design and implement a platform using in-house reporting tools, model metadata, and build reports and dashboards.Collaborate with business customers to understand requirements and implement solutions for analytical and reporting needs.Work with one of the world's largest and most complex data warehouse environments.\nRequired Qualifications\nEducation: A Bachelor’s degree is required.\n \nExperience: A minimum of 3-5 years of data engineering experience is required. This includes experience with data modeling, data warehousing, building ETL pipelines, and operating large-scale data structures for business intelligence analytics.\n \nTechnical Skills:\nHigh proficiency in SQL and Data Analysis.Strong knowledge of Python.Demonstrated experience with ETL processes.\n \nPreferred Qualifications\nExperience with the AWS stack, including Redshift, S3, AWS Glue, EMR, Kinesis, FireHose, and Lambda.Experience with data modeling and data warehousing.Experience with non-relational databases or data stores.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of starting, with a company match after 12 months of tenure</t>
         </is>
       </c>
     </row>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EDI Analyst</t>
+          <t>Data Governance Analyst</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, 94588, US</t>
+          <t>Addison, TX, 75001, US</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049338_usa/edi-analyst</t>
+          <t>https://www.apexsystems.com/job/3049583_usa/data-governance-analyst</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>cdeada8cdc6c7ee778db</t>
+          <t>a07be263f1f9283f435b</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Apex Systems is hiring an EDI Analyst for a large Healthcare client.Location: Fully remote anywhere in the United States.18 months contract with potential to extend. Role OverviewThe EDI Analyst supports the channel partner integration ecosystem by building, testing, and maintaining connection points with external partners such as brokers, TPAs, payroll vendors, and benefits administration platforms. This role requires EDI troubleshooting skills, cross-functional coordination, and hands-on experience with enrollment transactions. Key ResponsibilitiesSupport onboarding and maintenance of channel partner integrations (EDI, API, XML).Validate and troubleshoot enrollment data feeds, including 834 transactions.Analyze transaction discrepancies, demographic mismatches, and rejected records.Coordinate issue resolution with internal teams and external partners.Monitor recurring transmission failures and escalate defects as needed.Document workflows, connection requirements, and partner-specific configurations.Participate in integration testing and connection validation for new partners.Required QualificationsExperience: 2–4+ years of healthcare EDI experience, with 834 transaction experience required. Experience supporting external partners or clients in a payer, TPA, or benefits administration environment is necessary. Technical Skills: Candidates must have the ability to read and interpret X12 transaction files, including loops, segments, and benefit codes. Strong analytical skills with Excel (VLOOKUP/XLOOKUP, pivot tables) are required. Preferred QualificationsMulti-transaction EDI experience is preferred.Familiarity with API payloads (JSON/XML) is a plus.Excellent communication and documentation skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional la</t>
+          <t>Data Governance AnalystLocation: Addison, Texas (On-site)Employment Type: ContractContract Duration: 12 Months Role OverviewThis role is responsible for developing and delivering complex requirements to accomplish business goals. The position involves ensuring that software is developed to meet functional, non-functional, and compliance requirements. The ideal candidate will code solutions, perform unit tests, and ensure successful integration into the overall application/system with clear, robust, and well-tested interfaces. Key ResponsibilitiesDevelop and deliver complex requirements to meet business goals.Ensure software development meets functional, non-functional, and compliance standards.Code solutions, conduct unit tests, and ensure successful system integration.Collaborate with teams to improve the developer experience and advance technology platforms.Reduce risk and improve quality by aligning with enterprise architecture strategy.Drive accessibility of applications for teammates and customers.Perform root cause analysis and recommend remediation for data governance and quality issues.Design and recommend governance structures and control frameworks for data management.Required QualificationsEducation: A BA/BS degree or equivalent practical experience is required. Experience: 3-5 years of experience working with data management, data analytics, and/or governance is required. Technical Skills: Experience with PostgreSQL is strongly preferred. Proficiency in data analysis and data management is required. Preferred QualificationsAdvanced communication and influencing skills for a diverse audience, including senior management.Capability to evaluate business needs and risks broadly across the enterprise.Personal initiative to find opportunities, lead change, improve processes, and solve problems.Demonstrated ability to perform root cause analysis.Basic knowledge of automation and continuous delivery practices (DevOps).Working knowledge of Agile/Waterfall frameworks.Basic understanding of financial data and risk management principles.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed o</t>
         </is>
       </c>
     </row>
@@ -4162,17 +4162,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Engineering Technical Analyst</t>
+          <t>Data Product Manager</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Milford, MI, 48380, US</t>
+          <t>Saint Paul, MN, 55101, US</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049312_usa/engineering-technical-analyst</t>
+          <t>https://www.apexsystems.com/job/3049530_usa/data-product-manager</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>515e13c6fdb330459626</t>
+          <t>4ec7ef1500689b82668b</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Job Title: Engineering Technical AnalystLocation: Milford, MI (Onsite)Contract Duration - 12 MonthsPay Rate: $23/hr - $26/hrNote: We are not able to consider C2C or third-party submissions Role OverviewThe main function of an engineering tech analyst is to provide technical support on various engineering projects and assignments. This role is responsible for obtaining blueprints, inspecting hardware, tracking project updates, compiling data, and assisting engineering teams to overcome project roadblocks. Key ResponsibilitiesObtain blueprints, math data, PDMs, and other graphical information with various levels of direction.Inspect and compare physical hardware such as parts, vehicles, and mockup bucks to graphical information, noting discrepancies and potential root causes.Obtain specific data from available databases, sort or organize it by designated characteristics, and report required information in specified formats.Plan, schedule, and coordinate technical reviews of outlined issues, drawings, parts, or vehicles.Document technical discussions, action plans, and assignments.Monitor and report the status of projects and assignments.Compile cost comparison data or performance comparison data.Compile data and convert it into standard specification formats and documents.Identify the data, analysis method, and report format required to present and explain an issue, phenomenon, or potential solution.Participate in the design and implementation of action plans.Identify ways to improve the implementation of the Vehicle Development Process.Required QualificationsEducation: Bachelor’s Degree in Engineering, Mathematics, Computer Science, or a related technical field. Experience: 5-7 years of experience is required, including experience as an auto mechanic or technician. Technical Skills:Ability to identify relevant drawings, layouts, and graphic illustrations to investigate issues.Understanding of vehicle architecture and function, including packaging and dynamic interactions of components.Ability to create, file data, and retrieve information from electronic databases.Knowledge of data processing techniques, methods, software, and their application.Proficiency with Microsoft Word.Ability to develop work plans, including the identification and retrieval of necessary information, data, and drawings.Strong written and verbal communication skills.Ability to work independently and with a team.Ability to utilize existing or new information and processes to resolve issues.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States an</t>
+          <t>Program Manager - RemoteSample Tasks· Product Strategy &amp; Vision: o Define the vision and roadmap for data products (e.g., data platforms, analytics tools, ML infrastructure). o Identify high value opportunities by investigating the data landscape, pain points, and business needs. o Align data product strategy with organizational priorities and long-term data architecture, in partnership with the Enterprise Architecture team and various interested parties. o Connect data capabilities to business outcomes and organize efforts to achieve the business outcomes. o Align engineering, analytics, and business teams. Uses metrics to guide prioritization and product evolution.· Data Product Development: o Lead the end-to-end lifecycle of data products: requirements, design, development, testing, launch, and iteration. o Partner with data engineers and data scientists to build scalable pipelines, models, and data services. Ensure data quality, governance, lineage, and documentation standards are met. o Translate business logic into data transformations, metadata, and domain specific rules. Skilled in or adept at data architecture, modeling, and pipelines. o Ensures data products are reliable, governed, and scalable. · Interested Parties Management: o Serve as the primary liaison between technical teams at Minnesota IT Services (MNIT) and business partners across DCYF. o Communicate product value, roadmap, and use cases to leadership and cross-functional teams. o Prioritize incoming requests and balance competing needs across teams. · Analytics, Insights &amp; Measurement: o Define success metrics and measure product performance and adoption. o Ensure data products deliver actionable insights and support decision making. o Partner with analytics teams to design dashboards, KPIs, and reporting frameworks. · Governance, Compliance &amp; Ethical Data Use: o Uphold data governance, privacy, and ethical AI standards. o Ensure compliance with regulatory and organizational data policies. o Advocate for responsible data use across the human services space served by and supported through DCYF and MNIT DCYF. · Provide knowledge transferDesired Qualifications· Desired 4–7 years of experience in Data management, data analytics, data engineering, or related fields. · Demonstrated Product leadership skills and ability to work in ambiguity.· Strong understanding of data systems: pipelines, warehousing, modeling, metadata, governance.· Proficiency collaborating with data Architecture, data engineering and data science teams.· Ability to translate complex technical concepts into business-friendly language.· Strong communication, prioritization, and stakeholder management skills.· Experience with analytics tools (dbt, Looker, Tableau, Power BI, Google Analytics).· Understanding of large organizational data sharing constraints and data sharing agreements.· Experience with SQL, data lakes, data and data pipelines / ETL.· Significant experience with Databricks. · Familiarity with Java a</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Epic Application Analyst (Pharmacy)</t>
+          <t>Digital Data Analyst (Adobe/CJA)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, 80222, US</t>
+          <t>Various, MO, 99999, US</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049073_usa/epic-application-analyst-pharmacy</t>
+          <t>https://www.apexsystems.com/job/3049706_usa/digital-data-analyst-adobecja</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -4280,17 +4280,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>aa36f12d3e211f205b96</t>
+          <t>bdf8d14886ec0791b883</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Epic Application Analyst (Pharmacy)Department: Clinical Application Services (non-clinical role)Length: 4 Months, contractDesired Start Date: Urgent NeedShift: 8:00 AM – 4:00 PMWork Location: RemoteRequirements Education: Epic Willow IP Certification Experience: 5+ years of Epic build experiencePreferredWillow InventoryPharmacist or Pharmacy Technician Position SummaryEssential Functions: -Analyze and diagnose complex system issues; identify root causes and resolve or escalate appropriately -Plan, design, implement, maintain, optimize, and support applications -Gather, validate, and translate complex technical requirements into design and development specifications-Collaborate with clinical users and IT teams through evaluation, design, testing, implementation, and maintenance -Address highly technical issues during installation and maintenance -Coordinate preparation, coding, testing, and debugging of complex programs -Design, analyze, and build workflows to meet user needs-Configure and integrate electronic and mechanical hardware with software solutions -Gather and analyze data to troubleshoot incidents; document process and resolution -Document design, application, and technical specifications; assist with support and training materials -Identify reporting needs and collaborate with report developers -Partner with vendors to resolve system issues and improve performance and usability -Recommend system improvements to vendors -Review documentation for upgrades and monthly system updates; assess impacts -Provide Tier 2 and Tier 3 end-user support -Mentor team members on technical and customer support skills -Act as project lead for complex initiatives -Participate in on-call rotation as required Scope &amp; Level Guidelines Broad knowledge of concepts, practices, and procedures within specialization Complexity Broad, complex duties requiring advanced organizational and specialty knowledge -Decision Making: independent judgment with authority to escalate high-impact or complex decisions -Communication: communicates complex, interpretive information using discretion and independent judgment Supervision Limited supervision with high independence; supported by lower-level staff as applicableThis is a fully remote Epic Analyst opportunity supporting one of the nation's leading pediatric healthcare organizations.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details</t>
+          <t>Apex Systems is hiring a Digital Data Analyst (CJA focus) for a large healthcare client.Location: Fully remote anywhere in the United States.**YOU MUST BE AUTHORIZED TO WORK IN THE US WITHOUT SPONSORSHIP.This is a 6-month contract with a possibility to extend or convert. Role OverviewThis position offers an opportunity to connect business objectives with site usage metrics. The role involves pioneering behavioral usage tracking and collaborating with product and business teams to demonstrate the impact of data-driven decisions. The work will help shape the future of the organization's digital landscape by creating experiences that meet and exceed member expectations. Key ResponsibilitiesCreate, modify, and update dashboards for assigned feature sets.Monitor dashboards, investigate anomalies or unexpected behavior, and communicate findings.Check new tracking in lower-level environments to ensure adherence to standards.Attend daily stand-ups with agile development teams.Participate in design reviews for new development work to understand the purpose and formulate measurements for success.Contribute to daily Data Analytics touch-bases to maintain internal alignment.Facilitate ad hoc design and requirements reviews with analytics team members.Engage in weekly discussions with the Analytics Launch Developer to coordinate with Agile Development Teams.Required QualificationsEducation: A bachelor's degree in Data Science, Business Analytics, or a related field is required. Experience: A minimum of 10 years of experience in behavioral analytics, specializing in Adobe Analytics and Customer Journey Analytics is required. Candidates must have experience with custom report and dashboard creation using Adobe Customer Journey Analytics workspaces, and extensive experience in tying digital analytics tracking requirements to business goals. Technical Skills: Proficiency in data visualization and the ability to critically evaluate designs to ensure alignment with business objectives and site performance are necessary. Strong analytical skills to interpret complex data sets are also required. Preferred QualificationsAdobe Customer Journey Analytics Business Practitioner Professional Certification.Background in the health care industry.Experience with user experience (UX) design principles.Familiarity with agile project management methodologies.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click</t>
         </is>
       </c>
     </row>
@@ -4302,12 +4302,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gen AI Engineer Lead</t>
+          <t>EDI Analyst</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ridgeland, MS, 39157, US</t>
+          <t>Pleasanton, CA, 94588, US</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049490_usa/gen-ai-engineer-lead</t>
+          <t>https://www.apexsystems.com/job/3049338_usa/edi-analyst</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>8c8c419ec698f77eff7f</t>
+          <t>cdeada8cdc6c7ee778db</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GenAI Product Engineering LeadSummaryWe are seeking an accomplished and strategic GenAI Product Engineering Lead to drive the design, development, and delivery of an enterprise-grade AI platform on Microsoft Azure. This role is ideal for a technical leader with deep expertise in Generative AI, agent-based systems, Power Platform, and cloud-native engineering. You will lead a multidisciplinary team to build scalable, secure, and intelligent solutions that transform business operations and deliver exceptional value to clients and internal users. Your leadership will be instrumental in shaping the technical direction, fostering innovation, and ensuring operational excellence across all aspects of platform engineering.Position SummarySeeking an experienced and visionary GenAI Product Engineering Lead to architect, build, and scale our next-generation enterprise platform on Microsoft Azure. You will lead a multidisciplinary team of developers and engineers, driving innovation and operational excellence in building intelligent, secure, and scalable business solutions.Key ResponsibilitiesTechnical Leadership &amp; Team ManagementLead, mentor, and grow a high-performing engineering team, fostering a culture of innovation, accountability, and continuous improvement.Establish and enforce engineering best practices, focusing on code quality, reliability, and operational efficiency.Set technical direction and ensure alignment with enterprise goals and standards.Enterprise Platform ArchitectureArchitect scalable, secure, and resilient AI systems on Azure (and other cloud environments as needed), working with Large Language Models (LLMs), and collaborating with cross-functional teams to integrate AI into products and processes. A strong technical foundation in areas like Python, AI/ML frameworks, and cloud platforms, combined with project management and leadership skills, are essential for this role.Define Power Platform apps from end-to-end, including backend data pipelines.Define and enforce architectural standards, including microservices, event-driven design, and API-first principles.Multi-Tenancy &amp; SaaS ArchitectureArchitect multi-tenant B2B environments with tenant-aware data partitions using Cosmos DB and Azure AD B2C/Entra ID to ensure data, security, and cost isolation.Build per-tenant vector stores, knowledge bases, and connectors to support customer-specific document ingestion and retrieval.Implement telemetry, metering, and consumption-based billing dashboards to track tenant-level usage and optimize resource allocation.GenAI &amp; Agent IntegrationDesign and implement advanced GenAI solutions, including agent-based systems for automation, orchestration, and intelligent workflows.Integrate large language models (LLMs), Retrieval-Augmented Generation (RAG), and custom agents with business processes and user-facing applications.Lead design using frameworks such as Semantic Kernel, LangChain, AutoGen, or CrewAI to build orchestration among multiple specialize</t>
+          <t>Apex Systems is hiring an EDI Analyst for a large Healthcare client.Location: Fully remote anywhere in the United States.18 months contract with potential to extend. Role OverviewThe EDI Analyst supports the channel partner integration ecosystem by building, testing, and maintaining connection points with external partners such as brokers, TPAs, payroll vendors, and benefits administration platforms. This role requires EDI troubleshooting skills, cross-functional coordination, and hands-on experience with enrollment transactions. Key ResponsibilitiesSupport onboarding and maintenance of channel partner integrations (EDI, API, XML).Validate and troubleshoot enrollment data feeds, including 834 transactions.Analyze transaction discrepancies, demographic mismatches, and rejected records.Coordinate issue resolution with internal teams and external partners.Monitor recurring transmission failures and escalate defects as needed.Document workflows, connection requirements, and partner-specific configurations.Participate in integration testing and connection validation for new partners.Required QualificationsExperience: 2–4+ years of healthcare EDI experience, with 834 transaction experience required. Experience supporting external partners or clients in a payer, TPA, or benefits administration environment is necessary. Technical Skills: Candidates must have the ability to read and interpret X12 transaction files, including loops, segments, and benefit codes. Strong analytical skills with Excel (VLOOKUP/XLOOKUP, pivot tables) are required. Preferred QualificationsMulti-transaction EDI experience is preferred.Familiarity with API payloads (JSON/XML) is a plus.Excellent communication and documentation skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional la</t>
         </is>
       </c>
     </row>
@@ -4372,17 +4372,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Engineering Technical Analyst</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, 94588, US</t>
+          <t>Milford, MI, 48380, US</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049493_usa/generative-ai-developer</t>
+          <t>https://www.apexsystems.com/job/3049312_usa/engineering-technical-analyst</t>
         </is>
       </c>
       <c r="J57" t="b">
@@ -4420,17 +4420,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>e63c68fd69e531e282e7</t>
+          <t>515e13c6fdb330459626</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Apex Systems is hiring a Generative AI Developer for a large Healthcare client.Location: Fully remote anywhere in the US. Role OverviewAn experienced Generative AI Developer is sought to design, build, and deploy enterprise-grade AI applications leveraging Large Language Models (LLMs), Retrieval-Augmented Generation (RAG), agentic workflows, and cloud-native architectures. The role combines software engineering expertise with modern AI technologies to deliver scalable, secure, and responsible AI solutions that create measurable business value. Key ResponsibilitiesDesign effective system prompts, instructions, structured output templates, and evaluation-driven prompt improvements for accuracy, consistency, and cost efficiency.Implement AI guardrails, content safety controls, privacy practices, responsible AI workflows, and human-in-the-loop review patterns.Establish evaluation frameworks to measure accuracy, relevance, latency, cost, and user satisfaction.Monitor production systems and continuously optimize performance.Translate complex AI concepts into business-focused solutions.Collaborate effectively with product managers, data scientists, cloud engineers, security teams, and stakeholders.Required QualificationsStrong proficiency in Python for application development, API integrations, and AI workflow implementation.Experience building REST APIs, microservices, and backend services.Strong understanding of software engineering best practices, version control with Git, automated testing, and CI/CD.Hands-on experience with LLM providers such as Azure OpenAI, OpenAI, Anthropic Claude, Google Gemini, and open-source models.Experience implementing chat applications, AI copilots, agents, function calling, tool integration, and multi-modal AI capabilities.Experience building Retrieval-Augmented Generation (RAG) solutions and proficiency with frameworks like LangChain, LangGraph, LlamaIndex, and Semantic Kernel.Experience with embeddings, semantic search, and knowledge of vector database platforms such as Pinecone, Weaviate, Chroma, Azure AI Search, and FAISS.Experience deploying AI applications using Microsoft Azure platform services, including Azure OpenAI, Azure AI Services, and Azure Kubernetes Service (AKS).Hands-on experience with Docker, Kubernetes, Infrastructure as Code, CI/CD pipelines, and monitoring frameworks.Experience integrating enterprise data sources, APIs, databases, and document repositories.Bachelor's degree in Computer Science, Artificial Intelligence, Data Science, Software Engineering, or a related field.Preferred Qualifications5+ years of software engineering experience.2+ years of experience building Generative AI or Machine Learning solutions.Experience developing enterprise AI applications in healthcare, finance, or large-scale business environments.Microsoft Azure certifications are preferred.Agentic AI development and multi-agent orchestration.Fine-tuning, model customization, and evaluation pipelines.Experience with AI obs</t>
+          <t>Job Title: Engineering Technical AnalystLocation: Milford, MI (Onsite)Contract Duration - 12 MonthsPay Rate: $23/hr - $26/hrNote: We are not able to consider C2C or third-party submissions Role OverviewThe main function of an engineering tech analyst is to provide technical support on various engineering projects and assignments. This role is responsible for obtaining blueprints, inspecting hardware, tracking project updates, compiling data, and assisting engineering teams to overcome project roadblocks. Key ResponsibilitiesObtain blueprints, math data, PDMs, and other graphical information with various levels of direction.Inspect and compare physical hardware such as parts, vehicles, and mockup bucks to graphical information, noting discrepancies and potential root causes.Obtain specific data from available databases, sort or organize it by designated characteristics, and report required information in specified formats.Plan, schedule, and coordinate technical reviews of outlined issues, drawings, parts, or vehicles.Document technical discussions, action plans, and assignments.Monitor and report the status of projects and assignments.Compile cost comparison data or performance comparison data.Compile data and convert it into standard specification formats and documents.Identify the data, analysis method, and report format required to present and explain an issue, phenomenon, or potential solution.Participate in the design and implementation of action plans.Identify ways to improve the implementation of the Vehicle Development Process.Required QualificationsEducation: Bachelor’s Degree in Engineering, Mathematics, Computer Science, or a related technical field. Experience: 5-7 years of experience is required, including experience as an auto mechanic or technician. Technical Skills:Ability to identify relevant drawings, layouts, and graphic illustrations to investigate issues.Understanding of vehicle architecture and function, including packaging and dynamic interactions of components.Ability to create, file data, and retrieve information from electronic databases.Knowledge of data processing techniques, methods, software, and their application.Proficiency with Microsoft Word.Ability to develop work plans, including the identification and retrieval of necessary information, data, and drawings.Strong written and verbal communication skills.Ability to work independently and with a team.Ability to utilize existing or new information and processes to resolve issues.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States an</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IAM Audit Analyst</t>
+          <t>Epic Application Analyst (Pharmacy)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, 60603, US</t>
+          <t>Denver, CO, 80222, US</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049785_usa/iam-audit-analyst</t>
+          <t>https://www.apexsystems.com/job/3049073_usa/epic-application-analyst-pharmacy</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -4490,17 +4490,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>890b6429e3601509338b</t>
+          <t>aa36f12d3e211f205b96</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>IAM Audit Analyst\nLocation: Chicago, Illinois (Partial Remote)\n \nRole Overview\nWe are seeking an IAM Audit Analyst to lead audit engagements focused on Identity and Access Management (IAM), IT controls, and cybersecurity. This role involves overseeing the execution of audit requests, evaluating evidence, and collaborating with stakeholders to define scope and develop effective testing documentation. You will provide technical expertise in risk, controls, and IAM technologies to ensure strong governance and compliance across access management processes.\n \nKey Responsibilities\nLead projects related to Identity and Access Management (IAM) controls, IT General Controls (ITGC), information security, and IT governance.Provide oversight and guidance to stakeholders on IAM Audit requests and Evidence Requests.Partner with implementation owners to define audit scope, objectives, and develop appropriate testing strategies based on risk assessment.Assist in developing evidence testing timelines based on scope and risk.Finalize and review audit planning and scoping documentation.Conduct and review walkthroughs and testing of application controls, interface controls, and IAM processes such as provisioning, de-provisioning, access reviews, and Privileged Access Management (PAM).Ensure work meets departmental standards and quality requirements.Analyze implementation plans and follow up on milestones for issues identified by internal teams and auditors.Work with stakeholders across business, technology, risk, and control functions to drive issue resolution and remediation tracking.Communicate audit status and findings to business stakeholders and leadership.Draft audit findings, reports, and recommendations for status updates and closure packages.Identify and evaluate risks, control gaps, and remediation actions.Coordinate with other teams to ensure comprehensive coverage of risk areas.\nRequired Qualifications\n5–10 years of experience in IT Audit, Risk, Controls, or IAM-focused audits.Knowledge of audit standards, methodologies, and procedures.Understanding of IT systems, applications, and cybersecurity risks.Knowledge of Identity and Access Management (IAM) principles, including user lifecycle management, role-based access control (RBAC), and Privileged Access Management (PAM).Experience with IAM technologies such as SailPoint, Saviynt, Okta, Azure AD, or CyberArk.Understanding of IT General Controls (ITGC) and compliance frameworks (SOX, ISO, etc.).Ability to lead and execute walkthroughs, design, and operational effectiveness testing.Analytical, documentation, and reporting skills.Communication and stakeholder management skills.\nPreferred Qualifications\nCertifications such as CISA, CISSP, or CRISC.Experience in IAM governance, access certification programs, and Cloud IAM environments (Azure, AWS, GCP).Ability to manage multiple projects simultaneously and meet deadlines.Everforth Apex is a world-class IT services company that serves thousands of cl</t>
+          <t>Epic Application Analyst (Pharmacy)Department: Clinical Application Services (non-clinical role)Length: 4 Months, contractDesired Start Date: Urgent NeedShift: 8:00 AM – 4:00 PMWork Location: RemoteRequirements Education: Epic Willow IP Certification Experience: 5+ years of Epic build experiencePreferredWillow InventoryPharmacist or Pharmacy Technician Position SummaryEssential Functions: -Analyze and diagnose complex system issues; identify root causes and resolve or escalate appropriately -Plan, design, implement, maintain, optimize, and support applications -Gather, validate, and translate complex technical requirements into design and development specifications-Collaborate with clinical users and IT teams through evaluation, design, testing, implementation, and maintenance -Address highly technical issues during installation and maintenance -Coordinate preparation, coding, testing, and debugging of complex programs -Design, analyze, and build workflows to meet user needs-Configure and integrate electronic and mechanical hardware with software solutions -Gather and analyze data to troubleshoot incidents; document process and resolution -Document design, application, and technical specifications; assist with support and training materials -Identify reporting needs and collaborate with report developers -Partner with vendors to resolve system issues and improve performance and usability -Recommend system improvements to vendors -Review documentation for upgrades and monthly system updates; assess impacts -Provide Tier 2 and Tier 3 end-user support -Mentor team members on technical and customer support skills -Act as project lead for complex initiatives -Participate in on-call rotation as required Scope &amp; Level Guidelines Broad knowledge of concepts, practices, and procedures within specialization Complexity Broad, complex duties requiring advanced organizational and specialty knowledge -Decision Making: independent judgment with authority to escalate high-impact or complex decisions -Communication: communicates complex, interpretive information using discretion and independent judgment Supervision Limited supervision with high independence; supported by lower-level staff as applicableThis is a fully remote Epic Analyst opportunity supporting one of the nation's leading pediatric healthcare organizations.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details</t>
         </is>
       </c>
     </row>
@@ -4512,17 +4512,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IT Business Analyst II</t>
+          <t>Gen AI Engineer Lead</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, 32256, US</t>
+          <t>Ridgeland, MS, 39157, US</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049724_usa/it-business-analyst-ii</t>
+          <t>https://www.apexsystems.com/job/3049490_usa/gen-ai-engineer-lead</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>7f428722efeb4ffc8de3</t>
+          <t>8c8c419ec698f77eff7f</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>IT Business Analyst II\nLocation: Jacksonville, Florida (Onsite)\n \nRole Overview\nWe are seeking an IT Business Analyst to join our team. This role involves managing access administration requests, ensuring user satisfaction through diligent troubleshooting, and contributing to process improvements. The ideal candidate will have a strong understanding of Identity and Access Management (IAM) principles and will be proficient in handling both routine and complex administrative tasks within a technical environment.\n \nKey Responsibilities\nComplete routine and complex requests for access administration, including creating tickets, verifying approvals, and providing user communications.Track access status, application installations, and system setups.Serve as a single point of contact (SPOC) by facilitating security administration processes.Ensure user satisfaction by providing preventative maintenance and resolving routine problems.Actively identify and pursue process improvements within access management functions.Participate in special projects as needed.Exercise judgment within defined procedures and practices to determine appropriate action.\n \nRequired Qualifications\nExperience:\nWorking experience with Access Request Management tools, CyberArk, and Privileged Access Management (PAM) solutions.Experience with Data Driven Access Requests (DDAR) and Straight Through Provisioning (STP).A strong understanding and experience of Identity and Access Management (IAM) principles and best practices.\n \nTechnical Skills:\nProficient in the Microsoft Office suite (Word, Excel, PowerPoint, Outlook, Access) with the ability to analyze and synthesize data.\n \nPreferred Qualifications\nExcellent customer service and interpersonal skills with the ability to build partnerships across teams.Strong written and verbal communication skills in English.Ability to multi-task and work independently while displaying strong attention to detail.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https</t>
+          <t>GenAI Product Engineering LeadSummaryWe are seeking an accomplished and strategic GenAI Product Engineering Lead to drive the design, development, and delivery of an enterprise-grade AI platform on Microsoft Azure. This role is ideal for a technical leader with deep expertise in Generative AI, agent-based systems, Power Platform, and cloud-native engineering. You will lead a multidisciplinary team to build scalable, secure, and intelligent solutions that transform business operations and deliver exceptional value to clients and internal users. Your leadership will be instrumental in shaping the technical direction, fostering innovation, and ensuring operational excellence across all aspects of platform engineering.Position SummarySeeking an experienced and visionary GenAI Product Engineering Lead to architect, build, and scale our next-generation enterprise platform on Microsoft Azure. You will lead a multidisciplinary team of developers and engineers, driving innovation and operational excellence in building intelligent, secure, and scalable business solutions.Key ResponsibilitiesTechnical Leadership &amp; Team ManagementLead, mentor, and grow a high-performing engineering team, fostering a culture of innovation, accountability, and continuous improvement.Establish and enforce engineering best practices, focusing on code quality, reliability, and operational efficiency.Set technical direction and ensure alignment with enterprise goals and standards.Enterprise Platform ArchitectureArchitect scalable, secure, and resilient AI systems on Azure (and other cloud environments as needed), working with Large Language Models (LLMs), and collaborating with cross-functional teams to integrate AI into products and processes. A strong technical foundation in areas like Python, AI/ML frameworks, and cloud platforms, combined with project management and leadership skills, are essential for this role.Define Power Platform apps from end-to-end, including backend data pipelines.Define and enforce architectural standards, including microservices, event-driven design, and API-first principles.Multi-Tenancy &amp; SaaS ArchitectureArchitect multi-tenant B2B environments with tenant-aware data partitions using Cosmos DB and Azure AD B2C/Entra ID to ensure data, security, and cost isolation.Build per-tenant vector stores, knowledge bases, and connectors to support customer-specific document ingestion and retrieval.Implement telemetry, metering, and consumption-based billing dashboards to track tenant-level usage and optimize resource allocation.GenAI &amp; Agent IntegrationDesign and implement advanced GenAI solutions, including agent-based systems for automation, orchestration, and intelligent workflows.Integrate large language models (LLMs), Retrieval-Augmented Generation (RAG), and custom agents with business processes and user-facing applications.Lead design using frameworks such as Semantic Kernel, LangChain, AutoGen, or CrewAI to build orchestration among multiple specialize</t>
         </is>
       </c>
     </row>
@@ -4582,17 +4582,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JP1964 - IT Business Analyst - Niche</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Toronto, ON, 99999, CA</t>
+          <t>Pleasanton, CA, 94588, US</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3050085_usa/jp1964---it-business-analyst---niche</t>
+          <t>https://www.apexsystems.com/job/3049493_usa/generative-ai-developer</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>82191d615dbeb7516214</t>
+          <t>e63c68fd69e531e282e7</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Product Business Analyst - Post Trade TechnologyDuration: 12-Month ContractHybrid: 2-3 Days OnsiteWorking hours: 9-5Our client, a Top 5 Canadian Bank, is seeking an experienced Product Business Analyst to support the enhancement and development of their post-trade technology platform. This role is ideal for someone with deep experience in capital markets and the ideal candidate brings broad product knowledge across equities, options, futures, and fixed income post-trade operations. You will define, prioritize, and deliver solutions that enable efficient post trade lifecycle management, strengthen risk controls, and improve operational effectiveness across global markets post trade functions. Acting as the bridge between business stakeholders and technology teams, you will ensure post-trade processes are streamlined, compliant, and supported by robust technology design, solutioning, implementation, and delivery. Key ResponsibilitiesProduct Management, Strategy &amp; Roadmap AccountabilityDevelop and maintain the product vision and roadmap for post-trade platforms, ensuring alignment with business objectives and strategic goals.Oversee end-to-end product management, including planning, prioritization, delivery, support and continuous improvement.Track roadmap milestones against delivery progress, address gaps, and implement corrective actions.Stakeholder Management Collaborate across Front Office, Middle Office &amp; Back Office operations, compliance, and technology teams to gather requirements and prioritize features.Assess functional, project &amp; delivery dependencies &amp; risk and communicate mitigating actions to the stakeholders.Provide transparent reporting to stakeholders on roadmap adherence.Engage vendors, Lines of Business, Developers and Support teams to ensure successful delivery.Requirements &amp; Delivery Translate business needs into clear, actionable user stories and acceptance criteria.Manage backlog, prioritize features, and ensure timely delivery of enhancements.Monitor delivery against roadmap commitments and provide transparent reporting to stakeholders. Prepare and document business use cases.Develop technical specifications and requirements, including process flow diagrams and data mappings.Prepare and document test cases and test conditions and conduct functional testing.Process Optimization Identify opportunities to automate and streamline trade capture, allocation, confirmation, and settlement processes.Ensure robust controls for trade breaks, reconciliations, and exception management.Data &amp; Reporting Drive improvements in data quality, trade reporting, and operational transparency.Technology Partnership Partner with vendor engineering teams to deliver scalable, resilient, and high-performing post-trade solutions that support operational efficiency and business growth.Support integration with upstream (Front Office) and Post Trade systems.Required Skills &amp; Qualifications:Experience:7+ years in Product Management, Business Analysis, Middle</t>
+          <t>Apex Systems is hiring a Generative AI Developer for a large Healthcare client.Location: Fully remote anywhere in the US. Role OverviewAn experienced Generative AI Developer is sought to design, build, and deploy enterprise-grade AI applications leveraging Large Language Models (LLMs), Retrieval-Augmented Generation (RAG), agentic workflows, and cloud-native architectures. The role combines software engineering expertise with modern AI technologies to deliver scalable, secure, and responsible AI solutions that create measurable business value. Key ResponsibilitiesDesign effective system prompts, instructions, structured output templates, and evaluation-driven prompt improvements for accuracy, consistency, and cost efficiency.Implement AI guardrails, content safety controls, privacy practices, responsible AI workflows, and human-in-the-loop review patterns.Establish evaluation frameworks to measure accuracy, relevance, latency, cost, and user satisfaction.Monitor production systems and continuously optimize performance.Translate complex AI concepts into business-focused solutions.Collaborate effectively with product managers, data scientists, cloud engineers, security teams, and stakeholders.Required QualificationsStrong proficiency in Python for application development, API integrations, and AI workflow implementation.Experience building REST APIs, microservices, and backend services.Strong understanding of software engineering best practices, version control with Git, automated testing, and CI/CD.Hands-on experience with LLM providers such as Azure OpenAI, OpenAI, Anthropic Claude, Google Gemini, and open-source models.Experience implementing chat applications, AI copilots, agents, function calling, tool integration, and multi-modal AI capabilities.Experience building Retrieval-Augmented Generation (RAG) solutions and proficiency with frameworks like LangChain, LangGraph, LlamaIndex, and Semantic Kernel.Experience with embeddings, semantic search, and knowledge of vector database platforms such as Pinecone, Weaviate, Chroma, Azure AI Search, and FAISS.Experience deploying AI applications using Microsoft Azure platform services, including Azure OpenAI, Azure AI Services, and Azure Kubernetes Service (AKS).Hands-on experience with Docker, Kubernetes, Infrastructure as Code, CI/CD pipelines, and monitoring frameworks.Experience integrating enterprise data sources, APIs, databases, and document repositories.Bachelor's degree in Computer Science, Artificial Intelligence, Data Science, Software Engineering, or a related field.Preferred Qualifications5+ years of software engineering experience.2+ years of experience building Generative AI or Machine Learning solutions.Experience developing enterprise AI applications in healthcare, finance, or large-scale business environments.Microsoft Azure certifications are preferred.Agentic AI development and multi-agent orchestration.Fine-tuning, model customization, and evaluation pipelines.Experience with AI obs</t>
         </is>
       </c>
     </row>
@@ -4652,17 +4652,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lead AI/ML Engineer</t>
+          <t>IAM Audit Analyst</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, 48126, US</t>
+          <t>Chicago, IL, 60603, US</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049472_usa/lead-aiml-engineer</t>
+          <t>https://www.apexsystems.com/job/3049785_usa/iam-audit-analyst</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>443b88b56d2bead746b2</t>
+          <t>890b6429e3601509338b</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Position Description:Support the client's AI and ML engineering capability, including model fine-tuning oversight, agentic orchestration architecture, and LLM evaluation Oversee vendor fine-tuning of Google Cloud Vertex AI using proprietary diagnostic data, ensuring compliance with Ford's IP protection requirements and model weight storage architecture Design and build the client's Orchestration Layer. The integration framework that connects external AI engine with other internal AI engines and platform services Evaluate AI engine outputs against defined accuracy, latency, and first-time fix rate metrics; drive iterative improvement through structured feedback loops Define model evaluation frameworks and acceptance criteria for AI-generated triage recommendations, ensuring clinical accuracy before dealer-facing deployment Build internal tooling for model monitoring, drift detection, and retraining triggers within the client's GCP environment Collaborate with the client's data engineering team to define data preparation and feature engineering requirements that support model fine-tuning and inference quality Partner with the GCP Cloud Engineers to ensure model artifact storage, versioning, and access controls comply with the client's IP and security policiesContribute to the long-term insourcing roadmap by documenting model architectures, training pipelines, and prompt frameworks in sufficient detail to enable internal replication Represent AI and ML engineering in architecture reviews and vendor technical discussions.Skills Required:Technical Communication – 2–5 years translating complex technical concepts — such as ML model behavior, data pipeline architecture, or platform design decisions — into clear documentation, proposals, and presentations for both technical and non-technical audiences including engineering leads and product stakeholders. Communications – 2–5 years of demonstrated ability to communicate effectively across cross-functional teams, including facilitating technical discussions, contributing to design reviews, and keeping stakeholders aligned on project status, risks, and decisions. Google Cloud Platform – 2–5 years of hands-on experience with GCP services relevant to AI/ML and data workloads, including Vertex AI, BigQuery, GCS, Dataflow, or Cloud Composer, with the ability to deploy and manage workloads in a production cloud environment. TensorFlow – 2–5 years building, training, and evaluating machine learning models using TensorFlow or TensorFlow Extended (TFX), including experience with model versioning, pipeline integration, and deploying models to production serving infrastructure. Data Governance – 2–4 years applying data governance principles including data lineage, access controls, metadata management, and compliance standards to ensure telemetry and ML datasets meet quality, security, and regulatory requirements. Machine Learning – 3–5 years of applied ML experience including feature engineering, model selection, trai</t>
+          <t>IAM Audit Analyst\nLocation: Chicago, Illinois (Partial Remote)\n \nRole Overview\nWe are seeking an IAM Audit Analyst to lead audit engagements focused on Identity and Access Management (IAM), IT controls, and cybersecurity. This role involves overseeing the execution of audit requests, evaluating evidence, and collaborating with stakeholders to define scope and develop effective testing documentation. You will provide technical expertise in risk, controls, and IAM technologies to ensure strong governance and compliance across access management processes.\n \nKey Responsibilities\nLead projects related to Identity and Access Management (IAM) controls, IT General Controls (ITGC), information security, and IT governance.Provide oversight and guidance to stakeholders on IAM Audit requests and Evidence Requests.Partner with implementation owners to define audit scope, objectives, and develop appropriate testing strategies based on risk assessment.Assist in developing evidence testing timelines based on scope and risk.Finalize and review audit planning and scoping documentation.Conduct and review walkthroughs and testing of application controls, interface controls, and IAM processes such as provisioning, de-provisioning, access reviews, and Privileged Access Management (PAM).Ensure work meets departmental standards and quality requirements.Analyze implementation plans and follow up on milestones for issues identified by internal teams and auditors.Work with stakeholders across business, technology, risk, and control functions to drive issue resolution and remediation tracking.Communicate audit status and findings to business stakeholders and leadership.Draft audit findings, reports, and recommendations for status updates and closure packages.Identify and evaluate risks, control gaps, and remediation actions.Coordinate with other teams to ensure comprehensive coverage of risk areas.\nRequired Qualifications\n5–10 years of experience in IT Audit, Risk, Controls, or IAM-focused audits.Knowledge of audit standards, methodologies, and procedures.Understanding of IT systems, applications, and cybersecurity risks.Knowledge of Identity and Access Management (IAM) principles, including user lifecycle management, role-based access control (RBAC), and Privileged Access Management (PAM).Experience with IAM technologies such as SailPoint, Saviynt, Okta, Azure AD, or CyberArk.Understanding of IT General Controls (ITGC) and compliance frameworks (SOX, ISO, etc.).Ability to lead and execute walkthroughs, design, and operational effectiveness testing.Analytical, documentation, and reporting skills.Communication and stakeholder management skills.\nPreferred Qualifications\nCertifications such as CISA, CISSP, or CRISC.Experience in IAM governance, access certification programs, and Cloud IAM environments (Azure, AWS, GCP).Ability to manage multiple projects simultaneously and meet deadlines.Everforth Apex is a world-class IT services company that serves thousands of cl</t>
         </is>
       </c>
     </row>
@@ -4722,17 +4722,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Legal &amp; Product Security - Security Compliance Analyst II</t>
+          <t>IT Business Analyst II</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kirkland, WA, 98033, US</t>
+          <t>Jacksonville, FL, 32256, US</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049701_usa/legal--product-security---security-compliance-analyst-ii</t>
+          <t>https://www.apexsystems.com/job/3049724_usa/it-business-analyst-ii</t>
         </is>
       </c>
       <c r="J62" t="b">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>25c908a86dd784e46ccd</t>
+          <t>7f428722efeb4ffc8de3</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Legal &amp; Product Security - Security Compliance Analyst IILocation: Kirkland, Washington (Remote)COMPENSATION: $43 - $53 HOURLY Role OverviewA skilled and experienced Security Engineer is sought to join a Data Center security team. The role involves ensuring the security and integrity of a rapidly scaling Data Center infrastructure and operations. The ideal candidate will be a subject matter expert in design and operations for both general data center operations and physical security, capable of defining a mid-to-long term vision and driving cross-functional security initiatives. Key ResponsibilitiesDefine a clear mid-to-long term vision for data center physical security based on strategic business priorities.Drive and support cross-functional projects and programs related to security.Influence partners to prioritize and execute critical security initiatives.Set physical security and network security strategy for critical infrastructure.Oversee physical security design and network security considerations in the physical environment.Manage guard force operations, alarm response, and incident response.Standardize and optimize processes and procedures.Contribute to business continuity planning.Required QualificationsExperience: A minimum of 5 years of experience in mission-critical infrastructure and physical security design is required. Technical Skills: Candidates should possess broad knowledge across physical security and risk management, be an expert in developing and administering security strategies and standards, and have a general understanding of incident response, business continuity, and disaster recovery. Experience working with technical and non-technical partners, communicating security requirements, and building relationships with business leaders is also required. Preferred QualificationsRelevant security certifications (e.g., CPP, PSP, PCI, CC, CISP, etc.).Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benef</t>
+          <t>IT Business Analyst II\nLocation: Jacksonville, Florida (Onsite)\n \nRole Overview\nWe are seeking an IT Business Analyst to join our team. This role involves managing access administration requests, ensuring user satisfaction through diligent troubleshooting, and contributing to process improvements. The ideal candidate will have a strong understanding of Identity and Access Management (IAM) principles and will be proficient in handling both routine and complex administrative tasks within a technical environment.\n \nKey Responsibilities\nComplete routine and complex requests for access administration, including creating tickets, verifying approvals, and providing user communications.Track access status, application installations, and system setups.Serve as a single point of contact (SPOC) by facilitating security administration processes.Ensure user satisfaction by providing preventative maintenance and resolving routine problems.Actively identify and pursue process improvements within access management functions.Participate in special projects as needed.Exercise judgment within defined procedures and practices to determine appropriate action.\n \nRequired Qualifications\nExperience:\nWorking experience with Access Request Management tools, CyberArk, and Privileged Access Management (PAM) solutions.Experience with Data Driven Access Requests (DDAR) and Straight Through Provisioning (STP).A strong understanding and experience of Identity and Access Management (IAM) principles and best practices.\n \nTechnical Skills:\nProficient in the Microsoft Office suite (Word, Excel, PowerPoint, Outlook, Access) with the ability to analyze and synthesize data.\n \nPreferred Qualifications\nExcellent customer service and interpersonal skills with the ability to build partnerships across teams.Strong written and verbal communication skills in English.Ability to multi-task and work independently while displaying strong attention to detail.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https</t>
         </is>
       </c>
     </row>
@@ -4792,17 +4792,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mid-Level Data Scientist</t>
+          <t>JP1964 - IT Business Analyst - Niche</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Merrifield, VA, 22119-3000, US</t>
+          <t>Toronto, ON, 99999, CA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049606_usa/mid-level-data-scientist</t>
+          <t>https://www.apexsystems.com/job/3050085_usa/jp1964---it-business-analyst---niche</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -4840,17 +4840,17 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>cc66f42128402c9e8cf8</t>
+          <t>82191d615dbeb7516214</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Mid-Level Data Scientist\nLocation: Merrifield, Virginia (Hybrid)\n \nRole Overview\nWe are seeking a motivated and talented mid-level data scientist to join a growing digital data science department. This role involves building predictive solutions for mobile applications and online business operations. The position will collaborate with senior team members, leaders, and business units to create custom solutions and data science models that provide insights into customer digital behavior and enhance user experience.\n \nKey Responsibilities\nCollaborate with senior data scientists and leaders to design and implement predictive models and custom solutions.Partner with business units to gather requirements and develop data science solutions that address specific business challenges.Write efficient code in Python and SQL to manipulate and analyze data.Design, develop, and evaluate predictive models and algorithms with moderate to high complexity.Utilize traditional and machine learning techniques to build a variety of models.Analyze and interpret complex results.Develop and code modeling programs, algorithms, and automated processes.Use modeling and trend analysis to analyze data.Collaborate with team members on projects and initiatives.Utilize effective written and verbal communication to document and present findings.\nRequired Qualifications\nEducation: Bachelor’s degree in data science, statistics, economics, mathematics, computer science, engineering, or a similar quantitative field.\n \nExperience: 3-7 years of experience in data science, statistics, and data analytics.\n \nTechnical Skills:\nStrong programming abilities in SQL, Python, PySpark, R, or similar languages for data exploration, preparation, modeling, and statistical analysis.Experience with machine learning techniques and tools such as logistic regression, XGBoost, neural networks, NLP, and clustering.Ability to use data and cloud environments such as Azure, Databricks, AWS, or Hadoop.Technical writing skills.Strong communication and data storytelling presentation skills.\n \nPreferred Qualifications\nMaster’s degree in data science, statistics, mathematics, or a similar quantitative field.Familiarity with project management tools such as Azure DevOps (ADO) or JIRA.Knowledge or insights into financial services and banking products.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By ap</t>
+          <t>Product Business Analyst - Post Trade TechnologyDuration: 12-Month ContractHybrid: 2-3 Days OnsiteWorking hours: 9-5Our client, a Top 5 Canadian Bank, is seeking an experienced Product Business Analyst to support the enhancement and development of their post-trade technology platform. This role is ideal for someone with deep experience in capital markets and the ideal candidate brings broad product knowledge across equities, options, futures, and fixed income post-trade operations. You will define, prioritize, and deliver solutions that enable efficient post trade lifecycle management, strengthen risk controls, and improve operational effectiveness across global markets post trade functions. Acting as the bridge between business stakeholders and technology teams, you will ensure post-trade processes are streamlined, compliant, and supported by robust technology design, solutioning, implementation, and delivery. Key ResponsibilitiesProduct Management, Strategy &amp; Roadmap AccountabilityDevelop and maintain the product vision and roadmap for post-trade platforms, ensuring alignment with business objectives and strategic goals.Oversee end-to-end product management, including planning, prioritization, delivery, support and continuous improvement.Track roadmap milestones against delivery progress, address gaps, and implement corrective actions.Stakeholder Management Collaborate across Front Office, Middle Office &amp; Back Office operations, compliance, and technology teams to gather requirements and prioritize features.Assess functional, project &amp; delivery dependencies &amp; risk and communicate mitigating actions to the stakeholders.Provide transparent reporting to stakeholders on roadmap adherence.Engage vendors, Lines of Business, Developers and Support teams to ensure successful delivery.Requirements &amp; Delivery Translate business needs into clear, actionable user stories and acceptance criteria.Manage backlog, prioritize features, and ensure timely delivery of enhancements.Monitor delivery against roadmap commitments and provide transparent reporting to stakeholders. Prepare and document business use cases.Develop technical specifications and requirements, including process flow diagrams and data mappings.Prepare and document test cases and test conditions and conduct functional testing.Process Optimization Identify opportunities to automate and streamline trade capture, allocation, confirmation, and settlement processes.Ensure robust controls for trade breaks, reconciliations, and exception management.Data &amp; Reporting Drive improvements in data quality, trade reporting, and operational transparency.Technology Partnership Partner with vendor engineering teams to deliver scalable, resilient, and high-performing post-trade solutions that support operational efficiency and business growth.Support integration with upstream (Front Office) and Post Trade systems.Required Skills &amp; Qualifications:Experience:7+ years in Product Management, Business Analysis, Middle</t>
         </is>
       </c>
     </row>
@@ -4862,17 +4862,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Onboarding Coordinator/Analyst</t>
+          <t>Lead AI/ML Engineer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, 33647, US</t>
+          <t>Dearborn, MI, 48126, US</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049627_usa/onboarding-coordinatoranalyst</t>
+          <t>https://www.apexsystems.com/job/3049472_usa/lead-aiml-engineer</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>c1feb5890cc21e067e84</t>
+          <t>443b88b56d2bead746b2</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Onboarding Coordinator/Analyst\nLocation: Tampa, Florida (Hybrid)\n \nRole Overview\nThe Onboarding Analyst is responsible for coordinating end-to-end preboarding and onboarding activities for employees and contingent workers in a highly regulated environment. This role serves as a central point of coordination across candidates, hiring managers, HR Operations, Talent Acquisition, IT, Security, Procurement, and Compliance. The objective is to deliver a seamless, compliant, and operationally ready onboarding experience.\n \nKey Responsibilities\nCoordinate end-to-end preboarding and onboarding activities for employees and contingent workers, ensuring adherence to company policy, governance standards, and regional requirements.Initiate onboarding workflows and monitor cases to ensure timely completion of required activities.Track onboarding progress and proactively manage follow-up activities, escalations, and outstanding requirements.Serve as the primary point of contact for candidates, contingent workers, hiring managers, and cross-functional onboarding partners.Provide regional and time zone-aligned onboarding support across multiple worker populations and business units.Support onboarding access gating controls to help ensure required activities are completed prior to worker activation or access provisioning.Coordinate identity verification activities through onboarding and Day 1 processes and support employment eligibility or right-to-work verification requirements where applicable.Ensure required onboarding documents, agreements, attestations, and acknowledgements are completed accurately and on time.Partner with HR Operations, Talent Acquisition, Procurement, Compliance, Security, and hiring managers to resolve onboarding issues and delays.Ensure onboarding records and documentation are maintained in accordance with company standards and audit requirements.\nRequired Qualifications\nEducation: Bachelor’s degree in Human Resources, Business Administration, or a related field.\n \nExperience: 3+ years of experience supporting onboarding operations, HR operations, workforce administration, or related operational functions. Experience coordinating onboarding or workforce administration activities for employees and/or contingent workers is required.\n \nSkills: Strong organization and coordination skills with the ability to manage multiple onboarding cases simultaneously. Strong attention to detail and the ability to manage sensitive and confidential information. Strong communication and customer service skills are necessary to partner effectively across multiple teams and stakeholders.\n \nPreferred Qualifications\nExperience working in a regulated or compliance-driven environment.Experience with HRIS and onboarding technologies, including Fieldglass and Oracle.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, coll</t>
+          <t>Position Description:Support the client's AI and ML engineering capability, including model fine-tuning oversight, agentic orchestration architecture, and LLM evaluation Oversee vendor fine-tuning of Google Cloud Vertex AI using proprietary diagnostic data, ensuring compliance with Ford's IP protection requirements and model weight storage architecture Design and build the client's Orchestration Layer. The integration framework that connects external AI engine with other internal AI engines and platform services Evaluate AI engine outputs against defined accuracy, latency, and first-time fix rate metrics; drive iterative improvement through structured feedback loops Define model evaluation frameworks and acceptance criteria for AI-generated triage recommendations, ensuring clinical accuracy before dealer-facing deployment Build internal tooling for model monitoring, drift detection, and retraining triggers within the client's GCP environment Collaborate with the client's data engineering team to define data preparation and feature engineering requirements that support model fine-tuning and inference quality Partner with the GCP Cloud Engineers to ensure model artifact storage, versioning, and access controls comply with the client's IP and security policiesContribute to the long-term insourcing roadmap by documenting model architectures, training pipelines, and prompt frameworks in sufficient detail to enable internal replication Represent AI and ML engineering in architecture reviews and vendor technical discussions.Skills Required:Technical Communication – 2–5 years translating complex technical concepts — such as ML model behavior, data pipeline architecture, or platform design decisions — into clear documentation, proposals, and presentations for both technical and non-technical audiences including engineering leads and product stakeholders. Communications – 2–5 years of demonstrated ability to communicate effectively across cross-functional teams, including facilitating technical discussions, contributing to design reviews, and keeping stakeholders aligned on project status, risks, and decisions. Google Cloud Platform – 2–5 years of hands-on experience with GCP services relevant to AI/ML and data workloads, including Vertex AI, BigQuery, GCS, Dataflow, or Cloud Composer, with the ability to deploy and manage workloads in a production cloud environment. TensorFlow – 2–5 years building, training, and evaluating machine learning models using TensorFlow or TensorFlow Extended (TFX), including experience with model versioning, pipeline integration, and deploying models to production serving infrastructure. Data Governance – 2–4 years applying data governance principles including data lineage, access controls, metadata management, and compliance standards to ensure telemetry and ML datasets meet quality, security, and regulatory requirements. Machine Learning – 3–5 years of applied ML experience including feature engineering, model selection, trai</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Palantir Foundry Application Support Analyst</t>
+          <t>Legal &amp; Product Security - Security Compliance Analyst II</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tulsa, OK, 74103, US</t>
+          <t>Kirkland, WA, 98033, US</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3048801_usa/palantir-foundry-application-support-analyst</t>
+          <t>https://www.apexsystems.com/job/3049701_usa/legal--product-security---security-compliance-analyst-ii</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>a6697fdd3b29f050a4ad</t>
+          <t>25c908a86dd784e46ccd</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Title: Palantir User Support AnalystLocation: Tulsa, Oklahoma - RemotePay: $45-$65/hrDuration: 12 month contract w/ potential to convert full timeJob SummaryWe are seeking a Palantir Foundry User Support Analyst to support and maintain a portfolio of production Palantir Foundry applications used by field operations teams across the organization. This role is responsible for ensuring users have timely access to critical applications, resolving data and application issues, and making lightweight enhancements that improve the user experience. The ideal candidate has hands-on experience working within the Foundry platform, enjoys troubleshooting complex operational issues, and is interested in expanding their expertise toward application development. This position offers a unique opportunity to work closely with a senior Foundry developer and gain exposure to a large portfolio of enterprise applications while directly impacting day-to-day business operations.Day-to-Day ResponsibilitiesUser Support &amp; Access ManagementProvision, modify, and manage user access, roles, and permissions across multiple Palantir Foundry applications.Support user onboarding and offboarding processes, including access requests for contractors and rotating field teams.Perform backend updates and administrative changes on behalf of users when required.Serve as a primary point of contact for application support inquiries.Application Monitoring &amp; Issue ResolutionMonitor Microsoft Teams support channels and be available to support users beginning at 7:00 AM Central Time.Diagnose and resolve application, configuration, data quality, and user access issues directly within the Foundry platform.Identify recurring or widespread issues affecting multiple users and implement solutions efficiently.Escalate complex defects and enhancement requests to the Foundry Application Developer when necessary.Track recurring issues and trends to support continuous improvement initiatives.Application Maintenance &amp; EnhancementImplement minor application enhancements such as adding filters, modifying views, creating dropdown selections, and improving usability.Perform data corrections and support routine maintenance activities within Foundry.Assist with simple application development and AI Analyst-related tasks as business needs arise.Partner with development teams on testing and deployment activities.Documentation &amp; CommunicationCreate and maintain troubleshooting guides, knowledge articles, and user-facing documentation.Develop training materials and support resources for end users.Communicate application updates, releases, fixes, and known issues to operational teams.Participate in knowledge transfer activities with implementation and development partners.QualificationsRequired Qualifications1+ years of hands-on experience working within Palantir Foundry.3+ years of hand-on user support experience; Tier 1-Tier 2.Proven ability to troubleshoot and resolve application, user access, and data-related is</t>
+          <t>Legal &amp; Product Security - Security Compliance Analyst IILocation: Kirkland, Washington (Remote)COMPENSATION: $43 - $53 HOURLY Role OverviewA skilled and experienced Security Engineer is sought to join a Data Center security team. The role involves ensuring the security and integrity of a rapidly scaling Data Center infrastructure and operations. The ideal candidate will be a subject matter expert in design and operations for both general data center operations and physical security, capable of defining a mid-to-long term vision and driving cross-functional security initiatives. Key ResponsibilitiesDefine a clear mid-to-long term vision for data center physical security based on strategic business priorities.Drive and support cross-functional projects and programs related to security.Influence partners to prioritize and execute critical security initiatives.Set physical security and network security strategy for critical infrastructure.Oversee physical security design and network security considerations in the physical environment.Manage guard force operations, alarm response, and incident response.Standardize and optimize processes and procedures.Contribute to business continuity planning.Required QualificationsExperience: A minimum of 5 years of experience in mission-critical infrastructure and physical security design is required. Technical Skills: Candidates should possess broad knowledge across physical security and risk management, be an expert in developing and administering security strategies and standards, and have a general understanding of incident response, business continuity, and disaster recovery. Experience working with technical and non-technical partners, communicating security requirements, and building relationships with business leaders is also required. Preferred QualificationsRelevant security certifications (e.g., CPP, PSP, PCI, CC, CISP, etc.).Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benef</t>
         </is>
       </c>
     </row>
@@ -5002,12 +5002,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Product Owner / Business Analyst</t>
+          <t>Mid-Level Data Scientist</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newark, DE, 19713, US</t>
+          <t>Merrifield, VA, 22119-3000, US</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049579_usa/product-owner--business-analyst</t>
+          <t>https://www.apexsystems.com/job/3049606_usa/mid-level-data-scientist</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>f2249c5801f881533c34</t>
+          <t>cc66f42128402c9e8cf8</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Product Owner / Business AnalystLocation: Newark, Delaware (Hybrid)Employment Type: ContractContract Duration: 12 MonthsRole OverviewThe technical product owner/business analyst will work with IT and Business partners to define and deliver solutions that meet business objectives. This role serves as a facilitator between Business and IT, understanding business needs and playing a key part in the management and success of projects. This position leads the planning, eliciting, analyzing, validating, and managing of requirements, business processes, and solution design through the entire project lifecycle. Key ResponsibilitiesLead the planning, eliciting, analyzing, validating, and managing of requirements and business processes.Partner with Project Managers, Business Stakeholders, and IT interfacing groups to define solutions.Manage high-level solution design, test case design, and implementation planning and support.Combine business and technology skills with leadership, communication, negotiation, and facilitation.Handle multiple projects concurrently, adapting to changing priorities in a dynamic environment.Required QualificationsEducation: A Bachelor's Degree or equivalent four-year experience in a related field is required. Experience: A minimum of five years of experience in a technical product owner or business analyst role within a project-based environment is required. Prior development experience is a plus. Technical Skills:Strong understanding of agile and waterfall methodologies; experience with tools like Jira is preferable.Proficiency in project and software development methodologies and techniques.Intermediate skill level in Microsoft Word and Microsoft Excel.Experience working on multiple projects simultaneously.Strong interpersonal, negotiation, and conflict-management skills.Effective communication skills for interacting at different levels within the organization.Solid presentation, facilitation, and workshop skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy</t>
+          <t>Mid-Level Data Scientist\nLocation: Merrifield, Virginia (Hybrid)\n \nRole Overview\nWe are seeking a motivated and talented mid-level data scientist to join a growing digital data science department. This role involves building predictive solutions for mobile applications and online business operations. The position will collaborate with senior team members, leaders, and business units to create custom solutions and data science models that provide insights into customer digital behavior and enhance user experience.\n \nKey Responsibilities\nCollaborate with senior data scientists and leaders to design and implement predictive models and custom solutions.Partner with business units to gather requirements and develop data science solutions that address specific business challenges.Write efficient code in Python and SQL to manipulate and analyze data.Design, develop, and evaluate predictive models and algorithms with moderate to high complexity.Utilize traditional and machine learning techniques to build a variety of models.Analyze and interpret complex results.Develop and code modeling programs, algorithms, and automated processes.Use modeling and trend analysis to analyze data.Collaborate with team members on projects and initiatives.Utilize effective written and verbal communication to document and present findings.\nRequired Qualifications\nEducation: Bachelor’s degree in data science, statistics, economics, mathematics, computer science, engineering, or a similar quantitative field.\n \nExperience: 3-7 years of experience in data science, statistics, and data analytics.\n \nTechnical Skills:\nStrong programming abilities in SQL, Python, PySpark, R, or similar languages for data exploration, preparation, modeling, and statistical analysis.Experience with machine learning techniques and tools such as logistic regression, XGBoost, neural networks, NLP, and clustering.Ability to use data and cloud environments such as Azure, Databricks, AWS, or Hadoop.Technical writing skills.Strong communication and data storytelling presentation skills.\n \nPreferred Qualifications\nMaster’s degree in data science, statistics, mathematics, or a similar quantitative field.Familiarity with project management tools such as Azure DevOps (ADO) or JIRA.Knowledge or insights into financial services and banking products.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By ap</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>Onboarding Coordinator/Analyst</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, 23228-6501, US</t>
+          <t>Tampa, FL, 33647, US</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049735_usa/production-support-analyst</t>
+          <t>https://www.apexsystems.com/job/3049627_usa/onboarding-coordinatoranalyst</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0d0f4e445b2783001eb0</t>
+          <t>c1feb5890cc21e067e84</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Production Support AnalystLocation: Richmond, VirginiaEmployment Type: ContractContract Duration: 12 MonthsRole OverviewWe are seeking a Production and Technical Support professional to join our Data Transaction Services team. This role involves supporting secure data exchange facilities for external clients, interfacing with various internal processing systems, and providing a single point of contact for data exchange issues. The position requires working in a hybrid model, with the initial training period being fully onsite. Key ResponsibilitiesAddress and resolve file transmission issues for trading partners and business units.Monitor and respond to system alerts to ensure operational stability.Manage and resolve configuration issues within the data exchange platform.Handle critical system issues and escalate them to the appropriate level when necessary.Perform password resets and file replays as requested by clients.Provide excellent customer service and document detailed descriptions of problem situations and their resolutions. Required QualificationsCustomer service experience with the ability to manage changing priorities.Problem-solving and critical thinking skills.Strong verbal and written communication skills.Flexibility to work any shift, including weekends and holidays.Basic knowledge of Unix and Mainframes.Familiarity with transmission protocols and networks. Preferred QualificationsPrevious helpdesk or command center experience.Knowledge of Linux, Gentran Integration Suite, or Mainframe environments.Network and midrange experience.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of</t>
+          <t>Onboarding Coordinator/Analyst\nLocation: Tampa, Florida (Hybrid)\n \nRole Overview\nThe Onboarding Analyst is responsible for coordinating end-to-end preboarding and onboarding activities for employees and contingent workers in a highly regulated environment. This role serves as a central point of coordination across candidates, hiring managers, HR Operations, Talent Acquisition, IT, Security, Procurement, and Compliance. The objective is to deliver a seamless, compliant, and operationally ready onboarding experience.\n \nKey Responsibilities\nCoordinate end-to-end preboarding and onboarding activities for employees and contingent workers, ensuring adherence to company policy, governance standards, and regional requirements.Initiate onboarding workflows and monitor cases to ensure timely completion of required activities.Track onboarding progress and proactively manage follow-up activities, escalations, and outstanding requirements.Serve as the primary point of contact for candidates, contingent workers, hiring managers, and cross-functional onboarding partners.Provide regional and time zone-aligned onboarding support across multiple worker populations and business units.Support onboarding access gating controls to help ensure required activities are completed prior to worker activation or access provisioning.Coordinate identity verification activities through onboarding and Day 1 processes and support employment eligibility or right-to-work verification requirements where applicable.Ensure required onboarding documents, agreements, attestations, and acknowledgements are completed accurately and on time.Partner with HR Operations, Talent Acquisition, Procurement, Compliance, Security, and hiring managers to resolve onboarding issues and delays.Ensure onboarding records and documentation are maintained in accordance with company standards and audit requirements.\nRequired Qualifications\nEducation: Bachelor’s degree in Human Resources, Business Administration, or a related field.\n \nExperience: 3+ years of experience supporting onboarding operations, HR operations, workforce administration, or related operational functions. Experience coordinating onboarding or workforce administration activities for employees and/or contingent workers is required.\n \nSkills: Strong organization and coordination skills with the ability to manage multiple onboarding cases simultaneously. Strong attention to detail and the ability to manage sensitive and confidential information. Strong communication and customer service skills are necessary to partner effectively across multiple teams and stakeholders.\n \nPreferred Qualifications\nExperience working in a regulated or compliance-driven environment.Experience with HRIS and onboarding technologies, including Fieldglass and Oracle.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, coll</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RHTP Workforce Program Analyst</t>
+          <t>Palantir Foundry Application Support Analyst</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Providence, RI, 02908, US</t>
+          <t>Tulsa, OK, 74103, US</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049318_usa/rhtp-workforce-program-analyst</t>
+          <t>https://www.apexsystems.com/job/3048801_usa/palantir-foundry-application-support-analyst</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0657c035400174050c2e</t>
+          <t>a6697fdd3b29f050a4ad</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Apex Systems is a world class technology services business that incorporates industry or insights and experience to deliver solutions that fulfill our clients’ digital visions. Apex has an opportunity for a RHTP Workforce Program Analyst. For applicants who are interested in this opportunity, send your updated resume to lleavitt@apexsystems.com Here are the details: Position: RHTP Workforce Program AnalystLocation: Providence, RI Project Duration: 1 Year from Projected Start Date Job DescriptionAt a professional working level, perform analytical, administrative, and programmatic assignments related to the implementation of workforce initiatives within Rhode Island’s federally funded Rural Health Transformation Program (RHTP). Responsibilities shall include project operations, grant and contract administration, research, data analysis, reporting, and stakeholder engagement. Work shall be carried out under the direction of the Rural Health Workforce Transformation Coordinator in support of RHTP and related EOHHS workforce initiatives. Work under the direction and guidance of the Rural Health Workforce Transformation Coordinator, the Director of Health Workforce Transformation, and/or other senior EOHHS program leadership. Work is performed within established federal and state requirements, program objectives, policies, and procedures, with latitude for the exercise of initiative and judgment in completing assigned responsibilities.Pre-employment and incumbent worker job training Career and Technical Education Professional Development and Continuing Education Primary Care Residency Ladders to Licensure Clinical Placement Consortium Recruitment and Retention Incentives Behavioral Health Certificate for Home Care Support the development, administration, and monitoring of grants, contracts, subrecipient activities, and vendor deliverables in accordance with applicable federal and state requirements. Maintain project workplans, timelines, performance-tracking systems, reporting processes, and program records. Support data collection, analysis, reporting, and program-evaluation activities. Assist with project-level operations, partner coordination, meeting preparation, communications, and follow-up. Research relevant workforce, education, rural health, healthcare, and grant-related policies and programs to inform program design and implementation. Assist with the development of program materials, implementation processes, guidance, reports, and other written products. Support engagement with employers, educational institutions, healthcare providers, state agencies, and other workforce partners. Support coordination between RHTP workforce initiatives and related EOHHS health workforce and healthcare system planning activities. Monitor assigned activities and elevate implementation, compliance, or reporting concerns to the Rural Health Workforce Transformation Coordinator. Serve as a member of internal RHTP teams as necessary to support compliance with pro</t>
+          <t>Title: Palantir User Support AnalystLocation: Tulsa, Oklahoma - RemotePay: $45-$65/hrDuration: 12 month contract w/ potential to convert full timeJob SummaryWe are seeking a Palantir Foundry User Support Analyst to support and maintain a portfolio of production Palantir Foundry applications used by field operations teams across the organization. This role is responsible for ensuring users have timely access to critical applications, resolving data and application issues, and making lightweight enhancements that improve the user experience. The ideal candidate has hands-on experience working within the Foundry platform, enjoys troubleshooting complex operational issues, and is interested in expanding their expertise toward application development. This position offers a unique opportunity to work closely with a senior Foundry developer and gain exposure to a large portfolio of enterprise applications while directly impacting day-to-day business operations.Day-to-Day ResponsibilitiesUser Support &amp; Access ManagementProvision, modify, and manage user access, roles, and permissions across multiple Palantir Foundry applications.Support user onboarding and offboarding processes, including access requests for contractors and rotating field teams.Perform backend updates and administrative changes on behalf of users when required.Serve as a primary point of contact for application support inquiries.Application Monitoring &amp; Issue ResolutionMonitor Microsoft Teams support channels and be available to support users beginning at 7:00 AM Central Time.Diagnose and resolve application, configuration, data quality, and user access issues directly within the Foundry platform.Identify recurring or widespread issues affecting multiple users and implement solutions efficiently.Escalate complex defects and enhancement requests to the Foundry Application Developer when necessary.Track recurring issues and trends to support continuous improvement initiatives.Application Maintenance &amp; EnhancementImplement minor application enhancements such as adding filters, modifying views, creating dropdown selections, and improving usability.Perform data corrections and support routine maintenance activities within Foundry.Assist with simple application development and AI Analyst-related tasks as business needs arise.Partner with development teams on testing and deployment activities.Documentation &amp; CommunicationCreate and maintain troubleshooting guides, knowledge articles, and user-facing documentation.Develop training materials and support resources for end users.Communicate application updates, releases, fixes, and known issues to operational teams.Participate in knowledge transfer activities with implementation and development partners.QualificationsRequired Qualifications1+ years of hands-on experience working within Palantir Foundry.3+ years of hand-on user support experience; Tier 1-Tier 2.Proven ability to troubleshoot and resolve application, user access, and data-related is</t>
         </is>
       </c>
     </row>
@@ -5212,17 +5212,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SAP Production Planning Analyst</t>
+          <t>Product Owner / Business Analyst</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Erie, PA, 16509, US</t>
+          <t>Newark, DE, 19713, US</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3044713_usa/sap-production-planning-analyst</t>
+          <t>https://www.apexsystems.com/job/3049579_usa/product-owner--business-analyst</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>49418132c72e0b60f4bf</t>
+          <t>f2249c5801f881533c34</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>JD:Senior Digital &amp; IT Analyst – SAP PPNVH Division – Erie, PAPosition SummaryDefines, configures, tests, trains, and supports business-related information technology requirements and systems. Collaborating with Group and Division subject matter experts and vendors, leads or co-leads single technology or regional IT projects with accountability for completing on time, budget, and meeting expectations.· Plan-to-Produce areas supporting our Production Planning, Materials Management, Quality Management, Plant Maintenance, and Operations teams.ResponsibilitiesProvide SAP configuration and integration expertise with the SAP Production Planning module. Provide day to day support for SAP ECC6 Eco-System.Develop and maintain a deep understanding of business processes and procedures to effectively identify and implement IT solutions. Actively engage key business partners to identify/validate opportunities, ensure alignment with business strategies and define functional area roadmap.Plan, manage and implement projects in the business systems and ERP space. Develop, document, communicate, and validate business and technical requirements. Ensure all are met during the project delivery process. Define project requirements by identifying project schedule, milestones, phases, and elements; forming project teams; establish and manage project budgets.Collaborate with users and peers to provide functional and technical support. Resolve complex user reported issues in a timely manner.Lead implementation of corporate and division initiatives and actively participate on teams. Create operational documentation and KPI metrics. Perform system, interface, and batch monitoring.Oversee user acceptance testing (UAT) activities to ensure business and system requirements are met.Conduct knowledge transfer and training to business users and IT team, including sharing best practices. Create, review, and deliver end-user documentation (user guide, process flow charts, training materials) and training for accuracy.QualificationsBachelor's degree in Business, Computer Science, or other closely related field.Seven or more years of experience integrating business function responsibilities with business analysis expertise. Must demonstrate a thorough understanding of SAP ECC application and PP module.Knowledge of application and system integration methods and computing environments.Experience working with ServiceNow or similar ticketing system.Capability to lead project teams and manage systems development lifecycle.Knowledge of integration with other SAP modules.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRat</t>
+          <t>Product Owner / Business AnalystLocation: Newark, Delaware (Hybrid)Employment Type: ContractContract Duration: 12 MonthsRole OverviewThe technical product owner/business analyst will work with IT and Business partners to define and deliver solutions that meet business objectives. This role serves as a facilitator between Business and IT, understanding business needs and playing a key part in the management and success of projects. This position leads the planning, eliciting, analyzing, validating, and managing of requirements, business processes, and solution design through the entire project lifecycle. Key ResponsibilitiesLead the planning, eliciting, analyzing, validating, and managing of requirements and business processes.Partner with Project Managers, Business Stakeholders, and IT interfacing groups to define solutions.Manage high-level solution design, test case design, and implementation planning and support.Combine business and technology skills with leadership, communication, negotiation, and facilitation.Handle multiple projects concurrently, adapting to changing priorities in a dynamic environment.Required QualificationsEducation: A Bachelor's Degree or equivalent four-year experience in a related field is required. Experience: A minimum of five years of experience in a technical product owner or business analyst role within a project-based environment is required. Prior development experience is a plus. Technical Skills:Strong understanding of agile and waterfall methodologies; experience with tools like Jira is preferable.Proficiency in project and software development methodologies and techniques.Intermediate skill level in Microsoft Word and Microsoft Excel.Experience working on multiple projects simultaneously.Strong interpersonal, negotiation, and conflict-management skills.Effective communication skills for interacting at different levels within the organization.Solid presentation, facilitation, and workshop skills.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy</t>
         </is>
       </c>
     </row>
@@ -5282,17 +5282,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Security Awareness Program Analyst</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, 63146, US</t>
+          <t>Richmond, VA, 23228-6501, US</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3048964_usa/security-awareness-program-analyst</t>
+          <t>https://www.apexsystems.com/job/3049735_usa/production-support-analyst</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>9099aea2d7f6281745d7</t>
+          <t>0d0f4e445b2783001eb0</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Security Awareness Program AnalystLocation: St. Louis, Missouri (Fully Remote) Position OverviewWe are seeking a Security Awareness Program Analyst to join an IT Communications and Security Awareness team. This role will support, operationalize, and advance a phishing awareness program and related reporting initiatives. The ideal candidate will work with internal stakeholders and third-party vendors to manage security awareness campaigns, phishing simulations, and data analysis. This individual will help drive reductions in cyber risk through education and awareness initiatives while providing insights to executive leadership through data visualization. Key ResponsibilitiesSupport operational and tactical activities that contribute to the overall Security Awareness strategy.Manage and enhance the phishing awareness program and associated campaigns.Collaborate with internal teams and external vendors to coordinate program activities and deliverables.Represent the Security Awareness team in cross-functional and vendor meetings.Research, evaluate, and adapt security awareness content, programs, and materials.Stay current with emerging trends, technologies, and best practices related to phishing prevention and cybersecurity awareness.Assist in the evaluation and management of vendor relationships.Monitor, analyze, and report on program metrics and organizational data to measure effectiveness.Transform complex data into clear visualizations and executive-level presentations.Identify opportunities to reduce cyber risk and improve user security behaviors.Troubleshoot program challenges and recommend solutions.Implement process improvements and task automation initiatives.Manage program timelines, milestones, and deliverables while communicating status to stakeholders.Maintain service level agreements and identify opportunities for improvement.Ensure program activities align with applicable regulations, standards, and compliance requirements.Required QualificationsMust be presently authorized to work in the U.S. without a requirement for work authorization sponsorship.2+ years of related experience.Experience administering or contributing to an IT Security Awareness program.Proficient with data analysis using Excel, including features such as pivot tables, VLOOKUPs, and macros.Experience with transforming data analysis into visual storytelling for leadership audiences.General understanding of cybersecurity principles and information technology practices.Experience planning projects, coordinating activities, and communicating project status.Experience contributing to the development of a team’s standards, processes, and procedures.Must be committed to handling information with discretion and confidentiality.Commitment to incorporating security and compliance in all decisions and daily job responsibilities.Preferred QualificationsBachelor's degree in Cybersecurity, Information Technology, Communications, or a related field.Experience with or key understand</t>
+          <t>Production Support AnalystLocation: Richmond, VirginiaEmployment Type: ContractContract Duration: 12 MonthsRole OverviewWe are seeking a Production and Technical Support professional to join our Data Transaction Services team. This role involves supporting secure data exchange facilities for external clients, interfacing with various internal processing systems, and providing a single point of contact for data exchange issues. The position requires working in a hybrid model, with the initial training period being fully onsite. Key ResponsibilitiesAddress and resolve file transmission issues for trading partners and business units.Monitor and respond to system alerts to ensure operational stability.Manage and resolve configuration issues within the data exchange platform.Handle critical system issues and escalate them to the appropriate level when necessary.Perform password resets and file replays as requested by clients.Provide excellent customer service and document detailed descriptions of problem situations and their resolutions. Required QualificationsCustomer service experience with the ability to manage changing priorities.Problem-solving and critical thinking skills.Strong verbal and written communication skills.Flexibility to work any shift, including weekends and holidays.Basic knowledge of Unix and Mainframes.Familiarity with transmission protocols and networks. Preferred QualificationsPrevious helpdesk or command center experience.Knowledge of Linux, Gentran Integration Suite, or Mainframe environments.Network and midrange experience.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employee stock purchase program) and a 401K program which allows you to contribute typically within 30 days of</t>
         </is>
       </c>
     </row>
@@ -5352,17 +5352,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>RHTP Workforce Program Analyst</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, 55344, US</t>
+          <t>Providence, RI, 02908, US</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3047631_usa/senior-business-analyst</t>
+          <t>https://www.apexsystems.com/job/3049318_usa/rhtp-workforce-program-analyst</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -5400,17 +5400,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>b5b724e28c81b5cd13ff</t>
+          <t>0657c035400174050c2e</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Senior Business Analyst – BOLT Orchestration $30-35/hrContract until End of Year, will extend into 2027Position SummaryThe Senior Business Analyst – BOLT Orchestration supports capability delivery across Trial Claim and Real Claim capabilities within the BOLT Orchestration program. This role is responsible for translating capability vision into detailed business and functional requirements, user stories, acceptance criteria, and audit-ready documentation. Working closely with Capability Managers, Enterprise Claim Asset teams, Enterprise Architecture, and Analytics partners, the Senior Business Analyst ensures end-to-end traceability, consistent requirements decomposition, and high-quality documentation that enables scalable orchestration delivery across strategic claim capabilities. Key ResponsibilitiesPartner with Capability Managers to translate business objectives and capability intent into detailed requirements and delivery artifacts.Decompose capabilities into features, user stories, acceptance criteria, process flows, and implementation-ready requirements.Create and maintain audit-ready traceability across AHA IDs, project identifiers, features, user stories, requirements, and testing artifacts.Document canonical request/response contracts and integration requirements across Enterprise Claim Asset services and orchestration workflows.Collaborate with Capability Owners, Enterprise Architecture, Analytics teams, business stakeholders, and technology partners to validate requirements and resolve gaps.Facilitate requirements elicitation, backlog refinement, story grooming, and requirements review sessions.Support delivery teams by clarifying requirements, managing requirement changes, and ensuring alignment with approved scope.Develop business process documentation, workflow diagrams, operational procedures, and implementation support materials.Ensure requirements, acceptance criteria, and supporting documentation meet audit, governance, and compliance expectations.Produce documentation and traceability packages supporting Trial Claim and Real Claim delivery milestones.Identify risks, dependencies, assumptions, and requirement impacts across integrated orchestration capabilities.Support readiness activities for future claim orchestration capabilities and enterprise business use cases. Required Qualifications7+ years of experience in business analysis, systems analysis, product delivery, program delivery, or related disciplines.3+ years of healthcare claims experience.Experience developing detailed business requirements, user stories, acceptance criteria, and traceability documentation.Demonstrated experience working within complex, matrixed organizations and cross-functional teams.Strong understanding of business process analysis, requirements management, and software delivery lifecycles.Experience managing requirements across multiple teams, dependencies, and delivery workstreams.Strong analytical, problem-solving, communication, and stakehold</t>
+          <t>Apex Systems is a world class technology services business that incorporates industry or insights and experience to deliver solutions that fulfill our clients’ digital visions. Apex has an opportunity for a RHTP Workforce Program Analyst. For applicants who are interested in this opportunity, send your updated resume to lleavitt@apexsystems.com Here are the details: Position: RHTP Workforce Program AnalystLocation: Providence, RI Project Duration: 1 Year from Projected Start Date Job DescriptionAt a professional working level, perform analytical, administrative, and programmatic assignments related to the implementation of workforce initiatives within Rhode Island’s federally funded Rural Health Transformation Program (RHTP). Responsibilities shall include project operations, grant and contract administration, research, data analysis, reporting, and stakeholder engagement. Work shall be carried out under the direction of the Rural Health Workforce Transformation Coordinator in support of RHTP and related EOHHS workforce initiatives. Work under the direction and guidance of the Rural Health Workforce Transformation Coordinator, the Director of Health Workforce Transformation, and/or other senior EOHHS program leadership. Work is performed within established federal and state requirements, program objectives, policies, and procedures, with latitude for the exercise of initiative and judgment in completing assigned responsibilities.Pre-employment and incumbent worker job training Career and Technical Education Professional Development and Continuing Education Primary Care Residency Ladders to Licensure Clinical Placement Consortium Recruitment and Retention Incentives Behavioral Health Certificate for Home Care Support the development, administration, and monitoring of grants, contracts, subrecipient activities, and vendor deliverables in accordance with applicable federal and state requirements. Maintain project workplans, timelines, performance-tracking systems, reporting processes, and program records. Support data collection, analysis, reporting, and program-evaluation activities. Assist with project-level operations, partner coordination, meeting preparation, communications, and follow-up. Research relevant workforce, education, rural health, healthcare, and grant-related policies and programs to inform program design and implementation. Assist with the development of program materials, implementation processes, guidance, reports, and other written products. Support engagement with employers, educational institutions, healthcare providers, state agencies, and other workforce partners. Support coordination between RHTP workforce initiatives and related EOHHS health workforce and healthcare system planning activities. Monitor assigned activities and elevate implementation, compliance, or reporting concerns to the Rural Health Workforce Transformation Coordinator. Serve as a member of internal RHTP teams as necessary to support compliance with pro</t>
         </is>
       </c>
     </row>
@@ -5422,17 +5422,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP Production Planning Analyst</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, 55344, US</t>
+          <t>Erie, PA, 16509, US</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3043949_usa/senior-data-engineer</t>
+          <t>https://www.apexsystems.com/job/3044713_usa/sap-production-planning-analyst</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -5470,17 +5470,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>b44e032e6a16678ff86e</t>
+          <t>49418132c72e0b60f4bf</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Senior Data EngineerContract Duration: 6-monthsLocation: Remote (100% Telecommute)Hours: Monday–Friday, 9:00 AM–5:00 PMRate: $60/hrProject OverviewClient is seeking a hands-on Senior Data Engineer to support its CT Enterprise Data Warehouse (EDW) within the Enterprise Data Warehouse and Analytics organization. This individual will work with large healthcare datasets and help translate business requirements into scalable enterprise data solutions. The role will support key initiatives within the CT EDW while contributing to broader data governance, information management, analytics, privacy and security, data modeling, and modernization efforts across the organization.Key ResponsibilitiesDesign, develop, maintain, and optimize enterprise data warehouse solutions and data pipelines.Build and support ETL/ELT processes using Azure Data Factory (ADF), Databricks, Informatica PowerCenter, SSIS, and related technologies.Develop and maintain data integrations between multiple healthcare systems and enterprise data platforms.Create, troubleshoot, and optimize SQL code, stored procedures, and database objects within Oracle, Snowflake, SQL Server, and other relational databases.Process and integrate structured and unstructured healthcare data, including HL7 and FHIR data formats.Collaborate with business stakeholders, analysts, and technical teams to gather requirements and translate them into technical solutions.Develop detailed ETL specifications, technical designs, and documentation.Support data governance, data quality, privacy, and security initiatives.Utilize source control and DevOps tools such as GitHub, Azure DevOps, and SVN to manage code deployments and development lifecycle activities.Troubleshoot and resolve complex data integration and performance issues while identifying opportunities for optimization and automation.Required QualificationsBachelor's degree in Computer Science, Information Technology, Analytics, Mathematics, Statistics, Business, or a related field.8+ years of Data Engineering experience with a strong focus on Data Warehousing.5+ years of experience with Azure Data Factory (ADF) and Databricks.5+ years of ETL development experience using Informatica PowerCenter, SSIS, Azure Data Factory, or similar tools.5+ years of experience working with relational databases such as Oracle, Snowflake, and SQL Server.5+ years of experience developing stored procedures using Oracle PL/SQL, SQL Server T-SQL, or Snowflake SQL.3+ years of Python scripting experience.3+ years of experience utilizing source control and DevOps tools, including Azure DevOps, GitHub, SVN, or similar platforms.2+ years of experience processing structured and unstructured data.Experience working with healthcare interoperability standards, including HL7 and FHIR.3+ years of experience analyzing business requirements and creating detailed ETL specifications.Strong analytical, troubleshooting, and problem-solving skills.Preferred Qualifications3+ years of batch scripting o</t>
+          <t>JD:Senior Digital &amp; IT Analyst – SAP PPNVH Division – Erie, PAPosition SummaryDefines, configures, tests, trains, and supports business-related information technology requirements and systems. Collaborating with Group and Division subject matter experts and vendors, leads or co-leads single technology or regional IT projects with accountability for completing on time, budget, and meeting expectations.· Plan-to-Produce areas supporting our Production Planning, Materials Management, Quality Management, Plant Maintenance, and Operations teams.ResponsibilitiesProvide SAP configuration and integration expertise with the SAP Production Planning module. Provide day to day support for SAP ECC6 Eco-System.Develop and maintain a deep understanding of business processes and procedures to effectively identify and implement IT solutions. Actively engage key business partners to identify/validate opportunities, ensure alignment with business strategies and define functional area roadmap.Plan, manage and implement projects in the business systems and ERP space. Develop, document, communicate, and validate business and technical requirements. Ensure all are met during the project delivery process. Define project requirements by identifying project schedule, milestones, phases, and elements; forming project teams; establish and manage project budgets.Collaborate with users and peers to provide functional and technical support. Resolve complex user reported issues in a timely manner.Lead implementation of corporate and division initiatives and actively participate on teams. Create operational documentation and KPI metrics. Perform system, interface, and batch monitoring.Oversee user acceptance testing (UAT) activities to ensure business and system requirements are met.Conduct knowledge transfer and training to business users and IT team, including sharing best practices. Create, review, and deliver end-user documentation (user guide, process flow charts, training materials) and training for accuracy.QualificationsBachelor's degree in Business, Computer Science, or other closely related field.Seven or more years of experience integrating business function responsibilities with business analysis expertise. Must demonstrate a thorough understanding of SAP ECC application and PP module.Knowledge of application and system integration methods and computing environments.Experience working with ServiceNow or similar ticketing system.Capability to lead project teams and manage systems development lifecycle.Knowledge of integration with other SAP modules.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRat</t>
         </is>
       </c>
     </row>
@@ -5492,17 +5492,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Teradata Database Administrator</t>
+          <t>Security Awareness Program Analyst</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28255, US</t>
+          <t>St. Louis, MO, 63146, US</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3050186_usa/teradata-database-administrator</t>
+          <t>https://www.apexsystems.com/job/3048964_usa/security-awareness-program-analyst</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>679191a069c823092ab4</t>
+          <t>9099aea2d7f6281745d7</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Teradata Database AdministratorLocation: Charlotte, NC/Jacksonville, FL (Onsite)Employment Type: ContractContract Duration: 10 MonthsRole OverviewWe are seeking a Database Administrator with more than 10 years of experience for a key role supporting our enterprise data warehouse environments. The ideal candidate will have experience with Teradata V17.20 or higher and a strong background in application DBA functions. This position involves working with application project teams to implement database changes for large initiatives and providing on-call rotation support. Key ResponsibilitiesSupport Application DBA functions including DDL creation, SQL scripting, problem research, and change deployments.Assist with the design, development, implementation, and support of automated DBA processes using Teradata and Unix/Linux scripting.Support multiple Teradata systems, including development/UAT, disaster recovery, and production environments.Implement and administer access policies in conjunction with corporate standards.Support Mainframe administrative functions, including archive processing and job scheduling.Manage, design, and consult on storage management, archive, restore, and disaster recovery practices.Work closely with application project teams on the implementation of database changes.Work independently with minimal supervision, receiving general guidance from senior team members or managers.Required QualificationsExperience: More than 10 years of experience as a Teradata DBA. Technical Skills:Advanced working knowledge of Teradata RDBMS at both physical and logical levels.Advanced working knowledge of the Teradata suite of tools: Teradata Studio, TDWM, BTEQ, ARCMAIN, FASTLOAD, MLOAD, TPUMP, TPT, DBQL, PDCR.Working knowledge of Mainframe interfaces and execution: TDP, JCL, TSO, ISPF, FICON, NDM.Working knowledge of Viewpoint, Teradata Data Mover, and Teradata BAR technology.Working knowledge of Unix/Linux scripting (KSH, BASH, PERL).Working knowledge of job schedulers such as CA-7 and AutoSys, and replication technologies like Golden Gate. Preferred QualificationsFamiliarity with Teradata Systems setup, GDO, DBSControl, and Multitool.Working knowledge of QueryGrid, DSA, Taraserver, NPARC, and TASM.Familiarity with REXX scripting.Familiarity with Hadoop and Cloud concepts and technologies.Familiarity with project and change management solutions and automation software, such as Agile, Remedy, and Ansible.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.</t>
+          <t>Security Awareness Program AnalystLocation: St. Louis, Missouri (Fully Remote) Position OverviewWe are seeking a Security Awareness Program Analyst to join an IT Communications and Security Awareness team. This role will support, operationalize, and advance a phishing awareness program and related reporting initiatives. The ideal candidate will work with internal stakeholders and third-party vendors to manage security awareness campaigns, phishing simulations, and data analysis. This individual will help drive reductions in cyber risk through education and awareness initiatives while providing insights to executive leadership through data visualization. Key ResponsibilitiesSupport operational and tactical activities that contribute to the overall Security Awareness strategy.Manage and enhance the phishing awareness program and associated campaigns.Collaborate with internal teams and external vendors to coordinate program activities and deliverables.Represent the Security Awareness team in cross-functional and vendor meetings.Research, evaluate, and adapt security awareness content, programs, and materials.Stay current with emerging trends, technologies, and best practices related to phishing prevention and cybersecurity awareness.Assist in the evaluation and management of vendor relationships.Monitor, analyze, and report on program metrics and organizational data to measure effectiveness.Transform complex data into clear visualizations and executive-level presentations.Identify opportunities to reduce cyber risk and improve user security behaviors.Troubleshoot program challenges and recommend solutions.Implement process improvements and task automation initiatives.Manage program timelines, milestones, and deliverables while communicating status to stakeholders.Maintain service level agreements and identify opportunities for improvement.Ensure program activities align with applicable regulations, standards, and compliance requirements.Required QualificationsMust be presently authorized to work in the U.S. without a requirement for work authorization sponsorship.2+ years of related experience.Experience administering or contributing to an IT Security Awareness program.Proficient with data analysis using Excel, including features such as pivot tables, VLOOKUPs, and macros.Experience with transforming data analysis into visual storytelling for leadership audiences.General understanding of cybersecurity principles and information technology practices.Experience planning projects, coordinating activities, and communicating project status.Experience contributing to the development of a team’s standards, processes, and procedures.Must be committed to handling information with discretion and confidentiality.Commitment to incorporating security and compliance in all decisions and daily job responsibilities.Preferred QualificationsBachelor's degree in Cybersecurity, Information Technology, Communications, or a related field.Experience with or key understand</t>
         </is>
       </c>
     </row>
@@ -5562,12 +5562,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Unreal AI Engineer</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, 90064, US</t>
+          <t>Eden Prairie, MN, 55344, US</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://www.apexsystems.com/job/3049332_usa/unreal-ai-engineer</t>
+          <t>https://www.apexsystems.com/job/3047631_usa/senior-business-analyst</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -5610,44 +5610,49 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>423c5715c4b8caea5f04</t>
+          <t>b5b724e28c81b5cd13ff</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Applied AI/Agentic Engineer Location: United States (Remote)Work Type: Contract Role OverviewWe are seeking an Applied AI Engineer to join a dynamic team. This role involves hands-on development to build agentic AI experiences that automate common Unreal workflows for developers. The ideal candidate will be instrumental in creating infrastructure to distribute, develop, and maintain these workflows, collaborating closely with game development teams to identify impactful utilities. Key ResponsibilitiesBe hands-on in development, writing code that sets a high standard for other engineers.Develop agentic AI experiences that orchestrate tools and services to automate common Unreal workflows for developers, such as triaging issues, proposing fixes, and generating scaffolding.Create infrastructure to distribute, develop, and maintain agentic workflows for wide adoption.Collaborate with game development teams to understand utilities that can make an impact.Innovate with new ideas for AI-integrated workflows, iterate on them, and evaluate their value within the team.Required Qualifications5+ years of professional experience as a software engineer.Ability to identify problems and rapidly iterate with teams.Experience with developing agentic workflows.Experience with game development.Experience distributing technical solutions across multiple projects in different stages of development.Strong communication skills to articulate value and ideas within the team and interface with other game developers.Preferred QualificationsExperience with Unreal Engine.Experience working with large game teams.Experience shipping software to customers.Experience with tooling.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employ</t>
+          <t>Senior Business Analyst – BOLT Orchestration $30-35/hrContract until End of Year, will extend into 2027Position SummaryThe Senior Business Analyst – BOLT Orchestration supports capability delivery across Trial Claim and Real Claim capabilities within the BOLT Orchestration program. This role is responsible for translating capability vision into detailed business and functional requirements, user stories, acceptance criteria, and audit-ready documentation. Working closely with Capability Managers, Enterprise Claim Asset teams, Enterprise Architecture, and Analytics partners, the Senior Business Analyst ensures end-to-end traceability, consistent requirements decomposition, and high-quality documentation that enables scalable orchestration delivery across strategic claim capabilities. Key ResponsibilitiesPartner with Capability Managers to translate business objectives and capability intent into detailed requirements and delivery artifacts.Decompose capabilities into features, user stories, acceptance criteria, process flows, and implementation-ready requirements.Create and maintain audit-ready traceability across AHA IDs, project identifiers, features, user stories, requirements, and testing artifacts.Document canonical request/response contracts and integration requirements across Enterprise Claim Asset services and orchestration workflows.Collaborate with Capability Owners, Enterprise Architecture, Analytics teams, business stakeholders, and technology partners to validate requirements and resolve gaps.Facilitate requirements elicitation, backlog refinement, story grooming, and requirements review sessions.Support delivery teams by clarifying requirements, managing requirement changes, and ensuring alignment with approved scope.Develop business process documentation, workflow diagrams, operational procedures, and implementation support materials.Ensure requirements, acceptance criteria, and supporting documentation meet audit, governance, and compliance expectations.Produce documentation and traceability packages supporting Trial Claim and Real Claim delivery milestones.Identify risks, dependencies, assumptions, and requirement impacts across integrated orchestration capabilities.Support readiness activities for future claim orchestration capabilities and enterprise business use cases. Required Qualifications7+ years of experience in business analysis, systems analysis, product delivery, program delivery, or related disciplines.3+ years of healthcare claims experience.Experience developing detailed business requirements, user stories, acceptance criteria, and traceability documentation.Demonstrated experience working within complex, matrixed organizations and cross-functional teams.Strong understanding of business process analysis, requirements management, and software delivery lifecycles.Experience managing requirements across multiple teams, dependencies, and delivery workstreams.Strong analytical, problem-solving, communication, and stakehold</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Burtch Works</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sr Data Catalog Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>Eden Prairie, MN, 55344, US</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5657,12 +5662,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.burtchworks.com/s?jobId=a09Vv00000AJ5O1IAL%2Fsr-data-catalog-analyst-new-york-ny</t>
+          <t>https://www.apexsystems.com/job/3043949_usa/senior-data-engineer</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -5670,54 +5675,54 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-03T18:19:19+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>82a57506a3432f4761f7</t>
+          <t>b44e032e6a16678ff86e</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Burtch Works | Hire AI, Data, Engineering, Cyber &amp; Analytics Talent Loading × Sorry to interrupt CSS Error Refresh Skip to Navigation Skip to Main Content Toggle Menu Job Portal Home Return to Burtch Works More Login Find Jobs Search Jobs Type Select an Option Reset Search Operating Executive of AI &amp; Software Engineering Location Los Angeles, CA Posted Last Week Technical Project Manager Location Remote Posted Last Week Sr Data Catalog Analyst Location New York, NY Posted Last Week Lead UX Designer Location Lake Forest, IL Posted Last Week AI Software Engineer Location Remote 7 days ago Technical Product Manager Location Remote (U.S.) 8 days ago Data Engineering Manager Location Chicago, IL 10 days ago Sr Full Stack AI Engineer Location remote 11 days ago CVP, Model Validation &amp; AI Governance Location New York, NY 11 days ago Lead Data Engineer Location New York, NY 13 days ago &lt;&lt; &lt; 1 2 3 4 5 6 7 8 &gt; &gt;&gt; Page of 8 Sr Data Catalog Analyst New York, NY Type Permanent Pay Rate Salary $155000 - $178000 Apply Now Share This Job Sr Data Catalog Analyst Location: New York, NY - Hybrid (3 days per week) Position Overview Job Summary: The Senior Data Catalog Analyst plays a key role in advancing enterprise data governance initiatives. This individual contributor role is responsible for designing, implementing, and optimizing metadata management, data catalogs, lineage documentation, and governance workflows using platforms such as Atlan and Unity Catalog. Working closely with data product managers, business SMEs, and technology teams, the analyst enhances data discoverability, quality, and compliance across the enterprise, supporting the organization's Data Strategy and enabling timely, data-driven decisions built on trusted information. Key Responsibilities: Curate and maintain glossaries, taxonomies, and metadata for business and technical assets. Design and implement governance workflows including stewardship approvals, certifications, and data access protocols. Support PII/PHI classification, data quality checks, and lineage validation. Collaborate with data product managers, SMEs, and engineers to capture business context, align it with technical architectures, and strengthen metadata documentation. Drive adoption of governance tools through roadshows, training sessions, user enablement, and data owner/steward playbooks. Participate in Agile ceremonies by contributing to backlog building and sprint events in Jira. Requirements: 5–7+ years of professional experience, including 2–3+ years in a data governance function. Bachelor's degree in Business, Computer Science, Information Technology, or a related field. Strong understanding of data governance frameworks, metadata management, and data cataloging and lineage concepts. Proven ability to translate business needs into governance policies, standards, and workflows. Excellent communication and collaboration skills with experience working across business and technical teams. Hands-on experience with Atla</t>
+          <t>Senior Data EngineerContract Duration: 6-monthsLocation: Remote (100% Telecommute)Hours: Monday–Friday, 9:00 AM–5:00 PMRate: $60/hrProject OverviewClient is seeking a hands-on Senior Data Engineer to support its CT Enterprise Data Warehouse (EDW) within the Enterprise Data Warehouse and Analytics organization. This individual will work with large healthcare datasets and help translate business requirements into scalable enterprise data solutions. The role will support key initiatives within the CT EDW while contributing to broader data governance, information management, analytics, privacy and security, data modeling, and modernization efforts across the organization.Key ResponsibilitiesDesign, develop, maintain, and optimize enterprise data warehouse solutions and data pipelines.Build and support ETL/ELT processes using Azure Data Factory (ADF), Databricks, Informatica PowerCenter, SSIS, and related technologies.Develop and maintain data integrations between multiple healthcare systems and enterprise data platforms.Create, troubleshoot, and optimize SQL code, stored procedures, and database objects within Oracle, Snowflake, SQL Server, and other relational databases.Process and integrate structured and unstructured healthcare data, including HL7 and FHIR data formats.Collaborate with business stakeholders, analysts, and technical teams to gather requirements and translate them into technical solutions.Develop detailed ETL specifications, technical designs, and documentation.Support data governance, data quality, privacy, and security initiatives.Utilize source control and DevOps tools such as GitHub, Azure DevOps, and SVN to manage code deployments and development lifecycle activities.Troubleshoot and resolve complex data integration and performance issues while identifying opportunities for optimization and automation.Required QualificationsBachelor's degree in Computer Science, Information Technology, Analytics, Mathematics, Statistics, Business, or a related field.8+ years of Data Engineering experience with a strong focus on Data Warehousing.5+ years of experience with Azure Data Factory (ADF) and Databricks.5+ years of ETL development experience using Informatica PowerCenter, SSIS, Azure Data Factory, or similar tools.5+ years of experience working with relational databases such as Oracle, Snowflake, and SQL Server.5+ years of experience developing stored procedures using Oracle PL/SQL, SQL Server T-SQL, or Snowflake SQL.3+ years of Python scripting experience.3+ years of experience utilizing source control and DevOps tools, including Azure DevOps, GitHub, SVN, or similar platforms.2+ years of experience processing structured and unstructured data.Experience working with healthcare interoperability standards, including HL7 and FHIR.3+ years of experience analyzing business requirements and creating detailed ETL specifications.Strong analytical, troubleshooting, and problem-solving skills.Preferred Qualifications3+ years of batch scripting o</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CompuGain</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
+          <t>Teradata Database Administrator</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rockville Pike</t>
+          <t>Charlotte, NC, 28255, US</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5727,12 +5732,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
+          <t>https://www.apexsystems.com/job/3050186_usa/teradata-database-administrator</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -5740,54 +5745,54 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>52176647527c6698e6d4</t>
+          <t>679191a069c823092ab4</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Teradata Database AdministratorLocation: Charlotte, NC/Jacksonville, FL (Onsite)Employment Type: ContractContract Duration: 10 MonthsRole OverviewWe are seeking a Database Administrator with more than 10 years of experience for a key role supporting our enterprise data warehouse environments. The ideal candidate will have experience with Teradata V17.20 or higher and a strong background in application DBA functions. This position involves working with application project teams to implement database changes for large initiatives and providing on-call rotation support. Key ResponsibilitiesSupport Application DBA functions including DDL creation, SQL scripting, problem research, and change deployments.Assist with the design, development, implementation, and support of automated DBA processes using Teradata and Unix/Linux scripting.Support multiple Teradata systems, including development/UAT, disaster recovery, and production environments.Implement and administer access policies in conjunction with corporate standards.Support Mainframe administrative functions, including archive processing and job scheduling.Manage, design, and consult on storage management, archive, restore, and disaster recovery practices.Work closely with application project teams on the implementation of database changes.Work independently with minimal supervision, receiving general guidance from senior team members or managers.Required QualificationsExperience: More than 10 years of experience as a Teradata DBA. Technical Skills:Advanced working knowledge of Teradata RDBMS at both physical and logical levels.Advanced working knowledge of the Teradata suite of tools: Teradata Studio, TDWM, BTEQ, ARCMAIN, FASTLOAD, MLOAD, TPUMP, TPT, DBQL, PDCR.Working knowledge of Mainframe interfaces and execution: TDP, JCL, TSO, ISPF, FICON, NDM.Working knowledge of Viewpoint, Teradata Data Mover, and Teradata BAR technology.Working knowledge of Unix/Linux scripting (KSH, BASH, PERL).Working knowledge of job schedulers such as CA-7 and AutoSys, and replication technologies like Golden Gate. Preferred QualificationsFamiliarity with Teradata Systems setup, GDO, DBSControl, and Multitool.Working knowledge of QueryGrid, DSA, Taraserver, NPARC, and TASM.Familiarity with REXX scripting.Familiarity with Hadoop and Cloud concepts and technologies.Familiarity with project and change management solutions and automation software, such as Agile, Remedy, and Ansible.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CompuGain</t>
+          <t>Apex Systems</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Unreal AI Engineer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rockville Pike</t>
+          <t>Los Angeles, CA, 90064, US</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5797,12 +5802,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
+          <t>https://www.apexsystems.com/job/3049332_usa/unreal-ai-engineer</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -5810,54 +5815,49 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>406d96610632ccfd5711</t>
+          <t>423c5715c4b8caea5f04</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Applied AI/Agentic Engineer Location: United States (Remote)Work Type: Contract Role OverviewWe are seeking an Applied AI Engineer to join a dynamic team. This role involves hands-on development to build agentic AI experiences that automate common Unreal workflows for developers. The ideal candidate will be instrumental in creating infrastructure to distribute, develop, and maintain these workflows, collaborating closely with game development teams to identify impactful utilities. Key ResponsibilitiesBe hands-on in development, writing code that sets a high standard for other engineers.Develop agentic AI experiences that orchestrate tools and services to automate common Unreal workflows for developers, such as triaging issues, proposing fixes, and generating scaffolding.Create infrastructure to distribute, develop, and maintain agentic workflows for wide adoption.Collaborate with game development teams to understand utilities that can make an impact.Innovate with new ideas for AI-integrated workflows, iterate on them, and evaluate their value within the team.Required Qualifications5+ years of professional experience as a software engineer.Ability to identify problems and rapidly iterate with teams.Experience with developing agentic workflows.Experience with game development.Experience distributing technical solutions across multiple projects in different stages of development.Strong communication skills to articulate value and ideas within the team and interface with other game developers.Preferred QualificationsExperience with Unreal Engine.Experience working with large game teams.Experience shipping software to customers.Experience with tooling.Everforth Apex is a world-class IT services company that serves thousands of clients across the globe. When you join Everforth Apex, you become part of a team that values innovation, collaboration, and continuous learning. We offer quality career resources, training, certifications, development opportunities, and a comprehensive benefits package. Our commitment to excellence is reflected in many awards, including ClearlyRateds Best of Staffing® in Talent Satisfaction in the United States and Great Place to Work® in the United Kingdom and Mexico.Everforth Apex uses a virtual recruiter as part of the application process. Click here for more details. By applying for this job, you agree to receive calls, AI-generated calls, text messages, or emails from Everforth Apex and its affiliates, and contracted partners. Frequency varies for text messages. Message and data rates may apply. Carriers are not liable for delayed or undelivered messages. You can reply STOP to cancel and HELP for help. You can access our privacy policy at https://www.apexsystems.com/privacy-policyEverforth Apex Benefits Overview: Everforth Apex offers a range of supplemental benefits, including medical, dental, vision, life, disability, and other insurance plans that offer an optional layer of financial protection. We offer an ESPP (employ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>Burtch Works</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aerospace Quality Support Analyst</t>
+          <t>Sr Data Catalog Analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Temporary</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/aerospace-quality-support-analyst/406018</t>
+          <t>https://jobs.burtchworks.com/s?jobId=a09Vv00000AJ5O1IAL%2Fsr-data-catalog-analyst-new-york-ny</t>
         </is>
       </c>
       <c r="J78" t="b">
@@ -5880,39 +5880,39 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-07T07:45:06+00:00</t>
+          <t>2026-09-03T18:19:19+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>53445de4641ed1bd7973</t>
+          <t>82a57506a3432f4761f7</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Aerospace Quality Support Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Aerospace Quality Support Analyst Reference Number: 406018 Published Date: 09/07/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in aerospace manufacturing and maintenance, is seeking a dedicated and detail-oriented Aerospace Quality Support Analyst o join their team. As an Aerospace Quality Support Analyst, you will be an integral part of the quality and engineering organization supporting aerospace maintenance, repair, and overhaul (MRO) operations. The ideal candidate will demonstrate strong analytical skills, effective communication, and a proactive approach to problem-solving, which will enable you to thrive within this dynamic environment. Job Title: Aerospace Quality Support Analyst Location: Miramar, Florida Pay Range: $40-$45/hr DOE plus OT, benefits What's the Job? Review quality logs, inspection records, and manufacturing documentation to ensure compliance with internal standards, FAA regulations, and customer requirements. Help manage nonconformance reports, log quality escapes, and track customer or audit complaints using factory operating systems like SAP. Collect, organize, and analyze quality metrics and data trends to identify factory risks and minimize workflow disruptions. Partner closely with Quality Inspectors, Operations, Supply Chain, and Manufacturing Engineers on the production floor to maintain product conformity and resolve shop-floor bottlenecks. Participate in daily quality clinics, Material Review Board (MRB) actions, and continuous improvement initiatives (CORE/Lean). What's Needed? Experience reviewing quality documentation and ensuring compliance with industry</t>
+          <t>Burtch Works | Hire AI, Data, Engineering, Cyber &amp; Analytics Talent Loading × Sorry to interrupt CSS Error Refresh Skip to Navigation Skip to Main Content Toggle Menu Job Portal Home Return to Burtch Works More Login Find Jobs Search Jobs Type Select an Option Reset Search Operating Executive of AI &amp; Software Engineering Location Los Angeles, CA Posted Last Week Technical Project Manager Location Remote Posted Last Week Sr Data Catalog Analyst Location New York, NY Posted Last Week Lead UX Designer Location Lake Forest, IL Posted Last Week AI Software Engineer Location Remote 8 days ago Technical Product Manager Location Remote (U.S.) 9 days ago Data Engineering Manager Location Chicago, IL 11 days ago Sr Full Stack AI Engineer Location remote 12 days ago CVP, Model Validation &amp; AI Governance Location New York, NY 12 days ago Lead Data Engineer Location New York, NY 14 days ago &lt;&lt; &lt; 1 2 3 4 5 6 7 8 &gt; &gt;&gt; Page of 8 Sr Data Catalog Analyst New York, NY Type Permanent Pay Rate Salary $155000 - $178000 Apply Now Share This Job Sr Data Catalog Analyst Location: New York, NY - Hybrid (3 days per week) Position Overview Job Summary: The Senior Data Catalog Analyst plays a key role in advancing enterprise data governance initiatives. This individual contributor role is responsible for designing, implementing, and optimizing metadata management, data catalogs, lineage documentation, and governance workflows using platforms such as Atlan and Unity Catalog. Working closely with data product managers, business SMEs, and technology teams, the analyst enhances data discoverability, quality, and compliance across the enterprise, supporting the organization's Data Strategy and enabling timely, data-driven decisions built on trusted information. Key Responsibilities: Curate and maintain glossaries, taxonomies, and metadata for business and technical assets. Design and implement governance workflows including stewardship approvals, certifications, and data access protocols. Support PII/PHI classification, data quality checks, and lineage validation. Collaborate with data product managers, SMEs, and engineers to capture business context, align it with technical architectures, and strengthen metadata documentation. Drive adoption of governance tools through roadshows, training sessions, user enablement, and data owner/steward playbooks. Participate in Agile ceremonies by contributing to backlog building and sprint events in Jira. Requirements: 5–7+ years of professional experience, including 2–3+ years in a data governance function. Bachelor's degree in Business, Computer Science, Information Technology, or a related field. Strong understanding of data governance frameworks, metadata management, and data cataloging and lineage concepts. Proven ability to translate business needs into governance policies, standards, and workflows. Excellent communication and collaboration skills with experience working across business and technical teams. Hands-on experience with Atla</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>CompuGain</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Analyst Contract Administration Pricing</t>
+          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US</t>
+          <t>Rockville Pike</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/analyst-contract-administration-pricing-/5881609</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -5950,39 +5950,39 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-04T22:49:38+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>dceb0bc92800a731de96</t>
+          <t>52176647527c6698e6d4</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Sr. Financial Analyst Contract Administration and Pricing Location: Westminster, CO Manpower in partnership with Ball Corporation Pay : $40 - $55 / hour based on experience About the Role We are seeking a detail-oriented and analytical Financial Analyst, Contract Administration &amp; Pricing to join our team. This role is responsible for contract compliance analysis, customer pricing administration, sales accrual reconciliations, revenue forecasting, and financial reporting. The successful candidate will work closely with Sales, Contract Administration, Accounts Receivable, IT, and customers to ensure accurate pricing, invoicing, and financial settlements. This is an excellent opportunity for an early-career finance professional who enjoys working with large data sets, financial analysis, pricing administration, and cross-functional collaboration. Key Responsibilities Financial Analysis &amp; Contract Administration Complete financial analyses related to customer contract compliance. Administer and reconcile customer contract provisions. Calculate and review monthly sales accruals. Prepare periodic customer financial settlements of accrued amounts. Review and approve accrual-related billings, credits, and payments. Support contract renewals, pricing reviews, and contract development activities. Pricing &amp; Systems Management Maintain customer pricing, formulas, and pricing tables within JD Edwards (JDE) to ensure accurate invoicing. Develop and maintain customer price sheets and pricing change documentation. Initiate workflows for new customer setup, including pricing implementation in JDE. Monitor business changes that may impact customer pricing and recommend adjustments. Reporting &amp; Forecasting Retrieve and analyze sales and financial data from reporting systems and data warehouses. Generate monthly customer sales and pricing reports. Manage quarterly revenue forecasts and annual revenue budgeting processes. Perform customer-specific price reconciliations and freight analyses. Provide recommendations based on financial and operational data. Collaboration &amp; Continuous Improvement Partner with Commercial, Accounts Receivable, Contract Administration, and customer teams to resolve pricing discrepancies. Collaborate with IT to improve reporting tools, systems, and processes. Identify and implement continuous improvement opportunities that enhance efficiency and accuracy. Qualifications Education Bachelor's Degree in Finance, Accounting, Business Administration, Economics, or a related field required. MUST have used JD Edwards previousl y Experience 1-3 years of relevant experience in financial analysis, pricing, contract administration, accounting, or a related field. Experience working with ERP systems, preferably JD Edwards EnterpriseOne. Skills &amp; Competencies Strong analytical and problem-solving abilities. Advanced Microsoft Excel skills and financial modeling capabilities. Ability to analyze complex data and develop actionable recommendations. Strong c</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>CompuGain</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Credit Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Rockville Pike</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/credit-analyst/5876680</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-04T07:40:39+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>eb7055df9c90f5595b0b</t>
+          <t>406d96610632ccfd5711</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Credit Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Credit Analyst Reference Number: 5876680 Published Date: 09/04/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Join the Manpower Team Supporting Acushnet Company! We're hiring a Credit Analyst to support Acushnet Company, the organization behind industry-leading brands like Titleist and FootJoy. This position offers the opportunity to contribute to a globally recognized company while building your experience in credit analysis and financial risk management. If you're analytical, detail-oriented, and looking for an opportunity to grow your finance career, we'd love to hear from you. What's In It for You? Competitive pay at $32 per hour Hybrid flexibility - office is in Fairhaven, MA Full-time schedule with consistent hours Weekly pay through Manpower Opportunity to support a globally recognized organization Build valuable experience in credit analysis and finance Potential for contract extension based on business needs and performance What You'll Do As a Credit Analyst, you'll play a key role in managing credit risk and supporting the company's financial operations by: Managing a portfolio of customer accounts throughout the order-to-cash process Reviewing financial statements, credit reports, and supporting data to assess creditworthiness Establishing and maintaining appropriate credit limits Monitoring customer accounts and addressing delinquent balances Negotiating payment solutions and helping reduce financial risk Processing new customer credit applications and maintaining accurate account records Collaborating with Sales, Customer Service, and Finance teams to support efficient credit and collection activities What We're Looking</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ESG Data Analyst</t>
+          <t>Aerospace Quality Support Analyst</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/esg-data-analyst/5871423</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/aerospace-quality-support-analyst/406018</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -6090,22 +6090,22 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-04T07:40:39+00:00</t>
+          <t>2026-09-07T07:45:06+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>040409077b1d09f62743</t>
+          <t>53445de4641ed1bd7973</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>ESG Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) ESG Data Analyst Reference Number: 5871423 Published Date: 09/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, an organization committed to sustainability and responsible business practices, is seeking a ESG Data Analyst I to join their team. As a ESG Data Analyst I, you will be part of the Environmental, Social, and Governance department supporting ESG reporting and data management initiatives. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: ESG Data Analyst I Location: Remote Pay Range: $40.87 What's the Job? Support ESG data collection and disclosure preparation for internal and external reporting Assist with GHG emissions and environmental reporting, including Scope 1, Scope 2, and Scope 3 data Clean, organize, and analyze ESG data, performing preliminary calculations and variance checks Monitor ESG reporting frameworks and help organize information for reporting alignment Support the use and management of ESG reporting platforms and tools What's Needed? Bachelor’s degree in environmental science, sustainability, data science, information systems, business, finance, or related field 1–2 years of experience supporting ESG, sustainability, or climate reporting activities Experience collecting, organizing, reviewing, and analyzing data from multiple sources Familiarity with ESG, sustainability, or climate-related reporting concepts and frameworks Proficiency with Microsoft Excel or similar data management tools What's in it for me? Opportunity to build hands-on experience in ESG data management and sustaina</t>
+          <t>Aerospace Quality Support Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Aerospace Quality Support Analyst Reference Number: 406018 Published Date: 09/07/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in aerospace manufacturing and maintenance, is seeking a dedicated and detail-oriented Aerospace Quality Support Analyst o join their team. As an Aerospace Quality Support Analyst, you will be an integral part of the quality and engineering organization supporting aerospace maintenance, repair, and overhaul (MRO) operations. The ideal candidate will demonstrate strong analytical skills, effective communication, and a proactive approach to problem-solving, which will enable you to thrive within this dynamic environment. Job Title: Aerospace Quality Support Analyst Location: Miramar, Florida Pay Range: $40-$45/hr DOE plus OT, benefits What's the Job? Review quality logs, inspection records, and manufacturing documentation to ensure compliance with internal standards, FAA regulations, and customer requirements. Help manage nonconformance reports, log quality escapes, and track customer or audit complaints using factory operating systems like SAP. Collect, organize, and analyze quality metrics and data trends to identify factory risks and minimize workflow disruptions. Partner closely with Quality Inspectors, Operations, Supply Chain, and Manufacturing Engineers on the production floor to maintain product conformity and resolve shop-floor bottlenecks. Participate in daily quality clinics, Material Review Board (MRB) actions, and continuous improvement initiatives (CORE/Lean). What's Needed? Experience reviewing quality documentation and ensuring compliance with industry</t>
         </is>
       </c>
     </row>
@@ -6117,17 +6117,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst</t>
+          <t>Analyst Contract Administration Pricing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Broomfield, CO, US</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
+          <t>https://www.manpower.com/en/job/business-operations/analyst-contract-administration-pricing-/5881609</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -6160,22 +6160,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-04T07:40:39+00:00</t>
+          <t>2026-09-04T22:49:38+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>f177712205fd7fd46f19</t>
+          <t>dceb0bc92800a731de96</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 09/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
+          <t>Sr. Financial Analyst Contract Administration and Pricing Location: Westminster, CO Manpower in partnership with Ball Corporation Pay : $40 - $55 / hour based on experience About the Role We are seeking a detail-oriented and analytical Financial Analyst, Contract Administration &amp; Pricing to join our team. This role is responsible for contract compliance analysis, customer pricing administration, sales accrual reconciliations, revenue forecasting, and financial reporting. The successful candidate will work closely with Sales, Contract Administration, Accounts Receivable, IT, and customers to ensure accurate pricing, invoicing, and financial settlements. This is an excellent opportunity for an early-career finance professional who enjoys working with large data sets, financial analysis, pricing administration, and cross-functional collaboration. Key Responsibilities Financial Analysis &amp; Contract Administration Complete financial analyses related to customer contract compliance. Administer and reconcile customer contract provisions. Calculate and review monthly sales accruals. Prepare periodic customer financial settlements of accrued amounts. Review and approve accrual-related billings, credits, and payments. Support contract renewals, pricing reviews, and contract development activities. Pricing &amp; Systems Management Maintain customer pricing, formulas, and pricing tables within JD Edwards (JDE) to ensure accurate invoicing. Develop and maintain customer price sheets and pricing change documentation. Initiate workflows for new customer setup, including pricing implementation in JDE. Monitor business changes that may impact customer pricing and recommend adjustments. Reporting &amp; Forecasting Retrieve and analyze sales and financial data from reporting systems and data warehouses. Generate monthly customer sales and pricing reports. Manage quarterly revenue forecasts and annual revenue budgeting processes. Perform customer-specific price reconciliations and freight analyses. Provide recommendations based on financial and operational data. Collaboration &amp; Continuous Improvement Partner with Commercial, Accounts Receivable, Contract Administration, and customer teams to resolve pricing discrepancies. Collaborate with IT to improve reporting tools, systems, and processes. Identify and implement continuous improvement opportunities that enhance efficiency and accuracy. Qualifications Education Bachelor's Degree in Finance, Accounting, Business Administration, Economics, or a related field required. MUST have used JD Edwards previousl y Experience 1-3 years of relevant experience in financial analysis, pricing, contract administration, accounting, or a related field. Experience working with ERP systems, preferably JD Edwards EnterpriseOne. Skills &amp; Competencies Strong analytical and problem-solving abilities. Advanced Microsoft Excel skills and financial modeling capabilities. Ability to analyze complex data and develop actionable recommendations. Strong c</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Inventory Control Analyst 2</t>
+          <t>ESG Data Analyst</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/inventory-control-analyst-2/5884425</t>
+          <t>https://www.manpower.com/en/job/computer/esg-data-analyst/5871423</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -6230,22 +6230,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-06T07:35:17+00:00</t>
+          <t>2026-09-04T07:40:39+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>60e5466912b68450ff5a</t>
+          <t>040409077b1d09f62743</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Inventory Control Analyst 2 | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Inventory Control Analyst 2 Reference Number: 5884425 Published Date: 09/06/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the logistics and supply chain industry, is seeking an Inventory Control Analyst 2 to join their team. As an Inventory Control Analyst 2, you will be part of the Inventory Management Department supporting operational excellence and accuracy. The ideal candidate will demonstrate attention to detail, analytical thinking, and strong organizational skills, which will align successfully in the organization. Job Title: Inventory Control Analyst Location: Boise, ID Pay Range: $26.44 an hour Shift: Day - Mon to Fri - 8 Hours What's the Job? Ensure security and accountability of inventory through transaction documentation, process and procedure verification, and system review. Conduct physical inventories and lead cycle counts to maintain inventory accuracy. Analyze and, when able, correct cycle count discrepancies to ensure data integrity. Audit incoming and outgoing shipments to verify quality and accuracy. Compile and document all transactions for data entry and reporting purposes. What's Needed? 3-5 years of experience in inventory management or related fields. Strong analytical and problem-solving skills. Excellent attention to detail and organizational abilities. Ability to work effectively in a team environment. Proficiency with inventory management systems and data entry. What's in it for me? Opportunity to work with a dynamic and supportive team. Engagement in meaningful and impactful work within the supply chain sector. Potential for professional growth and developmen</t>
+          <t>ESG Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) ESG Data Analyst Reference Number: 5871423 Published Date: 09/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, an organization committed to sustainability and responsible business practices, is seeking a ESG Data Analyst I to join their team. As a ESG Data Analyst I, you will be part of the Environmental, Social, and Governance department supporting ESG reporting and data management initiatives. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: ESG Data Analyst I Location: Remote Pay Range: $40.87 What's the Job? Support ESG data collection and disclosure preparation for internal and external reporting Assist with GHG emissions and environmental reporting, including Scope 1, Scope 2, and Scope 3 data Clean, organize, and analyze ESG data, performing preliminary calculations and variance checks Monitor ESG reporting frameworks and help organize information for reporting alignment Support the use and management of ESG reporting platforms and tools What's Needed? Bachelor’s degree in environmental science, sustainability, data science, information systems, business, finance, or related field 1–2 years of experience supporting ESG, sustainability, or climate reporting activities Experience collecting, organizing, reviewing, and analyzing data from multiple sources Familiarity with ESG, sustainability, or climate-related reporting concepts and frameworks Proficiency with Microsoft Excel or similar data management tools What's in it for me? Opportunity to build hands-on experience in ESG data management and sustaina</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Logistics Analyst</t>
+          <t>Inventory Control Analyst 2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
+          <t>https://www.manpower.com/en/job/business-operations/inventory-control-analyst-2/5884425</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -6300,22 +6300,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-05T01:24:44+00:00</t>
+          <t>2026-09-06T07:35:17+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>55a327dd3e52a4c3c560</t>
+          <t>60e5466912b68450ff5a</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 09/05/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
+          <t>Inventory Control Analyst 2 | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Inventory Control Analyst 2 Reference Number: 5884425 Published Date: 09/06/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the logistics and supply chain industry, is seeking an Inventory Control Analyst 2 to join their team. As an Inventory Control Analyst 2, you will be part of the Inventory Management Department supporting operational excellence and accuracy. The ideal candidate will demonstrate attention to detail, analytical thinking, and strong organizational skills, which will align successfully in the organization. Job Title: Inventory Control Analyst Location: Boise, ID Pay Range: $26.44 an hour Shift: Day - Mon to Fri - 8 Hours What's the Job? Ensure security and accountability of inventory through transaction documentation, process and procedure verification, and system review. Conduct physical inventories and lead cycle counts to maintain inventory accuracy. Analyze and, when able, correct cycle count discrepancies to ensure data integrity. Audit incoming and outgoing shipments to verify quality and accuracy. Compile and document all transactions for data entry and reporting purposes. What's Needed? 3-5 years of experience in inventory management or related fields. Strong analytical and problem-solving skills. Excellent attention to detail and organizational abilities. Ability to work effectively in a team environment. Proficiency with inventory management systems and data entry. What's in it for me? Opportunity to work with a dynamic and supportive team. Engagement in meaningful and impactful work within the supply chain sector. Potential for professional growth and developmen</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Order Analyst</t>
+          <t>Logistics Analyst</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/order-analyst/5887599</t>
+          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -6375,17 +6375,17 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>88427c805b04ffbefddc</t>
+          <t>55a327dd3e52a4c3c560</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Order Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Order Analyst Reference Number: 5887599 Published Date: 09/05/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, an industry leader in oil and gas operations, is seeking an Order Analyst to join their team. As an Order Analyst, you will be part of the Division Order team supporting the Outside Operated Properties department. The ideal candidate will demonstrate strong analytical skills, attention to detail, and effective communication, which will align successfully in the organization. Job Title: Order Analyst Location: HOUSTON, TX Pay Range: DOE Shift: What's the Job? Review and monitor well reports for designated geographic areas to ensure accurate ownership records. Assist in the setup of operated and non-operated wells, including ownership changes and related documentation. Prepare and review division orders, supplemental division orders, and transfer orders for disbursement of payments. Analyze legal documents such as leases, title opinions, deeds, and contracts to verify ownership interests. Collaborate with team members and external stakeholders to resolve ownership discrepancies and ensure regulatory compliance. What's Needed? Proficiency in Microsoft Office Suite; familiarity with Quorum Land System or SAP is a plus. Strong interpersonal and communication skills, both written and verbal. Excellent organizational skills with a keen eye for detail. Knowledge of basic land principles and terminology. Minimum of 4 years of relevant experience with a Bachelor's degree. What's in it for me? Opportunity to work with a leading organization in the oil and gas industry. Engagement in meaningful projects that impact company operations</t>
+          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 09/05/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Portfolio Analyst</t>
+          <t>Order Analyst</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/portfolio-analyst/5880074</t>
+          <t>https://www.manpower.com/en/job/business-operations/order-analyst/5887599</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -6440,22 +6440,22 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-07T07:45:06+00:00</t>
+          <t>2026-09-05T01:24:44+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>f77ac6ead1d5cb115b1b</t>
+          <t>88427c805b04ffbefddc</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Portfolio Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Portfolio Analyst Reference Number: 5880074 Published Date: 09/07/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the energy and infrastructure sector, is seeking a Portfolio Analyst to join their team. As a Portfolio Analyst, you will be part of the Business Services department supporting project and program management initiatives. The ideal candidate will have strong communication skills, analytical thinking, and a proactive approach, which will align successfully in the organization. Job Title: Portfolio Analyst Location: White Plains, NY Pay Range: Shift: Monday through Friday, 7.5-hour workday with a 0.5-hour unpaid lunch What's the Job? Assist in reviewing project and program progress from initiation to closeout, ensuring alignment with organizational strategies and financial targets. Oversee and guide project teams in developing comprehensive business cases and maintaining governance standards. Prepare portfolio-level analysis and reporting on financial control, resource utilization, risk, and benefits, comparing planned versus actual performance. Lead reviews of significant initiatives and provide recommendations on project continuation, modification, or discontinuation. Develop monthly and ad hoc status reports, highlighting issues, conflicts, and key milestone movements to stakeholders. What's Needed? 5-10 years of experience in construction, engineering, or related fields with a focus on project or portfolio management. Bachelor’s degree in business administration, finance, engineering, or a related field; Master’s degree preferred. Proficiency with Microsoft Office Suite, including</t>
+          <t>Order Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Order Analyst Reference Number: 5887599 Published Date: 09/05/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, an industry leader in oil and gas operations, is seeking an Order Analyst to join their team. As an Order Analyst, you will be part of the Division Order team supporting the Outside Operated Properties department. The ideal candidate will demonstrate strong analytical skills, attention to detail, and effective communication, which will align successfully in the organization. Job Title: Order Analyst Location: HOUSTON, TX Pay Range: DOE Shift: What's the Job? Review and monitor well reports for designated geographic areas to ensure accurate ownership records. Assist in the setup of operated and non-operated wells, including ownership changes and related documentation. Prepare and review division orders, supplemental division orders, and transfer orders for disbursement of payments. Analyze legal documents such as leases, title opinions, deeds, and contracts to verify ownership interests. Collaborate with team members and external stakeholders to resolve ownership discrepancies and ensure regulatory compliance. What's Needed? Proficiency in Microsoft Office Suite; familiarity with Quorum Land System or SAP is a plus. Strong interpersonal and communication skills, both written and verbal. Excellent organizational skills with a keen eye for detail. Knowledge of basic land principles and terminology. Minimum of 4 years of relevant experience with a Bachelor's degree. What's in it for me? Opportunity to work with a leading organization in the oil and gas industry. Engagement in meaningful projects that impact company operations</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Remote Data Analyst</t>
+          <t>Portfolio Analyst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-/5879174</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/portfolio-analyst/5880074</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -6510,22 +6510,22 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-04T07:40:39+00:00</t>
+          <t>2026-09-07T07:45:06+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>b8bb41fbf34c4234c974</t>
+          <t>f77ac6ead1d5cb115b1b</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Remote Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst Reference Number: 5879174 Published Date: 09/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the legal and restructuring sector, is seeking a Remote CA ONLY Data Analyst to join their team. As a Remote CA ONLY Data Analyst, you will be part of the Corporate Restructuring department supporting various operational and administrative functions. The ideal candidate will demonstrate attention to detail, strong communication skills, and adaptability, which will align successfully in the organization. Job Title: Remote CA ONLY Data Analyst Location: Remote (El Segundo, CA) Pay Range:$28.00hr to $30.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status and claims Assist with preparing claim and solicitation binders for court submission Manage and log case voicemails, perform internet research for creditor information Coordinate, input, and review ballots, address changes, and proofs of claim What's Needed? Ability to quickly learn and navigate proprietary software and applications Solid attention to detail and accuracy in work Strong written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training preferred What's in it for me? Remote work opportunity with flexible hours Weekly pay every Friday Potential for overtime and career growth True contract-to-hire opportunity with the possibility of direct employment Competitive</t>
+          <t>Portfolio Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Portfolio Analyst Reference Number: 5880074 Published Date: 09/07/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the energy and infrastructure sector, is seeking a Portfolio Analyst to join their team. As a Portfolio Analyst, you will be part of the Business Services department supporting project and program management initiatives. The ideal candidate will have strong communication skills, analytical thinking, and a proactive approach, which will align successfully in the organization. Job Title: Portfolio Analyst Location: White Plains, NY Pay Range: Shift: Monday through Friday, 7.5-hour workday with a 0.5-hour unpaid lunch What's the Job? Assist in reviewing project and program progress from initiation to closeout, ensuring alignment with organizational strategies and financial targets. Oversee and guide project teams in developing comprehensive business cases and maintaining governance standards. Prepare portfolio-level analysis and reporting on financial control, resource utilization, risk, and benefits, comparing planned versus actual performance. Lead reviews of significant initiatives and provide recommendations on project continuation, modification, or discontinuation. Develop monthly and ad hoc status reports, highlighting issues, conflicts, and key milestone movements to stakeholders. What's Needed? 5-10 years of experience in construction, engineering, or related fields with a focus on project or portfolio management. Bachelor’s degree in business administration, finance, engineering, or a related field; Master’s degree preferred. Proficiency with Microsoft Office Suite, including</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only</t>
+          <t>Remote Data Analyst</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-ca-only-/5889335</t>
+          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-/5879174</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-05T01:24:44+00:00</t>
+          <t>2026-09-04T07:40:39+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>1c85522cebc8534c6229</t>
+          <t>b8bb41fbf34c4234c974</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst CA only Reference Number: 5889335 Published Date: 09/02/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the restructuring and legal support industry, is seeking a dedicated and detail-oriented Remote Data Analyst CA only to join their team. As a Remote Data Analyst CA only, you will be part of the Corporate Restructuring department supporting critical legal and administrative functions. The ideal candidate will demonstrate strong organizational skills, excellent communication abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Remote Data Analyst CA only Location: El Segundo, CA Pay Range: $27.00 to $29.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status, claim deadlines, and disbursements Assist with preparing and reviewing legal documents, ballots, and proofs of claim Coordinate mailings, compile service lists, and prepare affidavits of service Perform administrative quality control reviews to ensure accuracy and compliance What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus but not required What's in it for me? Weekly pay, with opportunities for overtime True contract-to-hire opportun</t>
+          <t>Remote Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst Reference Number: 5879174 Published Date: 09/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the legal and restructuring sector, is seeking a Remote CA ONLY Data Analyst to join their team. As a Remote CA ONLY Data Analyst, you will be part of the Corporate Restructuring department supporting various operational and administrative functions. The ideal candidate will demonstrate attention to detail, strong communication skills, and adaptability, which will align successfully in the organization. Job Title: Remote CA ONLY Data Analyst Location: Remote (El Segundo, CA) Pay Range:$28.00hr to $30.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status and claims Assist with preparing claim and solicitation binders for court submission Manage and log case voicemails, perform internet research for creditor information Coordinate, input, and review ballots, address changes, and proofs of claim What's Needed? Ability to quickly learn and navigate proprietary software and applications Solid attention to detail and accuracy in work Strong written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training preferred What's in it for me? Remote work opportunity with flexible hours Weekly pay every Friday Potential for overtime and career growth True contract-to-hire opportunity with the possibility of direct employment Competitive</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -9787,32 +9787,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Operations Analyst II</t>
+          <t>AI Prompt Engineer - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Phoenix, Arizona, 85001, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9827,7 +9822,7 @@
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006259563/Operations-Analyst-II</t>
+          <t>https://www.judge.com/jobs/details/1146776</t>
         </is>
       </c>
       <c r="J135" t="b">
@@ -9835,22 +9830,22 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>f5c31f27d3200ab710e7</t>
+          <t>03227ef1e4accb60da7c</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Operations Analyst II - SQL experience required Remote | $30 hour (non-negotiable) | Schedule: Must be able to work Tuesday-Saturday Shift Starting at 9pm-5:30am Highlights: Fully Remote - Overnight position must be okay with working Saturday No Phones - all analytical work - very independent role Benefits of the role: Opportunity to work for one of the top Start up companies in the country Benefits available on the first day of each month Weekly pay Independent role Ability for pay raises after 6 months-year if performance well Necessary Experience/Skills: Basic proficiency in Excel/Google Sheets [mandatory] Understand excel formulas, data entry Comfortable w/ Pivot Tables, cleaning data comfortable in a fast-paced environment [making quick decisions, escalating issues] Strong project management, organization and communication skills. Detail oriented! experience that is nice to have: operations, supply chain analyst, catalog, Parcel Support NEED Logistics, operations and data hands-on experience A day in the role: Delivery Order Re-scheduling / Assignment Support for High Volume/Impact Partners when manual intervention is Communicate with Ops stakeholders when orders are not received, picked up, or returned at facility by canceling, rescheduling, or creating orders using Google sheets Communicate damaged packages that arrive at facility to Operations to share with Merchants Monitor order assignments at the end of delivery windows for orders across time zones and scrape orders that missed getting assigned. Scrape orders not assigned and take action based on Merchant preference [reschedule or cancel; share orders with Ops team for Merchant comms] Consolidate and share with Ops team for trend analysis and reactive action plan Communicate and manage time-sensitive information to Ops team and partners NEED Logistics, operations and data hands-on experience Next steps: Please apply directly to this job posting and I will reach out to you in the next 1-10 business days to discuss next steps! This position does require aa remote client interview if you are qualified and hiring manager decides to interview you! Job Type &amp; Location This is a Contract position based out of Phoenix, AZ. Pay and Benefits The pay range for this position is $30.00 - $30.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Vo</t>
+          <t>AI Prompt Engineer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9857,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AI Prompt Engineer - Charlotte, NC | Judge Group</t>
+          <t>Agent AI Architect - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9872,7 +9867,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9892,7 +9887,7 @@
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146776</t>
+          <t>https://www.judge.com/jobs/details/1148840</t>
         </is>
       </c>
       <c r="J136" t="b">
@@ -9905,17 +9900,17 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>03227ef1e4accb60da7c</t>
+          <t>6b6b85b07519a890036a</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>AI Prompt Engineer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Agent AI Architect - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9922,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Agent AI Architect - REMOTE | Judge Group</t>
+          <t>Agentic AI Developer - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9937,7 +9932,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9957,7 +9952,7 @@
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148840</t>
+          <t>https://www.judge.com/jobs/details/1149623</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9970,17 +9965,17 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>6b6b85b07519a890036a</t>
+          <t>c15fa838b2e4c9d28d55</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Agent AI Architect - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Agentic AI Developer - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9987,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Agentic AI Developer - Irving, TX | Judge Group</t>
+          <t>Analyst, Sales Operations - San Jose, CA | Judge Group</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -10022,7 +10017,7 @@
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1149623</t>
+          <t>https://www.judge.com/jobs/details/1148139</t>
         </is>
       </c>
       <c r="J138" t="b">
@@ -10030,22 +10025,22 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-08-20T00:04:09+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>c15fa838b2e4c9d28d55</t>
+          <t>68dfd25047875496bc9e</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Agentic AI Developer - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Analyst, Sales Operations - San Jose, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10052,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Analyst, Sales Operations - San Jose, CA | Judge Group</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10087,7 +10082,7 @@
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148139</t>
+          <t>https://www.judge.com/jobs/details/1148290</t>
         </is>
       </c>
       <c r="J139" t="b">
@@ -10095,22 +10090,22 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-20T00:04:09+00:00</t>
+          <t>2026-08-21T15:20:48+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>68dfd25047875496bc9e</t>
+          <t>8a6f124e5d536c8ef414</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Analyst, Sales Operations - San Jose, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10117,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
+          <t>Business Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10132,7 +10127,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10152,7 +10147,7 @@
       </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148290</t>
+          <t>https://www.judge.com/jobs/details/1146274</t>
         </is>
       </c>
       <c r="J140" t="b">
@@ -10160,22 +10155,22 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-21T15:20:48+00:00</t>
+          <t>2026-08-10T15:43:04+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>8a6f124e5d536c8ef414</t>
+          <t>896ab02a0c7ad4507e98</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Business Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10182,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Business Analyst - REMOTE | Judge Group</t>
+          <t>Business Analyst - Salem, OR | Judge Group</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10197,7 +10192,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10217,7 +10212,7 @@
       </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146274</t>
+          <t>https://www.judge.com/jobs/details/1148909</t>
         </is>
       </c>
       <c r="J141" t="b">
@@ -10225,22 +10220,22 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-08-10T15:43:04+00:00</t>
+          <t>2026-08-25T18:14:19+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>896ab02a0c7ad4507e98</t>
+          <t>0f78d9cee82931065244</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Business Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Business Analyst - Salem, OR | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10247,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Business Analyst - Salem, OR | Judge Group</t>
+          <t>Business Analyst/ Implementation Analyst - Omaha, NE | Judge Group</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10282,7 +10277,7 @@
       </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148909</t>
+          <t>https://www.judge.com/jobs/details/1137985</t>
         </is>
       </c>
       <c r="J142" t="b">
@@ -10290,22 +10285,22 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-08-25T18:14:19+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>0f78d9cee82931065244</t>
+          <t>06fee3abbc71f14aa0ea</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Business Analyst - Salem, OR | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Business Analyst/ Implementation Analyst - Omaha, NE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10312,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Business Analyst/ Implementation Analyst - Omaha, NE | Judge Group</t>
+          <t>Business Process Testing Analyst - Canton, MA | Judge Group</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10347,7 +10342,7 @@
       </c>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1137985</t>
+          <t>https://www.judge.com/jobs/details/1144985</t>
         </is>
       </c>
       <c r="J143" t="b">
@@ -10355,22 +10350,22 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-04T18:05:42+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>06fee3abbc71f14aa0ea</t>
+          <t>ec248084a1b21fa7a296</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Business Analyst/ Implementation Analyst - Omaha, NE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Business Process Testing Analyst - Canton, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10377,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Business Process Testing Analyst - Canton, MA | Judge Group</t>
+          <t>DATA ENGINEER - Conshohocken, PA | Judge Group</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10412,7 +10407,7 @@
       </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1144985</t>
+          <t>https://www.judge.com/jobs/details/1136597</t>
         </is>
       </c>
       <c r="J144" t="b">
@@ -10420,22 +10415,22 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-09-04T18:05:42+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>ec248084a1b21fa7a296</t>
+          <t>fa71c26c55e9d797f3b2</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Business Process Testing Analyst - Canton, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>DATA ENGINEER - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10442,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DATA ENGINEER - Conshohocken, PA | Judge Group</t>
+          <t>Data Analyst - Arlington, TX | Judge Group</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10477,7 +10472,7 @@
       </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136597</t>
+          <t>https://www.judge.com/jobs/details/1149500</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -10485,22 +10480,22 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-28T00:17:47+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>fa71c26c55e9d797f3b2</t>
+          <t>a1d1290b3b51a2659308</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>DATA ENGINEER - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Analyst - Arlington, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10507,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Data Analyst - Arlington, TX | Judge Group</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10542,7 +10537,7 @@
       </c>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1149500</t>
+          <t>https://www.judge.com/jobs/details/1136576</t>
         </is>
       </c>
       <c r="J146" t="b">
@@ -10550,22 +10545,22 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-28T00:17:47+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>a1d1290b3b51a2659308</t>
+          <t>c0ccf3207abc77a8082c</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Data Analyst - Arlington, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10572,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
+          <t>Data Analyst - Raleigh, NC | Judge Group</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10607,7 +10602,7 @@
       </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136576</t>
+          <t>https://www.judge.com/jobs/details/1148342</t>
         </is>
       </c>
       <c r="J147" t="b">
@@ -10615,22 +10610,22 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-20T21:14:14+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>c0ccf3207abc77a8082c</t>
+          <t>f19e41e24774007ea610</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Analyst - Raleigh, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10637,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Data Analyst - Raleigh, NC | Judge Group</t>
+          <t>Data Architect -1 - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10652,7 +10647,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10672,7 +10667,7 @@
       </c>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148342</t>
+          <t>https://www.judge.com/jobs/details/1146814</t>
         </is>
       </c>
       <c r="J148" t="b">
@@ -10680,22 +10675,22 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-20T21:14:14+00:00</t>
+          <t>2026-08-12T15:43:45+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>f19e41e24774007ea610</t>
+          <t>6dcf89d4064d1c6eff1c</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Data Analyst - Raleigh, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Architect -1 - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10702,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Data Architect -1 - REMOTE | Judge Group</t>
+          <t>Data Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10737,7 +10732,7 @@
       </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146814</t>
+          <t>https://www.judge.com/jobs/details/1132071</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -10745,22 +10740,22 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-12T15:43:45+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>6dcf89d4064d1c6eff1c</t>
+          <t>8bd9f9b74bda16e276f6</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Data Architect -1 - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10767,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Data Engineer - REMOTE | Judge Group</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10782,7 +10777,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10802,7 +10797,7 @@
       </c>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1132071</t>
+          <t>https://www.judge.com/jobs/details/1144820</t>
         </is>
       </c>
       <c r="J150" t="b">
@@ -10810,22 +10805,22 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-07T20:10:32+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>8bd9f9b74bda16e276f6</t>
+          <t>31d0b821f28109290adb</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Data Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10832,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
+          <t>Data Management Analyst - Minneapolis, MN | Judge Group</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10867,7 +10862,7 @@
       </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1144820</t>
+          <t>https://www.judge.com/jobs/details/1147192</t>
         </is>
       </c>
       <c r="J151" t="b">
@@ -10875,22 +10870,22 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-09-07T20:10:32+00:00</t>
+          <t>2026-08-24T12:11:33+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>31d0b821f28109290adb</t>
+          <t>b20180747e3847edc344</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Management Analyst - Minneapolis, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10897,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Minneapolis, MN | Judge Group</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10932,7 +10927,7 @@
       </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1147192</t>
+          <t>https://www.judge.com/jobs/details/1135310</t>
         </is>
       </c>
       <c r="J152" t="b">
@@ -10940,22 +10935,22 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-24T12:11:33+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>b20180747e3847edc344</t>
+          <t>a89c4407724b716bd195</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Minneapolis, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10962,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
+          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10997,7 +10992,7 @@
       </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1135310</t>
+          <t>https://www.judge.com/jobs/details/1146284</t>
         </is>
       </c>
       <c r="J153" t="b">
@@ -11005,22 +11000,22 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-10T15:43:04+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>a89c4407724b716bd195</t>
+          <t>3cc2077fc0d4218f6327</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11027,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group</t>
+          <t>Generative AI Engineer - Buffalo, NY | Judge Group</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11062,7 +11057,7 @@
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146284</t>
+          <t>https://www.judge.com/jobs/details/1146257</t>
         </is>
       </c>
       <c r="J154" t="b">
@@ -11070,22 +11065,22 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-08-10T15:43:04+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>3cc2077fc0d4218f6327</t>
+          <t>dde66cba6bfca28776b8</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Generative AI Engineer - Buffalo, NY | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11092,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Generative AI Engineer - Buffalo, NY | Judge Group</t>
+          <t>IT Business Analyst - Fort Washington, PA | Judge Group</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11127,7 +11122,7 @@
       </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146257</t>
+          <t>https://www.judge.com/jobs/details/1145874</t>
         </is>
       </c>
       <c r="J155" t="b">
@@ -11135,22 +11130,22 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-08-26T16:21:09+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>dde66cba6bfca28776b8</t>
+          <t>ea991137e8a0dc4b872d</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Generative AI Engineer - Buffalo, NY | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>IT Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11157,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IT Business Analyst - Fort Washington, PA | Judge Group</t>
+          <t>Information Security Analyst - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11192,7 +11187,7 @@
       </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145874</t>
+          <t>https://www.judge.com/jobs/details/1149269</t>
         </is>
       </c>
       <c r="J156" t="b">
@@ -11200,22 +11195,22 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-26T16:21:09+00:00</t>
+          <t>2026-09-03T23:02:33+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>ea991137e8a0dc4b872d</t>
+          <t>17518a45a03c4f46471b</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>IT Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Information Security Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11222,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Information Security Analyst - Charlotte, NC | Judge Group</t>
+          <t>Lead Coupa Business Analyst - Horsham, PA | Judge Group</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11257,7 +11252,7 @@
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1149269</t>
+          <t>https://www.judge.com/jobs/details/1145765</t>
         </is>
       </c>
       <c r="J157" t="b">
@@ -11265,22 +11260,22 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-09-03T23:02:33+00:00</t>
+          <t>2026-09-07T14:41:31+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>17518a45a03c4f46471b</t>
+          <t>7f653182fc6c72d8d03e</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Information Security Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Lead Coupa Business Analyst - Horsham, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11287,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lead Coupa Business Analyst - Horsham, PA | Judge Group</t>
+          <t>Lead Data Engineer - New York City, NY | Judge Group</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11322,7 +11317,7 @@
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145765</t>
+          <t>https://www.judge.com/jobs/details/1142545</t>
         </is>
       </c>
       <c r="J158" t="b">
@@ -11330,22 +11325,22 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-09-07T14:41:31+00:00</t>
+          <t>2026-08-05T11:13:16+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>7f653182fc6c72d8d03e</t>
+          <t>dcd61bccb8041928ed9d</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Lead Coupa Business Analyst - Horsham, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Lead Data Engineer - New York City, NY | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11352,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lead Data Engineer - New York City, NY | Judge Group</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11387,7 +11382,7 @@
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1142545</t>
+          <t>https://www.judge.com/jobs/details/1140197</t>
         </is>
       </c>
       <c r="J159" t="b">
@@ -11395,22 +11390,22 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-05T11:13:16+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>dcd61bccb8041928ed9d</t>
+          <t>94849065fcdb6cf16558</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Lead Data Engineer - New York City, NY | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11417,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
+          <t>OA-EISO-SOC Analyst 1 - Harrisburg, PA | Judge Group</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11452,7 +11447,7 @@
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1140197</t>
+          <t>https://www.judge.com/jobs/details/1145036</t>
         </is>
       </c>
       <c r="J160" t="b">
@@ -11460,22 +11455,22 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-07-31T16:38:03+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>94849065fcdb6cf16558</t>
+          <t>c709551a9770921be954</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>OA-EISO-SOC Analyst 1 - Harrisburg, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11482,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OA-EISO-SOC Analyst 1 - Harrisburg, PA | Judge Group</t>
+          <t>Project Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11497,7 +11492,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -11517,7 +11512,7 @@
       </c>
       <c r="I161" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145036</t>
+          <t>https://www.judge.com/jobs/details/1146967</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -11525,22 +11520,22 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-31T16:38:03+00:00</t>
+          <t>2026-08-13T15:43:44+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>c709551a9770921be954</t>
+          <t>267ea50a371a6bb88c8a</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>OA-EISO-SOC Analyst 1 - Harrisburg, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Project Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11547,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Project Analyst - REMOTE | Judge Group</t>
+          <t>Security IT Business Analyst - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11562,7 +11557,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -11582,7 +11577,7 @@
       </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146967</t>
+          <t>https://www.judge.com/jobs/details/1148935</t>
         </is>
       </c>
       <c r="J162" t="b">
@@ -11590,22 +11585,22 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-13T15:43:44+00:00</t>
+          <t>2026-09-04T18:05:42+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>267ea50a371a6bb88c8a</t>
+          <t>245f2f69a4a1b35f67de</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Project Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Security IT Business Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11617,7 +11612,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Security IT Business Analyst - Quincy, MA | Judge Group</t>
+          <t>Senior .NET AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11647,7 +11642,7 @@
       </c>
       <c r="I163" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148935</t>
+          <t>https://www.judge.com/jobs/details/1145595</t>
         </is>
       </c>
       <c r="J163" t="b">
@@ -11655,22 +11650,22 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-09-04T18:05:42+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>245f2f69a4a1b35f67de</t>
+          <t>55db5243bf9d57991614</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Security IT Business Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior .NET AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11677,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Senior .NET AI Developer - Austin, TX | Judge Group</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11712,7 +11707,7 @@
       </c>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145595</t>
+          <t>https://www.judge.com/jobs/details/1134711</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11725,17 +11720,17 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>55db5243bf9d57991614</t>
+          <t>780df2da3a341d97cc3d</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Senior .NET AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11742,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Senior AI Developer - Southlake, TX | Judge Group</t>
+          <t>Senior AI Engineer - Mesquite, TX | Judge Group</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11777,7 +11772,7 @@
       </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1134711</t>
+          <t>https://www.judge.com/jobs/details/1127907</t>
         </is>
       </c>
       <c r="J165" t="b">
@@ -11790,17 +11785,17 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>780df2da3a341d97cc3d</t>
+          <t>1b88795b2a995bcfec03</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Senior AI Developer - Southlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior AI Engineer - Mesquite, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11807,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Mesquite, TX | Judge Group</t>
+          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11842,7 +11837,7 @@
       </c>
       <c r="I166" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1127907</t>
+          <t>https://www.judge.com/jobs/details/1136598</t>
         </is>
       </c>
       <c r="J166" t="b">
@@ -11855,17 +11850,17 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>1b88795b2a995bcfec03</t>
+          <t>7d81f6ff26fd959356ed</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Mesquite, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11872,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11907,7 +11902,7 @@
       </c>
       <c r="I167" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136598</t>
+          <t>https://www.judge.com/jobs/details/1148934</t>
         </is>
       </c>
       <c r="J167" t="b">
@@ -11915,22 +11910,22 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-09-03T23:02:33+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>7d81f6ff26fd959356ed</t>
+          <t>07bfae59552b3c821572</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11937,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11972,7 +11967,7 @@
       </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148934</t>
+          <t>https://www.judge.com/jobs/details/1145633</t>
         </is>
       </c>
       <c r="J168" t="b">
@@ -11980,22 +11975,22 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-09-03T23:02:33+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>07bfae59552b3c821572</t>
+          <t>feac664cd0965bceede2</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12007,7 +12002,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Senior Java AI Developer - Austin, TX | Judge Group</t>
+          <t>Sr Data Scientist - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12017,7 +12012,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12037,7 +12032,7 @@
       </c>
       <c r="I169" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145633</t>
+          <t>https://www.judge.com/jobs/details/1146486</t>
         </is>
       </c>
       <c r="J169" t="b">
@@ -12045,22 +12040,22 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-08-11T15:42:09+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>feac664cd0965bceede2</t>
+          <t>04e52949354d049458f7</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Senior Java AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Sr Data Scientist - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12067,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - REMOTE | Judge Group</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -12102,7 +12097,7 @@
       </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146486</t>
+          <t>https://www.judge.com/jobs/details/1146485</t>
         </is>
       </c>
       <c r="J170" t="b">
@@ -12110,22 +12105,22 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-08-11T15:42:09+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>04e52949354d049458f7</t>
+          <t>c8fc83cf9a9fbd548fd2</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12132,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -12147,7 +12142,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -12167,7 +12162,7 @@
       </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146485</t>
+          <t>https://www.judge.com/jobs/details/1147907</t>
         </is>
       </c>
       <c r="J171" t="b">
@@ -12180,17 +12175,17 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>c8fc83cf9a9fbd548fd2</t>
+          <t>94c82ba3d6ab78504fcf</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12197,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12212,7 +12207,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -12232,7 +12227,7 @@
       </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1147907</t>
+          <t>https://www.judge.com/jobs/details/1099718</t>
         </is>
       </c>
       <c r="J172" t="b">
@@ -12240,22 +12235,22 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-08-28T00:17:47+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>94c82ba3d6ab78504fcf</t>
+          <t>867e313f74ad45486e73</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12262,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
+          <t>Tech Operations Analyst - Chandler, AZ | Judge Group</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -12277,7 +12272,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -12297,7 +12292,7 @@
       </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1099718</t>
+          <t>https://www.judge.com/jobs/details/1148055</t>
         </is>
       </c>
       <c r="J173" t="b">
@@ -12305,22 +12300,22 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-08-28T00:17:47+00:00</t>
+          <t>2026-09-02T18:23:08+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>867e313f74ad45486e73</t>
+          <t>add8e597ed5d1fe351c0</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Tech Operations Analyst - Chandler, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12327,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tech Operations Analyst - Chandler, AZ | Judge Group</t>
+          <t>Technical Data Analyst - Boston, MA | Judge Group</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12362,7 +12357,7 @@
       </c>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148055</t>
+          <t>https://www.judge.com/jobs/details/1144888</t>
         </is>
       </c>
       <c r="J174" t="b">
@@ -12370,22 +12365,22 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-09-02T18:23:08+00:00</t>
+          <t>2026-09-01T23:05:19+00:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>add8e597ed5d1fe351c0</t>
+          <t>f93c587ed1e982533e25</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Tech Operations Analyst - Chandler, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Technical Data Analyst - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12392,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Technical Data Analyst - Boston, MA | Judge Group</t>
+          <t>Technology Operations Analyst - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -12427,7 +12422,7 @@
       </c>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1144888</t>
+          <t>https://www.judge.com/jobs/details/1148781</t>
         </is>
       </c>
       <c r="J175" t="b">
@@ -12435,34 +12430,34 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-09-01T23:05:19+00:00</t>
+          <t>2026-09-07T14:41:31+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>f93c587ed1e982533e25</t>
+          <t>462707ef84ef247acdd9</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Technical Data Analyst - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>Technology Operations Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Technology Operations Analyst - Irving, TX | Judge Group</t>
+          <t>Administrative Assistant/Entry Level Business Analyst</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12477,7 +12472,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148781</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -12500,22 +12500,22 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-09-07T14:41:31+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>462707ef84ef247acdd9</t>
+          <t>0824e44805cde39b3822</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Technology Operations Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Administrative Assistant/Entry Level Business Analyst</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2015-10-20</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J177" t="b">
@@ -12575,17 +12575,17 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>0824e44805cde39b3822</t>
+          <t>4299b8fc9cc8be3bfc33</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Applications System Analyst</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2016-01-13</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
         </is>
       </c>
       <c r="J178" t="b">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>4299b8fc9cc8be3bfc33</t>
+          <t>e8f6fd68f0c8963a7a1b</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applications System Analyst</t>
+          <t>Business Analyst/Qlikeview Developer</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12715,17 +12715,17 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>e8f6fd68f0c8963a7a1b</t>
+          <t>9247a1e706741e8b0544</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Business Analyst/Qlikeview Developer</t>
+          <t>Business analyst</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12785,17 +12785,17 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>9247a1e706741e8b0544</t>
+          <t>62f9684d4a4312d88e6f</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J181" t="b">
@@ -12855,17 +12855,17 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>62f9684d4a4312d88e6f</t>
+          <t>cc841923fe467641e8cf</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Business analyst</t>
+          <t>Computer Vision Algorithm Engineer</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2016-10-19</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
         </is>
       </c>
       <c r="J182" t="b">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>cc841923fe467641e8cf</t>
+          <t>17b90594009fe99d1583</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
         </is>
       </c>
     </row>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Computer Vision Algorithm Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2017-02-07</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
         </is>
       </c>
       <c r="J183" t="b">
@@ -12995,17 +12995,17 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>17b90594009fe99d1583</t>
+          <t>02e4361c9124b313e587</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2017-02-07</t>
+          <t>2016-10-25</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
         </is>
       </c>
       <c r="J184" t="b">
@@ -13065,17 +13065,17 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>02e4361c9124b313e587</t>
+          <t>2b87177fd8a91d1b3c10</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Security analyst</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2016-10-25</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
         </is>
       </c>
       <c r="J185" t="b">
@@ -13135,17 +13135,17 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2b87177fd8a91d1b3c10</t>
+          <t>bce9bd6942bda16e1d08</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Data Security analyst</t>
+          <t>EDI Programmer Analyst &amp; Manager</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -13172,12 +13172,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
+          <t>2016-06-29</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>bce9bd6942bda16e1d08</t>
+          <t>36926768d7d1374bbba5</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EDI Programmer Analyst &amp; Manager</t>
+          <t>EFT Processing Analyst</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2016-06-29</t>
+          <t>2015-12-09</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
         </is>
       </c>
       <c r="J187" t="b">
@@ -13275,17 +13275,17 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>36926768d7d1374bbba5</t>
+          <t>ff66976e897c4a7cacad</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EFT Processing Analyst</t>
+          <t>MDM Data Analyst I</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
+          <t>2016-12-06</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -13345,17 +13345,17 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>ff66976e897c4a7cacad</t>
+          <t>3a12d7e1695e93f24087</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MDM Data Analyst I</t>
+          <t>Mobile Automation Test Analyst</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2016-06-08</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -13415,17 +13415,17 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>3a12d7e1695e93f24087</t>
+          <t>80c10598e102ec2e4da0</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
         </is>
       </c>
     </row>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Mobile Automation Test Analyst</t>
+          <t>Shipboard Business Systems Analyst</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2016-06-08</t>
+          <t>2015-12-11</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -13485,17 +13485,17 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>80c10598e102ec2e4da0</t>
+          <t>c6ecd4c346de62f82786</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Shipboard Business Systems Analyst</t>
+          <t>Sr. Data Analyst/BIE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2015-12-11</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -13555,17 +13555,17 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>c6ecd4c346de62f82786</t>
+          <t>598b89494bc90bc7bd81</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst/BIE</t>
+          <t>Sr. IT Communication Analyst</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13587,17 +13587,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -13625,17 +13625,17 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>598b89494bc90bc7bd81</t>
+          <t>618dae4b9e249bc47945</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sr. IT Communication Analyst</t>
+          <t>Support Analyst</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -13695,29 +13695,29 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>618dae4b9e249bc47945</t>
+          <t>2a655a025e9258d5b76f</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Support Analyst</t>
+          <t>AI Architect - Agentic AI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13732,12 +13732,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2017-03-01</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13747,12 +13742,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
+          <t>https://careers.wipro.com/job/AI-Architect-Agentic-AI/191866-en_US</t>
         </is>
       </c>
       <c r="J194" t="b">
@@ -13760,22 +13755,22 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-06T05:54:14+00:00</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2a655a025e9258d5b76f</t>
+          <t>1e0078f336199470d02f</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
+          <t>AI Architect - Agentic AI Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Architect - Agentic AI City: Seongnam-si State/Province: Gyeonggido Posting Start Date: 8/14/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at w</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13782,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>AI Architect - Agentic AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13817,7 +13812,7 @@
       </c>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/AI-Architect-Agentic-AI/191866-en_US</t>
+          <t>https://careers.wipro.com/job/AI-Engineer/192784-en_US</t>
         </is>
       </c>
       <c r="J195" t="b">
@@ -13825,22 +13820,22 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-08-06T05:54:14+00:00</t>
+          <t>2026-08-07T15:38:07+00:00</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>1e0078f336199470d02f</t>
+          <t>9c78a109514702595d71</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>AI Architect - Agentic AI Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Architect - Agentic AI City: Seongnam-si State/Province: Gyeonggido Posting Start Date: 8/14/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at w</t>
+          <t>AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Engineer City: Austin State/Province: Texas Posting Start Date: 8/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13847,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>ANALYST L2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13882,7 +13877,7 @@
       </c>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/AI-Engineer/192784-en_US</t>
+          <t>https://careers.wipro.com/job/ANALYST-L2/193243-en_US</t>
         </is>
       </c>
       <c r="J196" t="b">
@@ -13890,22 +13885,22 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-08-07T15:38:07+00:00</t>
+          <t>2026-08-26T09:29:59+00:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>9c78a109514702595d71</t>
+          <t>226c03a4ad5d97c18697</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Engineer City: Austin State/Province: Texas Posting Start Date: 8/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
+          <t>ANALYST L2 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L2 City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/16/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13912,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ANALYST L2</t>
+          <t>ANALYST L3</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13947,7 +13942,7 @@
       </c>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/ANALYST-L2/193243-en_US</t>
+          <t>https://careers.wipro.com/job/ANALYST-L3/191665-en_US</t>
         </is>
       </c>
       <c r="J197" t="b">
@@ -13960,17 +13955,17 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>226c03a4ad5d97c18697</t>
+          <t>b60ef76300a4cd102640</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>ANALYST L2 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L2 City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/16/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
+          <t>ANALYST L3 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L3 City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/5/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Extr</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13977,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ANALYST L3</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14012,7 +14007,7 @@
       </c>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/ANALYST-L3/191665-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
         </is>
       </c>
       <c r="J198" t="b">
@@ -14020,22 +14015,22 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-08-26T09:29:59+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>b60ef76300a4cd102640</t>
+          <t>712e3cf849669eebaeb3</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>ANALYST L3 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L3 City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/5/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Extr</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14072,7 @@
       </c>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
         </is>
       </c>
       <c r="J199" t="b">
@@ -14090,17 +14085,17 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>712e3cf849669eebaeb3</t>
+          <t>2309aeb0bc27a46040b3</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14137,7 @@
       </c>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/175124-en_US</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -14150,22 +14145,22 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-31T18:28:48+00:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2309aeb0bc27a46040b3</t>
+          <t>0acf0fdae972a16bd140</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/31/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Descrip</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14202,7 @@
       </c>
       <c r="I201" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/175124-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
         </is>
       </c>
       <c r="J201" t="b">
@@ -14215,22 +14210,22 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-08-31T18:28:48+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>0acf0fdae972a16bd140</t>
+          <t>bb5a134aabb09236d773</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/31/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Descrip</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14267,7 @@
       </c>
       <c r="I202" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
         </is>
       </c>
       <c r="J202" t="b">
@@ -14280,22 +14275,22 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-03T17:08:04+00:00</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>bb5a134aabb09236d773</t>
+          <t>97dfd4270978d9297118</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
         </is>
       </c>
     </row>
@@ -14307,7 +14302,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -14337,7 +14332,7 @@
       </c>
       <c r="I203" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
+          <t>https://careers.wipro.com/job/Azure-Data-Engineer/190565-en_US</t>
         </is>
       </c>
       <c r="J203" t="b">
@@ -14345,22 +14340,22 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026-08-03T17:08:04+00:00</t>
+          <t>2026-08-29T01:26:31+00:00</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>97dfd4270978d9297118</t>
+          <t>0d932056066305d25bae</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
+          <t>Azure Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Azure Data Engineer City: Toronto State/Province: Ontario Posting Start Date: 8/28/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job D</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14367,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>DATA ANALYST</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14402,7 +14397,7 @@
       </c>
       <c r="I204" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Azure-Data-Engineer/190565-en_US</t>
+          <t>https://careers.wipro.com/job/DATA-ANALYST/197280-en_US</t>
         </is>
       </c>
       <c r="J204" t="b">
@@ -14410,22 +14405,22 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026-08-29T01:26:31+00:00</t>
+          <t>2026-09-03T13:16:22+00:00</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>0d932056066305d25bae</t>
+          <t>d0914ba92a9b445faf35</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Azure Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Azure Data Engineer City: Toronto State/Province: Ontario Posting Start Date: 8/28/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job D</t>
+          <t>DATA ANALYST Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST City: Bengaluru State/Province: Karnataka Posting Start Date: 9/3/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description:</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14432,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DATA ANALYST</t>
+          <t>DATA ARCHITECT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -14467,7 +14462,7 @@
       </c>
       <c r="I205" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/DATA-ANALYST/197280-en_US</t>
+          <t>https://careers.wipro.com/job/DATA-ARCHITECT/195081-en_US</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -14475,22 +14470,22 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-09-03T13:16:22+00:00</t>
+          <t>2026-08-20T18:13:00+00:00</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>d0914ba92a9b445faf35</t>
+          <t>526ef0e719524b9d4f5f</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>DATA ANALYST Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST City: Bengaluru State/Province: Karnataka Posting Start Date: 9/3/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description:</t>
+          <t>DATA ARCHITECT Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ARCHITECT City: Guadalajara State/Province: Jalisco Posting Start Date: 8/20/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descrip</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14497,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -14532,7 +14527,7 @@
       </c>
       <c r="I206" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/DATA-ARCHITECT/195081-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Analyst/196228-en_US</t>
         </is>
       </c>
       <c r="J206" t="b">
@@ -14540,22 +14535,22 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-08-20T18:13:00+00:00</t>
+          <t>2026-08-29T01:26:31+00:00</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>526ef0e719524b9d4f5f</t>
+          <t>f7d25f7312ae32cfbc12</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ARCHITECT City: Guadalajara State/Province: Jalisco Posting Start Date: 8/20/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descrip</t>
+          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14562,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -14597,7 +14592,7 @@
       </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/196228-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer/199324-en_US</t>
         </is>
       </c>
       <c r="J207" t="b">
@@ -14605,22 +14600,22 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-08-29T01:26:31+00:00</t>
+          <t>2026-09-07T07:45:06+00:00</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>f7d25f7312ae32cfbc12</t>
+          <t>bc77bcdc513a8a41f82f</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
+          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Hyderabad State/Province: Telangana Posting Start Date: 9/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14657,7 @@
       </c>
       <c r="I208" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer/199324-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer/190373-en_US</t>
         </is>
       </c>
       <c r="J208" t="b">
@@ -14670,22 +14665,22 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-09-07T07:45:06+00:00</t>
+          <t>2026-08-26T23:59:09+00:00</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>bc77bcdc513a8a41f82f</t>
+          <t>d34b365710648b2f54ed</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Hyderabad State/Province: Telangana Posting Start Date: 9/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
+          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Sao Paulo State/Province: Sao Paulo Posting Start Date: 8/26/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descripti</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14722,7 @@
       </c>
       <c r="I209" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer/190373-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer/192310-en_US</t>
         </is>
       </c>
       <c r="J209" t="b">
@@ -14735,22 +14730,22 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-08-26T23:59:09+00:00</t>
+          <t>2026-08-18T21:08:33+00:00</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>d34b365710648b2f54ed</t>
+          <t>d47c28254b000471923e</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Sao Paulo State/Province: Sao Paulo Posting Start Date: 8/26/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descripti</t>
+          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Fremont State/Province: California Posting Start Date: 8/12/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14757,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14792,7 +14787,7 @@
       </c>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer/192310-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Governance/179068-en_US</t>
         </is>
       </c>
       <c r="J210" t="b">
@@ -14805,17 +14800,17 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>d47c28254b000471923e</t>
+          <t>3f7c4b325f4b1f4d7d95</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Fremont State/Province: California Posting Start Date: 8/12/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
+          <t>Data Governance Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance City: Hyderabad State/Province: Telangana Posting Start Date: 8/4/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descri</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14822,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Data Governance</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -14857,7 +14852,7 @@
       </c>
       <c r="I211" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Governance/179068-en_US</t>
+          <t>https://careers.wipro.com/job/Gen-AI-Architect/152257-en_US</t>
         </is>
       </c>
       <c r="J211" t="b">
@@ -14865,22 +14860,22 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-08-18T21:08:33+00:00</t>
+          <t>2026-09-01T23:05:19+00:00</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>3f7c4b325f4b1f4d7d95</t>
+          <t>e99cb1d635fb3c6084f4</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Data Governance Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance City: Hyderabad State/Province: Telangana Posting Start Date: 8/4/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descri</t>
+          <t>Gen AI Architect Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Gen AI Architect City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14887,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14922,7 +14917,7 @@
       </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Gen-AI-Architect/152257-en_US</t>
+          <t>https://careers.wipro.com/job/Generative-AI-Engineer/187523-en_US</t>
         </is>
       </c>
       <c r="J212" t="b">
@@ -14930,22 +14925,22 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-09-01T23:05:19+00:00</t>
+          <t>2026-08-19T18:08:19+00:00</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>e99cb1d635fb3c6084f4</t>
+          <t>6f69e0d39b8c90e69cfb</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Gen AI Architect Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Gen AI Architect City: Chennai State/Province: Tamil Nadu Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
+          <t>Generative AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Generative AI Engineer City: Bengaluru State/Province: Karnataka Posting Start Date: 8/19/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14952,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Job Description: Data Operations, Investment Data Management</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -14987,7 +14982,7 @@
       </c>
       <c r="I213" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Generative-AI-Engineer/187523-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Operations%2C-Investment-Data-Management/192721-en_US</t>
         </is>
       </c>
       <c r="J213" t="b">
@@ -14995,22 +14990,22 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-08-19T18:08:19+00:00</t>
+          <t>2026-08-18T21:08:33+00:00</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>6f69e0d39b8c90e69cfb</t>
+          <t>280de90787812a9f6d98</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Generative AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Generative AI Engineer City: Bengaluru State/Province: Karnataka Posting Start Date: 8/19/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.</t>
+          <t>Data Operations, Investment Data Management Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Operations, Investment Data Management City: Curitiba State/Province: Parana Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For addition</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15017,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Job Description: Data Operations, Investment Data Management</t>
+          <t>Lead Analyst</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -15052,7 +15047,7 @@
       </c>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Operations%2C-Investment-Data-Management/192721-en_US</t>
+          <t>https://careers.wipro.com/job/Lead-Analyst/123472-en_US</t>
         </is>
       </c>
       <c r="J214" t="b">
@@ -15060,22 +15055,22 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-08-18T21:08:33+00:00</t>
+          <t>2026-08-08T00:15:00+00:00</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>280de90787812a9f6d98</t>
+          <t>5b23b17405108c284d71</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Data Operations, Investment Data Management Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Operations, Investment Data Management City: Curitiba State/Province: Parana Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For addition</t>
+          <t>Lead Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Lead Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 6/18/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15082,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Lead Analyst</t>
+          <t>Senior Analyst</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -15117,7 +15112,7 @@
       </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Lead-Analyst/123472-en_US</t>
+          <t>https://careers.wipro.com/job/Senior-Analyst/16386-en_US</t>
         </is>
       </c>
       <c r="J215" t="b">
@@ -15125,22 +15120,22 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>5b23b17405108c284d71</t>
+          <t>891e384b5304d97d4cca</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>Lead Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Lead Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 6/18/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
+          <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: State/Province: Posting Start Date: 4/3/25 Job Description: Job Description JOB DESCRIPTION – Legal &amp; Compliance Services LOB Financial Services PREFERRED SECTOR/INDUSTRY Legal &amp; Compliance DESIGNATION B2 – Sr. Analyst QUALIFICATION • CS. (Must) • LL. B (preferred but not mandatory) JOB LOCATION Delhi/NCR EXPERIENCE REQUIRED 3.5- 6 years JOB RESPONSIBILITIES The role of Sr. Analyst in Legal &amp; Compliance shall encompass various tasks including, but not limited to, the following: • Preparation of management committee meetings, board meetings and the GP’s of Client funds • Drafting of management committee and board meetings minutes and review of GP minutes including maintaining policies/minutes trackers/action logs in t</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15177,7 @@
       </c>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Senior-Analyst/16386-en_US</t>
+          <t>https://careers.wipro.com/job/Senior-Analyst/14307-en_US</t>
         </is>
       </c>
       <c r="J216" t="b">
@@ -15190,92 +15185,27 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-07-30T19:17:06+00:00</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-07T23:14:59+00:00</t>
+          <t>2026-09-08T01:36:21+00:00</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>891e384b5304d97d4cca</t>
+          <t>39bd94d407e60c75b549</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: State/Province: Posting Start Date: 4/3/25 Job Description: Job Description JOB DESCRIPTION – Legal &amp; Compliance Services LOB Financial Services PREFERRED SECTOR/INDUSTRY Legal &amp; Compliance DESIGNATION B2 – Sr. Analyst QUALIFICATION • CS. (Must) • LL. B (preferred but not mandatory) JOB LOCATION Delhi/NCR EXPERIENCE REQUIRED 3.5- 6 years JOB RESPONSIBILITIES The role of Sr. Analyst in Legal &amp; Compliance shall encompass various tasks including, but not limited to, the following: • Preparation of management committee meetings, board meetings and the GP’s of Client funds • Drafting of management committee and board meetings minutes and review of GP minutes including maintaining policies/minutes trackers/action logs in t</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Senior Analyst</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>HTTP+Playwright</t>
-        </is>
-      </c>
-      <c r="I217" s="1" t="inlineStr">
-        <is>
-          <t>https://careers.wipro.com/job/Senior-Analyst/14307-en_US</t>
-        </is>
-      </c>
-      <c r="J217" t="b">
-        <v>0</v>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>2026-07-30T19:17:06+00:00</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>2026-09-07T23:14:59+00:00</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>39bd94d407e60c75b549</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
           <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: Gurugram State/Province: Haryana Posting Start Date: 4/11/25 Job Description: Job Description Job title: Senior Analyst – Investment Management – Structured Finance Band: B2 - Senior Analyst Experience Range: Minimum 4 year Shift Timings-: 2:00 PM - 11:30 PM IST Responsibilities: • Deal Management: Collaborate closely with ABF Deal Analysts to assist in investment management and monitoring activities for structured finance deals. • IC Memos: Support the deal team in updating Investment Committee approval memos, ensuring a comprehensive understanding of each deal's intricacies. • Term sheets: Analyze closing documents such as credit agreements, indentures and note purchase agreements and set up processes for analyzing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N217"/>
+  <autoFilter ref="A1:N216"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -15492,7 +15422,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId216"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/data-ai-jobs.xlsx
+++ b/output/data-ai-jobs.xlsx
@@ -517,17 +517,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Annapolis, Maryland, 21401, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,12 +537,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,7 +552,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006267663/Business-Analyst</t>
+          <t>https://www.judge.com/jobs/details/1145633</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -565,22 +560,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>f23928c645d5b3a7d52b</t>
+          <t>feac664cd0965bceede2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Job Title: Business Analyst Job Description The Business Analyst plays a key role in translating business, user, and product needs into clear, actionable requirements that support software and platform development in a complex, compliance-driven environment. This position partners closely with product, engineering, and quality assurance teams to ensure requirements are technically sound, testable, and fully traceable across the system lifecycle. Responsibilities Elicit, analyze, and document business, user, and product requirements that capture functional, non-functional, and compliance-related needs. Partner with Product Owners, Engineering, and QA teams to ensure requirements are technically sound, testable, and interconnected across systems. Analyze how requirements impact one another and identify dependencies, constraints, and interactions within integrated system components. Ensure compliance-driven and policy-related requirements are accurately reflected and traceable throughout the system lifecycle. Support QA processes by linking requirements to test cases and validation criteria to achieve complete coverage and end-to-end traceability. Maintain organized, high-quality documentation across Jira, Confluence, and related collaboration and tracking tools. Facilitate requirement review sessions to confirm accuracy, resolve ambiguities, and promote shared understanding across delivery teams. Interpret data flows, system integrations, and functional dependencies to inform requirement design and impact analysis. Collaborate with stakeholders from both technical and business domains to align requirements with strategic objectives and user needs. Essential Skills Minimum of 5 years of experience as a Business Analyst or Systems Analyst supporting software or platform development. Bachelor’s degree in Business, Information Systems, or a related field, or equivalent professional experience. Proven experience in requirements gathering and documentation across business, user, and product domains. Strong understanding of how business, user, and product requirements interrelate within complex system environments. Technical fluency sufficient to interpret data flows, system integrations, and functional dependencies. Experience supporting QA workflows and maintaining requirements-to-test-case traceability. Exceptional analytical skills with the ability to break down complex problems and define clear, structured requirements. Strong communication skills with the ability to bridge technical and business audiences and facilitate collaborative discussions. Ability to ensure compliance and security-related requirements are incorporated into system design and documentation. Additional Skills &amp; Qualifications Proficiency with Jira and Confluence for requirements management, documentation, and collaboration. Experience supporting government programs or compliance-driven software delivery initiatives. Knowledge of NIST standards, FedRAMP requirements, or Departmen</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved.</t>
         </is>
       </c>
     </row>
@@ -592,22 +587,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clinical Research Billing Compliance Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Haven, Connecticut, 06501, USA</t>
+          <t>Annapolis, Maryland, 21401, USA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["FULL_TIME"]</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -627,11 +622,11 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006264842/Clinical-Research-Billing-Compliance-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006267663/Business-Analyst</t>
         </is>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -640,17 +635,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>26fb9a39607014c232de</t>
+          <t>f23928c645d5b3a7d52b</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Clinical Research Billing Compliance Analyst Location: Remote (Candidates must NOT reside in: AK, CA, CT, MS, MO, MT, NV, NM, ND, SD, WY) Position Overview The Clinical Research Billing Compliance Analyst serves as a key liaison between clinical research teams and centralized billing offices. This role is responsible for ensuring accurate billing and compliance with Medicare (CMS) regulations, institutional policies, and clinical trial requirements. The analyst will review billing charges, assess compliance risks, and collaborate with cross-functional stakeholders to drive process improvements and maintain regulatory adherence. Key Responsibilities Conduct risk assessments for clinical trials with billable services using OnCore and protocol documentation Review and validate medical documentation, coding, and billing for accuracy (ICD-10, CPT-4, HCPCS, modifiers) in compliance with regulatory standards Evaluate billing charges from hospital and professional billing offices, ensuring proper designation and compliance alignment Identify discrepancies and collaborate with stakeholders (e.g., Office of Sponsored Projects) to resolve documentation and billing issues Review clinical trial encounters using systems such as OnCore and Epic Maintain detailed logs, dashboards, and audit reports; analyze trends and identify potential risk areas Develop and support corrective action plans with Principal Investigators and study teams Contribute to ongoing monitoring and enhancement of the Research Billing Compliance Program Generate reports and perform data analysis using clinical trial management tools Support training initiatives for research teams on billing compliance, coding accuracy, and regulatory guidelines Stay current with evolving CMS regulations and industry best practices; maintain CPC certification through CEUs Required Skills &amp; Qualifications Bachelor’s degree in a related field 3+ years of clinical research billing, charge review, or compliance experience Experience with clinical trial systems, protocol tracking, and reporting (OnCore required) Strong knowledge of protocols, ICFs, MCA, CTAs, and research billing compliance Proficiency in medical documentation review and coding (ICD-10, CPT, HCPCS) Strong analytical, problem-solving, and critical thinking skills Ability to manage multiple priorities independently in a fast-paced environment Excellent communication, stakeholder engagement, and collaboration skills Proficiency in Microsoft Office (Excel, Word, PowerPoint) Experience with coverage analysis; oncology experience a plus Experience with bridging clinical research and finance Strong presentation and conflict resolution skills Job Type &amp; Location This is a Permanent position based out of New Haven, CT. Pay and Benefits The pay range for this position is $70000.00 - $98000.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowle</t>
+          <t>Job Title: Business Analyst Job Description The Business Analyst plays a key role in translating business, user, and product needs into clear, actionable requirements that support software and platform development in a complex, compliance-driven environment. This position partners closely with product, engineering, and quality assurance teams to ensure requirements are technically sound, testable, and fully traceable across the system lifecycle. Responsibilities Elicit, analyze, and document business, user, and product requirements that capture functional, non-functional, and compliance-related needs. Partner with Product Owners, Engineering, and QA teams to ensure requirements are technically sound, testable, and interconnected across systems. Analyze how requirements impact one another and identify dependencies, constraints, and interactions within integrated system components. Ensure compliance-driven and policy-related requirements are accurately reflected and traceable throughout the system lifecycle. Support QA processes by linking requirements to test cases and validation criteria to achieve complete coverage and end-to-end traceability. Maintain organized, high-quality documentation across Jira, Confluence, and related collaboration and tracking tools. Facilitate requirement review sessions to confirm accuracy, resolve ambiguities, and promote shared understanding across delivery teams. Interpret data flows, system integrations, and functional dependencies to inform requirement design and impact analysis. Collaborate with stakeholders from both technical and business domains to align requirements with strategic objectives and user needs. Essential Skills Minimum of 5 years of experience as a Business Analyst or Systems Analyst supporting software or platform development. Bachelor’s degree in Business, Information Systems, or a related field, or equivalent professional experience. Proven experience in requirements gathering and documentation across business, user, and product domains. Strong understanding of how business, user, and product requirements interrelate within complex system environments. Technical fluency sufficient to interpret data flows, system integrations, and functional dependencies. Experience supporting QA workflows and maintaining requirements-to-test-case traceability. Exceptional analytical skills with the ability to break down complex problems and define clear, structured requirements. Strong communication skills with the ability to bridge technical and business audiences and facilitate collaborative discussions. Ability to ensure compliance and security-related requirements are incorporated into system design and documentation. Additional Skills &amp; Qualifications Proficiency with Jira and Confluence for requirements management, documentation, and collaboration. Experience supporting government programs or compliance-driven software delivery initiatives. Knowledge of NIST standards, FedRAMP requirements, or Departmen</t>
         </is>
       </c>
     </row>
@@ -662,27 +657,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical Research Billing Compliance Analyst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, Virginia, 20170, USA</t>
+          <t>New Haven, Connecticut, 06501, USA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["OTHER"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -697,11 +692,11 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-005234473/Data-Engineer</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006264842/Clinical-Research-Billing-Compliance-Analyst</t>
         </is>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -710,17 +705,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2c3bb40f9ec572ed5611</t>
+          <t>26fb9a39607014c232de</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Job Title: Data Engineer 🚨NO C2C🚨 *This will be a W2 contract Job Description Collaborate with Business Intelligence Engineering team members, engineering stakeholders, partner technical teams, and business stakeholders to gather business and functional requirements. Translate these requirements into a robust, scalable, and operable data infrastructure that integrates well within the overall AWS data architecture, leading to improved engineering decisions. Responsibilities Develop a deep understanding and awareness of operational data from the AWS fleet and build mechanisms for retrieving and aggregating such data for use by downstream business intelligence solutions. Develop a deep understanding of our vast data sources and provide continuous recommendations for their use to solve specific business problems. Take ownership of data reliability by performing deep-dives to find root causes of potential data anomalies and taking subsequent action to address these anomalies. Continuously optimize the performance of data queries and address extract, transform, and load (ETL) procedures. Insist on the highest standards by recognizing and adopting best practices in reporting and analysis, including data integrity, test design, analysis, validation, and documentation. Essential Skills Proficient in SQL. Experience in at least one modern scripting or programming language, such as Python, Java, Scala, or NodeJS. Experience with AWS technologies like Redshift, S3, AWS Glue, EMR, Kinesis, Lambda, and IAM roles and permissions. Additional Skills &amp; Qualifications 3+ years of experience in a related field. Bachelor’s degree in computer science, data engineering, or data analytics. Work Environment This position is onsite, requiring presence in the office 5 days a week. 🌟Additional Information: This is a W2 contract opportunity. No C2C. No relocation is offered/provided. Contract is currently set for 6 months. Pay rate is flexible based on experience. Benefits offered. Pay and Benefits The pay range for this position is $50.00 - $60.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Herndon,VA. Application Deadline This position is anticipated to close on Apr 30, 2025. About Actalent Actalent is a global leader in engineering and sciences services and talent solutions. We help visi</t>
+          <t>Clinical Research Billing Compliance Analyst Location: Remote (Candidates must NOT reside in: AK, CA, CT, MS, MO, MT, NV, NM, ND, SD, WY) Position Overview The Clinical Research Billing Compliance Analyst serves as a key liaison between clinical research teams and centralized billing offices. This role is responsible for ensuring accurate billing and compliance with Medicare (CMS) regulations, institutional policies, and clinical trial requirements. The analyst will review billing charges, assess compliance risks, and collaborate with cross-functional stakeholders to drive process improvements and maintain regulatory adherence. Key Responsibilities Conduct risk assessments for clinical trials with billable services using OnCore and protocol documentation Review and validate medical documentation, coding, and billing for accuracy (ICD-10, CPT-4, HCPCS, modifiers) in compliance with regulatory standards Evaluate billing charges from hospital and professional billing offices, ensuring proper designation and compliance alignment Identify discrepancies and collaborate with stakeholders (e.g., Office of Sponsored Projects) to resolve documentation and billing issues Review clinical trial encounters using systems such as OnCore and Epic Maintain detailed logs, dashboards, and audit reports; analyze trends and identify potential risk areas Develop and support corrective action plans with Principal Investigators and study teams Contribute to ongoing monitoring and enhancement of the Research Billing Compliance Program Generate reports and perform data analysis using clinical trial management tools Support training initiatives for research teams on billing compliance, coding accuracy, and regulatory guidelines Stay current with evolving CMS regulations and industry best practices; maintain CPC certification through CEUs Required Skills &amp; Qualifications Bachelor’s degree in a related field 3+ years of clinical research billing, charge review, or compliance experience Experience with clinical trial systems, protocol tracking, and reporting (OnCore required) Strong knowledge of protocols, ICFs, MCA, CTAs, and research billing compliance Proficiency in medical documentation review and coding (ICD-10, CPT, HCPCS) Strong analytical, problem-solving, and critical thinking skills Ability to manage multiple priorities independently in a fast-paced environment Excellent communication, stakeholder engagement, and collaboration skills Proficiency in Microsoft Office (Excel, Word, PowerPoint) Experience with coverage analysis; oncology experience a plus Experience with bridging clinical research and finance Strong presentation and conflict resolution skills Job Type &amp; Location This is a Permanent position based out of New Haven, CT. Pay and Benefits The pay range for this position is $70000.00 - $98000.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowle</t>
         </is>
       </c>
     </row>
@@ -732,12 +727,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Environmental Monitoring Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, North Carolina, 27601, USA</t>
+          <t>Herndon, Virginia, 20170, USA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -747,12 +742,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["OTHER"]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -767,11 +762,11 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006262189/Environmental-Monitoring-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-005234473/Data-Engineer</t>
         </is>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -780,17 +775,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22c9844ae229436a0a33</t>
+          <t>2c3bb40f9ec572ed5611</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Environmental Monitoring Analyst Launch Your Career in Pharmaceutical Quality &amp; Microbiology Are you a recent science graduate looking to start a rewarding career in the pharmaceutical or biotechnology industry? The Environmental Monitoring Analyst role is an excellent opportunity to gain hands-on experience in Quality Control, Microbiology, and GMP manufacturing while contributing directly to the production of life-changing medicines. In this role, you'll receive extensive training and mentorship as you learn how pharmaceutical facilities maintain sterile manufacturing environments and ensure the highest standards of product quality and patient safety. You'll work alongside experienced professionals in Quality, Manufacturing, and Laboratory Operations, developing highly sought-after skills that can lead to future opportunities in Microbiology, Quality Assurance, Quality Control, Validation, and other pharmaceutical science careers. What You'll Do Perform environmental monitoring activities throughout pharmaceutical manufacturing and laboratory areas to ensure cleanroom and facility compliance. Collect viable and non-viable air, surface, water, and utility samples used to evaluate contamination control programs. Incubate and analyze microbiological samples, interpret results, and document findings in electronic quality systems. Learn and apply industry-leading Good Manufacturing Practices (GMPs) and aseptic techniques used in regulated pharmaceutical environments. Support routine monitoring of cleanrooms, water systems, compressed gases, and other critical utilities that help ensure product quality and patient safety. Maintain accurate electronic documentation in compliance with pharmaceutical data integrity standards. Collaborate with Quality, Manufacturing, and Laboratory teams to investigate observations and maintain a state of control within the facility. Participate in ongoing training programs designed to develop expertise in environmental monitoring, microbiology, and pharmaceutical quality systems. Contribute to a culture of quality, compliance, teamwork, and continuous improvement. Why This Role is Great for New Graduates Strong training program with hands-on mentorship from experienced scientists and quality professionals. Opportunity to apply classroom knowledge in microbiology, biology, chemistry, and pharmaceutical sciences in a real-world GMP environment. Exposure to pharmaceutical manufacturing, microbiology testing, contamination control, and quality systems. Build foundational industry experience that can lead to advancement in Quality Control, Quality Assurance, Microbiology, Validation, Manufacturing Sciences, and other life sciences career paths. Work for an organization focused on innovation, patient safety, and professional development. What We're Looking For Bachelor's degree in Biology, Microbiology, Chemistry, Pharmaceutical Sciences, Environmental Science, or a related scientific discipline. Recent graduates are encourag</t>
+          <t>Job Title: Data Engineer 🚨NO C2C🚨 *This will be a W2 contract Job Description Collaborate with Business Intelligence Engineering team members, engineering stakeholders, partner technical teams, and business stakeholders to gather business and functional requirements. Translate these requirements into a robust, scalable, and operable data infrastructure that integrates well within the overall AWS data architecture, leading to improved engineering decisions. Responsibilities Develop a deep understanding and awareness of operational data from the AWS fleet and build mechanisms for retrieving and aggregating such data for use by downstream business intelligence solutions. Develop a deep understanding of our vast data sources and provide continuous recommendations for their use to solve specific business problems. Take ownership of data reliability by performing deep-dives to find root causes of potential data anomalies and taking subsequent action to address these anomalies. Continuously optimize the performance of data queries and address extract, transform, and load (ETL) procedures. Insist on the highest standards by recognizing and adopting best practices in reporting and analysis, including data integrity, test design, analysis, validation, and documentation. Essential Skills Proficient in SQL. Experience in at least one modern scripting or programming language, such as Python, Java, Scala, or NodeJS. Experience with AWS technologies like Redshift, S3, AWS Glue, EMR, Kinesis, Lambda, and IAM roles and permissions. Additional Skills &amp; Qualifications 3+ years of experience in a related field. Bachelor’s degree in computer science, data engineering, or data analytics. Work Environment This position is onsite, requiring presence in the office 5 days a week. 🌟Additional Information: This is a W2 contract opportunity. No C2C. No relocation is offered/provided. Contract is currently set for 6 months. Pay rate is flexible based on experience. Benefits offered. Pay and Benefits The pay range for this position is $50.00 - $60.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Herndon,VA. Application Deadline This position is anticipated to close on Apr 30, 2025. About Actalent Actalent is a global leader in engineering and sciences services and talent solutions. We help visi</t>
         </is>
       </c>
     </row>
@@ -802,12 +797,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Methods Analyst</t>
+          <t>Environmental Monitoring Analyst</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mississauga, Ontario, Canada</t>
+          <t>Raleigh, North Carolina, 27601, USA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -817,12 +812,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>["FULL_TIME"]</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -837,11 +832,11 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006260242/Methods-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006262189/Environmental-Monitoring-Analyst</t>
         </is>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -850,17 +845,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>942cb0fca55851f107fe</t>
+          <t>22c9844ae229436a0a33</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Job Title: Methods Analyst Job Description As a Methods Analyst, you will prepare, plan, and maintain work instructions, including product specifications, assembly manuals, PVA’s, and technique sheets that establish the information required to manufacture parts or assemblies. You will apply estimated standards for tool build times and set up, run, and assembly times to parts and assemblies. Additionally, you will analyze new and complex designs, recommend design changes, and show progressive manufacturing bills of material for parts and assemblies. Responsibilities Prepare, plan, and maintain work instructions including product specifications and assembly manuals. Apply estimated standards for tool build and assembly times. Analyze complex designs and recommend design changes. Issue instructions for tool design and fabrication. Generate requests, parts list, assembly sequence, and condition of supply information. Liaise with all departments to resolve technical problems and facilitate continuous improvement. Develop manufacturing plans based on product strategy. Develop resource plans and program schedules at and below the rate item level. Work in design build teams, providing process capability and produce ability commitments. Investigate discrepant parts and tools using lofted information. Collaborate with Production, Engineering, and Finance for root cause analysis and problem resolution. Essential Skills Methods analysis Continuous improvement Aerospace engineering Manufacturing engineering Preparation and maintenance of work instructions Manufacturing process knowledge Additional Skills &amp; Qualifications Degree in Aerospace, Mechanical, or Manufacturing Engineering 2+ years of manufacturing engineering experience, ideally in an aerospace environment Proficiency in root cause analysis, troubleshooting, and problem-solving Experience with Catia V5 Work Environment This is a union position, 100% on-site, with the requirement to work days, afternoons, and weekends as per the union agreement. Shifts include Days from 7am-3:30pm, Afternoons from 3pm-11:30pm, and Weekends with a 12-hour shift from 8am-8pm, including 8 hours on Friday and Monday. The role involves working closely with production to support root cause analysis on the production floor. Overtime is required and will be compensated in accordance with union rules under Local 673. Job Type &amp; Location This is a Permanent position based out of Mississauga, ON. Pay and Benefits The pay range for this position is $104251.00 - $104251.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Workplace Type This is a fully onsite position in Mississauga,ON. À propos d'Actalent Actalent est un leader mondial dans les services d’ingénierie et de sciences ainsi que dans les solutions de talents. Nous aidons</t>
+          <t>Environmental Monitoring Analyst Launch Your Career in Pharmaceutical Quality &amp; Microbiology Are you a recent science graduate looking to start a rewarding career in the pharmaceutical or biotechnology industry? The Environmental Monitoring Analyst role is an excellent opportunity to gain hands-on experience in Quality Control, Microbiology, and GMP manufacturing while contributing directly to the production of life-changing medicines. In this role, you'll receive extensive training and mentorship as you learn how pharmaceutical facilities maintain sterile manufacturing environments and ensure the highest standards of product quality and patient safety. You'll work alongside experienced professionals in Quality, Manufacturing, and Laboratory Operations, developing highly sought-after skills that can lead to future opportunities in Microbiology, Quality Assurance, Quality Control, Validation, and other pharmaceutical science careers. What You'll Do Perform environmental monitoring activities throughout pharmaceutical manufacturing and laboratory areas to ensure cleanroom and facility compliance. Collect viable and non-viable air, surface, water, and utility samples used to evaluate contamination control programs. Incubate and analyze microbiological samples, interpret results, and document findings in electronic quality systems. Learn and apply industry-leading Good Manufacturing Practices (GMPs) and aseptic techniques used in regulated pharmaceutical environments. Support routine monitoring of cleanrooms, water systems, compressed gases, and other critical utilities that help ensure product quality and patient safety. Maintain accurate electronic documentation in compliance with pharmaceutical data integrity standards. Collaborate with Quality, Manufacturing, and Laboratory teams to investigate observations and maintain a state of control within the facility. Participate in ongoing training programs designed to develop expertise in environmental monitoring, microbiology, and pharmaceutical quality systems. Contribute to a culture of quality, compliance, teamwork, and continuous improvement. Why This Role is Great for New Graduates Strong training program with hands-on mentorship from experienced scientists and quality professionals. Opportunity to apply classroom knowledge in microbiology, biology, chemistry, and pharmaceutical sciences in a real-world GMP environment. Exposure to pharmaceutical manufacturing, microbiology testing, contamination control, and quality systems. Build foundational industry experience that can lead to advancement in Quality Control, Quality Assurance, Microbiology, Validation, Manufacturing Sciences, and other life sciences career paths. Work for an organization focused on innovation, patient safety, and professional development. What We're Looking For Bachelor's degree in Biology, Microbiology, Chemistry, Pharmaceutical Sciences, Environmental Science, or a related scientific discipline. Recent graduates are encourag</t>
         </is>
       </c>
     </row>
@@ -872,12 +867,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Purchasing Analyst</t>
+          <t>Methods Analyst</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manchester, Connecticut, 06040, USA</t>
+          <t>Mississauga, Ontario, Canada</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -892,7 +887,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -907,11 +902,11 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006275829/Purchasing-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006260242/Methods-Analyst</t>
         </is>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -920,17 +915,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15babb871eabc81193fb</t>
+          <t>942cb0fca55851f107fe</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Job Title: Purchasing &amp; Quoting Analyst Job Description The Purchasing &amp; Quoting Analyst executes core procurement activities to support aerospace manufacturing operations, ensuring that materials and components are purchased, delivered, and managed in alignment with production schedules. This role owns the full purchasing lifecycle; from issuing RFQs and selecting suppliers to managing purchase orders and expediting deliveries, within a high-precision, regulated environment. The analyst collaborates closely with engineering, production, and quality teams to maintain accurate data, resolve supplier issues, and support reliable, flight-critical manufacturing output. Responsibilities Issue requests for quotation (RFQs) and evaluate supplier quotes to ensure competitive pricing, appropriate lead times, and required quality levels. Select suppliers based on cost, lead time, quality, and overall capability to support aerospace manufacturing requirements. Create, release, and manage purchase orders (POs) from initiation through closure, maintaining clear and accurate documentation. Track open purchase order lines and monitor delivery status to ensure materials arrive on time in alignment with production schedules. Expedite materials and components tied to production schedules, proactively addressing potential delays to minimize impact on manufacturing operations. Resolve supplier issues related to late deliveries, quality concerns, and documentation discrepancies, escalating as needed to protect production flow. Maintain accurate ERP/MRP data and purchase order line status, ensuring that system information reflects current commitments and deliveries. Support blueprint- and bill of materials (BOM)-driven purchasing by interpreting requirements and aligning orders with engineering specifications. Monitor supplier performance, including on-time delivery (OTD) and quality metrics, and escalate performance issues to appropriate stakeholders. Partner closely with engineering, production, and quality teams to align purchasing activities with technical requirements and operational priorities. Communicate frequently with suppliers to confirm order details, shipment status, and documentation needs in a regulated aerospace environment. Prioritize and manage multiple purchasing tasks simultaneously while working under time pressure and shifting production demands. Demonstrate hands-on ownership of the end-to-end procurement process, from RFQ and supplier selection through PO execution and delivery follow-up. Essential Skills Direct purchasing experience in aerospace or regulated manufacturing environments. Proven ownership of the full procurement cycle, including RFQ creation, supplier evaluation and selection, and purchase order execution. Experience purchasing machined components, fabricated parts, or assemblies for manufacturing operations. Demonstrated ability to manage open purchase order lines and maintain clear visibility of order status. Experience expedit</t>
+          <t>Job Title: Methods Analyst Job Description As a Methods Analyst, you will prepare, plan, and maintain work instructions, including product specifications, assembly manuals, PVA’s, and technique sheets that establish the information required to manufacture parts or assemblies. You will apply estimated standards for tool build times and set up, run, and assembly times to parts and assemblies. Additionally, you will analyze new and complex designs, recommend design changes, and show progressive manufacturing bills of material for parts and assemblies. Responsibilities Prepare, plan, and maintain work instructions including product specifications and assembly manuals. Apply estimated standards for tool build and assembly times. Analyze complex designs and recommend design changes. Issue instructions for tool design and fabrication. Generate requests, parts list, assembly sequence, and condition of supply information. Liaise with all departments to resolve technical problems and facilitate continuous improvement. Develop manufacturing plans based on product strategy. Develop resource plans and program schedules at and below the rate item level. Work in design build teams, providing process capability and produce ability commitments. Investigate discrepant parts and tools using lofted information. Collaborate with Production, Engineering, and Finance for root cause analysis and problem resolution. Essential Skills Methods analysis Continuous improvement Aerospace engineering Manufacturing engineering Preparation and maintenance of work instructions Manufacturing process knowledge Additional Skills &amp; Qualifications Degree in Aerospace, Mechanical, or Manufacturing Engineering 2+ years of manufacturing engineering experience, ideally in an aerospace environment Proficiency in root cause analysis, troubleshooting, and problem-solving Experience with Catia V5 Work Environment This is a union position, 100% on-site, with the requirement to work days, afternoons, and weekends as per the union agreement. Shifts include Days from 7am-3:30pm, Afternoons from 3pm-11:30pm, and Weekends with a 12-hour shift from 8am-8pm, including 8 hours on Friday and Monday. The role involves working closely with production to support root cause analysis on the production floor. Overtime is required and will be compensated in accordance with union rules under Local 673. Job Type &amp; Location This is a Permanent position based out of Mississauga, ON. Pay and Benefits The pay range for this position is $104251.00 - $104251.00/yr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Workplace Type This is a fully onsite position in Mississauga,ON. À propos d'Actalent Actalent est un leader mondial dans les services d’ingénierie et de sciences ainsi que dans les solutions de talents. Nous aidons</t>
         </is>
       </c>
     </row>
@@ -942,12 +937,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QC Analyst II</t>
+          <t>Purchasing Analyst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milford, Massachusetts, 01757, USA</t>
+          <t>Manchester, Connecticut, 06040, USA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -957,12 +952,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -977,11 +972,11 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006273305/QC-Analyst-II</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006275829/Purchasing-Analyst</t>
         </is>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -990,17 +985,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3c10374312613d9a6249</t>
+          <t>15babb871eabc81193fb</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Job Title: QC Analyst II Job Description The QC Analyst II plays a key role in ensuring the quality and compliance of raw materials, in-process samples, stability samples, and finished products within a GMP-regulated environment. This position performs routine and complex analytical testing, supports method development and optimization, and maintains rigorous documentation to meet regulatory and quality standards. The role actively promotes safe laboratory practices and contributes to continuous improvement across quality control operations. Responsibilities Demonstrate a strong commitment to laboratory safety, quality systems, and regulatory compliance in all daily operations. Support and promote a culture of safe laboratory practices by strictly following established environmental, health, and safety procedures. Perform routine analytical and laboratory testing on raw materials, in-process samples, stability samples, and finished products. Execute testing activities in accordance with approved analytical methods, internal quality standards, and applicable regulatory requirements. Operate and maintain analytical instruments such as HPLC, Karl Fischer, UV/VIS spectrophotometers, and LCMS systems in a GMP environment. Review and verify analytical data for accuracy, completeness, and adherence to established specifications and acceptance criteria. Document experimental results clearly and accurately in laboratory records and electronic systems, ensuring data integrity and traceability. Contribute to the preparation of technical reports, summaries, and stability assessments based on analytical data and observations. Assist in the development, qualification, and optimization of analytical methods, protocols, and laboratory procedures. Support the creation, revision, and maintenance of controlled documentation, including standard operating procedures, test methods, and product specifications. Collaborate with cross-functional teams to investigate laboratory issues, support troubleshooting activities, and implement corrective and preventive actions. Participate in continuous improvement initiatives to enhance laboratory efficiency, data quality, and compliance with cGMP requirements. Provide technical guidance, training, and mentorship to laboratory personnel as needed to ensure consistent application of methods and procedures. Essential Skills Bachelor’s degree (BS) in chemistry, biology, or a related scientific discipline. 2–5 years of experience as a QC analyst or chemist in a GMP or cGMP environment. Hands-on experience with analytical testing equipment and methodologies, including High Performance Liquid Chromatography (HPLC). Practical experience with LCMS (Liquid Chromatography–Mass Spectrometry) techniques and instrumentation. Proficiency in Karl Fischer titration for moisture or water content determination. Experience with UV/VIS spectrophotometry and related analytical methods. Strong understanding of quality control principles and practices</t>
+          <t>Job Title: Purchasing &amp; Quoting Analyst Job Description The Purchasing &amp; Quoting Analyst executes core procurement activities to support aerospace manufacturing operations, ensuring that materials and components are purchased, delivered, and managed in alignment with production schedules. This role owns the full purchasing lifecycle; from issuing RFQs and selecting suppliers to managing purchase orders and expediting deliveries, within a high-precision, regulated environment. The analyst collaborates closely with engineering, production, and quality teams to maintain accurate data, resolve supplier issues, and support reliable, flight-critical manufacturing output. Responsibilities Issue requests for quotation (RFQs) and evaluate supplier quotes to ensure competitive pricing, appropriate lead times, and required quality levels. Select suppliers based on cost, lead time, quality, and overall capability to support aerospace manufacturing requirements. Create, release, and manage purchase orders (POs) from initiation through closure, maintaining clear and accurate documentation. Track open purchase order lines and monitor delivery status to ensure materials arrive on time in alignment with production schedules. Expedite materials and components tied to production schedules, proactively addressing potential delays to minimize impact on manufacturing operations. Resolve supplier issues related to late deliveries, quality concerns, and documentation discrepancies, escalating as needed to protect production flow. Maintain accurate ERP/MRP data and purchase order line status, ensuring that system information reflects current commitments and deliveries. Support blueprint- and bill of materials (BOM)-driven purchasing by interpreting requirements and aligning orders with engineering specifications. Monitor supplier performance, including on-time delivery (OTD) and quality metrics, and escalate performance issues to appropriate stakeholders. Partner closely with engineering, production, and quality teams to align purchasing activities with technical requirements and operational priorities. Communicate frequently with suppliers to confirm order details, shipment status, and documentation needs in a regulated aerospace environment. Prioritize and manage multiple purchasing tasks simultaneously while working under time pressure and shifting production demands. Demonstrate hands-on ownership of the end-to-end procurement process, from RFQ and supplier selection through PO execution and delivery follow-up. Essential Skills Direct purchasing experience in aerospace or regulated manufacturing environments. Proven ownership of the full procurement cycle, including RFQ creation, supplier evaluation and selection, and purchase order execution. Experience purchasing machined components, fabricated parts, or assemblies for manufacturing operations. Demonstrated ability to manage open purchase order lines and maintain clear visibility of order status. Experience expedit</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1007,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quality Analyst</t>
+          <t>QC Analyst II</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Timmonsville, South Carolina, 29161, USA</t>
+          <t>Milford, Massachusetts, 01757, USA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1032,7 +1027,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1047,11 +1042,11 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006276084/Quality-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006273305/QC-Analyst-II</t>
         </is>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1060,17 +1055,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6067bd653ac257bf8b1d</t>
+          <t>3c10374312613d9a6249</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Job Title: Mass Production Parts Quality Analyst Job Description This role focuses on ensuring the quality of mass production parts supplied to an OEM automotive assembly plant, with dedicated positions supporting weld suppliers and plastics suppliers. You will lead detailed analysis of quality issues, collaborate closely with suppliers and internal manufacturing departments, and drive robust corrective and preventive actions using established quality tools and systems. Responsibilities Lead in-depth analysis of quality problems, including detailed parts measurements, to identify root causes and implement actions that minimize impact on downstream manufacturing departments. Prepare and submit clear, technical documentation of quality issues to suppliers using the NARS Honda Trouble Report (HTR) system, ensuring issues are communicated effectively and countermeasure activities are initiated promptly. Set and define technical requirements for supplier part change points using the NA Change Point Control System (CPCS), and thoroughly evaluate supplier quality documents before management approval. Conduct complex problem-solving analyses and investigations to resolve recurring or high-impact quality concerns affecting weld or plastic components. Lead supplier Quality Assurance Visits (QAVs) to communicate concerns, verify implementation of countermeasures, and confirm that non-conforming conditions have been eliminated. Mentor new associates within the group on problem-solving methods, quality procedures, and the responsibilities of the Parts Quality function. Perform judgment, disposition, and handling activities for non-conforming parts, including deciding on rework, repair, or rejection as appropriate. Evaluate and judge the quality of parts received from suppliers to ensure they meet established specifications and standards. Effectively solve quality problems using PDCA (Plan-Do-Check-Act) and structured root cause analysis techniques. Review and approve supplier countermeasures and supplier change points before they are released for production use. Essential Skills Bachelor’s degree in Engineering. At least 2 years of quality engineering experience, preferably in an automotive manufacturing environment. Hands-on experience with quality engineering practices, including root cause and corrective action (RCCA). Strong expereince in quality assurance within mass production or automotive manufacturing. Working knowledge of TS16949 or similar automotive quality management standards. Experience using core quality tools such as Fishbone diagrams, 8D, 5WHY, and RCCA. Ability to apply PFMEA (Process Failure Mode and Effects Analysis) in evaluating and mitigating process risks. Proficiency in structured problem-solving methods, including PDCA. Strong analytical skills to interpret measurement data and assess part conformance. Effective written and verbal communication skills to prepare technical reports and interact with suppliers and internal stakeholders</t>
+          <t>Job Title: QC Analyst II Job Description The QC Analyst II plays a key role in ensuring the quality and compliance of raw materials, in-process samples, stability samples, and finished products within a GMP-regulated environment. This position performs routine and complex analytical testing, supports method development and optimization, and maintains rigorous documentation to meet regulatory and quality standards. The role actively promotes safe laboratory practices and contributes to continuous improvement across quality control operations. Responsibilities Demonstrate a strong commitment to laboratory safety, quality systems, and regulatory compliance in all daily operations. Support and promote a culture of safe laboratory practices by strictly following established environmental, health, and safety procedures. Perform routine analytical and laboratory testing on raw materials, in-process samples, stability samples, and finished products. Execute testing activities in accordance with approved analytical methods, internal quality standards, and applicable regulatory requirements. Operate and maintain analytical instruments such as HPLC, Karl Fischer, UV/VIS spectrophotometers, and LCMS systems in a GMP environment. Review and verify analytical data for accuracy, completeness, and adherence to established specifications and acceptance criteria. Document experimental results clearly and accurately in laboratory records and electronic systems, ensuring data integrity and traceability. Contribute to the preparation of technical reports, summaries, and stability assessments based on analytical data and observations. Assist in the development, qualification, and optimization of analytical methods, protocols, and laboratory procedures. Support the creation, revision, and maintenance of controlled documentation, including standard operating procedures, test methods, and product specifications. Collaborate with cross-functional teams to investigate laboratory issues, support troubleshooting activities, and implement corrective and preventive actions. Participate in continuous improvement initiatives to enhance laboratory efficiency, data quality, and compliance with cGMP requirements. Provide technical guidance, training, and mentorship to laboratory personnel as needed to ensure consistent application of methods and procedures. Essential Skills Bachelor’s degree (BS) in chemistry, biology, or a related scientific discipline. 2–5 years of experience as a QC analyst or chemist in a GMP or cGMP environment. Hands-on experience with analytical testing equipment and methodologies, including High Performance Liquid Chromatography (HPLC). Practical experience with LCMS (Liquid Chromatography–Mass Spectrometry) techniques and instrumentation. Proficiency in Karl Fischer titration for moisture or water content determination. Experience with UV/VIS spectrophotometry and related analytical methods. Strong understanding of quality control principles and practices</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1077,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quality Control Analyst</t>
+          <t>Quality Analyst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Baltimore, Maryland, 21201, USA</t>
+          <t>Timmonsville, South Carolina, 29161, USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1117,11 +1112,11 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006275922/Quality-Control-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006276084/Quality-Analyst</t>
         </is>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1130,17 +1125,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4387fcaa59e82c8a3482</t>
+          <t>6067bd653ac257bf8b1d</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Job Title: Quality Control Analyst Job Description The Quality Control Analyst (Sampler and Analyst) plays a hands-on role within the QC Analytical group at a large-molecule manufacturing facility. This position focuses on utility and environmental sampling, basic QC testing, and data integrity to support biologics drug substance development and manufacturing. The analyst collaborates closely with cross-functional teams, including QC Micro, Manufacturing, Quality Assurance, Regulatory Affairs, and Supply Chain, to ensure timely analysis, inspection readiness, and compliance with global regulatory standards. Responsibilities Perform day-to-day Quality Control operations, including collecting samples of utilities such as water and gas and conducting Environmental Monitoring (EM) activities. Serve as the primary resource for sample collection, ensuring accurate, consistent, and timely sampling of utilities and environmental areas. Conduct basic QC testing on collected samples and ensure results are accurate, reliable, and compliant with established procedures. Compile, organize, and maintain test results to support qualification reports and other quality documentation. Review test records to confirm they are complete, correct, and in compliance with internal procedures and regulatory expectations. Support testing of QC samples as needed to meet project timelines and manufacturing requirements. Collaborate with the Biologics Process Development team to execute testing activities that support drug substance development and manufacturing operations. Assist with laboratory incidents, out-of-specification (OOS) results, deviations, out-of-trend (OOT) findings, and client complaints related to QC testing. Ensure all documentation, including SOPs, IOPs, EOPs, and STPs, is periodically reviewed, updated, and maintained in alignment with the documentation control system. Complete QC activities according to project timelines and update work plans to accommodate changes in scope, priorities, or schedules. Adhere to ALCOA principles of data integrity and promote compliance with data integrity standards across the QC team. Participate in functional working teams to perform self-assessments of compliance with SOPs and data integrity requirements. Support and contribute to investigations related to QC testing, deviations, and quality events. Ensure laboratory safety protocols are followed at all times and help resolve technical issues in the QC Analytical lab effectively and promptly. Support QC Analytical documentation for regulatory filings, including prior approval submissions, renewals, updates, and supplements. Assist in monitoring QC analytical trends, complaints, failures, deviations, and changes to identify and drive opportunities for process, system, and product improvements. Plan and manage QC laboratory resources to support smooth and efficient operations. Essential Skills Bachelor’s degree in Chemistry, Biochemistry, Chemical Engineering, or a related</t>
+          <t>Job Title: Mass Production Parts Quality Analyst Job Description This role focuses on ensuring the quality of mass production parts supplied to an OEM automotive assembly plant, with dedicated positions supporting weld suppliers and plastics suppliers. You will lead detailed analysis of quality issues, collaborate closely with suppliers and internal manufacturing departments, and drive robust corrective and preventive actions using established quality tools and systems. Responsibilities Lead in-depth analysis of quality problems, including detailed parts measurements, to identify root causes and implement actions that minimize impact on downstream manufacturing departments. Prepare and submit clear, technical documentation of quality issues to suppliers using the NARS Honda Trouble Report (HTR) system, ensuring issues are communicated effectively and countermeasure activities are initiated promptly. Set and define technical requirements for supplier part change points using the NA Change Point Control System (CPCS), and thoroughly evaluate supplier quality documents before management approval. Conduct complex problem-solving analyses and investigations to resolve recurring or high-impact quality concerns affecting weld or plastic components. Lead supplier Quality Assurance Visits (QAVs) to communicate concerns, verify implementation of countermeasures, and confirm that non-conforming conditions have been eliminated. Mentor new associates within the group on problem-solving methods, quality procedures, and the responsibilities of the Parts Quality function. Perform judgment, disposition, and handling activities for non-conforming parts, including deciding on rework, repair, or rejection as appropriate. Evaluate and judge the quality of parts received from suppliers to ensure they meet established specifications and standards. Effectively solve quality problems using PDCA (Plan-Do-Check-Act) and structured root cause analysis techniques. Review and approve supplier countermeasures and supplier change points before they are released for production use. Essential Skills Bachelor’s degree in Engineering. At least 2 years of quality engineering experience, preferably in an automotive manufacturing environment. Hands-on experience with quality engineering practices, including root cause and corrective action (RCCA). Strong expereince in quality assurance within mass production or automotive manufacturing. Working knowledge of TS16949 or similar automotive quality management standards. Experience using core quality tools such as Fishbone diagrams, 8D, 5WHY, and RCCA. Ability to apply PFMEA (Process Failure Mode and Effects Analysis) in evaluating and mitigating process risks. Proficiency in structured problem-solving methods, including PDCA. Strong analytical skills to interpret measurement data and assess part conformance. Effective written and verbal communication skills to prepare technical reports and interact with suppliers and internal stakeholders</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1152,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Holly Springs, North Carolina, 27540, USA</t>
+          <t>Baltimore, Maryland, 21201, USA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1187,11 +1182,11 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006268343/Quality-Control-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006275922/Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1200,17 +1195,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>67560f09528fb1234dcf</t>
+          <t>4387fcaa59e82c8a3482</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Job Title: Quality Control Analyst Job Description The Quality Control Analyst works onsite in a GMP-regulated laboratory, performing raw material and product release testing to ensure that all samples meet established quality requirements. This role is available at multiple levels (I, II, or III), with level determined by the depth of experience. The analyst conducts chemistry-based testing, documents results in accordance with regulatory and corporate standards, and supports continuous improvement initiatives within the QC function. Responsibilities Perform raw material compendial chemistry testing for quality control samples in a GMP environment. Conduct product testing related to chemistry methods for quality control samples, ensuring accuracy and reliability of results. Execute GMP testing and associated laboratory tasks without errors, strictly following applicable standard operating procedures (SOPs) and protocols. Ensure all samples are tested according to established quality requirements and that reported results are valid, accurate, and fully documented. Comply with procedures designed to maintain adherence to legal regulations, health and safety standards, and regulatory requirements. Apply data integrity principles to all laboratory activities, ensuring that records are complete, consistent, and traceable. Participate in 6S lean lab operations to maintain an organized, efficient, and safe laboratory environment. Support preventive action and continuous improvement programs aimed at reducing costs and enhancing laboratory efficiency. Use laboratory information management systems (LIMS) to enter, manage, and retrieve test data and results. Operate analytical instruments and perform hands-on analytical testing in accordance with analytical methods and compendial standards. Essential Skills Bachelor's degree in a scientific discipline. Knowledge of Good Manufacturing Practices (GMPs) and their application in a laboratory environment. Strong understanding of laboratory documentation requirements and data integrity principles, including ALCOA. Experience with hands-on analytical testing and familiarity with analytical methods and related instrumentation. Experience using laboratory information management systems (LIMS), including GLIMS Labware. Experience testing with pharmaceutical compendia (USP/EP) or strong knowledge of compendial requirements. Ability to follow SOPs and protocols precisely and perform GMP testing without errors. Attention to detail and ability to generate accurate, valid, and compliant test results. Additional Skills &amp; Qualifications Understanding of GMP principles and their impact on product quality and regulatory compliance. Understanding of ALCOA data integrity principles (Attributable, Legible, Contemporaneous, Original, Accurate). Experience working with compendial testing standards such as USP and EP. Familiarity with 6S or lean laboratory practices and participation in continuous improvement initiatives. Ability</t>
+          <t>Job Title: Quality Control Analyst Job Description The Quality Control Analyst (Sampler and Analyst) plays a hands-on role within the QC Analytical group at a large-molecule manufacturing facility. This position focuses on utility and environmental sampling, basic QC testing, and data integrity to support biologics drug substance development and manufacturing. The analyst collaborates closely with cross-functional teams, including QC Micro, Manufacturing, Quality Assurance, Regulatory Affairs, and Supply Chain, to ensure timely analysis, inspection readiness, and compliance with global regulatory standards. Responsibilities Perform day-to-day Quality Control operations, including collecting samples of utilities such as water and gas and conducting Environmental Monitoring (EM) activities. Serve as the primary resource for sample collection, ensuring accurate, consistent, and timely sampling of utilities and environmental areas. Conduct basic QC testing on collected samples and ensure results are accurate, reliable, and compliant with established procedures. Compile, organize, and maintain test results to support qualification reports and other quality documentation. Review test records to confirm they are complete, correct, and in compliance with internal procedures and regulatory expectations. Support testing of QC samples as needed to meet project timelines and manufacturing requirements. Collaborate with the Biologics Process Development team to execute testing activities that support drug substance development and manufacturing operations. Assist with laboratory incidents, out-of-specification (OOS) results, deviations, out-of-trend (OOT) findings, and client complaints related to QC testing. Ensure all documentation, including SOPs, IOPs, EOPs, and STPs, is periodically reviewed, updated, and maintained in alignment with the documentation control system. Complete QC activities according to project timelines and update work plans to accommodate changes in scope, priorities, or schedules. Adhere to ALCOA principles of data integrity and promote compliance with data integrity standards across the QC team. Participate in functional working teams to perform self-assessments of compliance with SOPs and data integrity requirements. Support and contribute to investigations related to QC testing, deviations, and quality events. Ensure laboratory safety protocols are followed at all times and help resolve technical issues in the QC Analytical lab effectively and promptly. Support QC Analytical documentation for regulatory filings, including prior approval submissions, renewals, updates, and supplements. Assist in monitoring QC analytical trends, complaints, failures, deviations, and changes to identify and drive opportunities for process, system, and product improvements. Plan and manage QC laboratory resources to support smooth and efficient operations. Essential Skills Bachelor’s degree in Chemistry, Biochemistry, Chemical Engineering, or a related</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1217,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sap Analyst</t>
+          <t>Quality Control Analyst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cambridge, Massachusetts, 02138, USA</t>
+          <t>Holly Springs, North Carolina, 27540, USA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1242,7 +1237,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1257,11 +1252,11 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006275434/Sap-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006268343/Quality-Control-Analyst</t>
         </is>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1270,17 +1265,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>be48873593124b103c97</t>
+          <t>67560f09528fb1234dcf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Description Support supply planning activities within SAP IBP, including demand and supply reviews, scenario analysis, exception management, and supply commitments. Develop, maintain, and analyze supply plans supporting commercial, clinical, and non-GMP manufacturing operations. Translate demand forecasts, inventory targets, manufacturing assumptions, and capacity constraints into actionable supply plans. Partner with Operations and Manufacturing teams to ensure production schedules support on-time and in-full delivery objectives. Create rough-cut capacity plans and provide scheduling inputs to support manufacturing and supply chain decision-making. Identify and escalate supply risks, inventory constraints, capacity gaps, and data quality issues while providing recommendations for mitigation. Participate in cross-functional planning meetings, including Tier meetings, S&amp;OE processes, and supply review discussions. Maintain and validate SAP and SAP IBP master data, including materials, locations, planning parameters, lead times, and related attributes. Support item lifecycle management and master data governance activities, including setup, modifications, approvals, and obsolescence processes. Develop planning metrics, dashboards, and reporting tools to monitor supply plan performance, inventory levels, schedule adherence, and data accuracy. Conduct ad hoc supply chain analyses related to product launches, budgeting, forecasting, inventory optimization, and risk assessments. Skills Sap, integrated business process, supply planning, production planning, master data, demand planning, capacity planning, supply chain, inventory management, manufacturing planning Top Skills Details Sap,integrated business process,supply planning,production planning,master data,demand planning,capacity planning,supply chain,inventory management,manufacturing planning Additional Skills &amp; Qualifications Bachelor's degree in Supply Chain, Engineering, Business, Operations Management, or a related discipline. Minimum of 7 years of supply chain planning experience. Hands-on experience with SAP IBP, supply planning processes, and SAP master data management. Experience supporting production planning, inventory planning, capacity planning, and demand-supply balancing activities. Strong analytical, problem-solving, and cross-functional collaboration skills. Advanced proficiency in Excel and planning/reporting tools. Experience within pharmaceutical, biotechnology, life sciences, or other regulated manufacturing environments. Familiarity with Sales &amp; Operations Execution (S&amp;OE), Integrated Business Planning (IBP), and Supply Review processes. Experience supporting clinical and commercial manufacturing supply chains. Knowledge of planning metrics, dashboard development, and supply chain performance reporting. Experience Level Intermediate Level Job Type &amp; Location This is a Contract position based out of Cambridge, MA. Pay and Benefits The pay range for this position is $60.00 - $6</t>
+          <t>Job Title: Quality Control Analyst Job Description The Quality Control Analyst works onsite in a GMP-regulated laboratory, performing raw material and product release testing to ensure that all samples meet established quality requirements. This role is available at multiple levels (I, II, or III), with level determined by the depth of experience. The analyst conducts chemistry-based testing, documents results in accordance with regulatory and corporate standards, and supports continuous improvement initiatives within the QC function. Responsibilities Perform raw material compendial chemistry testing for quality control samples in a GMP environment. Conduct product testing related to chemistry methods for quality control samples, ensuring accuracy and reliability of results. Execute GMP testing and associated laboratory tasks without errors, strictly following applicable standard operating procedures (SOPs) and protocols. Ensure all samples are tested according to established quality requirements and that reported results are valid, accurate, and fully documented. Comply with procedures designed to maintain adherence to legal regulations, health and safety standards, and regulatory requirements. Apply data integrity principles to all laboratory activities, ensuring that records are complete, consistent, and traceable. Participate in 6S lean lab operations to maintain an organized, efficient, and safe laboratory environment. Support preventive action and continuous improvement programs aimed at reducing costs and enhancing laboratory efficiency. Use laboratory information management systems (LIMS) to enter, manage, and retrieve test data and results. Operate analytical instruments and perform hands-on analytical testing in accordance with analytical methods and compendial standards. Essential Skills Bachelor's degree in a scientific discipline. Knowledge of Good Manufacturing Practices (GMPs) and their application in a laboratory environment. Strong understanding of laboratory documentation requirements and data integrity principles, including ALCOA. Experience with hands-on analytical testing and familiarity with analytical methods and related instrumentation. Experience using laboratory information management systems (LIMS), including GLIMS Labware. Experience testing with pharmaceutical compendia (USP/EP) or strong knowledge of compendial requirements. Ability to follow SOPs and protocols precisely and perform GMP testing without errors. Attention to detail and ability to generate accurate, valid, and compliant test results. Additional Skills &amp; Qualifications Understanding of GMP principles and their impact on product quality and regulatory compliance. Understanding of ALCOA data integrity principles (Attributable, Legible, Contemporaneous, Original, Accurate). Experience working with compendial testing standards such as USP and EP. Familiarity with 6S or lean laboratory practices and participation in continuous improvement initiatives. Ability</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1322,11 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006275089/Sap-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006275434/Sap-Analyst</t>
         </is>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1340,12 +1335,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>cab7f4cdbc0e9a9fc1bd</t>
+          <t>be48873593124b103c97</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1357,27 +1352,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>268 results for Data Engineer jobs</t>
+          <t>Sap Analyst</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Cambridge, Massachusetts, 02138, USA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1387,16 +1387,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006275089/Sap-Analyst</t>
         </is>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-12T12:34:25+00:00</t>
+          <t>2026-09-12T17:32:54+00:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7bec10c8f69c337df13f</t>
+          <t>cab7f4cdbc0e9a9fc1bd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>268 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Full-Time talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2026 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 268 results for Data Engineer jobs Data Engineer Boston, MA onsite Temporary / Contract 39.5865 - 45.837 USD / Hourly We are looking for a Data Engineer to support enterprise data movement and application integration efforts in Boston, Massachusetts. This Long-term Contract position will focus on building, maintaining, and enhancing custom services that transfer, load, and transform data across multiple systems. The role works closely with technical and business teams to deliver reliable integration solutions using .NET/C#, APIs, and modern deployment practices. Responsibilities: • Design, support, and improve custom integration services that move data between enterprise platforms and applications. • Build and maintain ETL processes for data loading, transformation, and system-to-system exchange. • Develop microservice-based solutions in .NET/C# to replace larger legacy integration components where needed. • Create and support API-driven integrations, including services that rely on REST and SOAP protocols. • Partner with business analysts, developers, and solution stakeholders to translate operational needs into technical data workflows. • Monitor data pipelines and integration jobs, troubleshoot failures, and resolve performance or reliability issues. • Contribute to deployment and release activities using Azure DevOps or comparable CI/CD tools. • Support integrations involving key enterprise platforms such as Salesforce and higher education systems when applicable. 2026-09-11T00:00:00Z Data Engineer Dallas, TX onsite Permanent / Full Time 135000 - 160000 USD / Yearly We are looking for a Senior Data Engineer to develop and optimize enterprise data systems that support analytics and digital solutions. In this role, you will design and implement robust data architectures, ensuring seamless data integration and transformation processes across the organization. Your expertise will drive the creation of reliable pipelines and scalable infrastructure, enabling advanced analytics and machine learning capabilities. Responsibilities: • Design and implement scalable data pipelines using Databricks, Spark, and Delta Lake to support enterprise-level analytics. • Develop and maintain efficient data models tailored for A</t>
+          <t>Description Support supply planning activities within SAP IBP, including demand and supply reviews, scenario analysis, exception management, and supply commitments. Develop, maintain, and analyze supply plans supporting commercial, clinical, and non-GMP manufacturing operations. Translate demand forecasts, inventory targets, manufacturing assumptions, and capacity constraints into actionable supply plans. Partner with Operations and Manufacturing teams to ensure production schedules support on-time and in-full delivery objectives. Create rough-cut capacity plans and provide scheduling inputs to support manufacturing and supply chain decision-making. Identify and escalate supply risks, inventory constraints, capacity gaps, and data quality issues while providing recommendations for mitigation. Participate in cross-functio